--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4655,7 +4655,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:16</t>
+          <t>2026-09-06 05:42:17</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4410,7 +4410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4531,25 +4531,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4609,7 +4629,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4633,29 +4653,41 @@
       <c r="W2" t="n">
         <v>0.777</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>108.781</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.6508217</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>897594847</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Healthcare Plans</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.unitedhealthgroup.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>UnitedHealth Group Incorporated operates as a health care company in the United States and internationally. It operates through four segments: Optum Health, Optum Insight, Optum Rx; and UnitedHealthcare. The Optum Health segment provides care delivery, care management, wellness and consumer engagement, and health financial services with patients, consumers, care delivery systems, providers, employers, payers, and public-sector entities. The Optum Insight segment offers software and information products, advisory consulting arrangements, and managed services outsourcing contracts to hospital systems, physicians, health plans, public entities, life sciences companies and other organizations. The Optum Rx segment provides pharmacy care services and programs, including retail network contracting, home delivery, specialty and community health pharmacy services, infusion, and purchasing and clinical capabilities, as well as develops programs in the areas of step therapy, formulary management, drug adherence, and disease and drug therapy management. The UnitedHealthcare segment offers consumer-oriented health benefit plans and services for national employers, public sector employers, mid-sized employers, small businesses, and individuals; Medicaid plans, including Temporary Assistance to Needy Families; Children's Health Insurance Programs; Dual SNPs; Long-Term Services and Supports; Aged, Blind and Disabled; and other federal, state, and community health care programs. and health care benefits products and services to state programs caring for the economically disadvantaged, medically underserved, and those without the benefit of employer-funded health care coverage. UnitedHealth Group Incorporated was founded in 1974 and is based in Eden Prairie, Minnesota.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:17</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:20</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:20</t>
+          <t>2026-09-06 16:24:56</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:56</t>
+          <t>2026-09-06 16:34:51</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:51</t>
+          <t>2026-09-06 16:49:24</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4631,15 +4631,11 @@
       <c r="Q2" t="n">
         <v>2.34</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.03135</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.07132999600000001</v>
       </c>
       <c r="T2" t="n">
         <v>0.14152999</v>
@@ -4687,7 +4683,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:24</t>
+          <t>2026-09-06 16:59:55</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4410,7 +4410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4551,25 +4551,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4661,29 +4676,38 @@
       <c r="AA2" t="n">
         <v>897594847</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>450525986816</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>405832826880</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26680999936</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Healthcare Plans</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.unitedhealthgroup.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>UnitedHealth Group Incorporated operates as a health care company in the United States and internationally. It operates through four segments: Optum Health, Optum Insight, Optum Rx; and UnitedHealthcare. The Optum Health segment provides care delivery, care management, wellness and consumer engagement, and health financial services with patients, consumers, care delivery systems, providers, employers, payers, and public-sector entities. The Optum Insight segment offers software and information products, advisory consulting arrangements, and managed services outsourcing contracts to hospital systems, physicians, health plans, public entities, life sciences companies and other organizations. The Optum Rx segment provides pharmacy care services and programs, including retail network contracting, home delivery, specialty and community health pharmacy services, infusion, and purchasing and clinical capabilities, as well as develops programs in the areas of step therapy, formulary management, drug adherence, and disease and drug therapy management. The UnitedHealthcare segment offers consumer-oriented health benefit plans and services for national employers, public sector employers, mid-sized employers, small businesses, and individuals; Medicaid plans, including Temporary Assistance to Needy Families; Children's Health Insurance Programs; Dual SNPs; Long-Term Services and Supports; Aged, Blind and Disabled; and other federal, state, and community health care programs. and health care benefits products and services to state programs caring for the economically disadvantaged, medically underserved, and those without the benefit of employer-funded health care coverage. UnitedHealth Group Incorporated was founded in 1974 and is based in Eden Prairie, Minnesota.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:55</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:21:00</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4707,7 +4707,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:21:00</t>
+          <t>2026-09-06 22:41:55</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -4707,7 +4707,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:55</t>
+          <t>2026-09-06 22:59:49</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>403.1900024414062</v>
+        <v>302.3426751055266</v>
       </c>
       <c r="C2" t="n">
-        <v>416.3599853515625</v>
+        <v>309.6470496882431</v>
       </c>
       <c r="D2" t="n">
-        <v>397.7999877929688</v>
+        <v>300.1611114077264</v>
       </c>
       <c r="E2" t="n">
-        <v>412.75</v>
+        <v>307.16357421875</v>
       </c>
       <c r="F2" t="n">
-        <v>5399000</v>
+        <v>14126700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>415.2699890136719</v>
+        <v>311.3709271996748</v>
       </c>
       <c r="C3" t="n">
-        <v>416.9700012207031</v>
+        <v>313.2603281414504</v>
       </c>
       <c r="D3" t="n">
-        <v>402.3999938964844</v>
+        <v>305.6150754302345</v>
       </c>
       <c r="E3" t="n">
-        <v>403.9700012207031</v>
+        <v>311.8968505859375</v>
       </c>
       <c r="F3" t="n">
-        <v>4712400</v>
+        <v>18438600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>401.5899963378906</v>
+        <v>323.8273141699113</v>
       </c>
       <c r="C4" t="n">
-        <v>410.6400146484375</v>
+        <v>342.5362463146478</v>
       </c>
       <c r="D4" t="n">
-        <v>400.6600036621094</v>
+        <v>318.6266023750954</v>
       </c>
       <c r="E4" t="n">
-        <v>407.0799865722656</v>
+        <v>338.8451232910156</v>
       </c>
       <c r="F4" t="n">
-        <v>4095900</v>
+        <v>46408900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>408.6000061035156</v>
+        <v>336.5466531982527</v>
       </c>
       <c r="C5" t="n">
-        <v>413.0700073242188</v>
+        <v>339.4781519824642</v>
       </c>
       <c r="D5" t="n">
-        <v>407.989990234375</v>
+        <v>332.4951561509477</v>
       </c>
       <c r="E5" t="n">
-        <v>408.739990234375</v>
+        <v>337.7348327636719</v>
       </c>
       <c r="F5" t="n">
-        <v>3182200</v>
+        <v>17804300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>409</v>
+        <v>339.8969462743543</v>
       </c>
       <c r="C6" t="n">
-        <v>410.8999938964844</v>
+        <v>351.5644796571226</v>
       </c>
       <c r="D6" t="n">
-        <v>401.3200073242188</v>
+        <v>336.8193657730168</v>
       </c>
       <c r="E6" t="n">
-        <v>402.1900024414062</v>
+        <v>344.3866882324219</v>
       </c>
       <c r="F6" t="n">
-        <v>3398900</v>
+        <v>18943500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>400.9800109863281</v>
+        <v>346.6169306487971</v>
       </c>
       <c r="C7" t="n">
-        <v>407.2000122070312</v>
+        <v>352.8597399573416</v>
       </c>
       <c r="D7" t="n">
-        <v>400.5</v>
+        <v>343.2666549867767</v>
       </c>
       <c r="E7" t="n">
-        <v>405.5899963378906</v>
+        <v>343.3153686523438</v>
       </c>
       <c r="F7" t="n">
-        <v>3317200</v>
+        <v>14016200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,25 +625,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>405.5899963378906</v>
+        <v>344.2562617205344</v>
       </c>
       <c r="C8" t="n">
-        <v>407.3200073242188</v>
+        <v>344.6972712574788</v>
       </c>
       <c r="D8" t="n">
-        <v>398.5899963378906</v>
+        <v>335.7003177947291</v>
       </c>
       <c r="E8" t="n">
-        <v>399.0599975585938</v>
+        <v>340.9534606933594</v>
       </c>
       <c r="F8" t="n">
-        <v>4170200</v>
+        <v>11035900</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>398</v>
+        <v>340.5711991051483</v>
       </c>
       <c r="C9" t="n">
-        <v>403.1799926757812</v>
+        <v>342.0805014268064</v>
       </c>
       <c r="D9" t="n">
-        <v>396.5599975585938</v>
+        <v>331.5742462609258</v>
       </c>
       <c r="E9" t="n">
-        <v>401.7300109863281</v>
+        <v>333.005126953125</v>
       </c>
       <c r="F9" t="n">
-        <v>3476400</v>
+        <v>12695800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>398.5700073242188</v>
+        <v>330.9568224057415</v>
       </c>
       <c r="C10" t="n">
-        <v>398.8999938964844</v>
+        <v>336.1609442520178</v>
       </c>
       <c r="D10" t="n">
-        <v>391.4299926757812</v>
+        <v>330.9568224057415</v>
       </c>
       <c r="E10" t="n">
-        <v>395.6199951171875</v>
+        <v>334.7986450195312</v>
       </c>
       <c r="F10" t="n">
-        <v>5295100</v>
+        <v>8467700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>397.4299926757812</v>
+        <v>336.6803662104043</v>
       </c>
       <c r="C11" t="n">
-        <v>398.7900085449219</v>
+        <v>338.0524456778033</v>
       </c>
       <c r="D11" t="n">
-        <v>393.510009765625</v>
+        <v>327.4579882805058</v>
       </c>
       <c r="E11" t="n">
-        <v>393.9299926757812</v>
+        <v>328.14404296875</v>
       </c>
       <c r="F11" t="n">
-        <v>3605100</v>
+        <v>11255600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>394.5700073242188</v>
+        <v>329.7905316198508</v>
       </c>
       <c r="C12" t="n">
-        <v>396.7999877929688</v>
+        <v>334.161595373165</v>
       </c>
       <c r="D12" t="n">
-        <v>386.3299865722656</v>
+        <v>327.1835657302883</v>
       </c>
       <c r="E12" t="n">
-        <v>388.6099853515625</v>
+        <v>329.9767456054688</v>
       </c>
       <c r="F12" t="n">
-        <v>5268500</v>
+        <v>13656800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>388.25</v>
+        <v>327.7912281730855</v>
       </c>
       <c r="C13" t="n">
-        <v>392.7099914550781</v>
+        <v>335.6513373618812</v>
       </c>
       <c r="D13" t="n">
-        <v>383.8299865722656</v>
+        <v>325.9683288776566</v>
       </c>
       <c r="E13" t="n">
-        <v>384.8500061035156</v>
+        <v>334.4948425292969</v>
       </c>
       <c r="F13" t="n">
-        <v>4497200</v>
+        <v>8903700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>386</v>
+        <v>334.2008052062361</v>
       </c>
       <c r="C14" t="n">
-        <v>393.6600036621094</v>
+        <v>345.6675310141911</v>
       </c>
       <c r="D14" t="n">
-        <v>386</v>
+        <v>333.1815333788629</v>
       </c>
       <c r="E14" t="n">
-        <v>390.1099853515625</v>
+        <v>340.7574157714844</v>
       </c>
       <c r="F14" t="n">
-        <v>4879600</v>
+        <v>12504100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>391.0400085449219</v>
+        <v>343.217373716776</v>
       </c>
       <c r="C15" t="n">
-        <v>399.5799865722656</v>
+        <v>347.4316240476539</v>
       </c>
       <c r="D15" t="n">
-        <v>390.8599853515625</v>
+        <v>340.9044142070616</v>
       </c>
       <c r="E15" t="n">
-        <v>398.760009765625</v>
+        <v>344.7952575683594</v>
       </c>
       <c r="F15" t="n">
-        <v>4683900</v>
+        <v>9016300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>397.7999877929688</v>
+        <v>341.9432916493518</v>
       </c>
       <c r="C16" t="n">
-        <v>399.0299987792969</v>
+        <v>343.2075787683629</v>
       </c>
       <c r="D16" t="n">
-        <v>395.6199951171875</v>
+        <v>336.7489800892123</v>
       </c>
       <c r="E16" t="n">
-        <v>396.5899963378906</v>
+        <v>338.6698913574219</v>
       </c>
       <c r="F16" t="n">
-        <v>2655000</v>
+        <v>8104900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>396.3299865722656</v>
+        <v>340.9926010114185</v>
       </c>
       <c r="C17" t="n">
-        <v>406.25</v>
+        <v>342.9919337348455</v>
       </c>
       <c r="D17" t="n">
-        <v>396.010009765625</v>
+        <v>334.4947920920956</v>
       </c>
       <c r="E17" t="n">
-        <v>401.010009765625</v>
+        <v>337.2193603515625</v>
       </c>
       <c r="F17" t="n">
-        <v>3557000</v>
+        <v>6774700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>396.8699951171875</v>
+        <v>337.1214299699541</v>
       </c>
       <c r="C18" t="n">
-        <v>399.8800048828125</v>
+        <v>338.6601031752857</v>
       </c>
       <c r="D18" t="n">
-        <v>393.7699890136719</v>
+        <v>334.641876568426</v>
       </c>
       <c r="E18" t="n">
-        <v>395.0499877929688</v>
+        <v>338.2974853515625</v>
       </c>
       <c r="F18" t="n">
-        <v>3668200</v>
+        <v>6878900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>396.4200134277344</v>
+        <v>336.8959869118207</v>
       </c>
       <c r="C19" t="n">
-        <v>396.739990234375</v>
+        <v>342.3549341542898</v>
       </c>
       <c r="D19" t="n">
-        <v>392.6600036621094</v>
+        <v>335.5042870567964</v>
       </c>
       <c r="E19" t="n">
-        <v>392.9500122070312</v>
+        <v>338.4150695800781</v>
       </c>
       <c r="F19" t="n">
-        <v>2455500</v>
+        <v>7429700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>393.5199890136719</v>
+        <v>337.042992446128</v>
       </c>
       <c r="C20" t="n">
-        <v>394.489990234375</v>
+        <v>341.7473034781017</v>
       </c>
       <c r="D20" t="n">
-        <v>387.7099914550781</v>
+        <v>334.8182646079004</v>
       </c>
       <c r="E20" t="n">
-        <v>389.4100036621094</v>
+        <v>341.3552551269531</v>
       </c>
       <c r="F20" t="n">
-        <v>5748000</v>
+        <v>8825500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>392.0799865722656</v>
+        <v>340.3653902924742</v>
       </c>
       <c r="C21" t="n">
-        <v>399.6000061035156</v>
+        <v>348.000043885751</v>
       </c>
       <c r="D21" t="n">
-        <v>391.7799987792969</v>
+        <v>337.7780149171845</v>
       </c>
       <c r="E21" t="n">
-        <v>396.2999877929688</v>
+        <v>346.6671752929688</v>
       </c>
       <c r="F21" t="n">
-        <v>3716200</v>
+        <v>8564200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>399.2699890136719</v>
+        <v>350.126813283771</v>
       </c>
       <c r="C22" t="n">
-        <v>401.1400146484375</v>
+        <v>360.6624696666976</v>
       </c>
       <c r="D22" t="n">
-        <v>396.510009765625</v>
+        <v>349.4995598497266</v>
       </c>
       <c r="E22" t="n">
-        <v>399.6600036621094</v>
+        <v>353.0180053710938</v>
       </c>
       <c r="F22" t="n">
-        <v>3265300</v>
+        <v>13494800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>400.0199890136719</v>
+        <v>353.8314638081978</v>
       </c>
       <c r="C23" t="n">
-        <v>405.1600036621094</v>
+        <v>355.2917453013463</v>
       </c>
       <c r="D23" t="n">
-        <v>395.2999877929688</v>
+        <v>349.9896110702735</v>
       </c>
       <c r="E23" t="n">
-        <v>400.9400024414062</v>
+        <v>351.6165161132812</v>
       </c>
       <c r="F23" t="n">
-        <v>5488900</v>
+        <v>7181700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>352.243767379212</v>
+      </c>
+      <c r="C24" t="n">
+        <v>357.4478894842047</v>
+      </c>
+      <c r="D24" t="n">
+        <v>350.9206788979734</v>
+      </c>
+      <c r="E24" t="n">
+        <v>356.4090270996094</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7236200</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>359.613786634634</v>
+      </c>
+      <c r="C25" t="n">
+        <v>367.1602685308417</v>
+      </c>
+      <c r="D25" t="n">
+        <v>358.5063128850491</v>
+      </c>
+      <c r="E25" t="n">
+        <v>362.544189453125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9438300</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>365.0923551123336</v>
+      </c>
+      <c r="C26" t="n">
+        <v>368.7185931947143</v>
+      </c>
+      <c r="D26" t="n">
+        <v>358.7807591507652</v>
+      </c>
+      <c r="E26" t="n">
+        <v>360.3586730957031</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8759800</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>362.0345442209324</v>
+      </c>
+      <c r="C27" t="n">
+        <v>362.0345442209324</v>
+      </c>
+      <c r="D27" t="n">
+        <v>345.4813287153903</v>
+      </c>
+      <c r="E27" t="n">
+        <v>347.431640625</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13141900</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>347.6668450586018</v>
+      </c>
+      <c r="C28" t="n">
+        <v>351.9987280315978</v>
+      </c>
+      <c r="D28" t="n">
+        <v>346.2751751256885</v>
+      </c>
+      <c r="E28" t="n">
+        <v>351.5086975097656</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5659400</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>347.8726721794402</v>
+      </c>
+      <c r="C29" t="n">
+        <v>355.1054974076654</v>
+      </c>
+      <c r="D29" t="n">
+        <v>346.3535596478916</v>
+      </c>
+      <c r="E29" t="n">
+        <v>352.7533569335938</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5974800</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>352.2241789356418</v>
+      </c>
+      <c r="C30" t="n">
+        <v>356.9578609672659</v>
+      </c>
+      <c r="D30" t="n">
+        <v>348.7547542094708</v>
+      </c>
+      <c r="E30" t="n">
+        <v>353.9490661621094</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6579600</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>354.6252788942206</v>
+      </c>
+      <c r="C31" t="n">
+        <v>354.7820922478407</v>
+      </c>
+      <c r="D31" t="n">
+        <v>347.3336224508748</v>
+      </c>
+      <c r="E31" t="n">
+        <v>349.5583801269531</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5872100</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>344.0013987080436</v>
+      </c>
+      <c r="C32" t="n">
+        <v>351.2440635956089</v>
+      </c>
+      <c r="D32" t="n">
+        <v>343.8347751839987</v>
+      </c>
+      <c r="E32" t="n">
+        <v>349.48974609375</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8608400</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>351.3911117321571</v>
+      </c>
+      <c r="C33" t="n">
+        <v>358.2809400014152</v>
+      </c>
+      <c r="D33" t="n">
+        <v>350.3816500053927</v>
+      </c>
+      <c r="E33" t="n">
+        <v>357.2126770019531</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5996500</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>357.8594745050165</v>
+      </c>
+      <c r="C34" t="n">
+        <v>363.6516084782733</v>
+      </c>
+      <c r="D34" t="n">
+        <v>354.2920382421501</v>
+      </c>
+      <c r="E34" t="n">
+        <v>358.0848693847656</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6885300</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>356.7029783280342</v>
+      </c>
+      <c r="C35" t="n">
+        <v>356.7421891409456</v>
+      </c>
+      <c r="D35" t="n">
+        <v>350.8618233858751</v>
+      </c>
+      <c r="E35" t="n">
+        <v>354.2822265625</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7833000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>348.4901083853841</v>
+      </c>
+      <c r="C36" t="n">
+        <v>355.0565296362527</v>
+      </c>
+      <c r="D36" t="n">
+        <v>346.5888173917132</v>
+      </c>
+      <c r="E36" t="n">
+        <v>353.2630310058594</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5756700</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>354.1646210665127</v>
+      </c>
+      <c r="C37" t="n">
+        <v>358.1338858633925</v>
+      </c>
+      <c r="D37" t="n">
+        <v>352.8513429813036</v>
+      </c>
+      <c r="E37" t="n">
+        <v>355.2720947265625</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5462100</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>356.252207496177</v>
+      </c>
+      <c r="C38" t="n">
+        <v>358.9179748669274</v>
+      </c>
+      <c r="D38" t="n">
+        <v>354.1940732179572</v>
+      </c>
+      <c r="E38" t="n">
+        <v>358.6827697753906</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7766400</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>373.0896257903608</v>
+      </c>
+      <c r="C39" t="n">
+        <v>373.4032524981995</v>
+      </c>
+      <c r="D39" t="n">
+        <v>351.4792920385495</v>
+      </c>
+      <c r="E39" t="n">
+        <v>360.5056457519531</v>
+      </c>
+      <c r="F39" t="n">
+        <v>18858700</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>357.0166226761716</v>
+      </c>
+      <c r="C40" t="n">
+        <v>358.8493319750526</v>
+      </c>
+      <c r="D40" t="n">
+        <v>346.8239941782638</v>
+      </c>
+      <c r="E40" t="n">
+        <v>348.1764831542969</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11874900</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>340.5908266262187</v>
+      </c>
+      <c r="C41" t="n">
+        <v>347.4708747692525</v>
+      </c>
+      <c r="D41" t="n">
+        <v>336.7490038190758</v>
+      </c>
+      <c r="E41" t="n">
+        <v>337.8760681152344</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11441900</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>337.5232539470514</v>
+      </c>
+      <c r="C42" t="n">
+        <v>339.3755538588451</v>
+      </c>
+      <c r="D42" t="n">
+        <v>330.3981906639274</v>
+      </c>
+      <c r="E42" t="n">
+        <v>334.7496643066406</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8390800</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>332.3681048776954</v>
+      </c>
+      <c r="C43" t="n">
+        <v>333.9068078868114</v>
+      </c>
+      <c r="D43" t="n">
+        <v>320.0879412577473</v>
+      </c>
+      <c r="E43" t="n">
+        <v>327.1345825195312</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11181400</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>321.0974041522996</v>
+      </c>
+      <c r="C44" t="n">
+        <v>329.7905408141606</v>
+      </c>
+      <c r="D44" t="n">
+        <v>320.6759850821896</v>
+      </c>
+      <c r="E44" t="n">
+        <v>324.2335815429688</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9646600</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>319.7939098851405</v>
+      </c>
+      <c r="C45" t="n">
+        <v>323.6259521945154</v>
+      </c>
+      <c r="D45" t="n">
+        <v>317.7553960532753</v>
+      </c>
+      <c r="E45" t="n">
+        <v>321.2052001953125</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9697100</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>322.3617025788201</v>
+      </c>
+      <c r="C46" t="n">
+        <v>325.7428953487219</v>
+      </c>
+      <c r="D46" t="n">
+        <v>315.0406451379028</v>
+      </c>
+      <c r="E46" t="n">
+        <v>315.1484375</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7922100</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>313.2863393626572</v>
+      </c>
+      <c r="C47" t="n">
+        <v>318.0788226584959</v>
+      </c>
+      <c r="D47" t="n">
+        <v>307.8960032344128</v>
+      </c>
+      <c r="E47" t="n">
+        <v>317.74560546875</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9402900</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>313.6097362529</v>
+      </c>
+      <c r="C48" t="n">
+        <v>317.7848060357201</v>
+      </c>
+      <c r="D48" t="n">
+        <v>310.8459867308537</v>
+      </c>
+      <c r="E48" t="n">
+        <v>315.1680297851562</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9283800</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>316.8537128676349</v>
+      </c>
+      <c r="C49" t="n">
+        <v>321.3227886847148</v>
+      </c>
+      <c r="D49" t="n">
+        <v>313.5019209593692</v>
+      </c>
+      <c r="E49" t="n">
+        <v>320.9209899902344</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7157800</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>321.9010364932658</v>
+      </c>
+      <c r="C50" t="n">
+        <v>336.3275351202159</v>
+      </c>
+      <c r="D50" t="n">
+        <v>320.5583278451826</v>
+      </c>
+      <c r="E50" t="n">
+        <v>332.2994689941406</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10403300</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>331.6036653013031</v>
+      </c>
+      <c r="C51" t="n">
+        <v>332.2700996432553</v>
+      </c>
+      <c r="D51" t="n">
+        <v>324.6844366173477</v>
+      </c>
+      <c r="E51" t="n">
+        <v>325.889892578125</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7788700</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>320.4309500487702</v>
+      </c>
+      <c r="C52" t="n">
+        <v>321.6658065479886</v>
+      </c>
+      <c r="D52" t="n">
+        <v>314.0997345701073</v>
+      </c>
+      <c r="E52" t="n">
+        <v>315.4424133300781</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8676500</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>314.2075720220705</v>
+      </c>
+      <c r="C53" t="n">
+        <v>321.3424151200708</v>
+      </c>
+      <c r="D53" t="n">
+        <v>313.06088745762</v>
+      </c>
+      <c r="E53" t="n">
+        <v>314.129150390625</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6485400</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>310.6891466030926</v>
+      </c>
+      <c r="C54" t="n">
+        <v>311.1693669212913</v>
+      </c>
+      <c r="D54" t="n">
+        <v>302.6134236399317</v>
+      </c>
+      <c r="E54" t="n">
+        <v>307.3275146484375</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9182100</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>307.6705548284651</v>
+      </c>
+      <c r="C55" t="n">
+        <v>308.7192273184903</v>
+      </c>
+      <c r="D55" t="n">
+        <v>298.4579870426836</v>
+      </c>
+      <c r="E55" t="n">
+        <v>302.9270629882812</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8181100</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>304.6127916915999</v>
+      </c>
+      <c r="C56" t="n">
+        <v>308.4742348638782</v>
+      </c>
+      <c r="D56" t="n">
+        <v>303.8189445839627</v>
+      </c>
+      <c r="E56" t="n">
+        <v>305.3282470703125</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7337600</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>305.6908291650661</v>
+      </c>
+      <c r="C57" t="n">
+        <v>317.3829496811602</v>
+      </c>
+      <c r="D57" t="n">
+        <v>305.23019930011</v>
+      </c>
+      <c r="E57" t="n">
+        <v>313.5901184082031</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8406300</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>318.0592220645265</v>
+      </c>
+      <c r="C58" t="n">
+        <v>319.3529098722476</v>
+      </c>
+      <c r="D58" t="n">
+        <v>311.2869963920142</v>
+      </c>
+      <c r="E58" t="n">
+        <v>312.6884765625</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10773800</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>314.71720383448</v>
+      </c>
+      <c r="C59" t="n">
+        <v>321.4600287348608</v>
+      </c>
+      <c r="D59" t="n">
+        <v>314.5015892042089</v>
+      </c>
+      <c r="E59" t="n">
+        <v>319.7743225097656</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6149100</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>320.078109327525</v>
+      </c>
+      <c r="C60" t="n">
+        <v>328.5066396704157</v>
+      </c>
+      <c r="D60" t="n">
+        <v>319.3920845924249</v>
+      </c>
+      <c r="E60" t="n">
+        <v>323.1358947753906</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5504200</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>325.0568419581102</v>
+      </c>
+      <c r="C61" t="n">
+        <v>325.4390501917724</v>
+      </c>
+      <c r="D61" t="n">
+        <v>322.3322736002218</v>
+      </c>
+      <c r="E61" t="n">
+        <v>323.1947021484375</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2464500</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>320.6367866787963</v>
+      </c>
+      <c r="C62" t="n">
+        <v>323.478957830369</v>
+      </c>
+      <c r="D62" t="n">
+        <v>316.5891296309611</v>
+      </c>
+      <c r="E62" t="n">
+        <v>316.7655334472656</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6154600</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>316.9223461399793</v>
+      </c>
+      <c r="C63" t="n">
+        <v>322.1460884369951</v>
+      </c>
+      <c r="D63" t="n">
+        <v>316.3637041471038</v>
+      </c>
+      <c r="E63" t="n">
+        <v>318.0690307617188</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7978100</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>319.4998951185618</v>
+      </c>
+      <c r="C64" t="n">
+        <v>334.6026391486864</v>
+      </c>
+      <c r="D64" t="n">
+        <v>318.529644271779</v>
+      </c>
+      <c r="E64" t="n">
+        <v>332.9365234375</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9770000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>332.632709971988</v>
+      </c>
+      <c r="C65" t="n">
+        <v>334.4556390535126</v>
+      </c>
+      <c r="D65" t="n">
+        <v>322.1656652751352</v>
+      </c>
+      <c r="E65" t="n">
+        <v>326.8405456542969</v>
+      </c>
+      <c r="F65" t="n">
+        <v>8061600</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>328.3204578992349</v>
+      </c>
+      <c r="C66" t="n">
+        <v>329.0162928832224</v>
+      </c>
+      <c r="D66" t="n">
+        <v>321.9598711365138</v>
+      </c>
+      <c r="E66" t="n">
+        <v>324.31201171875</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5906000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>324.3120366886073</v>
+      </c>
+      <c r="C67" t="n">
+        <v>324.7066908730135</v>
+      </c>
+      <c r="D67" t="n">
+        <v>318.5203728665016</v>
+      </c>
+      <c r="E67" t="n">
+        <v>319.2998352050781</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4782800</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>318.8459617269979</v>
+      </c>
+      <c r="C68" t="n">
+        <v>322.0032250879344</v>
+      </c>
+      <c r="D68" t="n">
+        <v>318.1750466501944</v>
+      </c>
+      <c r="E68" t="n">
+        <v>319.2800903320312</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4628400</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>318.4414486886093</v>
+      </c>
+      <c r="C69" t="n">
+        <v>324.341629514822</v>
+      </c>
+      <c r="D69" t="n">
+        <v>315.3335056374652</v>
+      </c>
+      <c r="E69" t="n">
+        <v>323.9864196777344</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5910500</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>325.9597199441495</v>
+      </c>
+      <c r="C70" t="n">
+        <v>334.7211811769636</v>
+      </c>
+      <c r="D70" t="n">
+        <v>324.3712270965368</v>
+      </c>
+      <c r="E70" t="n">
+        <v>332.2348327636719</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7513200</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>332.9945215393808</v>
+      </c>
+      <c r="C71" t="n">
+        <v>340.3746776267931</v>
+      </c>
+      <c r="D71" t="n">
+        <v>332.8662521653069</v>
+      </c>
+      <c r="E71" t="n">
+        <v>337.2765808105469</v>
+      </c>
+      <c r="F71" t="n">
+        <v>7979000</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>336.4379310634787</v>
+      </c>
+      <c r="C72" t="n">
+        <v>340.3549345980833</v>
+      </c>
+      <c r="D72" t="n">
+        <v>332.5012053593197</v>
+      </c>
+      <c r="E72" t="n">
+        <v>336.5464782714844</v>
+      </c>
+      <c r="F72" t="n">
+        <v>6447200</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>335.875584402924</v>
+      </c>
+      <c r="C73" t="n">
+        <v>336.4379523174861</v>
+      </c>
+      <c r="D73" t="n">
+        <v>326.6109215358994</v>
+      </c>
+      <c r="E73" t="n">
+        <v>329.7386169433594</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6334000</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>329.1564601038647</v>
+      </c>
+      <c r="C74" t="n">
+        <v>331.0409661792534</v>
+      </c>
+      <c r="D74" t="n">
+        <v>326.0682693196749</v>
+      </c>
+      <c r="E74" t="n">
+        <v>327.2029113769531</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4685600</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>324.5389231377919</v>
+      </c>
+      <c r="C75" t="n">
+        <v>325.7722361921053</v>
+      </c>
+      <c r="D75" t="n">
+        <v>320.2371416572342</v>
+      </c>
+      <c r="E75" t="n">
+        <v>323.7594909667969</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6354900</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>323.6805434123363</v>
+      </c>
+      <c r="C76" t="n">
+        <v>330.1332457701224</v>
+      </c>
+      <c r="D76" t="n">
+        <v>321.7171186569828</v>
+      </c>
+      <c r="E76" t="n">
+        <v>323.0491027832031</v>
+      </c>
+      <c r="F76" t="n">
+        <v>10553000</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>318.5894351738589</v>
+      </c>
+      <c r="C77" t="n">
+        <v>325.3973174895482</v>
+      </c>
+      <c r="D77" t="n">
+        <v>317.3561220691985</v>
+      </c>
+      <c r="E77" t="n">
+        <v>320.8192749023438</v>
+      </c>
+      <c r="F77" t="n">
+        <v>7872400</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>319.6747419864576</v>
+      </c>
+      <c r="C78" t="n">
+        <v>323.4240016076582</v>
+      </c>
+      <c r="D78" t="n">
+        <v>319.4379555165406</v>
+      </c>
+      <c r="E78" t="n">
+        <v>320.4640502929688</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4463300</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>320.8587672253223</v>
+      </c>
+      <c r="C79" t="n">
+        <v>324.5981510876156</v>
+      </c>
+      <c r="D79" t="n">
+        <v>319.8030439224821</v>
+      </c>
+      <c r="E79" t="n">
+        <v>323.2069702148438</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2842700</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>322.8320412014528</v>
+      </c>
+      <c r="C80" t="n">
+        <v>327.4594342482506</v>
+      </c>
+      <c r="D80" t="n">
+        <v>321.9045873641298</v>
+      </c>
+      <c r="E80" t="n">
+        <v>327.4002075195312</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4359300</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>326.4728087048146</v>
+      </c>
+      <c r="C81" t="n">
+        <v>329.787940036587</v>
+      </c>
+      <c r="D81" t="n">
+        <v>323.8976351612195</v>
+      </c>
+      <c r="E81" t="n">
+        <v>324.548828125</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4346800</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>325.3282463216964</v>
+      </c>
+      <c r="C82" t="n">
+        <v>331.6625250102778</v>
+      </c>
+      <c r="D82" t="n">
+        <v>325.1111820298963</v>
+      </c>
+      <c r="E82" t="n">
+        <v>327.7257995605469</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4432500</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>327.8837053458195</v>
+      </c>
+      <c r="C83" t="n">
+        <v>328.8802018879278</v>
+      </c>
+      <c r="D83" t="n">
+        <v>325.4762756879338</v>
+      </c>
+      <c r="E83" t="n">
+        <v>325.7031860351562</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4285200</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>326.4826326508298</v>
+      </c>
+      <c r="C84" t="n">
+        <v>335.717696654991</v>
+      </c>
+      <c r="D84" t="n">
+        <v>323.1280270938765</v>
+      </c>
+      <c r="E84" t="n">
+        <v>331.9092102050781</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6863600</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>330.9719222150325</v>
+      </c>
+      <c r="C85" t="n">
+        <v>342.3085268229226</v>
+      </c>
+      <c r="D85" t="n">
+        <v>329.3932753932535</v>
+      </c>
+      <c r="E85" t="n">
+        <v>337.4541931152344</v>
+      </c>
+      <c r="F85" t="n">
+        <v>7956600</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>343.6996829189171</v>
+      </c>
+      <c r="C86" t="n">
+        <v>347.9027932709801</v>
+      </c>
+      <c r="D86" t="n">
+        <v>340.5127911940015</v>
+      </c>
+      <c r="E86" t="n">
+        <v>344.3114013671875</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9441900</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>344.3213032237757</v>
+      </c>
+      <c r="C87" t="n">
+        <v>345.4361929991165</v>
+      </c>
+      <c r="D87" t="n">
+        <v>333.527344316932</v>
+      </c>
+      <c r="E87" t="n">
+        <v>337.1384887695312</v>
+      </c>
+      <c r="F87" t="n">
+        <v>7461400</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>336.4576913463828</v>
+      </c>
+      <c r="C88" t="n">
+        <v>343.2556975271264</v>
+      </c>
+      <c r="D88" t="n">
+        <v>336.2504730653109</v>
+      </c>
+      <c r="E88" t="n">
+        <v>342.2197265625</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5059300</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>342.6143671222478</v>
+      </c>
+      <c r="C89" t="n">
+        <v>344.4002020193836</v>
+      </c>
+      <c r="D89" t="n">
+        <v>337.9080553379447</v>
+      </c>
+      <c r="E89" t="n">
+        <v>339.3880310058594</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4129100</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>336.8622415935578</v>
+      </c>
+      <c r="C90" t="n">
+        <v>338.0758024907637</v>
+      </c>
+      <c r="D90" t="n">
+        <v>329.4820846932586</v>
+      </c>
+      <c r="E90" t="n">
+        <v>335.9643859863281</v>
+      </c>
+      <c r="F90" t="n">
+        <v>7146400</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>336.9411188846722</v>
+      </c>
+      <c r="C91" t="n">
+        <v>337.2765764147031</v>
+      </c>
+      <c r="D91" t="n">
+        <v>328.4065987621919</v>
+      </c>
+      <c r="E91" t="n">
+        <v>329.47216796875</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5605900</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>330.8929641448377</v>
+      </c>
+      <c r="C92" t="n">
+        <v>335.5696777492312</v>
+      </c>
+      <c r="D92" t="n">
+        <v>329.639928884428</v>
+      </c>
+      <c r="E92" t="n">
+        <v>330.4884338378906</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5740900</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>330.7252428593728</v>
+      </c>
+      <c r="C93" t="n">
+        <v>334.9185072715596</v>
+      </c>
+      <c r="D93" t="n">
+        <v>323.6805441940115</v>
+      </c>
+      <c r="E93" t="n">
+        <v>334.4350280761719</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6943500</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>330.3897780779105</v>
+      </c>
+      <c r="C94" t="n">
+        <v>331.7119162692861</v>
+      </c>
+      <c r="D94" t="n">
+        <v>326.0189235086448</v>
+      </c>
+      <c r="E94" t="n">
+        <v>326.6010437011719</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8039100</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>323.0293559592084</v>
+      </c>
+      <c r="C95" t="n">
+        <v>335.3526407320732</v>
+      </c>
+      <c r="D95" t="n">
+        <v>322.1413765634589</v>
+      </c>
+      <c r="E95" t="n">
+        <v>333.912109375</v>
+      </c>
+      <c r="F95" t="n">
+        <v>7596500</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>334.8987575018528</v>
+      </c>
+      <c r="C96" t="n">
+        <v>343.4332779356386</v>
+      </c>
+      <c r="D96" t="n">
+        <v>334.168645798694</v>
+      </c>
+      <c r="E96" t="n">
+        <v>343.1076965332031</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8933300</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>342.5453159613966</v>
+      </c>
+      <c r="C97" t="n">
+        <v>350.2116096750548</v>
+      </c>
+      <c r="D97" t="n">
+        <v>342.1407856401066</v>
+      </c>
+      <c r="E97" t="n">
+        <v>349.7380065917969</v>
+      </c>
+      <c r="F97" t="n">
+        <v>7491400</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>349.5505410261084</v>
+      </c>
+      <c r="C98" t="n">
+        <v>353.0926127392032</v>
+      </c>
+      <c r="D98" t="n">
+        <v>348.2777534390037</v>
+      </c>
+      <c r="E98" t="n">
+        <v>351.5041198730469</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9082200</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>349.2249303389971</v>
+      </c>
+      <c r="C99" t="n">
+        <v>350.0537130836444</v>
+      </c>
+      <c r="D99" t="n">
+        <v>342.6340826093485</v>
+      </c>
+      <c r="E99" t="n">
+        <v>346.9457702636719</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10399500</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>290.0456258453373</v>
+      </c>
+      <c r="C100" t="n">
+        <v>295.5018014762001</v>
+      </c>
+      <c r="D100" t="n">
+        <v>276.6567723884028</v>
+      </c>
+      <c r="E100" t="n">
+        <v>278.9260864257812</v>
+      </c>
+      <c r="F100" t="n">
+        <v>65836900</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>279.9324825435024</v>
+      </c>
+      <c r="C101" t="n">
+        <v>291.0027024164021</v>
+      </c>
+      <c r="D101" t="n">
+        <v>279.9324825435024</v>
+      </c>
+      <c r="E101" t="n">
+        <v>290.094970703125</v>
+      </c>
+      <c r="F101" t="n">
+        <v>23396900</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>290.4008374442539</v>
+      </c>
+      <c r="C102" t="n">
+        <v>291.6539028887257</v>
+      </c>
+      <c r="D102" t="n">
+        <v>285.3590676854078</v>
+      </c>
+      <c r="E102" t="n">
+        <v>288.3880920410156</v>
+      </c>
+      <c r="F102" t="n">
+        <v>13456400</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>288.200605503728</v>
+      </c>
+      <c r="C103" t="n">
+        <v>289.0392644171012</v>
+      </c>
+      <c r="D103" t="n">
+        <v>280.8993981188336</v>
+      </c>
+      <c r="E103" t="n">
+        <v>283.099609375</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12022200</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>282.201779365365</v>
+      </c>
+      <c r="C104" t="n">
+        <v>286.5233135903719</v>
+      </c>
+      <c r="D104" t="n">
+        <v>278.5117159450099</v>
+      </c>
+      <c r="E104" t="n">
+        <v>281.7775268554688</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8664200</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>280.899399533992</v>
+      </c>
+      <c r="C105" t="n">
+        <v>284.2441289542904</v>
+      </c>
+      <c r="D105" t="n">
+        <v>274.8808256732182</v>
+      </c>
+      <c r="E105" t="n">
+        <v>280.3863220214844</v>
+      </c>
+      <c r="F105" t="n">
+        <v>10809100</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>278.2453003524489</v>
+      </c>
+      <c r="C106" t="n">
+        <v>280.7020503139632</v>
+      </c>
+      <c r="D106" t="n">
+        <v>270.3915411669698</v>
+      </c>
+      <c r="E106" t="n">
+        <v>272.2366027832031</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12944100</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>270.6283910377749</v>
+      </c>
+      <c r="C107" t="n">
+        <v>273.1936885205944</v>
+      </c>
+      <c r="D107" t="n">
+        <v>262.7351865430599</v>
+      </c>
+      <c r="E107" t="n">
+        <v>264.9649963378906</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13035300</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>263.494873693566</v>
+      </c>
+      <c r="C108" t="n">
+        <v>274.1013663098342</v>
+      </c>
+      <c r="D108" t="n">
+        <v>262.8535569062469</v>
+      </c>
+      <c r="E108" t="n">
+        <v>272.9568481445312</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9572800</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>270.4902050418196</v>
+      </c>
+      <c r="C109" t="n">
+        <v>276.4397058352786</v>
+      </c>
+      <c r="D109" t="n">
+        <v>269.6712984464802</v>
+      </c>
+      <c r="E109" t="n">
+        <v>272.01953125</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10371600</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>273.8152476410468</v>
+      </c>
+      <c r="C110" t="n">
+        <v>275.7589504136547</v>
+      </c>
+      <c r="D110" t="n">
+        <v>269.010264317998</v>
+      </c>
+      <c r="E110" t="n">
+        <v>269.5726623535156</v>
+      </c>
+      <c r="F110" t="n">
+        <v>7284700</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>268.8030763257778</v>
+      </c>
+      <c r="C111" t="n">
+        <v>275.9562927620499</v>
+      </c>
+      <c r="D111" t="n">
+        <v>266.198304439543</v>
+      </c>
+      <c r="E111" t="n">
+        <v>275.1867065429688</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6333100</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>274.4467004687212</v>
+      </c>
+      <c r="C112" t="n">
+        <v>282.4878958393087</v>
+      </c>
+      <c r="D112" t="n">
+        <v>272.1280658242715</v>
+      </c>
+      <c r="E112" t="n">
+        <v>280.5737915039062</v>
+      </c>
+      <c r="F112" t="n">
+        <v>12336900</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>281.8169569225497</v>
+      </c>
+      <c r="C113" t="n">
+        <v>289.5424162609187</v>
+      </c>
+      <c r="D113" t="n">
+        <v>280.7119132986369</v>
+      </c>
+      <c r="E113" t="n">
+        <v>289.2760314941406</v>
+      </c>
+      <c r="F113" t="n">
+        <v>10281900</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>290.0752312306441</v>
+      </c>
+      <c r="C114" t="n">
+        <v>290.3021716729731</v>
+      </c>
+      <c r="D114" t="n">
+        <v>284.4907860910092</v>
+      </c>
+      <c r="E114" t="n">
+        <v>285.2307739257812</v>
+      </c>
+      <c r="F114" t="n">
+        <v>6091700</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>286.1286505407075</v>
+      </c>
+      <c r="C115" t="n">
+        <v>286.2569199258207</v>
+      </c>
+      <c r="D115" t="n">
+        <v>282.4681855456762</v>
+      </c>
+      <c r="E115" t="n">
+        <v>284.3526916503906</v>
+      </c>
+      <c r="F115" t="n">
+        <v>6632000</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>287.0067764654547</v>
+      </c>
+      <c r="C116" t="n">
+        <v>287.0067764654547</v>
+      </c>
+      <c r="D116" t="n">
+        <v>283.0601744920274</v>
+      </c>
+      <c r="E116" t="n">
+        <v>286.0595703125</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4931800</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>285.0433100706192</v>
+      </c>
+      <c r="C117" t="n">
+        <v>286.9179399107358</v>
+      </c>
+      <c r="D117" t="n">
+        <v>281.7380250284705</v>
+      </c>
+      <c r="E117" t="n">
+        <v>286.1286315917969</v>
+      </c>
+      <c r="F117" t="n">
+        <v>6974100</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>284.6979833712643</v>
+      </c>
+      <c r="C118" t="n">
+        <v>287.8749991147026</v>
+      </c>
+      <c r="D118" t="n">
+        <v>277.9098533754537</v>
+      </c>
+      <c r="E118" t="n">
+        <v>278.5708923339844</v>
+      </c>
+      <c r="F118" t="n">
+        <v>7247500</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>278.4327740747045</v>
+      </c>
+      <c r="C119" t="n">
+        <v>278.6300861021672</v>
+      </c>
+      <c r="D119" t="n">
+        <v>268.1715851207944</v>
+      </c>
+      <c r="E119" t="n">
+        <v>270.2929077148438</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9684500</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>273.5883087457124</v>
+      </c>
+      <c r="C120" t="n">
+        <v>280.9388364524249</v>
+      </c>
+      <c r="D120" t="n">
+        <v>273.1739023127244</v>
+      </c>
+      <c r="E120" t="n">
+        <v>280.4060668945312</v>
+      </c>
+      <c r="F120" t="n">
+        <v>11380600</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>283.1489568057956</v>
+      </c>
+      <c r="C121" t="n">
+        <v>291.3184213223429</v>
+      </c>
+      <c r="D121" t="n">
+        <v>281.422318519362</v>
+      </c>
+      <c r="E121" t="n">
+        <v>282.8332214355469</v>
+      </c>
+      <c r="F121" t="n">
+        <v>10210000</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>280.899378965855</v>
+      </c>
+      <c r="C122" t="n">
+        <v>290.2034849465505</v>
+      </c>
+      <c r="D122" t="n">
+        <v>280.0607201096653</v>
+      </c>
+      <c r="E122" t="n">
+        <v>289.3549499511719</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9723300</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>284.3132152404683</v>
+      </c>
+      <c r="C123" t="n">
+        <v>291.3677603814479</v>
+      </c>
+      <c r="D123" t="n">
+        <v>283.6620222891216</v>
+      </c>
+      <c r="E123" t="n">
+        <v>290.9928283691406</v>
+      </c>
+      <c r="F123" t="n">
+        <v>8141400</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>285.1321178149137</v>
+      </c>
+      <c r="C124" t="n">
+        <v>289.8187076809586</v>
+      </c>
+      <c r="D124" t="n">
+        <v>280.5639211910132</v>
+      </c>
+      <c r="E124" t="n">
+        <v>285.3491821289062</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7051100</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>285.1518685944145</v>
+      </c>
+      <c r="C125" t="n">
+        <v>290.4107024732037</v>
+      </c>
+      <c r="D125" t="n">
+        <v>283.8396065771265</v>
+      </c>
+      <c r="E125" t="n">
+        <v>288.0624694824219</v>
+      </c>
+      <c r="F125" t="n">
+        <v>7796000</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>286.1779504316799</v>
+      </c>
+      <c r="C126" t="n">
+        <v>287.5000885291143</v>
+      </c>
+      <c r="D126" t="n">
+        <v>282.9121398572339</v>
+      </c>
+      <c r="E126" t="n">
+        <v>284.9150390625</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5397900</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>283.5041446062434</v>
+      </c>
+      <c r="C127" t="n">
+        <v>287.4408703764128</v>
+      </c>
+      <c r="D127" t="n">
+        <v>279.2714056266989</v>
+      </c>
+      <c r="E127" t="n">
+        <v>282.6556396484375</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6816900</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>280.3985261413432</v>
+      </c>
+      <c r="C128" t="n">
+        <v>283.5803655260448</v>
+      </c>
+      <c r="D128" t="n">
+        <v>277.0774975936055</v>
+      </c>
+      <c r="E128" t="n">
+        <v>283.550537109375</v>
+      </c>
+      <c r="F128" t="n">
+        <v>10348800</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>285.7479583300972</v>
+      </c>
+      <c r="C129" t="n">
+        <v>285.9468043127463</v>
+      </c>
+      <c r="D129" t="n">
+        <v>277.3161057836816</v>
+      </c>
+      <c r="E129" t="n">
+        <v>280.736572265625</v>
+      </c>
+      <c r="F129" t="n">
+        <v>6075600</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>280.7763694963311</v>
+      </c>
+      <c r="C130" t="n">
+        <v>284.5945585040109</v>
+      </c>
+      <c r="D130" t="n">
+        <v>279.0064793259336</v>
+      </c>
+      <c r="E130" t="n">
+        <v>283.6300659179688</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6878800</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>283.1627358622739</v>
+      </c>
+      <c r="C131" t="n">
+        <v>285.9269470548217</v>
+      </c>
+      <c r="D131" t="n">
+        <v>274.7209602020642</v>
+      </c>
+      <c r="E131" t="n">
+        <v>275.4766235351562</v>
+      </c>
+      <c r="F131" t="n">
+        <v>10512300</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>276.4808941849521</v>
+      </c>
+      <c r="C132" t="n">
+        <v>281.2735286763525</v>
+      </c>
+      <c r="D132" t="n">
+        <v>276.2323139355343</v>
+      </c>
+      <c r="E132" t="n">
+        <v>280.4880065917969</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4737600</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>282.3672788368328</v>
+      </c>
+      <c r="C133" t="n">
+        <v>285.767839547621</v>
+      </c>
+      <c r="D133" t="n">
+        <v>279.4439727693734</v>
+      </c>
+      <c r="E133" t="n">
+        <v>283.8686828613281</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4854000</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>286.1655640520241</v>
+      </c>
+      <c r="C134" t="n">
+        <v>287.3488084380985</v>
+      </c>
+      <c r="D134" t="n">
+        <v>283.2223824666901</v>
+      </c>
+      <c r="E134" t="n">
+        <v>285.9368896484375</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5752000</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>283.5803557381978</v>
+      </c>
+      <c r="C135" t="n">
+        <v>286.7621646688093</v>
+      </c>
+      <c r="D135" t="n">
+        <v>281.4624471949345</v>
+      </c>
+      <c r="E135" t="n">
+        <v>282.7152709960938</v>
+      </c>
+      <c r="F135" t="n">
+        <v>4544100</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>282.3871618979052</v>
+      </c>
+      <c r="C136" t="n">
+        <v>285.9169892839216</v>
+      </c>
+      <c r="D136" t="n">
+        <v>278.4794876796185</v>
+      </c>
+      <c r="E136" t="n">
+        <v>278.8473815917969</v>
+      </c>
+      <c r="F136" t="n">
+        <v>5542100</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>277.4056183419098</v>
+      </c>
+      <c r="C137" t="n">
+        <v>281.4922936115716</v>
+      </c>
+      <c r="D137" t="n">
+        <v>273.4382870867091</v>
+      </c>
+      <c r="E137" t="n">
+        <v>274.0249328613281</v>
+      </c>
+      <c r="F137" t="n">
+        <v>38893000</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>277.5547645320462</v>
+      </c>
+      <c r="C138" t="n">
+        <v>279.1556066962045</v>
+      </c>
+      <c r="D138" t="n">
+        <v>267.5618207785692</v>
+      </c>
+      <c r="E138" t="n">
+        <v>268.00927734375</v>
+      </c>
+      <c r="F138" t="n">
+        <v>10424200</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>267.3430655755382</v>
+      </c>
+      <c r="C139" t="n">
+        <v>271.8274627132414</v>
+      </c>
+      <c r="D139" t="n">
+        <v>266.0703359894755</v>
+      </c>
+      <c r="E139" t="n">
+        <v>270.7337036132812</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5911700</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>273.4382596260376</v>
+      </c>
+      <c r="C140" t="n">
+        <v>274.5121128941823</v>
+      </c>
+      <c r="D140" t="n">
+        <v>265.5930528118823</v>
+      </c>
+      <c r="E140" t="n">
+        <v>269.0135192871094</v>
+      </c>
+      <c r="F140" t="n">
+        <v>8121200</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>268.4567257080549</v>
+      </c>
+      <c r="C141" t="n">
+        <v>273.0803427820733</v>
+      </c>
+      <c r="D141" t="n">
+        <v>265.6626860357957</v>
+      </c>
+      <c r="E141" t="n">
+        <v>266.5277404785156</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6218800</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>265.9808641274938</v>
+      </c>
+      <c r="C142" t="n">
+        <v>266.1499120468286</v>
+      </c>
+      <c r="D142" t="n">
+        <v>254.516344356629</v>
+      </c>
+      <c r="E142" t="n">
+        <v>257.5490112304688</v>
+      </c>
+      <c r="F142" t="n">
+        <v>10735300</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>258.7024415515604</v>
+      </c>
+      <c r="C143" t="n">
+        <v>260.8402257240527</v>
+      </c>
+      <c r="D143" t="n">
+        <v>255.2123953265358</v>
+      </c>
+      <c r="E143" t="n">
+        <v>260.3033142089844</v>
+      </c>
+      <c r="F143" t="n">
+        <v>7774700</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>261.506421503485</v>
+      </c>
+      <c r="C144" t="n">
+        <v>270.3359967880393</v>
+      </c>
+      <c r="D144" t="n">
+        <v>261.1186217504552</v>
+      </c>
+      <c r="E144" t="n">
+        <v>269.0533142089844</v>
+      </c>
+      <c r="F144" t="n">
+        <v>9170800</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>272.6527466700565</v>
+      </c>
+      <c r="C145" t="n">
+        <v>273.7365528939259</v>
+      </c>
+      <c r="D145" t="n">
+        <v>269.2223575051711</v>
+      </c>
+      <c r="E145" t="n">
+        <v>272.424072265625</v>
+      </c>
+      <c r="F145" t="n">
+        <v>5473400</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>270.7436786461413</v>
+      </c>
+      <c r="C146" t="n">
+        <v>277.4553455215711</v>
+      </c>
+      <c r="D146" t="n">
+        <v>269.9879849618526</v>
+      </c>
+      <c r="E146" t="n">
+        <v>275.6854553222656</v>
+      </c>
+      <c r="F146" t="n">
+        <v>6407000</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>276.3019282869355</v>
+      </c>
+      <c r="C147" t="n">
+        <v>281.6911311912249</v>
+      </c>
+      <c r="D147" t="n">
+        <v>275.6755011928929</v>
+      </c>
+      <c r="E147" t="n">
+        <v>279.7621459960938</v>
+      </c>
+      <c r="F147" t="n">
+        <v>7097000</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>307.0960565749332</v>
+      </c>
+      <c r="C148" t="n">
+        <v>310.6557125153819</v>
+      </c>
+      <c r="D148" t="n">
+        <v>299.0420501528358</v>
+      </c>
+      <c r="E148" t="n">
+        <v>305.982421875</v>
+      </c>
+      <c r="F148" t="n">
+        <v>22099800</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>310.2281413790238</v>
+      </c>
+      <c r="C149" t="n">
+        <v>311.1926339297742</v>
+      </c>
+      <c r="D149" t="n">
+        <v>303.0988467016243</v>
+      </c>
+      <c r="E149" t="n">
+        <v>304.2423400878906</v>
+      </c>
+      <c r="F149" t="n">
+        <v>9645000</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>304.0832470042582</v>
+      </c>
+      <c r="C150" t="n">
+        <v>306.1414986993597</v>
+      </c>
+      <c r="D150" t="n">
+        <v>302.4127950535677</v>
+      </c>
+      <c r="E150" t="n">
+        <v>305.1670532226562</v>
+      </c>
+      <c r="F150" t="n">
+        <v>5742000</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>306.2011519366599</v>
+      </c>
+      <c r="C151" t="n">
+        <v>308.607391668382</v>
+      </c>
+      <c r="D151" t="n">
+        <v>302.4724483346268</v>
+      </c>
+      <c r="E151" t="n">
+        <v>302.6016845703125</v>
+      </c>
+      <c r="F151" t="n">
+        <v>5212900</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>301.5278433900291</v>
+      </c>
+      <c r="C152" t="n">
+        <v>311.5406631473035</v>
+      </c>
+      <c r="D152" t="n">
+        <v>301.199730811355</v>
+      </c>
+      <c r="E152" t="n">
+        <v>311.2224731445312</v>
+      </c>
+      <c r="F152" t="n">
+        <v>7972200</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>310.7352487756957</v>
+      </c>
+      <c r="C153" t="n">
+        <v>317.8048561417646</v>
+      </c>
+      <c r="D153" t="n">
+        <v>310.7352487756957</v>
+      </c>
+      <c r="E153" t="n">
+        <v>312.4057006835938</v>
+      </c>
+      <c r="F153" t="n">
+        <v>5864500</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>314.2054174655202</v>
+      </c>
+      <c r="C154" t="n">
+        <v>315.9554320324556</v>
+      </c>
+      <c r="D154" t="n">
+        <v>309.3829548311358</v>
+      </c>
+      <c r="E154" t="n">
+        <v>312.2664794921875</v>
+      </c>
+      <c r="F154" t="n">
+        <v>5041200</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>313.2111061223722</v>
+      </c>
+      <c r="C155" t="n">
+        <v>316.8005902653832</v>
+      </c>
+      <c r="D155" t="n">
+        <v>311.3318249203894</v>
+      </c>
+      <c r="E155" t="n">
+        <v>314.6031494140625</v>
+      </c>
+      <c r="F155" t="n">
+        <v>5205600</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>318.2324307180975</v>
+      </c>
+      <c r="C156" t="n">
+        <v>323.4227876628706</v>
+      </c>
+      <c r="D156" t="n">
+        <v>315.338983249174</v>
+      </c>
+      <c r="E156" t="n">
+        <v>322.7864379882812</v>
+      </c>
+      <c r="F156" t="n">
+        <v>9414700</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>322.3489342821542</v>
+      </c>
+      <c r="C157" t="n">
+        <v>323.5520542213801</v>
+      </c>
+      <c r="D157" t="n">
+        <v>318.3020404433487</v>
+      </c>
+      <c r="E157" t="n">
+        <v>321.6429748535156</v>
+      </c>
+      <c r="F157" t="n">
+        <v>9050600</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>351.0052603166191</v>
+      </c>
+      <c r="C158" t="n">
+        <v>355.648722319699</v>
+      </c>
+      <c r="D158" t="n">
+        <v>343.2694442738866</v>
+      </c>
+      <c r="E158" t="n">
+        <v>344.0450134277344</v>
+      </c>
+      <c r="F158" t="n">
+        <v>26097300</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>348.8873678788304</v>
+      </c>
+      <c r="C159" t="n">
+        <v>356.5237461069854</v>
+      </c>
+      <c r="D159" t="n">
+        <v>347.1174776591131</v>
+      </c>
+      <c r="E159" t="n">
+        <v>351.5123596191406</v>
+      </c>
+      <c r="F159" t="n">
+        <v>11807300</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>352.6657614176121</v>
+      </c>
+      <c r="C160" t="n">
+        <v>354.8234513171886</v>
+      </c>
+      <c r="D160" t="n">
+        <v>348.5095069624251</v>
+      </c>
+      <c r="E160" t="n">
+        <v>352.5464477539062</v>
+      </c>
+      <c r="F160" t="n">
+        <v>7255800</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>354.4654798371856</v>
+      </c>
+      <c r="C161" t="n">
+        <v>356.2453229047883</v>
+      </c>
+      <c r="D161" t="n">
+        <v>349.3944670661433</v>
+      </c>
+      <c r="E161" t="n">
+        <v>352.9044189453125</v>
+      </c>
+      <c r="F161" t="n">
+        <v>8554600</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>351.9001510435625</v>
+      </c>
+      <c r="C162" t="n">
+        <v>354.4654858887946</v>
+      </c>
+      <c r="D162" t="n">
+        <v>346.9683273478323</v>
+      </c>
+      <c r="E162" t="n">
+        <v>352.6757202148438</v>
+      </c>
+      <c r="F162" t="n">
+        <v>7256100</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>354.8135029963465</v>
+      </c>
+      <c r="C163" t="n">
+        <v>367.5308771185002</v>
+      </c>
+      <c r="D163" t="n">
+        <v>353.6998683282982</v>
+      </c>
+      <c r="E163" t="n">
+        <v>364.6871032714844</v>
+      </c>
+      <c r="F163" t="n">
+        <v>10604100</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>363.9214802466298</v>
+      </c>
+      <c r="C164" t="n">
+        <v>368.7339901692348</v>
+      </c>
+      <c r="D164" t="n">
+        <v>362.9371121823581</v>
+      </c>
+      <c r="E164" t="n">
+        <v>368.6345520019531</v>
+      </c>
+      <c r="F164" t="n">
+        <v>9046600</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>366.4172241064422</v>
+      </c>
+      <c r="C165" t="n">
+        <v>369.87744160261</v>
+      </c>
+      <c r="D165" t="n">
+        <v>360.9385059451532</v>
+      </c>
+      <c r="E165" t="n">
+        <v>368.3760375976562</v>
+      </c>
+      <c r="F165" t="n">
+        <v>6879900</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>369.8476329800702</v>
+      </c>
+      <c r="C166" t="n">
+        <v>370.7822971534658</v>
+      </c>
+      <c r="D166" t="n">
+        <v>364.9356847817637</v>
+      </c>
+      <c r="E166" t="n">
+        <v>366.6856994628906</v>
+      </c>
+      <c r="F166" t="n">
+        <v>4945400</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>366.4569824541582</v>
+      </c>
+      <c r="C167" t="n">
+        <v>368.7240330587824</v>
+      </c>
+      <c r="D167" t="n">
+        <v>362.5791367283888</v>
+      </c>
+      <c r="E167" t="n">
+        <v>368.6445007324219</v>
+      </c>
+      <c r="F167" t="n">
+        <v>4916900</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>368.3760355922912</v>
+      </c>
+      <c r="C168" t="n">
+        <v>369.6885161814855</v>
+      </c>
+      <c r="D168" t="n">
+        <v>359.7552596250864</v>
+      </c>
+      <c r="E168" t="n">
+        <v>361.8035583496094</v>
+      </c>
+      <c r="F168" t="n">
+        <v>6489000</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>361.0379593902868</v>
+      </c>
+      <c r="C169" t="n">
+        <v>366.45699060703</v>
+      </c>
+      <c r="D169" t="n">
+        <v>356.2154964951898</v>
+      </c>
+      <c r="E169" t="n">
+        <v>365.1942138671875</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6695500</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>364.5578575186544</v>
+      </c>
+      <c r="C170" t="n">
+        <v>367.7098380224884</v>
+      </c>
+      <c r="D170" t="n">
+        <v>362.6487478916185</v>
+      </c>
+      <c r="E170" t="n">
+        <v>367.6402282714844</v>
+      </c>
+      <c r="F170" t="n">
+        <v>5235400</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>369.8774674335755</v>
+      </c>
+      <c r="C171" t="n">
+        <v>377.8221130371094</v>
+      </c>
+      <c r="D171" t="n">
+        <v>369.8774674335755</v>
+      </c>
+      <c r="E171" t="n">
+        <v>377.8221130371094</v>
+      </c>
+      <c r="F171" t="n">
+        <v>6455100</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>378.2894437474218</v>
+      </c>
+      <c r="C172" t="n">
+        <v>382.6246688242237</v>
+      </c>
+      <c r="D172" t="n">
+        <v>373.9343128299113</v>
+      </c>
+      <c r="E172" t="n">
+        <v>382.2567749023438</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6949600</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>380.6758011703357</v>
+      </c>
+      <c r="C173" t="n">
+        <v>395.1630654325308</v>
+      </c>
+      <c r="D173" t="n">
+        <v>379.8405751710962</v>
+      </c>
+      <c r="E173" t="n">
+        <v>394.138916015625</v>
+      </c>
+      <c r="F173" t="n">
+        <v>9236300</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>394.2482660415264</v>
+      </c>
+      <c r="C174" t="n">
+        <v>401.8548154208889</v>
+      </c>
+      <c r="D174" t="n">
+        <v>390.7681426338459</v>
+      </c>
+      <c r="E174" t="n">
+        <v>398.8818054199219</v>
+      </c>
+      <c r="F174" t="n">
+        <v>8454100</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>398.7227040337817</v>
+      </c>
+      <c r="C175" t="n">
+        <v>399.6175868268494</v>
+      </c>
+      <c r="D175" t="n">
+        <v>393.7510992453305</v>
+      </c>
+      <c r="E175" t="n">
+        <v>396.8235473632812</v>
+      </c>
+      <c r="F175" t="n">
+        <v>5342500</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>392.0607685404387</v>
+      </c>
+      <c r="C176" t="n">
+        <v>395.3718745508767</v>
+      </c>
+      <c r="D176" t="n">
+        <v>388.0337805215488</v>
+      </c>
+      <c r="E176" t="n">
+        <v>391.6133422851562</v>
+      </c>
+      <c r="F176" t="n">
+        <v>9811200</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>387.7851953583757</v>
+      </c>
+      <c r="C177" t="n">
+        <v>389.9130568930274</v>
+      </c>
+      <c r="D177" t="n">
+        <v>381.3221087690695</v>
+      </c>
+      <c r="E177" t="n">
+        <v>388.9087829589844</v>
+      </c>
+      <c r="F177" t="n">
+        <v>8400700</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>387.7851736187118</v>
+      </c>
+      <c r="C178" t="n">
+        <v>392.7468254889498</v>
+      </c>
+      <c r="D178" t="n">
+        <v>385.3093241434657</v>
+      </c>
+      <c r="E178" t="n">
+        <v>387.0294799804688</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5016800</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>387.3377362764213</v>
+      </c>
+      <c r="C179" t="n">
+        <v>391.1460027273716</v>
+      </c>
+      <c r="D179" t="n">
+        <v>378.5380196367677</v>
+      </c>
+      <c r="E179" t="n">
+        <v>381.1232299804688</v>
+      </c>
+      <c r="F179" t="n">
+        <v>7783900</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>378.9555995605828</v>
+      </c>
+      <c r="C180" t="n">
+        <v>383.9172514426562</v>
+      </c>
+      <c r="D180" t="n">
+        <v>378.3789067550467</v>
+      </c>
+      <c r="E180" t="n">
+        <v>380.3078918457031</v>
+      </c>
+      <c r="F180" t="n">
+        <v>4732500</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>379.7510949944643</v>
+      </c>
+      <c r="C181" t="n">
+        <v>388.322137279522</v>
+      </c>
+      <c r="D181" t="n">
+        <v>378.846259230469</v>
+      </c>
+      <c r="E181" t="n">
+        <v>386.2638854980469</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5598600</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>383.8078958628703</v>
+      </c>
+      <c r="C182" t="n">
+        <v>384.3249318452775</v>
+      </c>
+      <c r="D182" t="n">
+        <v>374.2723613660349</v>
+      </c>
+      <c r="E182" t="n">
+        <v>374.7197875976562</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6498100</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>376.2808953624811</v>
+      </c>
+      <c r="C183" t="n">
+        <v>382.3462596379654</v>
+      </c>
+      <c r="D183" t="n">
+        <v>374.9485088403697</v>
+      </c>
+      <c r="E183" t="n">
+        <v>381.8292236328125</v>
+      </c>
+      <c r="F183" t="n">
+        <v>4544000</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>382.7737976901378</v>
+      </c>
+      <c r="C184" t="n">
+        <v>387.0493961299752</v>
+      </c>
+      <c r="D184" t="n">
+        <v>378.7965137522062</v>
+      </c>
+      <c r="E184" t="n">
+        <v>380.3576049804688</v>
+      </c>
+      <c r="F184" t="n">
+        <v>4330800</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>381.6005025160485</v>
+      </c>
+      <c r="C185" t="n">
+        <v>382.9328889810419</v>
+      </c>
+      <c r="D185" t="n">
+        <v>373.317822146985</v>
+      </c>
+      <c r="E185" t="n">
+        <v>378.1502075195312</v>
+      </c>
+      <c r="F185" t="n">
+        <v>10257900</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>373.9740550559011</v>
+      </c>
+      <c r="C186" t="n">
+        <v>381.172959697494</v>
+      </c>
+      <c r="D186" t="n">
+        <v>373.7851619834815</v>
+      </c>
+      <c r="E186" t="n">
+        <v>377.7027587890625</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6623700</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>375.8334605430848</v>
+      </c>
+      <c r="C187" t="n">
+        <v>377.9215103567756</v>
+      </c>
+      <c r="D187" t="n">
+        <v>372.5919643898307</v>
+      </c>
+      <c r="E187" t="n">
+        <v>375.7738037109375</v>
+      </c>
+      <c r="F187" t="n">
+        <v>3874400</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>377.8419717237235</v>
+      </c>
+      <c r="C188" t="n">
+        <v>385.259597724852</v>
+      </c>
+      <c r="D188" t="n">
+        <v>374.6700853756592</v>
+      </c>
+      <c r="E188" t="n">
+        <v>374.8590087890625</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6808400</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>387.7851867936407</v>
+      </c>
+      <c r="C189" t="n">
+        <v>399.1005645351637</v>
+      </c>
+      <c r="D189" t="n">
+        <v>387.606216297745</v>
+      </c>
+      <c r="E189" t="n">
+        <v>394.2184448242188</v>
+      </c>
+      <c r="F189" t="n">
+        <v>12666100</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>397.2710257691138</v>
+      </c>
+      <c r="C190" t="n">
+        <v>401.7454703246708</v>
+      </c>
+      <c r="D190" t="n">
+        <v>394.9443182415365</v>
+      </c>
+      <c r="E190" t="n">
+        <v>397.201416015625</v>
+      </c>
+      <c r="F190" t="n">
+        <v>10897300</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>394.8746856398852</v>
+      </c>
+      <c r="C191" t="n">
+        <v>406.3889089451397</v>
+      </c>
+      <c r="D191" t="n">
+        <v>392.7468242313375</v>
+      </c>
+      <c r="E191" t="n">
+        <v>404.2610778808594</v>
+      </c>
+      <c r="F191" t="n">
+        <v>6963200</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>407.6616556237274</v>
+      </c>
+      <c r="C192" t="n">
+        <v>410.6545715332031</v>
+      </c>
+      <c r="D192" t="n">
+        <v>405.1261492204914</v>
+      </c>
+      <c r="E192" t="n">
+        <v>410.6545715332031</v>
+      </c>
+      <c r="F192" t="n">
+        <v>8590400</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>411.1517339543602</v>
+      </c>
+      <c r="C193" t="n">
+        <v>413.6176609610221</v>
+      </c>
+      <c r="D193" t="n">
+        <v>402.2525488568183</v>
+      </c>
+      <c r="E193" t="n">
+        <v>405.1460266113281</v>
+      </c>
+      <c r="F193" t="n">
+        <v>6512900</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>406.3889145916303</v>
+      </c>
+      <c r="C194" t="n">
+        <v>407.6517216421196</v>
+      </c>
+      <c r="D194" t="n">
+        <v>400.820711098459</v>
+      </c>
+      <c r="E194" t="n">
+        <v>403.2468566894531</v>
+      </c>
+      <c r="F194" t="n">
+        <v>4938100</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>406.6872501409831</v>
+      </c>
+      <c r="C195" t="n">
+        <v>407.5622574937536</v>
+      </c>
+      <c r="D195" t="n">
+        <v>402.5110897188582</v>
+      </c>
+      <c r="E195" t="n">
+        <v>406.2000122070312</v>
+      </c>
+      <c r="F195" t="n">
+        <v>7269600</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>406.7000122070312</v>
+      </c>
+      <c r="C196" t="n">
+        <v>414.1600036621094</v>
+      </c>
+      <c r="D196" t="n">
+        <v>399.6499938964844</v>
+      </c>
+      <c r="E196" t="n">
+        <v>411.0400085449219</v>
+      </c>
+      <c r="F196" t="n">
+        <v>6777900</v>
+      </c>
+      <c r="G196" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>410.6799926757812</v>
+      </c>
+      <c r="C197" t="n">
+        <v>411.75</v>
+      </c>
+      <c r="D197" t="n">
+        <v>406.5400085449219</v>
+      </c>
+      <c r="E197" t="n">
+        <v>407.6499938964844</v>
+      </c>
+      <c r="F197" t="n">
+        <v>4815100</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>409.1199951171875</v>
+      </c>
+      <c r="C198" t="n">
+        <v>411.1600036621094</v>
+      </c>
+      <c r="D198" t="n">
+        <v>398.5899963378906</v>
+      </c>
+      <c r="E198" t="n">
+        <v>399.5299987792969</v>
+      </c>
+      <c r="F198" t="n">
+        <v>5838800</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>402.7699890136719</v>
+      </c>
+      <c r="C199" t="n">
+        <v>406.2000122070312</v>
+      </c>
+      <c r="D199" t="n">
+        <v>399.1499938964844</v>
+      </c>
+      <c r="E199" t="n">
+        <v>400.9599914550781</v>
+      </c>
+      <c r="F199" t="n">
+        <v>11896900</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>402.1400146484375</v>
+      </c>
+      <c r="C200" t="n">
+        <v>409.4599914550781</v>
+      </c>
+      <c r="D200" t="n">
+        <v>402.1400146484375</v>
+      </c>
+      <c r="E200" t="n">
+        <v>406.6799926757812</v>
+      </c>
+      <c r="F200" t="n">
+        <v>5818600</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>409.5199890136719</v>
+      </c>
+      <c r="C201" t="n">
+        <v>409.8999938964844</v>
+      </c>
+      <c r="D201" t="n">
+        <v>402.8399963378906</v>
+      </c>
+      <c r="E201" t="n">
+        <v>409.25</v>
+      </c>
+      <c r="F201" t="n">
+        <v>6675900</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>410.5400085449219</v>
+      </c>
+      <c r="C202" t="n">
+        <v>413.4299926757812</v>
+      </c>
+      <c r="D202" t="n">
+        <v>400</v>
+      </c>
+      <c r="E202" t="n">
+        <v>405.7999877929688</v>
+      </c>
+      <c r="F202" t="n">
+        <v>6858800</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>406.6499938964844</v>
+      </c>
+      <c r="C203" t="n">
+        <v>417.5799865722656</v>
+      </c>
+      <c r="D203" t="n">
+        <v>406.6499938964844</v>
+      </c>
+      <c r="E203" t="n">
+        <v>415.5299987792969</v>
+      </c>
+      <c r="F203" t="n">
+        <v>6014400</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>416.1600036621094</v>
+      </c>
+      <c r="C204" t="n">
+        <v>427.9299926757812</v>
+      </c>
+      <c r="D204" t="n">
+        <v>416.1600036621094</v>
+      </c>
+      <c r="E204" t="n">
+        <v>427.8900146484375</v>
+      </c>
+      <c r="F204" t="n">
+        <v>10588200</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>426.5299987792969</v>
+      </c>
+      <c r="C205" t="n">
+        <v>426.7000122070312</v>
+      </c>
+      <c r="D205" t="n">
+        <v>415.8099975585938</v>
+      </c>
+      <c r="E205" t="n">
+        <v>419.8200073242188</v>
+      </c>
+      <c r="F205" t="n">
+        <v>5167400</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>422.7200012207031</v>
+      </c>
+      <c r="C206" t="n">
+        <v>422.739990234375</v>
+      </c>
+      <c r="D206" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="E206" t="n">
+        <v>415.6300048828125</v>
+      </c>
+      <c r="F206" t="n">
+        <v>5779800</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>417.1099853515625</v>
+      </c>
+      <c r="C207" t="n">
+        <v>428.0199890136719</v>
+      </c>
+      <c r="D207" t="n">
+        <v>413.7300109863281</v>
+      </c>
+      <c r="E207" t="n">
+        <v>426.5400085449219</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4985900</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>428.1300048828125</v>
+      </c>
+      <c r="C208" t="n">
+        <v>430.2000122070312</v>
+      </c>
+      <c r="D208" t="n">
+        <v>420.5400085449219</v>
+      </c>
+      <c r="E208" t="n">
+        <v>425.3599853515625</v>
+      </c>
+      <c r="F208" t="n">
+        <v>3928800</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>423.489990234375</v>
+      </c>
+      <c r="C209" t="n">
+        <v>424.4400024414062</v>
+      </c>
+      <c r="D209" t="n">
+        <v>415.0499877929688</v>
+      </c>
+      <c r="E209" t="n">
+        <v>417.989990234375</v>
+      </c>
+      <c r="F209" t="n">
+        <v>6379000</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>423.9500122070312</v>
+      </c>
+      <c r="C210" t="n">
+        <v>428.6000061035156</v>
+      </c>
+      <c r="D210" t="n">
+        <v>422.1300048828125</v>
+      </c>
+      <c r="E210" t="n">
+        <v>428.1900024414062</v>
+      </c>
+      <c r="F210" t="n">
+        <v>5800500</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>427.1499938964844</v>
+      </c>
+      <c r="C211" t="n">
+        <v>430.7699890136719</v>
+      </c>
+      <c r="D211" t="n">
+        <v>423.8299865722656</v>
+      </c>
+      <c r="E211" t="n">
+        <v>425.6000061035156</v>
+      </c>
+      <c r="F211" t="n">
+        <v>3859200</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>427.1099853515625</v>
+      </c>
+      <c r="C212" t="n">
+        <v>434.2999877929688</v>
+      </c>
+      <c r="D212" t="n">
+        <v>423.5199890136719</v>
+      </c>
+      <c r="E212" t="n">
+        <v>431.6799926757812</v>
+      </c>
+      <c r="F212" t="n">
+        <v>5566000</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>431.6700134277344</v>
+      </c>
+      <c r="C213" t="n">
+        <v>432.8599853515625</v>
+      </c>
+      <c r="D213" t="n">
+        <v>423.6499938964844</v>
+      </c>
+      <c r="E213" t="n">
+        <v>424.6199951171875</v>
+      </c>
+      <c r="F213" t="n">
+        <v>3798600</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>426.4700012207031</v>
+      </c>
+      <c r="C214" t="n">
+        <v>431.5499877929688</v>
+      </c>
+      <c r="D214" t="n">
+        <v>425.5299987792969</v>
+      </c>
+      <c r="E214" t="n">
+        <v>429.0899963378906</v>
+      </c>
+      <c r="F214" t="n">
+        <v>3863800</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>431</v>
+      </c>
+      <c r="C215" t="n">
+        <v>432.1499938964844</v>
+      </c>
+      <c r="D215" t="n">
+        <v>421.7900085449219</v>
+      </c>
+      <c r="E215" t="n">
+        <v>425.1900024414062</v>
+      </c>
+      <c r="F215" t="n">
+        <v>5135900</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>419.489990234375</v>
+      </c>
+      <c r="C216" t="n">
+        <v>424.1099853515625</v>
+      </c>
+      <c r="D216" t="n">
+        <v>414.3699951171875</v>
+      </c>
+      <c r="E216" t="n">
+        <v>418.5199890136719</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6764800</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>449.3900146484375</v>
+      </c>
+      <c r="C217" t="n">
+        <v>461.6199951171875</v>
+      </c>
+      <c r="D217" t="n">
+        <v>420.3699951171875</v>
+      </c>
+      <c r="E217" t="n">
+        <v>423.3800048828125</v>
+      </c>
+      <c r="F217" t="n">
+        <v>13281900</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>426.7200012207031</v>
+      </c>
+      <c r="C218" t="n">
+        <v>437.4700012207031</v>
+      </c>
+      <c r="D218" t="n">
+        <v>425.1000061035156</v>
+      </c>
+      <c r="E218" t="n">
+        <v>426.0899963378906</v>
+      </c>
+      <c r="F218" t="n">
+        <v>10718100</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>427.25</v>
+      </c>
+      <c r="C219" t="n">
+        <v>431.0199890136719</v>
+      </c>
+      <c r="D219" t="n">
+        <v>417.3800048828125</v>
+      </c>
+      <c r="E219" t="n">
+        <v>421.5499877929688</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4818800</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>422.4800109863281</v>
+      </c>
+      <c r="C220" t="n">
+        <v>437</v>
+      </c>
+      <c r="D220" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="E220" t="n">
+        <v>436.3500061035156</v>
+      </c>
+      <c r="F220" t="n">
+        <v>6833600</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>434.9500122070312</v>
+      </c>
+      <c r="C221" t="n">
+        <v>436.3200073242188</v>
+      </c>
+      <c r="D221" t="n">
+        <v>429.7000122070312</v>
+      </c>
+      <c r="E221" t="n">
+        <v>431.3099975585938</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4234100</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>428.2699890136719</v>
+      </c>
+      <c r="C222" t="n">
+        <v>430.489990234375</v>
+      </c>
+      <c r="D222" t="n">
+        <v>420.3999938964844</v>
+      </c>
+      <c r="E222" t="n">
+        <v>423.5599975585938</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4868700</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>425.239990234375</v>
+      </c>
+      <c r="C223" t="n">
+        <v>429</v>
+      </c>
+      <c r="D223" t="n">
+        <v>418.9200134277344</v>
+      </c>
+      <c r="E223" t="n">
+        <v>420.739990234375</v>
+      </c>
+      <c r="F223" t="n">
+        <v>3752500</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>422.510009765625</v>
+      </c>
+      <c r="C224" t="n">
+        <v>422.8800048828125</v>
+      </c>
+      <c r="D224" t="n">
+        <v>412.5400085449219</v>
+      </c>
+      <c r="E224" t="n">
+        <v>417.6400146484375</v>
+      </c>
+      <c r="F224" t="n">
+        <v>4615700</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>419.9299926757812</v>
+      </c>
+      <c r="C225" t="n">
+        <v>430.4599914550781</v>
+      </c>
+      <c r="D225" t="n">
+        <v>415.1099853515625</v>
+      </c>
+      <c r="E225" t="n">
+        <v>428.7900085449219</v>
+      </c>
+      <c r="F225" t="n">
+        <v>5917300</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>428.260009765625</v>
+      </c>
+      <c r="C226" t="n">
+        <v>431.6799926757812</v>
+      </c>
+      <c r="D226" t="n">
+        <v>420.3500061035156</v>
+      </c>
+      <c r="E226" t="n">
+        <v>420.5700073242188</v>
+      </c>
+      <c r="F226" t="n">
+        <v>5257900</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>415.1900024414062</v>
+      </c>
+      <c r="C227" t="n">
+        <v>427.3399963378906</v>
+      </c>
+      <c r="D227" t="n">
+        <v>411.2900085449219</v>
+      </c>
+      <c r="E227" t="n">
+        <v>421.4700012207031</v>
+      </c>
+      <c r="F227" t="n">
+        <v>3647500</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>422</v>
+      </c>
+      <c r="C228" t="n">
+        <v>422.8099975585938</v>
+      </c>
+      <c r="D228" t="n">
+        <v>414.0599975585938</v>
+      </c>
+      <c r="E228" t="n">
+        <v>414.3999938964844</v>
+      </c>
+      <c r="F228" t="n">
+        <v>3920900</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>417.4299926757812</v>
+      </c>
+      <c r="C229" t="n">
+        <v>419.3399963378906</v>
+      </c>
+      <c r="D229" t="n">
+        <v>413.3200073242188</v>
+      </c>
+      <c r="E229" t="n">
+        <v>415.3599853515625</v>
+      </c>
+      <c r="F229" t="n">
+        <v>3209600</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>415.5599975585938</v>
+      </c>
+      <c r="C230" t="n">
+        <v>416</v>
+      </c>
+      <c r="D230" t="n">
+        <v>406.6700134277344</v>
+      </c>
+      <c r="E230" t="n">
+        <v>407.5499877929688</v>
+      </c>
+      <c r="F230" t="n">
+        <v>5266300</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>403.1900024414062</v>
+      </c>
+      <c r="C231" t="n">
+        <v>416.3599853515625</v>
+      </c>
+      <c r="D231" t="n">
+        <v>397.7999877929688</v>
+      </c>
+      <c r="E231" t="n">
+        <v>412.75</v>
+      </c>
+      <c r="F231" t="n">
+        <v>5399000</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>415.2699890136719</v>
+      </c>
+      <c r="C232" t="n">
+        <v>416.9700012207031</v>
+      </c>
+      <c r="D232" t="n">
+        <v>402.3999938964844</v>
+      </c>
+      <c r="E232" t="n">
+        <v>403.9700012207031</v>
+      </c>
+      <c r="F232" t="n">
+        <v>4712400</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>401.5899963378906</v>
+      </c>
+      <c r="C233" t="n">
+        <v>410.6400146484375</v>
+      </c>
+      <c r="D233" t="n">
+        <v>400.6600036621094</v>
+      </c>
+      <c r="E233" t="n">
+        <v>407.0799865722656</v>
+      </c>
+      <c r="F233" t="n">
+        <v>4095900</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>408.6000061035156</v>
+      </c>
+      <c r="C234" t="n">
+        <v>413.0700073242188</v>
+      </c>
+      <c r="D234" t="n">
+        <v>407.989990234375</v>
+      </c>
+      <c r="E234" t="n">
+        <v>408.739990234375</v>
+      </c>
+      <c r="F234" t="n">
+        <v>3182200</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>409</v>
+      </c>
+      <c r="C235" t="n">
+        <v>410.8999938964844</v>
+      </c>
+      <c r="D235" t="n">
+        <v>401.3200073242188</v>
+      </c>
+      <c r="E235" t="n">
+        <v>402.1900024414062</v>
+      </c>
+      <c r="F235" t="n">
+        <v>3398900</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>400.9800109863281</v>
+      </c>
+      <c r="C236" t="n">
+        <v>407.2000122070312</v>
+      </c>
+      <c r="D236" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="E236" t="n">
+        <v>405.5899963378906</v>
+      </c>
+      <c r="F236" t="n">
+        <v>3317200</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>405.5899963378906</v>
+      </c>
+      <c r="C237" t="n">
+        <v>407.3200073242188</v>
+      </c>
+      <c r="D237" t="n">
+        <v>398.5899963378906</v>
+      </c>
+      <c r="E237" t="n">
+        <v>399.0599975585938</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4170200</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>398</v>
+      </c>
+      <c r="C238" t="n">
+        <v>403.1799926757812</v>
+      </c>
+      <c r="D238" t="n">
+        <v>396.5599975585938</v>
+      </c>
+      <c r="E238" t="n">
+        <v>401.7300109863281</v>
+      </c>
+      <c r="F238" t="n">
+        <v>3476400</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>398.5700073242188</v>
+      </c>
+      <c r="C239" t="n">
+        <v>398.8999938964844</v>
+      </c>
+      <c r="D239" t="n">
+        <v>391.4299926757812</v>
+      </c>
+      <c r="E239" t="n">
+        <v>395.6199951171875</v>
+      </c>
+      <c r="F239" t="n">
+        <v>5295100</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>397.4299926757812</v>
+      </c>
+      <c r="C240" t="n">
+        <v>398.7900085449219</v>
+      </c>
+      <c r="D240" t="n">
+        <v>393.510009765625</v>
+      </c>
+      <c r="E240" t="n">
+        <v>393.9299926757812</v>
+      </c>
+      <c r="F240" t="n">
+        <v>3605100</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>394.5700073242188</v>
+      </c>
+      <c r="C241" t="n">
+        <v>396.7999877929688</v>
+      </c>
+      <c r="D241" t="n">
+        <v>386.3299865722656</v>
+      </c>
+      <c r="E241" t="n">
+        <v>388.6099853515625</v>
+      </c>
+      <c r="F241" t="n">
+        <v>5268500</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="C242" t="n">
+        <v>392.7099914550781</v>
+      </c>
+      <c r="D242" t="n">
+        <v>383.8299865722656</v>
+      </c>
+      <c r="E242" t="n">
+        <v>384.8500061035156</v>
+      </c>
+      <c r="F242" t="n">
+        <v>4497200</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>386</v>
+      </c>
+      <c r="C243" t="n">
+        <v>393.6600036621094</v>
+      </c>
+      <c r="D243" t="n">
+        <v>386</v>
+      </c>
+      <c r="E243" t="n">
+        <v>390.1099853515625</v>
+      </c>
+      <c r="F243" t="n">
+        <v>4879600</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>391.0400085449219</v>
+      </c>
+      <c r="C244" t="n">
+        <v>399.5799865722656</v>
+      </c>
+      <c r="D244" t="n">
+        <v>390.8599853515625</v>
+      </c>
+      <c r="E244" t="n">
+        <v>398.760009765625</v>
+      </c>
+      <c r="F244" t="n">
+        <v>4683900</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>397.7999877929688</v>
+      </c>
+      <c r="C245" t="n">
+        <v>399.0299987792969</v>
+      </c>
+      <c r="D245" t="n">
+        <v>395.6199951171875</v>
+      </c>
+      <c r="E245" t="n">
+        <v>396.5899963378906</v>
+      </c>
+      <c r="F245" t="n">
+        <v>2655000</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>396.3299865722656</v>
+      </c>
+      <c r="C246" t="n">
+        <v>406.25</v>
+      </c>
+      <c r="D246" t="n">
+        <v>396.010009765625</v>
+      </c>
+      <c r="E246" t="n">
+        <v>401.010009765625</v>
+      </c>
+      <c r="F246" t="n">
+        <v>3557000</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>396.8699951171875</v>
+      </c>
+      <c r="C247" t="n">
+        <v>399.8800048828125</v>
+      </c>
+      <c r="D247" t="n">
+        <v>393.7699890136719</v>
+      </c>
+      <c r="E247" t="n">
+        <v>395.0499877929688</v>
+      </c>
+      <c r="F247" t="n">
+        <v>3668200</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>396.4200134277344</v>
+      </c>
+      <c r="C248" t="n">
+        <v>396.739990234375</v>
+      </c>
+      <c r="D248" t="n">
+        <v>392.6600036621094</v>
+      </c>
+      <c r="E248" t="n">
+        <v>392.9500122070312</v>
+      </c>
+      <c r="F248" t="n">
+        <v>2455500</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>393.5199890136719</v>
+      </c>
+      <c r="C249" t="n">
+        <v>394.489990234375</v>
+      </c>
+      <c r="D249" t="n">
+        <v>387.7099914550781</v>
+      </c>
+      <c r="E249" t="n">
+        <v>389.4100036621094</v>
+      </c>
+      <c r="F249" t="n">
+        <v>5748000</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>392.0799865722656</v>
+      </c>
+      <c r="C250" t="n">
+        <v>399.6000061035156</v>
+      </c>
+      <c r="D250" t="n">
+        <v>391.7799987792969</v>
+      </c>
+      <c r="E250" t="n">
+        <v>396.2999877929688</v>
+      </c>
+      <c r="F250" t="n">
+        <v>3716200</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>399.2699890136719</v>
+      </c>
+      <c r="C251" t="n">
+        <v>401.1400146484375</v>
+      </c>
+      <c r="D251" t="n">
+        <v>396.510009765625</v>
+      </c>
+      <c r="E251" t="n">
+        <v>399.6600036621094</v>
+      </c>
+      <c r="F251" t="n">
+        <v>3265300</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>400.0199890136719</v>
+      </c>
+      <c r="C252" t="n">
+        <v>405.1600036621094</v>
+      </c>
+      <c r="D252" t="n">
+        <v>395.2999877929688</v>
+      </c>
+      <c r="E252" t="n">
+        <v>400.9400024414062</v>
+      </c>
+      <c r="F252" t="n">
+        <v>5488900</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>397.0499877929688</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>402.2300109863281</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>395.2000122070312</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>397.1400146484375</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>5565400</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4707,7 +10661,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:49</t>
+          <t>2026-09-07 03:08:40</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -10661,7 +10661,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:40</t>
+          <t>2026-09-08 08:52:31</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>302.3426751055266</v>
+        <v>323.8273433349329</v>
       </c>
       <c r="C2" t="n">
-        <v>309.6470496882431</v>
+        <v>342.5362771646614</v>
       </c>
       <c r="D2" t="n">
-        <v>300.1611114077264</v>
+        <v>318.6266310717227</v>
       </c>
       <c r="E2" t="n">
-        <v>307.16357421875</v>
+        <v>338.8451538085938</v>
       </c>
       <c r="F2" t="n">
-        <v>14126700</v>
+        <v>46408900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>311.3709271996748</v>
+        <v>336.5466531982527</v>
       </c>
       <c r="C3" t="n">
-        <v>313.2603281414504</v>
+        <v>339.4781519824642</v>
       </c>
       <c r="D3" t="n">
-        <v>305.6150754302345</v>
+        <v>332.4951561509477</v>
       </c>
       <c r="E3" t="n">
-        <v>311.8968505859375</v>
+        <v>337.7348327636719</v>
       </c>
       <c r="F3" t="n">
-        <v>18438600</v>
+        <v>17804300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>323.8273141699113</v>
+        <v>339.8969462743543</v>
       </c>
       <c r="C4" t="n">
-        <v>342.5362463146478</v>
+        <v>351.5644796571226</v>
       </c>
       <c r="D4" t="n">
-        <v>318.6266023750954</v>
+        <v>336.8193657730168</v>
       </c>
       <c r="E4" t="n">
-        <v>338.8451232910156</v>
+        <v>344.3866882324219</v>
       </c>
       <c r="F4" t="n">
-        <v>46408900</v>
+        <v>18943500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>336.5466531982527</v>
+        <v>346.6169614598537</v>
       </c>
       <c r="C5" t="n">
-        <v>339.4781519824642</v>
+        <v>352.8597713233265</v>
       </c>
       <c r="D5" t="n">
-        <v>332.4951561509477</v>
+        <v>343.2666855000246</v>
       </c>
       <c r="E5" t="n">
-        <v>337.7348327636719</v>
+        <v>343.3153991699219</v>
       </c>
       <c r="F5" t="n">
-        <v>17804300</v>
+        <v>14016200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,25 +573,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>339.8969462743543</v>
+        <v>344.2562617205344</v>
       </c>
       <c r="C6" t="n">
-        <v>351.5644796571226</v>
+        <v>344.6972712574788</v>
       </c>
       <c r="D6" t="n">
-        <v>336.8193657730168</v>
+        <v>335.7003177947291</v>
       </c>
       <c r="E6" t="n">
-        <v>344.3866882324219</v>
+        <v>340.9534606933594</v>
       </c>
       <c r="F6" t="n">
-        <v>18943500</v>
+        <v>11035900</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>346.6169306487971</v>
+        <v>340.5711991051483</v>
       </c>
       <c r="C7" t="n">
-        <v>352.8597399573416</v>
+        <v>342.0805014268064</v>
       </c>
       <c r="D7" t="n">
-        <v>343.2666549867767</v>
+        <v>331.5742462609258</v>
       </c>
       <c r="E7" t="n">
-        <v>343.3153686523438</v>
+        <v>333.005126953125</v>
       </c>
       <c r="F7" t="n">
-        <v>14016200</v>
+        <v>12695800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,25 +625,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>344.2562617205344</v>
+        <v>330.9568224057415</v>
       </c>
       <c r="C8" t="n">
-        <v>344.6972712574788</v>
+        <v>336.1609442520178</v>
       </c>
       <c r="D8" t="n">
-        <v>335.7003177947291</v>
+        <v>330.9568224057415</v>
       </c>
       <c r="E8" t="n">
-        <v>340.9534606933594</v>
+        <v>334.7986450195312</v>
       </c>
       <c r="F8" t="n">
-        <v>11035900</v>
+        <v>8467700</v>
       </c>
       <c r="G8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>340.5711991051483</v>
+        <v>336.6803662104043</v>
       </c>
       <c r="C9" t="n">
-        <v>342.0805014268064</v>
+        <v>338.0524456778033</v>
       </c>
       <c r="D9" t="n">
-        <v>331.5742462609258</v>
+        <v>327.4579882805058</v>
       </c>
       <c r="E9" t="n">
-        <v>333.005126953125</v>
+        <v>328.14404296875</v>
       </c>
       <c r="F9" t="n">
-        <v>12695800</v>
+        <v>11255600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>330.9568224057415</v>
+        <v>329.7905316198508</v>
       </c>
       <c r="C10" t="n">
-        <v>336.1609442520178</v>
+        <v>334.161595373165</v>
       </c>
       <c r="D10" t="n">
-        <v>330.9568224057415</v>
+        <v>327.1835657302883</v>
       </c>
       <c r="E10" t="n">
-        <v>334.7986450195312</v>
+        <v>329.9767456054688</v>
       </c>
       <c r="F10" t="n">
-        <v>8467700</v>
+        <v>13656800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>336.6803662104043</v>
+        <v>327.7912281730855</v>
       </c>
       <c r="C11" t="n">
-        <v>338.0524456778033</v>
+        <v>335.6513373618812</v>
       </c>
       <c r="D11" t="n">
-        <v>327.4579882805058</v>
+        <v>325.9683288776566</v>
       </c>
       <c r="E11" t="n">
-        <v>328.14404296875</v>
+        <v>334.4948425292969</v>
       </c>
       <c r="F11" t="n">
-        <v>11255600</v>
+        <v>8903700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>329.7905316198508</v>
+        <v>334.2008052062361</v>
       </c>
       <c r="C12" t="n">
-        <v>334.161595373165</v>
+        <v>345.6675310141911</v>
       </c>
       <c r="D12" t="n">
-        <v>327.1835657302883</v>
+        <v>333.1815333788629</v>
       </c>
       <c r="E12" t="n">
-        <v>329.9767456054688</v>
+        <v>340.7574157714844</v>
       </c>
       <c r="F12" t="n">
-        <v>13656800</v>
+        <v>12504100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>327.7912281730855</v>
+        <v>343.2174040946968</v>
       </c>
       <c r="C13" t="n">
-        <v>335.6513373618812</v>
+        <v>347.4316547985749</v>
       </c>
       <c r="D13" t="n">
-        <v>325.9683288776566</v>
+        <v>340.904444380264</v>
       </c>
       <c r="E13" t="n">
-        <v>334.4948425292969</v>
+        <v>344.7952880859375</v>
       </c>
       <c r="F13" t="n">
-        <v>8903700</v>
+        <v>9016300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>334.2008052062361</v>
+        <v>341.9432916493518</v>
       </c>
       <c r="C14" t="n">
-        <v>345.6675310141911</v>
+        <v>343.2075787683629</v>
       </c>
       <c r="D14" t="n">
-        <v>333.1815333788629</v>
+        <v>336.7489800892123</v>
       </c>
       <c r="E14" t="n">
-        <v>340.7574157714844</v>
+        <v>338.6698913574219</v>
       </c>
       <c r="F14" t="n">
-        <v>12504100</v>
+        <v>8104900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>343.217373716776</v>
+        <v>340.9926318704661</v>
       </c>
       <c r="C15" t="n">
-        <v>347.4316240476539</v>
+        <v>342.9919647748283</v>
       </c>
       <c r="D15" t="n">
-        <v>340.9044142070616</v>
+        <v>334.4948223631065</v>
       </c>
       <c r="E15" t="n">
-        <v>344.7952575683594</v>
+        <v>337.2193908691406</v>
       </c>
       <c r="F15" t="n">
-        <v>9016300</v>
+        <v>6774700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>341.9432916493518</v>
+        <v>337.1214299699541</v>
       </c>
       <c r="C16" t="n">
-        <v>343.2075787683629</v>
+        <v>338.6601031752857</v>
       </c>
       <c r="D16" t="n">
-        <v>336.7489800892123</v>
+        <v>334.641876568426</v>
       </c>
       <c r="E16" t="n">
-        <v>338.6698913574219</v>
+        <v>338.2974853515625</v>
       </c>
       <c r="F16" t="n">
-        <v>8104900</v>
+        <v>6878900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>340.9926010114185</v>
+        <v>336.8959565312304</v>
       </c>
       <c r="C17" t="n">
-        <v>342.9919337348455</v>
+        <v>342.3549032814228</v>
       </c>
       <c r="D17" t="n">
-        <v>334.4947920920956</v>
+        <v>335.5042568017067</v>
       </c>
       <c r="E17" t="n">
-        <v>337.2193603515625</v>
+        <v>338.4150390625</v>
       </c>
       <c r="F17" t="n">
-        <v>6774700</v>
+        <v>7429700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>337.1214299699541</v>
+        <v>337.042992446128</v>
       </c>
       <c r="C18" t="n">
-        <v>338.6601031752857</v>
+        <v>341.7473034781017</v>
       </c>
       <c r="D18" t="n">
-        <v>334.641876568426</v>
+        <v>334.8182646079004</v>
       </c>
       <c r="E18" t="n">
-        <v>338.2974853515625</v>
+        <v>341.3552551269531</v>
       </c>
       <c r="F18" t="n">
-        <v>6878900</v>
+        <v>8825500</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>336.8959869118207</v>
+        <v>340.3653902924742</v>
       </c>
       <c r="C19" t="n">
-        <v>342.3549341542898</v>
+        <v>348.000043885751</v>
       </c>
       <c r="D19" t="n">
-        <v>335.5042870567964</v>
+        <v>337.7780149171845</v>
       </c>
       <c r="E19" t="n">
-        <v>338.4150695800781</v>
+        <v>346.6671752929688</v>
       </c>
       <c r="F19" t="n">
-        <v>7429700</v>
+        <v>8564200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>337.042992446128</v>
+        <v>350.1267830161296</v>
       </c>
       <c r="C20" t="n">
-        <v>341.7473034781017</v>
+        <v>360.6624384882734</v>
       </c>
       <c r="D20" t="n">
-        <v>334.8182646079004</v>
+        <v>349.4995296363098</v>
       </c>
       <c r="E20" t="n">
-        <v>341.3552551269531</v>
+        <v>353.0179748535156</v>
       </c>
       <c r="F20" t="n">
-        <v>8825500</v>
+        <v>13494800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>340.3653902924742</v>
+        <v>353.8314330983794</v>
       </c>
       <c r="C21" t="n">
-        <v>348.000043885751</v>
+        <v>355.2917144647868</v>
       </c>
       <c r="D21" t="n">
-        <v>337.7780149171845</v>
+        <v>349.9895806938981</v>
       </c>
       <c r="E21" t="n">
-        <v>346.6671752929688</v>
+        <v>351.6164855957031</v>
       </c>
       <c r="F21" t="n">
-        <v>8564200</v>
+        <v>7181700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>350.126813283771</v>
+        <v>352.2437372182849</v>
       </c>
       <c r="C22" t="n">
-        <v>360.6624696666976</v>
+        <v>357.4478588776738</v>
       </c>
       <c r="D22" t="n">
-        <v>349.4995598497266</v>
+        <v>350.9206488503359</v>
       </c>
       <c r="E22" t="n">
-        <v>353.0180053710938</v>
+        <v>356.4089965820312</v>
       </c>
       <c r="F22" t="n">
-        <v>13494800</v>
+        <v>7236200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>353.8314638081978</v>
+        <v>359.613786634634</v>
       </c>
       <c r="C23" t="n">
-        <v>355.2917453013463</v>
+        <v>367.1602685308417</v>
       </c>
       <c r="D23" t="n">
-        <v>349.9896110702735</v>
+        <v>358.5063128850491</v>
       </c>
       <c r="E23" t="n">
-        <v>351.6165161132812</v>
+        <v>362.544189453125</v>
       </c>
       <c r="F23" t="n">
-        <v>7181700</v>
+        <v>9438300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>352.243767379212</v>
+        <v>365.0923241938757</v>
       </c>
       <c r="C24" t="n">
-        <v>357.4478894842047</v>
+        <v>368.7185619691624</v>
       </c>
       <c r="D24" t="n">
-        <v>350.9206788979734</v>
+        <v>358.7807287668154</v>
       </c>
       <c r="E24" t="n">
-        <v>356.4090270996094</v>
+        <v>360.358642578125</v>
       </c>
       <c r="F24" t="n">
-        <v>7236200</v>
+        <v>8759800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>359.613786634634</v>
+        <v>362.0345124206696</v>
       </c>
       <c r="C25" t="n">
-        <v>367.1602685308417</v>
+        <v>362.0345124206696</v>
       </c>
       <c r="D25" t="n">
-        <v>358.5063128850491</v>
+        <v>345.481298369123</v>
       </c>
       <c r="E25" t="n">
-        <v>362.544189453125</v>
+        <v>347.4316101074219</v>
       </c>
       <c r="F25" t="n">
-        <v>9438300</v>
+        <v>13141900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>365.0923551123336</v>
+        <v>347.6668450586018</v>
       </c>
       <c r="C26" t="n">
-        <v>368.7185931947143</v>
+        <v>351.9987280315978</v>
       </c>
       <c r="D26" t="n">
-        <v>358.7807591507652</v>
+        <v>346.2751751256885</v>
       </c>
       <c r="E26" t="n">
-        <v>360.3586730957031</v>
+        <v>351.5086975097656</v>
       </c>
       <c r="F26" t="n">
-        <v>8759800</v>
+        <v>5659400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>362.0345442209324</v>
+        <v>347.872702274778</v>
       </c>
       <c r="C27" t="n">
-        <v>362.0345442209324</v>
+        <v>355.1055281287331</v>
       </c>
       <c r="D27" t="n">
-        <v>345.4813287153903</v>
+        <v>346.3535896118073</v>
       </c>
       <c r="E27" t="n">
-        <v>347.431640625</v>
+        <v>352.7533874511719</v>
       </c>
       <c r="F27" t="n">
-        <v>13141900</v>
+        <v>5974800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>347.6668450586018</v>
+        <v>352.2241485667839</v>
       </c>
       <c r="C28" t="n">
-        <v>351.9987280315978</v>
+        <v>356.9578301902687</v>
       </c>
       <c r="D28" t="n">
-        <v>346.2751751256885</v>
+        <v>348.7547241397475</v>
       </c>
       <c r="E28" t="n">
-        <v>351.5086975097656</v>
+        <v>353.9490356445312</v>
       </c>
       <c r="F28" t="n">
-        <v>5659400</v>
+        <v>6579600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>347.8726721794402</v>
+        <v>354.6252788942206</v>
       </c>
       <c r="C29" t="n">
-        <v>355.1054974076654</v>
+        <v>354.7820922478407</v>
       </c>
       <c r="D29" t="n">
-        <v>346.3535596478916</v>
+        <v>347.3336224508748</v>
       </c>
       <c r="E29" t="n">
-        <v>352.7533569335938</v>
+        <v>349.5583801269531</v>
       </c>
       <c r="F29" t="n">
-        <v>5974800</v>
+        <v>5872100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>352.2241789356418</v>
+        <v>344.0014287463771</v>
       </c>
       <c r="C30" t="n">
-        <v>356.9578609672659</v>
+        <v>351.2440942663747</v>
       </c>
       <c r="D30" t="n">
-        <v>348.7547542094708</v>
+        <v>343.8348052077826</v>
       </c>
       <c r="E30" t="n">
-        <v>353.9490661621094</v>
+        <v>349.4897766113281</v>
       </c>
       <c r="F30" t="n">
-        <v>6579600</v>
+        <v>8608400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>354.6252788942206</v>
+        <v>351.3911117321571</v>
       </c>
       <c r="C31" t="n">
-        <v>354.7820922478407</v>
+        <v>358.2809400014152</v>
       </c>
       <c r="D31" t="n">
-        <v>347.3336224508748</v>
+        <v>350.3816500053927</v>
       </c>
       <c r="E31" t="n">
-        <v>349.5583801269531</v>
+        <v>357.2126770019531</v>
       </c>
       <c r="F31" t="n">
-        <v>5872100</v>
+        <v>5996500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>344.0013987080436</v>
+        <v>357.8594745050165</v>
       </c>
       <c r="C32" t="n">
-        <v>351.2440635956089</v>
+        <v>363.6516084782733</v>
       </c>
       <c r="D32" t="n">
-        <v>343.8347751839987</v>
+        <v>354.2920382421501</v>
       </c>
       <c r="E32" t="n">
-        <v>349.48974609375</v>
+        <v>358.0848693847656</v>
       </c>
       <c r="F32" t="n">
-        <v>8608400</v>
+        <v>6885300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>351.3911117321571</v>
+        <v>356.7029783280342</v>
       </c>
       <c r="C33" t="n">
-        <v>358.2809400014152</v>
+        <v>356.7421891409456</v>
       </c>
       <c r="D33" t="n">
-        <v>350.3816500053927</v>
+        <v>350.8618233858751</v>
       </c>
       <c r="E33" t="n">
-        <v>357.2126770019531</v>
+        <v>354.2822265625</v>
       </c>
       <c r="F33" t="n">
-        <v>5996500</v>
+        <v>7833000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>357.8594745050165</v>
+        <v>348.4901083853841</v>
       </c>
       <c r="C34" t="n">
-        <v>363.6516084782733</v>
+        <v>355.0565296362527</v>
       </c>
       <c r="D34" t="n">
-        <v>354.2920382421501</v>
+        <v>346.5888173917132</v>
       </c>
       <c r="E34" t="n">
-        <v>358.0848693847656</v>
+        <v>353.2630310058594</v>
       </c>
       <c r="F34" t="n">
-        <v>6885300</v>
+        <v>5756700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>356.7029783280342</v>
+        <v>354.1646514889598</v>
       </c>
       <c r="C35" t="n">
-        <v>356.7421891409456</v>
+        <v>358.1339166267961</v>
       </c>
       <c r="D35" t="n">
-        <v>350.8618233858751</v>
+        <v>352.8513732909411</v>
       </c>
       <c r="E35" t="n">
-        <v>354.2822265625</v>
+        <v>355.2721252441406</v>
       </c>
       <c r="F35" t="n">
-        <v>7833000</v>
+        <v>5462100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>348.4901083853841</v>
+        <v>356.2521771853968</v>
       </c>
       <c r="C36" t="n">
-        <v>355.0565296362527</v>
+        <v>358.9179443293374</v>
       </c>
       <c r="D36" t="n">
-        <v>346.5888173917132</v>
+        <v>354.194043082288</v>
       </c>
       <c r="E36" t="n">
-        <v>353.2630310058594</v>
+        <v>358.6827392578125</v>
       </c>
       <c r="F36" t="n">
-        <v>5756700</v>
+        <v>7766400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>354.1646210665127</v>
+        <v>373.0896573731999</v>
       </c>
       <c r="C37" t="n">
-        <v>358.1338858633925</v>
+        <v>373.4032841075878</v>
       </c>
       <c r="D37" t="n">
-        <v>352.8513429813036</v>
+        <v>351.4793217920273</v>
       </c>
       <c r="E37" t="n">
-        <v>355.2720947265625</v>
+        <v>360.5056762695312</v>
       </c>
       <c r="F37" t="n">
-        <v>5462100</v>
+        <v>18858700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>356.252207496177</v>
+        <v>357.0166539685856</v>
       </c>
       <c r="C38" t="n">
-        <v>358.9179748669274</v>
+        <v>358.8493634281032</v>
       </c>
       <c r="D38" t="n">
-        <v>354.1940732179572</v>
+        <v>346.8240245772966</v>
       </c>
       <c r="E38" t="n">
-        <v>358.6827697753906</v>
+        <v>348.176513671875</v>
       </c>
       <c r="F38" t="n">
-        <v>7766400</v>
+        <v>11874900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>373.0896257903608</v>
+        <v>340.5908266262187</v>
       </c>
       <c r="C39" t="n">
-        <v>373.4032524981995</v>
+        <v>347.4708747692525</v>
       </c>
       <c r="D39" t="n">
-        <v>351.4792920385495</v>
+        <v>336.7490038190758</v>
       </c>
       <c r="E39" t="n">
-        <v>360.5056457519531</v>
+        <v>337.8760681152344</v>
       </c>
       <c r="F39" t="n">
-        <v>18858700</v>
+        <v>11441900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>357.0166226761716</v>
+        <v>337.5232231766179</v>
       </c>
       <c r="C40" t="n">
-        <v>358.8493319750526</v>
+        <v>339.3755229195461</v>
       </c>
       <c r="D40" t="n">
-        <v>346.8239941782638</v>
+        <v>330.398160543053</v>
       </c>
       <c r="E40" t="n">
-        <v>348.1764831542969</v>
+        <v>334.7496337890625</v>
       </c>
       <c r="F40" t="n">
-        <v>11874900</v>
+        <v>8390800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>340.5908266262187</v>
+        <v>332.3681048776954</v>
       </c>
       <c r="C41" t="n">
-        <v>347.4708747692525</v>
+        <v>333.9068078868114</v>
       </c>
       <c r="D41" t="n">
-        <v>336.7490038190758</v>
+        <v>320.0879412577473</v>
       </c>
       <c r="E41" t="n">
-        <v>337.8760681152344</v>
+        <v>327.1345825195312</v>
       </c>
       <c r="F41" t="n">
-        <v>11441900</v>
+        <v>11181400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>337.5232539470514</v>
+        <v>321.0974041522996</v>
       </c>
       <c r="C42" t="n">
-        <v>339.3755538588451</v>
+        <v>329.7905408141606</v>
       </c>
       <c r="D42" t="n">
-        <v>330.3981906639274</v>
+        <v>320.6759850821896</v>
       </c>
       <c r="E42" t="n">
-        <v>334.7496643066406</v>
+        <v>324.2335815429688</v>
       </c>
       <c r="F42" t="n">
-        <v>8390800</v>
+        <v>9646600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>332.3681048776954</v>
+        <v>319.7938795016485</v>
       </c>
       <c r="C43" t="n">
-        <v>333.9068078868114</v>
+        <v>323.6259214469426</v>
       </c>
       <c r="D43" t="n">
-        <v>320.0879412577473</v>
+        <v>317.7553658634617</v>
       </c>
       <c r="E43" t="n">
-        <v>327.1345825195312</v>
+        <v>321.2051696777344</v>
       </c>
       <c r="F43" t="n">
-        <v>11181400</v>
+        <v>9697100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>321.0974041522996</v>
+        <v>322.3616713627413</v>
       </c>
       <c r="C44" t="n">
-        <v>329.7905408141606</v>
+        <v>325.7428638052234</v>
       </c>
       <c r="D44" t="n">
-        <v>320.6759850821896</v>
+        <v>315.0406146307628</v>
       </c>
       <c r="E44" t="n">
-        <v>324.2335815429688</v>
+        <v>315.1484069824219</v>
       </c>
       <c r="F44" t="n">
-        <v>9646600</v>
+        <v>7922100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>319.7939098851405</v>
+        <v>313.2863393626572</v>
       </c>
       <c r="C45" t="n">
-        <v>323.6259521945154</v>
+        <v>318.0788226584959</v>
       </c>
       <c r="D45" t="n">
-        <v>317.7553960532753</v>
+        <v>307.8960032344128</v>
       </c>
       <c r="E45" t="n">
-        <v>321.2052001953125</v>
+        <v>317.74560546875</v>
       </c>
       <c r="F45" t="n">
-        <v>9697100</v>
+        <v>9402900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>322.3617025788201</v>
+        <v>313.6097058862107</v>
       </c>
       <c r="C46" t="n">
-        <v>325.7428953487219</v>
+        <v>317.7847752647608</v>
       </c>
       <c r="D46" t="n">
-        <v>315.0406451379028</v>
+        <v>310.8459566317771</v>
       </c>
       <c r="E46" t="n">
-        <v>315.1484375</v>
+        <v>315.1679992675781</v>
       </c>
       <c r="F46" t="n">
-        <v>7922100</v>
+        <v>9283800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>313.2863393626572</v>
+        <v>316.8537429984404</v>
       </c>
       <c r="C47" t="n">
-        <v>318.0788226584959</v>
+        <v>321.3228192405015</v>
       </c>
       <c r="D47" t="n">
-        <v>307.8960032344128</v>
+        <v>313.5019507714403</v>
       </c>
       <c r="E47" t="n">
-        <v>317.74560546875</v>
+        <v>320.9210205078125</v>
       </c>
       <c r="F47" t="n">
-        <v>9402900</v>
+        <v>7157800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>313.6097362529</v>
+        <v>321.9010364932658</v>
       </c>
       <c r="C48" t="n">
-        <v>317.7848060357201</v>
+        <v>336.3275351202159</v>
       </c>
       <c r="D48" t="n">
-        <v>310.8459867308537</v>
+        <v>320.5583278451826</v>
       </c>
       <c r="E48" t="n">
-        <v>315.1680297851562</v>
+        <v>332.2994689941406</v>
       </c>
       <c r="F48" t="n">
-        <v>9283800</v>
+        <v>10403300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>316.8537128676349</v>
+        <v>331.6036342486655</v>
       </c>
       <c r="C49" t="n">
-        <v>321.3227886847148</v>
+        <v>332.2700685282101</v>
       </c>
       <c r="D49" t="n">
-        <v>313.5019209593692</v>
+        <v>324.6844062126531</v>
       </c>
       <c r="E49" t="n">
-        <v>320.9209899902344</v>
+        <v>325.8898620605469</v>
       </c>
       <c r="F49" t="n">
-        <v>7157800</v>
+        <v>7788700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>321.9010364932658</v>
+        <v>320.4309810489659</v>
       </c>
       <c r="C50" t="n">
-        <v>336.3275351202159</v>
+        <v>321.6658376676509</v>
       </c>
       <c r="D50" t="n">
-        <v>320.5583278451826</v>
+        <v>314.0997649577876</v>
       </c>
       <c r="E50" t="n">
-        <v>332.2994689941406</v>
+        <v>315.4424438476562</v>
       </c>
       <c r="F50" t="n">
-        <v>10403300</v>
+        <v>8676500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>331.6036653013031</v>
+        <v>314.2075720220705</v>
       </c>
       <c r="C51" t="n">
-        <v>332.2700996432553</v>
+        <v>321.3424151200708</v>
       </c>
       <c r="D51" t="n">
-        <v>324.6844366173477</v>
+        <v>313.06088745762</v>
       </c>
       <c r="E51" t="n">
-        <v>325.889892578125</v>
+        <v>314.129150390625</v>
       </c>
       <c r="F51" t="n">
-        <v>7788700</v>
+        <v>6485400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>320.4309500487702</v>
+        <v>310.6891774544803</v>
       </c>
       <c r="C52" t="n">
-        <v>321.6658065479886</v>
+        <v>311.1693978203648</v>
       </c>
       <c r="D52" t="n">
-        <v>314.0997345701073</v>
+        <v>302.6134536894014</v>
       </c>
       <c r="E52" t="n">
-        <v>315.4424133300781</v>
+        <v>307.3275451660156</v>
       </c>
       <c r="F52" t="n">
-        <v>8676500</v>
+        <v>9182100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>314.2075720220705</v>
+        <v>307.6705548284651</v>
       </c>
       <c r="C53" t="n">
-        <v>321.3424151200708</v>
+        <v>308.7192273184903</v>
       </c>
       <c r="D53" t="n">
-        <v>313.06088745762</v>
+        <v>298.4579870426836</v>
       </c>
       <c r="E53" t="n">
-        <v>314.129150390625</v>
+        <v>302.9270629882812</v>
       </c>
       <c r="F53" t="n">
-        <v>6485400</v>
+        <v>8181100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>310.6891466030926</v>
+        <v>304.6127916915999</v>
       </c>
       <c r="C54" t="n">
-        <v>311.1693669212913</v>
+        <v>308.4742348638782</v>
       </c>
       <c r="D54" t="n">
-        <v>302.6134236399317</v>
+        <v>303.8189445839627</v>
       </c>
       <c r="E54" t="n">
-        <v>307.3275146484375</v>
+        <v>305.3282470703125</v>
       </c>
       <c r="F54" t="n">
-        <v>9182100</v>
+        <v>7337600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>307.6705548284651</v>
+        <v>305.6908291650661</v>
       </c>
       <c r="C55" t="n">
-        <v>308.7192273184903</v>
+        <v>317.3829496811602</v>
       </c>
       <c r="D55" t="n">
-        <v>298.4579870426836</v>
+        <v>305.23019930011</v>
       </c>
       <c r="E55" t="n">
-        <v>302.9270629882812</v>
+        <v>313.5901184082031</v>
       </c>
       <c r="F55" t="n">
-        <v>8181100</v>
+        <v>8406300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>304.6127916915999</v>
+        <v>318.0591910227777</v>
       </c>
       <c r="C56" t="n">
-        <v>308.4742348638782</v>
+        <v>319.3528787042382</v>
       </c>
       <c r="D56" t="n">
-        <v>303.8189445839627</v>
+        <v>311.2869660112169</v>
       </c>
       <c r="E56" t="n">
-        <v>305.3282470703125</v>
+        <v>312.6884460449219</v>
       </c>
       <c r="F56" t="n">
-        <v>7337600</v>
+        <v>10773800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>305.6908291650661</v>
+        <v>314.71720383448</v>
       </c>
       <c r="C57" t="n">
-        <v>317.3829496811602</v>
+        <v>321.4600287348608</v>
       </c>
       <c r="D57" t="n">
-        <v>305.23019930011</v>
+        <v>314.5015892042089</v>
       </c>
       <c r="E57" t="n">
-        <v>313.5901184082031</v>
+        <v>319.7743225097656</v>
       </c>
       <c r="F57" t="n">
-        <v>8406300</v>
+        <v>6149100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>318.0592220645265</v>
+        <v>320.07813955632</v>
       </c>
       <c r="C58" t="n">
-        <v>319.3529098722476</v>
+        <v>328.5066706952173</v>
       </c>
       <c r="D58" t="n">
-        <v>311.2869963920142</v>
+        <v>319.3921147564304</v>
       </c>
       <c r="E58" t="n">
-        <v>312.6884765625</v>
+        <v>323.1359252929688</v>
       </c>
       <c r="F58" t="n">
-        <v>10773800</v>
+        <v>5504200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>314.71720383448</v>
+        <v>325.0568726515205</v>
       </c>
       <c r="C59" t="n">
-        <v>321.4600287348608</v>
+        <v>325.4390809212725</v>
       </c>
       <c r="D59" t="n">
-        <v>314.5015892042089</v>
+        <v>322.3323040363653</v>
       </c>
       <c r="E59" t="n">
-        <v>319.7743225097656</v>
+        <v>323.1947326660156</v>
       </c>
       <c r="F59" t="n">
-        <v>6149100</v>
+        <v>2464500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>320.078109327525</v>
+        <v>320.6367557882569</v>
       </c>
       <c r="C60" t="n">
-        <v>328.5066396704157</v>
+        <v>323.4789266660114</v>
       </c>
       <c r="D60" t="n">
-        <v>319.3920845924249</v>
+        <v>316.5890991303779</v>
       </c>
       <c r="E60" t="n">
-        <v>323.1358947753906</v>
+        <v>316.7655029296875</v>
       </c>
       <c r="F60" t="n">
-        <v>5504200</v>
+        <v>6154600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>325.0568419581102</v>
+        <v>316.9223157324214</v>
       </c>
       <c r="C61" t="n">
-        <v>325.4390501917724</v>
+        <v>322.146057528238</v>
       </c>
       <c r="D61" t="n">
-        <v>322.3322736002218</v>
+        <v>316.3636737931457</v>
       </c>
       <c r="E61" t="n">
-        <v>323.1947021484375</v>
+        <v>318.0690002441406</v>
       </c>
       <c r="F61" t="n">
-        <v>2464500</v>
+        <v>7978100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>320.6367866787963</v>
+        <v>319.4998951185618</v>
       </c>
       <c r="C62" t="n">
-        <v>323.478957830369</v>
+        <v>334.6026391486864</v>
       </c>
       <c r="D62" t="n">
-        <v>316.5891296309611</v>
+        <v>318.529644271779</v>
       </c>
       <c r="E62" t="n">
-        <v>316.7655334472656</v>
+        <v>332.9365234375</v>
       </c>
       <c r="F62" t="n">
-        <v>6154600</v>
+        <v>9770000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>316.9223461399793</v>
+        <v>332.632709971988</v>
       </c>
       <c r="C63" t="n">
-        <v>322.1460884369951</v>
+        <v>334.4556390535126</v>
       </c>
       <c r="D63" t="n">
-        <v>316.3637041471038</v>
+        <v>322.1656652751352</v>
       </c>
       <c r="E63" t="n">
-        <v>318.0690307617188</v>
+        <v>326.8405456542969</v>
       </c>
       <c r="F63" t="n">
-        <v>7978100</v>
+        <v>8061600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>319.4998951185618</v>
+        <v>328.3204578992349</v>
       </c>
       <c r="C64" t="n">
-        <v>334.6026391486864</v>
+        <v>329.0162928832224</v>
       </c>
       <c r="D64" t="n">
-        <v>318.529644271779</v>
+        <v>321.9598711365138</v>
       </c>
       <c r="E64" t="n">
-        <v>332.9365234375</v>
+        <v>324.31201171875</v>
       </c>
       <c r="F64" t="n">
-        <v>9770000</v>
+        <v>5906000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,25 +2107,25 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>332.632709971988</v>
+        <v>324.3120366886073</v>
       </c>
       <c r="C65" t="n">
-        <v>334.4556390535126</v>
+        <v>324.7066908730135</v>
       </c>
       <c r="D65" t="n">
-        <v>322.1656652751352</v>
+        <v>318.5203728665016</v>
       </c>
       <c r="E65" t="n">
-        <v>326.8405456542969</v>
+        <v>319.2998352050781</v>
       </c>
       <c r="F65" t="n">
-        <v>8061600</v>
+        <v>4782800</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>328.3204578992349</v>
+        <v>318.8459617269979</v>
       </c>
       <c r="C66" t="n">
-        <v>329.0162928832224</v>
+        <v>322.0032250879344</v>
       </c>
       <c r="D66" t="n">
-        <v>321.9598711365138</v>
+        <v>318.1750466501944</v>
       </c>
       <c r="E66" t="n">
-        <v>324.31201171875</v>
+        <v>319.2800903320312</v>
       </c>
       <c r="F66" t="n">
-        <v>5906000</v>
+        <v>4628400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>324.3120366886073</v>
+        <v>318.4414486886093</v>
       </c>
       <c r="C67" t="n">
-        <v>324.7066908730135</v>
+        <v>324.341629514822</v>
       </c>
       <c r="D67" t="n">
-        <v>318.5203728665016</v>
+        <v>315.3335056374652</v>
       </c>
       <c r="E67" t="n">
-        <v>319.2998352050781</v>
+        <v>323.9864196777344</v>
       </c>
       <c r="F67" t="n">
-        <v>4782800</v>
+        <v>5910500</v>
       </c>
       <c r="G67" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>318.8459617269979</v>
+        <v>325.9597199441495</v>
       </c>
       <c r="C68" t="n">
-        <v>322.0032250879344</v>
+        <v>334.7211811769636</v>
       </c>
       <c r="D68" t="n">
-        <v>318.1750466501944</v>
+        <v>324.3712270965368</v>
       </c>
       <c r="E68" t="n">
-        <v>319.2800903320312</v>
+        <v>332.2348327636719</v>
       </c>
       <c r="F68" t="n">
-        <v>4628400</v>
+        <v>7513200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>318.4414486886093</v>
+        <v>332.9945215393808</v>
       </c>
       <c r="C69" t="n">
-        <v>324.341629514822</v>
+        <v>340.3746776267931</v>
       </c>
       <c r="D69" t="n">
-        <v>315.3335056374652</v>
+        <v>332.8662521653069</v>
       </c>
       <c r="E69" t="n">
-        <v>323.9864196777344</v>
+        <v>337.2765808105469</v>
       </c>
       <c r="F69" t="n">
-        <v>5910500</v>
+        <v>7979000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>325.9597199441495</v>
+        <v>336.4379310634787</v>
       </c>
       <c r="C70" t="n">
-        <v>334.7211811769636</v>
+        <v>340.3549345980833</v>
       </c>
       <c r="D70" t="n">
-        <v>324.3712270965368</v>
+        <v>332.5012053593197</v>
       </c>
       <c r="E70" t="n">
-        <v>332.2348327636719</v>
+        <v>336.5464782714844</v>
       </c>
       <c r="F70" t="n">
-        <v>7513200</v>
+        <v>6447200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>332.9945215393808</v>
+        <v>335.875584402924</v>
       </c>
       <c r="C71" t="n">
-        <v>340.3746776267931</v>
+        <v>336.4379523174861</v>
       </c>
       <c r="D71" t="n">
-        <v>332.8662521653069</v>
+        <v>326.6109215358994</v>
       </c>
       <c r="E71" t="n">
-        <v>337.2765808105469</v>
+        <v>329.7386169433594</v>
       </c>
       <c r="F71" t="n">
-        <v>7979000</v>
+        <v>6334000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>336.4379310634787</v>
+        <v>329.1564601038647</v>
       </c>
       <c r="C72" t="n">
-        <v>340.3549345980833</v>
+        <v>331.0409661792534</v>
       </c>
       <c r="D72" t="n">
-        <v>332.5012053593197</v>
+        <v>326.0682693196749</v>
       </c>
       <c r="E72" t="n">
-        <v>336.5464782714844</v>
+        <v>327.2029113769531</v>
       </c>
       <c r="F72" t="n">
-        <v>6447200</v>
+        <v>4685600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>335.875584402924</v>
+        <v>324.5389231377919</v>
       </c>
       <c r="C73" t="n">
-        <v>336.4379523174861</v>
+        <v>325.7722361921053</v>
       </c>
       <c r="D73" t="n">
-        <v>326.6109215358994</v>
+        <v>320.2371416572342</v>
       </c>
       <c r="E73" t="n">
-        <v>329.7386169433594</v>
+        <v>323.7594909667969</v>
       </c>
       <c r="F73" t="n">
-        <v>6334000</v>
+        <v>6354900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>329.1564601038647</v>
+        <v>323.6805434123363</v>
       </c>
       <c r="C74" t="n">
-        <v>331.0409661792534</v>
+        <v>330.1332457701224</v>
       </c>
       <c r="D74" t="n">
-        <v>326.0682693196749</v>
+        <v>321.7171186569828</v>
       </c>
       <c r="E74" t="n">
-        <v>327.2029113769531</v>
+        <v>323.0491027832031</v>
       </c>
       <c r="F74" t="n">
-        <v>4685600</v>
+        <v>10553000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>324.5389231377919</v>
+        <v>318.5894351738589</v>
       </c>
       <c r="C75" t="n">
-        <v>325.7722361921053</v>
+        <v>325.3973174895482</v>
       </c>
       <c r="D75" t="n">
-        <v>320.2371416572342</v>
+        <v>317.3561220691985</v>
       </c>
       <c r="E75" t="n">
-        <v>323.7594909667969</v>
+        <v>320.8192749023438</v>
       </c>
       <c r="F75" t="n">
-        <v>6354900</v>
+        <v>7872400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>323.6805434123363</v>
+        <v>319.6747419864576</v>
       </c>
       <c r="C76" t="n">
-        <v>330.1332457701224</v>
+        <v>323.4240016076582</v>
       </c>
       <c r="D76" t="n">
-        <v>321.7171186569828</v>
+        <v>319.4379555165406</v>
       </c>
       <c r="E76" t="n">
-        <v>323.0491027832031</v>
+        <v>320.4640502929688</v>
       </c>
       <c r="F76" t="n">
-        <v>10553000</v>
+        <v>4463300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>318.5894351738589</v>
+        <v>320.8587672253223</v>
       </c>
       <c r="C77" t="n">
-        <v>325.3973174895482</v>
+        <v>324.5981510876156</v>
       </c>
       <c r="D77" t="n">
-        <v>317.3561220691985</v>
+        <v>319.8030439224821</v>
       </c>
       <c r="E77" t="n">
-        <v>320.8192749023438</v>
+        <v>323.2069702148438</v>
       </c>
       <c r="F77" t="n">
-        <v>7872400</v>
+        <v>2842700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>319.6747419864576</v>
+        <v>322.8320412014528</v>
       </c>
       <c r="C78" t="n">
-        <v>323.4240016076582</v>
+        <v>327.4594342482506</v>
       </c>
       <c r="D78" t="n">
-        <v>319.4379555165406</v>
+        <v>321.9045873641298</v>
       </c>
       <c r="E78" t="n">
-        <v>320.4640502929688</v>
+        <v>327.4002075195312</v>
       </c>
       <c r="F78" t="n">
-        <v>4463300</v>
+        <v>4359300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>320.8587672253223</v>
+        <v>326.4728087048146</v>
       </c>
       <c r="C79" t="n">
-        <v>324.5981510876156</v>
+        <v>329.787940036587</v>
       </c>
       <c r="D79" t="n">
-        <v>319.8030439224821</v>
+        <v>323.8976351612195</v>
       </c>
       <c r="E79" t="n">
-        <v>323.2069702148438</v>
+        <v>324.548828125</v>
       </c>
       <c r="F79" t="n">
-        <v>2842700</v>
+        <v>4346800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>322.8320412014528</v>
+        <v>325.3282463216964</v>
       </c>
       <c r="C80" t="n">
-        <v>327.4594342482506</v>
+        <v>331.6625250102778</v>
       </c>
       <c r="D80" t="n">
-        <v>321.9045873641298</v>
+        <v>325.1111820298963</v>
       </c>
       <c r="E80" t="n">
-        <v>327.4002075195312</v>
+        <v>327.7257995605469</v>
       </c>
       <c r="F80" t="n">
-        <v>4359300</v>
+        <v>4432500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>326.4728087048146</v>
+        <v>327.8837053458195</v>
       </c>
       <c r="C81" t="n">
-        <v>329.787940036587</v>
+        <v>328.8802018879278</v>
       </c>
       <c r="D81" t="n">
-        <v>323.8976351612195</v>
+        <v>325.4762756879338</v>
       </c>
       <c r="E81" t="n">
-        <v>324.548828125</v>
+        <v>325.7031860351562</v>
       </c>
       <c r="F81" t="n">
-        <v>4346800</v>
+        <v>4285200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>325.3282463216964</v>
+        <v>326.4826326508298</v>
       </c>
       <c r="C82" t="n">
-        <v>331.6625250102778</v>
+        <v>335.717696654991</v>
       </c>
       <c r="D82" t="n">
-        <v>325.1111820298963</v>
+        <v>323.1280270938765</v>
       </c>
       <c r="E82" t="n">
-        <v>327.7257995605469</v>
+        <v>331.9092102050781</v>
       </c>
       <c r="F82" t="n">
-        <v>4432500</v>
+        <v>6863600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>327.8837053458195</v>
+        <v>330.9719222150325</v>
       </c>
       <c r="C83" t="n">
-        <v>328.8802018879278</v>
+        <v>342.3085268229226</v>
       </c>
       <c r="D83" t="n">
-        <v>325.4762756879338</v>
+        <v>329.3932753932535</v>
       </c>
       <c r="E83" t="n">
-        <v>325.7031860351562</v>
+        <v>337.4541931152344</v>
       </c>
       <c r="F83" t="n">
-        <v>4285200</v>
+        <v>7956600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>326.4826326508298</v>
+        <v>343.6996829189171</v>
       </c>
       <c r="C84" t="n">
-        <v>335.717696654991</v>
+        <v>347.9027932709801</v>
       </c>
       <c r="D84" t="n">
-        <v>323.1280270938765</v>
+        <v>340.5127911940015</v>
       </c>
       <c r="E84" t="n">
-        <v>331.9092102050781</v>
+        <v>344.3114013671875</v>
       </c>
       <c r="F84" t="n">
-        <v>6863600</v>
+        <v>9441900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>330.9719222150325</v>
+        <v>344.3213032237757</v>
       </c>
       <c r="C85" t="n">
-        <v>342.3085268229226</v>
+        <v>345.4361929991165</v>
       </c>
       <c r="D85" t="n">
-        <v>329.3932753932535</v>
+        <v>333.527344316932</v>
       </c>
       <c r="E85" t="n">
-        <v>337.4541931152344</v>
+        <v>337.1384887695312</v>
       </c>
       <c r="F85" t="n">
-        <v>7956600</v>
+        <v>7461400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>343.6996829189171</v>
+        <v>336.4576913463828</v>
       </c>
       <c r="C86" t="n">
-        <v>347.9027932709801</v>
+        <v>343.2556975271264</v>
       </c>
       <c r="D86" t="n">
-        <v>340.5127911940015</v>
+        <v>336.2504730653109</v>
       </c>
       <c r="E86" t="n">
-        <v>344.3114013671875</v>
+        <v>342.2197265625</v>
       </c>
       <c r="F86" t="n">
-        <v>9441900</v>
+        <v>5059300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>344.3213032237757</v>
+        <v>342.6143671222478</v>
       </c>
       <c r="C87" t="n">
-        <v>345.4361929991165</v>
+        <v>344.4002020193836</v>
       </c>
       <c r="D87" t="n">
-        <v>333.527344316932</v>
+        <v>337.9080553379447</v>
       </c>
       <c r="E87" t="n">
-        <v>337.1384887695312</v>
+        <v>339.3880310058594</v>
       </c>
       <c r="F87" t="n">
-        <v>7461400</v>
+        <v>4129100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>336.4576913463828</v>
+        <v>336.8622415935578</v>
       </c>
       <c r="C88" t="n">
-        <v>343.2556975271264</v>
+        <v>338.0758024907637</v>
       </c>
       <c r="D88" t="n">
-        <v>336.2504730653109</v>
+        <v>329.4820846932586</v>
       </c>
       <c r="E88" t="n">
-        <v>342.2197265625</v>
+        <v>335.9643859863281</v>
       </c>
       <c r="F88" t="n">
-        <v>5059300</v>
+        <v>7146400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>342.6143671222478</v>
+        <v>336.9411188846722</v>
       </c>
       <c r="C89" t="n">
-        <v>344.4002020193836</v>
+        <v>337.2765764147031</v>
       </c>
       <c r="D89" t="n">
-        <v>337.9080553379447</v>
+        <v>328.4065987621919</v>
       </c>
       <c r="E89" t="n">
-        <v>339.3880310058594</v>
+        <v>329.47216796875</v>
       </c>
       <c r="F89" t="n">
-        <v>4129100</v>
+        <v>5605900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>336.8622415935578</v>
+        <v>330.8929641448377</v>
       </c>
       <c r="C90" t="n">
-        <v>338.0758024907637</v>
+        <v>335.5696777492312</v>
       </c>
       <c r="D90" t="n">
-        <v>329.4820846932586</v>
+        <v>329.639928884428</v>
       </c>
       <c r="E90" t="n">
-        <v>335.9643859863281</v>
+        <v>330.4884338378906</v>
       </c>
       <c r="F90" t="n">
-        <v>7146400</v>
+        <v>5740900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>336.9411188846722</v>
+        <v>330.7252428593728</v>
       </c>
       <c r="C91" t="n">
-        <v>337.2765764147031</v>
+        <v>334.9185072715596</v>
       </c>
       <c r="D91" t="n">
-        <v>328.4065987621919</v>
+        <v>323.6805441940115</v>
       </c>
       <c r="E91" t="n">
-        <v>329.47216796875</v>
+        <v>334.4350280761719</v>
       </c>
       <c r="F91" t="n">
-        <v>5605900</v>
+        <v>6943500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>330.8929641448377</v>
+        <v>330.3897780779105</v>
       </c>
       <c r="C92" t="n">
-        <v>335.5696777492312</v>
+        <v>331.7119162692861</v>
       </c>
       <c r="D92" t="n">
-        <v>329.639928884428</v>
+        <v>326.0189235086448</v>
       </c>
       <c r="E92" t="n">
-        <v>330.4884338378906</v>
+        <v>326.6010437011719</v>
       </c>
       <c r="F92" t="n">
-        <v>5740900</v>
+        <v>8039100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>330.7252428593728</v>
+        <v>323.0293559592084</v>
       </c>
       <c r="C93" t="n">
-        <v>334.9185072715596</v>
+        <v>335.3526407320732</v>
       </c>
       <c r="D93" t="n">
-        <v>323.6805441940115</v>
+        <v>322.1413765634589</v>
       </c>
       <c r="E93" t="n">
-        <v>334.4350280761719</v>
+        <v>333.912109375</v>
       </c>
       <c r="F93" t="n">
-        <v>6943500</v>
+        <v>7596500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>330.3897780779105</v>
+        <v>334.8987575018528</v>
       </c>
       <c r="C94" t="n">
-        <v>331.7119162692861</v>
+        <v>343.4332779356386</v>
       </c>
       <c r="D94" t="n">
-        <v>326.0189235086448</v>
+        <v>334.168645798694</v>
       </c>
       <c r="E94" t="n">
-        <v>326.6010437011719</v>
+        <v>343.1076965332031</v>
       </c>
       <c r="F94" t="n">
-        <v>8039100</v>
+        <v>8933300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>323.0293559592084</v>
+        <v>342.5453159613966</v>
       </c>
       <c r="C95" t="n">
-        <v>335.3526407320732</v>
+        <v>350.2116096750548</v>
       </c>
       <c r="D95" t="n">
-        <v>322.1413765634589</v>
+        <v>342.1407856401066</v>
       </c>
       <c r="E95" t="n">
-        <v>333.912109375</v>
+        <v>349.7380065917969</v>
       </c>
       <c r="F95" t="n">
-        <v>7596500</v>
+        <v>7491400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>334.8987575018528</v>
+        <v>349.5505410261084</v>
       </c>
       <c r="C96" t="n">
-        <v>343.4332779356386</v>
+        <v>353.0926127392032</v>
       </c>
       <c r="D96" t="n">
-        <v>334.168645798694</v>
+        <v>348.2777534390037</v>
       </c>
       <c r="E96" t="n">
-        <v>343.1076965332031</v>
+        <v>351.5041198730469</v>
       </c>
       <c r="F96" t="n">
-        <v>8933300</v>
+        <v>9082200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>342.5453159613966</v>
+        <v>349.2249303389971</v>
       </c>
       <c r="C97" t="n">
-        <v>350.2116096750548</v>
+        <v>350.0537130836444</v>
       </c>
       <c r="D97" t="n">
-        <v>342.1407856401066</v>
+        <v>342.6340826093485</v>
       </c>
       <c r="E97" t="n">
-        <v>349.7380065917969</v>
+        <v>346.9457702636719</v>
       </c>
       <c r="F97" t="n">
-        <v>7491400</v>
+        <v>10399500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>349.5505410261084</v>
+        <v>290.0456258453373</v>
       </c>
       <c r="C98" t="n">
-        <v>353.0926127392032</v>
+        <v>295.5018014762001</v>
       </c>
       <c r="D98" t="n">
-        <v>348.2777534390037</v>
+        <v>276.6567723884028</v>
       </c>
       <c r="E98" t="n">
-        <v>351.5041198730469</v>
+        <v>278.9260864257812</v>
       </c>
       <c r="F98" t="n">
-        <v>9082200</v>
+        <v>65836900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>349.2249303389971</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="C99" t="n">
-        <v>350.0537130836444</v>
+        <v>291.0027024164021</v>
       </c>
       <c r="D99" t="n">
-        <v>342.6340826093485</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="E99" t="n">
-        <v>346.9457702636719</v>
+        <v>290.094970703125</v>
       </c>
       <c r="F99" t="n">
-        <v>10399500</v>
+        <v>23396900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>290.0456258453373</v>
+        <v>290.4008374442539</v>
       </c>
       <c r="C100" t="n">
-        <v>295.5018014762001</v>
+        <v>291.6539028887257</v>
       </c>
       <c r="D100" t="n">
-        <v>276.6567723884028</v>
+        <v>285.3590676854078</v>
       </c>
       <c r="E100" t="n">
-        <v>278.9260864257812</v>
+        <v>288.3880920410156</v>
       </c>
       <c r="F100" t="n">
-        <v>65836900</v>
+        <v>13456400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>279.9324825435024</v>
+        <v>288.200605503728</v>
       </c>
       <c r="C101" t="n">
-        <v>291.0027024164021</v>
+        <v>289.0392644171012</v>
       </c>
       <c r="D101" t="n">
-        <v>279.9324825435024</v>
+        <v>280.8993981188336</v>
       </c>
       <c r="E101" t="n">
-        <v>290.094970703125</v>
+        <v>283.099609375</v>
       </c>
       <c r="F101" t="n">
-        <v>23396900</v>
+        <v>12022200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>290.4008374442539</v>
+        <v>282.201779365365</v>
       </c>
       <c r="C102" t="n">
-        <v>291.6539028887257</v>
+        <v>286.5233135903719</v>
       </c>
       <c r="D102" t="n">
-        <v>285.3590676854078</v>
+        <v>278.5117159450099</v>
       </c>
       <c r="E102" t="n">
-        <v>288.3880920410156</v>
+        <v>281.7775268554688</v>
       </c>
       <c r="F102" t="n">
-        <v>13456400</v>
+        <v>8664200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>288.200605503728</v>
+        <v>280.899399533992</v>
       </c>
       <c r="C103" t="n">
-        <v>289.0392644171012</v>
+        <v>284.2441289542904</v>
       </c>
       <c r="D103" t="n">
-        <v>280.8993981188336</v>
+        <v>274.8808256732182</v>
       </c>
       <c r="E103" t="n">
-        <v>283.099609375</v>
+        <v>280.3863220214844</v>
       </c>
       <c r="F103" t="n">
-        <v>12022200</v>
+        <v>10809100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>282.201779365365</v>
+        <v>278.2453003524489</v>
       </c>
       <c r="C104" t="n">
-        <v>286.5233135903719</v>
+        <v>280.7020503139632</v>
       </c>
       <c r="D104" t="n">
-        <v>278.5117159450099</v>
+        <v>270.3915411669698</v>
       </c>
       <c r="E104" t="n">
-        <v>281.7775268554688</v>
+        <v>272.2366027832031</v>
       </c>
       <c r="F104" t="n">
-        <v>8664200</v>
+        <v>12944100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>280.899399533992</v>
+        <v>270.6283910377749</v>
       </c>
       <c r="C105" t="n">
-        <v>284.2441289542904</v>
+        <v>273.1936885205944</v>
       </c>
       <c r="D105" t="n">
-        <v>274.8808256732182</v>
+        <v>262.7351865430599</v>
       </c>
       <c r="E105" t="n">
-        <v>280.3863220214844</v>
+        <v>264.9649963378906</v>
       </c>
       <c r="F105" t="n">
-        <v>10809100</v>
+        <v>13035300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>278.2453003524489</v>
+        <v>263.494873693566</v>
       </c>
       <c r="C106" t="n">
-        <v>280.7020503139632</v>
+        <v>274.1013663098342</v>
       </c>
       <c r="D106" t="n">
-        <v>270.3915411669698</v>
+        <v>262.8535569062469</v>
       </c>
       <c r="E106" t="n">
-        <v>272.2366027832031</v>
+        <v>272.9568481445312</v>
       </c>
       <c r="F106" t="n">
-        <v>12944100</v>
+        <v>9572800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>270.6283910377749</v>
+        <v>270.4902050418196</v>
       </c>
       <c r="C107" t="n">
-        <v>273.1936885205944</v>
+        <v>276.4397058352786</v>
       </c>
       <c r="D107" t="n">
-        <v>262.7351865430599</v>
+        <v>269.6712984464802</v>
       </c>
       <c r="E107" t="n">
-        <v>264.9649963378906</v>
+        <v>272.01953125</v>
       </c>
       <c r="F107" t="n">
-        <v>13035300</v>
+        <v>10371600</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>263.494873693566</v>
+        <v>273.8152476410468</v>
       </c>
       <c r="C108" t="n">
-        <v>274.1013663098342</v>
+        <v>275.7589504136547</v>
       </c>
       <c r="D108" t="n">
-        <v>262.8535569062469</v>
+        <v>269.010264317998</v>
       </c>
       <c r="E108" t="n">
-        <v>272.9568481445312</v>
+        <v>269.5726623535156</v>
       </c>
       <c r="F108" t="n">
-        <v>9572800</v>
+        <v>7284700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>270.4902050418196</v>
+        <v>268.8030763257778</v>
       </c>
       <c r="C109" t="n">
-        <v>276.4397058352786</v>
+        <v>275.9562927620499</v>
       </c>
       <c r="D109" t="n">
-        <v>269.6712984464802</v>
+        <v>266.198304439543</v>
       </c>
       <c r="E109" t="n">
-        <v>272.01953125</v>
+        <v>275.1867065429688</v>
       </c>
       <c r="F109" t="n">
-        <v>10371600</v>
+        <v>6333100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>273.8152476410468</v>
+        <v>274.4467004687212</v>
       </c>
       <c r="C110" t="n">
-        <v>275.7589504136547</v>
+        <v>282.4878958393087</v>
       </c>
       <c r="D110" t="n">
-        <v>269.010264317998</v>
+        <v>272.1280658242715</v>
       </c>
       <c r="E110" t="n">
-        <v>269.5726623535156</v>
+        <v>280.5737915039062</v>
       </c>
       <c r="F110" t="n">
-        <v>7284700</v>
+        <v>12336900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>268.8030763257778</v>
+        <v>281.8169569225497</v>
       </c>
       <c r="C111" t="n">
-        <v>275.9562927620499</v>
+        <v>289.5424162609187</v>
       </c>
       <c r="D111" t="n">
-        <v>266.198304439543</v>
+        <v>280.7119132986369</v>
       </c>
       <c r="E111" t="n">
-        <v>275.1867065429688</v>
+        <v>289.2760314941406</v>
       </c>
       <c r="F111" t="n">
-        <v>6333100</v>
+        <v>10281900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>274.4467004687212</v>
+        <v>290.0752312306441</v>
       </c>
       <c r="C112" t="n">
-        <v>282.4878958393087</v>
+        <v>290.3021716729731</v>
       </c>
       <c r="D112" t="n">
-        <v>272.1280658242715</v>
+        <v>284.4907860910092</v>
       </c>
       <c r="E112" t="n">
-        <v>280.5737915039062</v>
+        <v>285.2307739257812</v>
       </c>
       <c r="F112" t="n">
-        <v>12336900</v>
+        <v>6091700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>281.8169569225497</v>
+        <v>286.1286505407075</v>
       </c>
       <c r="C113" t="n">
-        <v>289.5424162609187</v>
+        <v>286.2569199258207</v>
       </c>
       <c r="D113" t="n">
-        <v>280.7119132986369</v>
+        <v>282.4681855456762</v>
       </c>
       <c r="E113" t="n">
-        <v>289.2760314941406</v>
+        <v>284.3526916503906</v>
       </c>
       <c r="F113" t="n">
-        <v>10281900</v>
+        <v>6632000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>290.0752312306441</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="C114" t="n">
-        <v>290.3021716729731</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="D114" t="n">
-        <v>284.4907860910092</v>
+        <v>283.0601744920274</v>
       </c>
       <c r="E114" t="n">
-        <v>285.2307739257812</v>
+        <v>286.0595703125</v>
       </c>
       <c r="F114" t="n">
-        <v>6091700</v>
+        <v>4931800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>286.1286505407075</v>
+        <v>285.0433100706192</v>
       </c>
       <c r="C115" t="n">
-        <v>286.2569199258207</v>
+        <v>286.9179399107358</v>
       </c>
       <c r="D115" t="n">
-        <v>282.4681855456762</v>
+        <v>281.7380250284705</v>
       </c>
       <c r="E115" t="n">
-        <v>284.3526916503906</v>
+        <v>286.1286315917969</v>
       </c>
       <c r="F115" t="n">
-        <v>6632000</v>
+        <v>6974100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>287.0067764654547</v>
+        <v>284.6979833712643</v>
       </c>
       <c r="C116" t="n">
-        <v>287.0067764654547</v>
+        <v>287.8749991147026</v>
       </c>
       <c r="D116" t="n">
-        <v>283.0601744920274</v>
+        <v>277.9098533754537</v>
       </c>
       <c r="E116" t="n">
-        <v>286.0595703125</v>
+        <v>278.5708923339844</v>
       </c>
       <c r="F116" t="n">
-        <v>4931800</v>
+        <v>7247500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>285.0433100706192</v>
+        <v>278.4327740747045</v>
       </c>
       <c r="C117" t="n">
-        <v>286.9179399107358</v>
+        <v>278.6300861021672</v>
       </c>
       <c r="D117" t="n">
-        <v>281.7380250284705</v>
+        <v>268.1715851207944</v>
       </c>
       <c r="E117" t="n">
-        <v>286.1286315917969</v>
+        <v>270.2929077148438</v>
       </c>
       <c r="F117" t="n">
-        <v>6974100</v>
+        <v>9684500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>284.6979833712643</v>
+        <v>273.5883087457124</v>
       </c>
       <c r="C118" t="n">
-        <v>287.8749991147026</v>
+        <v>280.9388364524249</v>
       </c>
       <c r="D118" t="n">
-        <v>277.9098533754537</v>
+        <v>273.1739023127244</v>
       </c>
       <c r="E118" t="n">
-        <v>278.5708923339844</v>
+        <v>280.4060668945312</v>
       </c>
       <c r="F118" t="n">
-        <v>7247500</v>
+        <v>11380600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>278.4327740747045</v>
+        <v>283.1489568057956</v>
       </c>
       <c r="C119" t="n">
-        <v>278.6300861021672</v>
+        <v>291.3184213223429</v>
       </c>
       <c r="D119" t="n">
-        <v>268.1715851207944</v>
+        <v>281.422318519362</v>
       </c>
       <c r="E119" t="n">
-        <v>270.2929077148438</v>
+        <v>282.8332214355469</v>
       </c>
       <c r="F119" t="n">
-        <v>9684500</v>
+        <v>10210000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>273.5883087457124</v>
+        <v>280.899378965855</v>
       </c>
       <c r="C120" t="n">
-        <v>280.9388364524249</v>
+        <v>290.2034849465505</v>
       </c>
       <c r="D120" t="n">
-        <v>273.1739023127244</v>
+        <v>280.0607201096653</v>
       </c>
       <c r="E120" t="n">
-        <v>280.4060668945312</v>
+        <v>289.3549499511719</v>
       </c>
       <c r="F120" t="n">
-        <v>11380600</v>
+        <v>9723300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>283.1489568057956</v>
+        <v>284.3132152404683</v>
       </c>
       <c r="C121" t="n">
-        <v>291.3184213223429</v>
+        <v>291.3677603814479</v>
       </c>
       <c r="D121" t="n">
-        <v>281.422318519362</v>
+        <v>283.6620222891216</v>
       </c>
       <c r="E121" t="n">
-        <v>282.8332214355469</v>
+        <v>290.9928283691406</v>
       </c>
       <c r="F121" t="n">
-        <v>10210000</v>
+        <v>8141400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>280.899378965855</v>
+        <v>285.1321178149137</v>
       </c>
       <c r="C122" t="n">
-        <v>290.2034849465505</v>
+        <v>289.8187076809586</v>
       </c>
       <c r="D122" t="n">
-        <v>280.0607201096653</v>
+        <v>280.5639211910132</v>
       </c>
       <c r="E122" t="n">
-        <v>289.3549499511719</v>
+        <v>285.3491821289062</v>
       </c>
       <c r="F122" t="n">
-        <v>9723300</v>
+        <v>7051100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>284.3132152404683</v>
+        <v>285.1518685944145</v>
       </c>
       <c r="C123" t="n">
-        <v>291.3677603814479</v>
+        <v>290.4107024732037</v>
       </c>
       <c r="D123" t="n">
-        <v>283.6620222891216</v>
+        <v>283.8396065771265</v>
       </c>
       <c r="E123" t="n">
-        <v>290.9928283691406</v>
+        <v>288.0624694824219</v>
       </c>
       <c r="F123" t="n">
-        <v>8141400</v>
+        <v>7796000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>285.1321178149137</v>
+        <v>286.1779504316799</v>
       </c>
       <c r="C124" t="n">
-        <v>289.8187076809586</v>
+        <v>287.5000885291143</v>
       </c>
       <c r="D124" t="n">
-        <v>280.5639211910132</v>
+        <v>282.9121398572339</v>
       </c>
       <c r="E124" t="n">
-        <v>285.3491821289062</v>
+        <v>284.9150390625</v>
       </c>
       <c r="F124" t="n">
-        <v>7051100</v>
+        <v>5397900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>285.1518685944145</v>
+        <v>283.5041446062434</v>
       </c>
       <c r="C125" t="n">
-        <v>290.4107024732037</v>
+        <v>287.4408703764128</v>
       </c>
       <c r="D125" t="n">
-        <v>283.8396065771265</v>
+        <v>279.2714056266989</v>
       </c>
       <c r="E125" t="n">
-        <v>288.0624694824219</v>
+        <v>282.6556396484375</v>
       </c>
       <c r="F125" t="n">
-        <v>7796000</v>
+        <v>6816900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,25 +3693,25 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>286.1779504316799</v>
+        <v>280.3985261413432</v>
       </c>
       <c r="C126" t="n">
-        <v>287.5000885291143</v>
+        <v>283.5803655260448</v>
       </c>
       <c r="D126" t="n">
-        <v>282.9121398572339</v>
+        <v>277.0774975936055</v>
       </c>
       <c r="E126" t="n">
-        <v>284.9150390625</v>
+        <v>283.550537109375</v>
       </c>
       <c r="F126" t="n">
-        <v>5397900</v>
+        <v>10348800</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>283.5041446062434</v>
+        <v>285.7479583300972</v>
       </c>
       <c r="C127" t="n">
-        <v>287.4408703764128</v>
+        <v>285.9468043127463</v>
       </c>
       <c r="D127" t="n">
-        <v>279.2714056266989</v>
+        <v>277.3161057836816</v>
       </c>
       <c r="E127" t="n">
-        <v>282.6556396484375</v>
+        <v>280.736572265625</v>
       </c>
       <c r="F127" t="n">
-        <v>6816900</v>
+        <v>6075600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>280.3985261413432</v>
+        <v>280.7763694963311</v>
       </c>
       <c r="C128" t="n">
-        <v>283.5803655260448</v>
+        <v>284.5945585040109</v>
       </c>
       <c r="D128" t="n">
-        <v>277.0774975936055</v>
+        <v>279.0064793259336</v>
       </c>
       <c r="E128" t="n">
-        <v>283.550537109375</v>
+        <v>283.6300659179688</v>
       </c>
       <c r="F128" t="n">
-        <v>10348800</v>
+        <v>6878800</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>285.7479583300972</v>
+        <v>283.1627358622739</v>
       </c>
       <c r="C129" t="n">
-        <v>285.9468043127463</v>
+        <v>285.9269470548217</v>
       </c>
       <c r="D129" t="n">
-        <v>277.3161057836816</v>
+        <v>274.7209602020642</v>
       </c>
       <c r="E129" t="n">
-        <v>280.736572265625</v>
+        <v>275.4766235351562</v>
       </c>
       <c r="F129" t="n">
-        <v>6075600</v>
+        <v>10512300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>280.7763694963311</v>
+        <v>276.4808941849521</v>
       </c>
       <c r="C130" t="n">
-        <v>284.5945585040109</v>
+        <v>281.2735286763525</v>
       </c>
       <c r="D130" t="n">
-        <v>279.0064793259336</v>
+        <v>276.2323139355343</v>
       </c>
       <c r="E130" t="n">
-        <v>283.6300659179688</v>
+        <v>280.4880065917969</v>
       </c>
       <c r="F130" t="n">
-        <v>6878800</v>
+        <v>4737600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>283.1627358622739</v>
+        <v>282.3672788368328</v>
       </c>
       <c r="C131" t="n">
-        <v>285.9269470548217</v>
+        <v>285.767839547621</v>
       </c>
       <c r="D131" t="n">
-        <v>274.7209602020642</v>
+        <v>279.4439727693734</v>
       </c>
       <c r="E131" t="n">
-        <v>275.4766235351562</v>
+        <v>283.8686828613281</v>
       </c>
       <c r="F131" t="n">
-        <v>10512300</v>
+        <v>4854000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>276.4808941849521</v>
+        <v>286.1655640520241</v>
       </c>
       <c r="C132" t="n">
-        <v>281.2735286763525</v>
+        <v>287.3488084380985</v>
       </c>
       <c r="D132" t="n">
-        <v>276.2323139355343</v>
+        <v>283.2223824666901</v>
       </c>
       <c r="E132" t="n">
-        <v>280.4880065917969</v>
+        <v>285.9368896484375</v>
       </c>
       <c r="F132" t="n">
-        <v>4737600</v>
+        <v>5752000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>282.3672788368328</v>
+        <v>283.5803557381978</v>
       </c>
       <c r="C133" t="n">
-        <v>285.767839547621</v>
+        <v>286.7621646688093</v>
       </c>
       <c r="D133" t="n">
-        <v>279.4439727693734</v>
+        <v>281.4624471949345</v>
       </c>
       <c r="E133" t="n">
-        <v>283.8686828613281</v>
+        <v>282.7152709960938</v>
       </c>
       <c r="F133" t="n">
-        <v>4854000</v>
+        <v>4544100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>286.1655640520241</v>
+        <v>282.3871618979052</v>
       </c>
       <c r="C134" t="n">
-        <v>287.3488084380985</v>
+        <v>285.9169892839216</v>
       </c>
       <c r="D134" t="n">
-        <v>283.2223824666901</v>
+        <v>278.4794876796185</v>
       </c>
       <c r="E134" t="n">
-        <v>285.9368896484375</v>
+        <v>278.8473815917969</v>
       </c>
       <c r="F134" t="n">
-        <v>5752000</v>
+        <v>5542100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>283.5803557381978</v>
+        <v>277.4056183419098</v>
       </c>
       <c r="C135" t="n">
-        <v>286.7621646688093</v>
+        <v>281.4922936115716</v>
       </c>
       <c r="D135" t="n">
-        <v>281.4624471949345</v>
+        <v>273.4382870867091</v>
       </c>
       <c r="E135" t="n">
-        <v>282.7152709960938</v>
+        <v>274.0249328613281</v>
       </c>
       <c r="F135" t="n">
-        <v>4544100</v>
+        <v>38893000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>282.3871618979052</v>
+        <v>277.5547645320462</v>
       </c>
       <c r="C136" t="n">
-        <v>285.9169892839216</v>
+        <v>279.1556066962045</v>
       </c>
       <c r="D136" t="n">
-        <v>278.4794876796185</v>
+        <v>267.5618207785692</v>
       </c>
       <c r="E136" t="n">
-        <v>278.8473815917969</v>
+        <v>268.00927734375</v>
       </c>
       <c r="F136" t="n">
-        <v>5542100</v>
+        <v>10424200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>277.4056183419098</v>
+        <v>267.3430655755382</v>
       </c>
       <c r="C137" t="n">
-        <v>281.4922936115716</v>
+        <v>271.8274627132414</v>
       </c>
       <c r="D137" t="n">
-        <v>273.4382870867091</v>
+        <v>266.0703359894755</v>
       </c>
       <c r="E137" t="n">
-        <v>274.0249328613281</v>
+        <v>270.7337036132812</v>
       </c>
       <c r="F137" t="n">
-        <v>38893000</v>
+        <v>5911700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>277.5547645320462</v>
+        <v>273.4382596260376</v>
       </c>
       <c r="C138" t="n">
-        <v>279.1556066962045</v>
+        <v>274.5121128941823</v>
       </c>
       <c r="D138" t="n">
-        <v>267.5618207785692</v>
+        <v>265.5930528118823</v>
       </c>
       <c r="E138" t="n">
-        <v>268.00927734375</v>
+        <v>269.0135192871094</v>
       </c>
       <c r="F138" t="n">
-        <v>10424200</v>
+        <v>8121200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>267.3430655755382</v>
+        <v>268.4567257080549</v>
       </c>
       <c r="C139" t="n">
-        <v>271.8274627132414</v>
+        <v>273.0803427820733</v>
       </c>
       <c r="D139" t="n">
-        <v>266.0703359894755</v>
+        <v>265.6626860357957</v>
       </c>
       <c r="E139" t="n">
-        <v>270.7337036132812</v>
+        <v>266.5277404785156</v>
       </c>
       <c r="F139" t="n">
-        <v>5911700</v>
+        <v>6218800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>273.4382596260376</v>
+        <v>265.9808641274938</v>
       </c>
       <c r="C140" t="n">
-        <v>274.5121128941823</v>
+        <v>266.1499120468286</v>
       </c>
       <c r="D140" t="n">
-        <v>265.5930528118823</v>
+        <v>254.516344356629</v>
       </c>
       <c r="E140" t="n">
-        <v>269.0135192871094</v>
+        <v>257.5490112304688</v>
       </c>
       <c r="F140" t="n">
-        <v>8121200</v>
+        <v>10735300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>268.4567257080549</v>
+        <v>258.7024415515604</v>
       </c>
       <c r="C141" t="n">
-        <v>273.0803427820733</v>
+        <v>260.8402257240527</v>
       </c>
       <c r="D141" t="n">
-        <v>265.6626860357957</v>
+        <v>255.2123953265358</v>
       </c>
       <c r="E141" t="n">
-        <v>266.5277404785156</v>
+        <v>260.3033142089844</v>
       </c>
       <c r="F141" t="n">
-        <v>6218800</v>
+        <v>7774700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>265.9808641274938</v>
+        <v>261.506421503485</v>
       </c>
       <c r="C142" t="n">
-        <v>266.1499120468286</v>
+        <v>270.3359967880393</v>
       </c>
       <c r="D142" t="n">
-        <v>254.516344356629</v>
+        <v>261.1186217504552</v>
       </c>
       <c r="E142" t="n">
-        <v>257.5490112304688</v>
+        <v>269.0533142089844</v>
       </c>
       <c r="F142" t="n">
-        <v>10735300</v>
+        <v>9170800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>258.7024415515604</v>
+        <v>272.6527466700565</v>
       </c>
       <c r="C143" t="n">
-        <v>260.8402257240527</v>
+        <v>273.7365528939259</v>
       </c>
       <c r="D143" t="n">
-        <v>255.2123953265358</v>
+        <v>269.2223575051711</v>
       </c>
       <c r="E143" t="n">
-        <v>260.3033142089844</v>
+        <v>272.424072265625</v>
       </c>
       <c r="F143" t="n">
-        <v>7774700</v>
+        <v>5473400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>261.506421503485</v>
+        <v>270.7436786461413</v>
       </c>
       <c r="C144" t="n">
-        <v>270.3359967880393</v>
+        <v>277.4553455215711</v>
       </c>
       <c r="D144" t="n">
-        <v>261.1186217504552</v>
+        <v>269.9879849618526</v>
       </c>
       <c r="E144" t="n">
-        <v>269.0533142089844</v>
+        <v>275.6854553222656</v>
       </c>
       <c r="F144" t="n">
-        <v>9170800</v>
+        <v>6407000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>272.6527466700565</v>
+        <v>276.3019282869355</v>
       </c>
       <c r="C145" t="n">
-        <v>273.7365528939259</v>
+        <v>281.6911311912249</v>
       </c>
       <c r="D145" t="n">
-        <v>269.2223575051711</v>
+        <v>275.6755011928929</v>
       </c>
       <c r="E145" t="n">
-        <v>272.424072265625</v>
+        <v>279.7621459960938</v>
       </c>
       <c r="F145" t="n">
-        <v>5473400</v>
+        <v>7097000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>270.7436786461413</v>
+        <v>307.0960565749332</v>
       </c>
       <c r="C146" t="n">
-        <v>277.4553455215711</v>
+        <v>310.6557125153819</v>
       </c>
       <c r="D146" t="n">
-        <v>269.9879849618526</v>
+        <v>299.0420501528358</v>
       </c>
       <c r="E146" t="n">
-        <v>275.6854553222656</v>
+        <v>305.982421875</v>
       </c>
       <c r="F146" t="n">
-        <v>6407000</v>
+        <v>22099800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>276.3019282869355</v>
+        <v>310.2281413790238</v>
       </c>
       <c r="C147" t="n">
-        <v>281.6911311912249</v>
+        <v>311.1926339297742</v>
       </c>
       <c r="D147" t="n">
-        <v>275.6755011928929</v>
+        <v>303.0988467016243</v>
       </c>
       <c r="E147" t="n">
-        <v>279.7621459960938</v>
+        <v>304.2423400878906</v>
       </c>
       <c r="F147" t="n">
-        <v>7097000</v>
+        <v>9645000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>307.0960565749332</v>
+        <v>304.0832470042582</v>
       </c>
       <c r="C148" t="n">
-        <v>310.6557125153819</v>
+        <v>306.1414986993597</v>
       </c>
       <c r="D148" t="n">
-        <v>299.0420501528358</v>
+        <v>302.4127950535677</v>
       </c>
       <c r="E148" t="n">
-        <v>305.982421875</v>
+        <v>305.1670532226562</v>
       </c>
       <c r="F148" t="n">
-        <v>22099800</v>
+        <v>5742000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>310.2281413790238</v>
+        <v>306.2011519366599</v>
       </c>
       <c r="C149" t="n">
-        <v>311.1926339297742</v>
+        <v>308.607391668382</v>
       </c>
       <c r="D149" t="n">
-        <v>303.0988467016243</v>
+        <v>302.4724483346268</v>
       </c>
       <c r="E149" t="n">
-        <v>304.2423400878906</v>
+        <v>302.6016845703125</v>
       </c>
       <c r="F149" t="n">
-        <v>9645000</v>
+        <v>5212900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>304.0832470042582</v>
+        <v>301.5278433900291</v>
       </c>
       <c r="C150" t="n">
-        <v>306.1414986993597</v>
+        <v>311.5406631473035</v>
       </c>
       <c r="D150" t="n">
-        <v>302.4127950535677</v>
+        <v>301.199730811355</v>
       </c>
       <c r="E150" t="n">
-        <v>305.1670532226562</v>
+        <v>311.2224731445312</v>
       </c>
       <c r="F150" t="n">
-        <v>5742000</v>
+        <v>7972200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>306.2011519366599</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="C151" t="n">
-        <v>308.607391668382</v>
+        <v>317.8048561417646</v>
       </c>
       <c r="D151" t="n">
-        <v>302.4724483346268</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="E151" t="n">
-        <v>302.6016845703125</v>
+        <v>312.4057006835938</v>
       </c>
       <c r="F151" t="n">
-        <v>5212900</v>
+        <v>5864500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>301.5278433900291</v>
+        <v>314.2054174655202</v>
       </c>
       <c r="C152" t="n">
-        <v>311.5406631473035</v>
+        <v>315.9554320324556</v>
       </c>
       <c r="D152" t="n">
-        <v>301.199730811355</v>
+        <v>309.3829548311358</v>
       </c>
       <c r="E152" t="n">
-        <v>311.2224731445312</v>
+        <v>312.2664794921875</v>
       </c>
       <c r="F152" t="n">
-        <v>7972200</v>
+        <v>5041200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>310.7352487756957</v>
+        <v>313.2111061223722</v>
       </c>
       <c r="C153" t="n">
-        <v>317.8048561417646</v>
+        <v>316.8005902653832</v>
       </c>
       <c r="D153" t="n">
-        <v>310.7352487756957</v>
+        <v>311.3318249203894</v>
       </c>
       <c r="E153" t="n">
-        <v>312.4057006835938</v>
+        <v>314.6031494140625</v>
       </c>
       <c r="F153" t="n">
-        <v>5864500</v>
+        <v>5205600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>314.2054174655202</v>
+        <v>318.2324307180975</v>
       </c>
       <c r="C154" t="n">
-        <v>315.9554320324556</v>
+        <v>323.4227876628706</v>
       </c>
       <c r="D154" t="n">
-        <v>309.3829548311358</v>
+        <v>315.338983249174</v>
       </c>
       <c r="E154" t="n">
-        <v>312.2664794921875</v>
+        <v>322.7864379882812</v>
       </c>
       <c r="F154" t="n">
-        <v>5041200</v>
+        <v>9414700</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>313.2111061223722</v>
+        <v>322.3489342821542</v>
       </c>
       <c r="C155" t="n">
-        <v>316.8005902653832</v>
+        <v>323.5520542213801</v>
       </c>
       <c r="D155" t="n">
-        <v>311.3318249203894</v>
+        <v>318.3020404433487</v>
       </c>
       <c r="E155" t="n">
-        <v>314.6031494140625</v>
+        <v>321.6429748535156</v>
       </c>
       <c r="F155" t="n">
-        <v>5205600</v>
+        <v>9050600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>318.2324307180975</v>
+        <v>351.0052603166191</v>
       </c>
       <c r="C156" t="n">
-        <v>323.4227876628706</v>
+        <v>355.648722319699</v>
       </c>
       <c r="D156" t="n">
-        <v>315.338983249174</v>
+        <v>343.2694442738866</v>
       </c>
       <c r="E156" t="n">
-        <v>322.7864379882812</v>
+        <v>344.0450134277344</v>
       </c>
       <c r="F156" t="n">
-        <v>9414700</v>
+        <v>26097300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>322.3489342821542</v>
+        <v>348.8873678788304</v>
       </c>
       <c r="C157" t="n">
-        <v>323.5520542213801</v>
+        <v>356.5237461069854</v>
       </c>
       <c r="D157" t="n">
-        <v>318.3020404433487</v>
+        <v>347.1174776591131</v>
       </c>
       <c r="E157" t="n">
-        <v>321.6429748535156</v>
+        <v>351.5123596191406</v>
       </c>
       <c r="F157" t="n">
-        <v>9050600</v>
+        <v>11807300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>351.0052603166191</v>
+        <v>352.6657614176121</v>
       </c>
       <c r="C158" t="n">
-        <v>355.648722319699</v>
+        <v>354.8234513171886</v>
       </c>
       <c r="D158" t="n">
-        <v>343.2694442738866</v>
+        <v>348.5095069624251</v>
       </c>
       <c r="E158" t="n">
-        <v>344.0450134277344</v>
+        <v>352.5464477539062</v>
       </c>
       <c r="F158" t="n">
-        <v>26097300</v>
+        <v>7255800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>348.8873678788304</v>
+        <v>354.4654798371856</v>
       </c>
       <c r="C159" t="n">
-        <v>356.5237461069854</v>
+        <v>356.2453229047883</v>
       </c>
       <c r="D159" t="n">
-        <v>347.1174776591131</v>
+        <v>349.3944670661433</v>
       </c>
       <c r="E159" t="n">
-        <v>351.5123596191406</v>
+        <v>352.9044189453125</v>
       </c>
       <c r="F159" t="n">
-        <v>11807300</v>
+        <v>8554600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>352.6657614176121</v>
+        <v>351.9001510435625</v>
       </c>
       <c r="C160" t="n">
-        <v>354.8234513171886</v>
+        <v>354.4654858887946</v>
       </c>
       <c r="D160" t="n">
-        <v>348.5095069624251</v>
+        <v>346.9683273478323</v>
       </c>
       <c r="E160" t="n">
-        <v>352.5464477539062</v>
+        <v>352.6757202148438</v>
       </c>
       <c r="F160" t="n">
-        <v>7255800</v>
+        <v>7256100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>354.4654798371856</v>
+        <v>354.8135029963465</v>
       </c>
       <c r="C161" t="n">
-        <v>356.2453229047883</v>
+        <v>367.5308771185002</v>
       </c>
       <c r="D161" t="n">
-        <v>349.3944670661433</v>
+        <v>353.6998683282982</v>
       </c>
       <c r="E161" t="n">
-        <v>352.9044189453125</v>
+        <v>364.6871032714844</v>
       </c>
       <c r="F161" t="n">
-        <v>8554600</v>
+        <v>10604100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>351.9001510435625</v>
+        <v>363.9214802466298</v>
       </c>
       <c r="C162" t="n">
-        <v>354.4654858887946</v>
+        <v>368.7339901692348</v>
       </c>
       <c r="D162" t="n">
-        <v>346.9683273478323</v>
+        <v>362.9371121823581</v>
       </c>
       <c r="E162" t="n">
-        <v>352.6757202148438</v>
+        <v>368.6345520019531</v>
       </c>
       <c r="F162" t="n">
-        <v>7256100</v>
+        <v>9046600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>354.8135029963465</v>
+        <v>366.4172241064422</v>
       </c>
       <c r="C163" t="n">
-        <v>367.5308771185002</v>
+        <v>369.87744160261</v>
       </c>
       <c r="D163" t="n">
-        <v>353.6998683282982</v>
+        <v>360.9385059451532</v>
       </c>
       <c r="E163" t="n">
-        <v>364.6871032714844</v>
+        <v>368.3760375976562</v>
       </c>
       <c r="F163" t="n">
-        <v>10604100</v>
+        <v>6879900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>363.9214802466298</v>
+        <v>369.8476329800702</v>
       </c>
       <c r="C164" t="n">
-        <v>368.7339901692348</v>
+        <v>370.7822971534658</v>
       </c>
       <c r="D164" t="n">
-        <v>362.9371121823581</v>
+        <v>364.9356847817637</v>
       </c>
       <c r="E164" t="n">
-        <v>368.6345520019531</v>
+        <v>366.6856994628906</v>
       </c>
       <c r="F164" t="n">
-        <v>9046600</v>
+        <v>4945400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>366.4172241064422</v>
+        <v>366.4569824541582</v>
       </c>
       <c r="C165" t="n">
-        <v>369.87744160261</v>
+        <v>368.7240330587824</v>
       </c>
       <c r="D165" t="n">
-        <v>360.9385059451532</v>
+        <v>362.5791367283888</v>
       </c>
       <c r="E165" t="n">
-        <v>368.3760375976562</v>
+        <v>368.6445007324219</v>
       </c>
       <c r="F165" t="n">
-        <v>6879900</v>
+        <v>4916900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>369.8476329800702</v>
+        <v>368.3760355922912</v>
       </c>
       <c r="C166" t="n">
-        <v>370.7822971534658</v>
+        <v>369.6885161814855</v>
       </c>
       <c r="D166" t="n">
-        <v>364.9356847817637</v>
+        <v>359.7552596250864</v>
       </c>
       <c r="E166" t="n">
-        <v>366.6856994628906</v>
+        <v>361.8035583496094</v>
       </c>
       <c r="F166" t="n">
-        <v>4945400</v>
+        <v>6489000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>366.4569824541582</v>
+        <v>361.0379593902868</v>
       </c>
       <c r="C167" t="n">
-        <v>368.7240330587824</v>
+        <v>366.45699060703</v>
       </c>
       <c r="D167" t="n">
-        <v>362.5791367283888</v>
+        <v>356.2154964951898</v>
       </c>
       <c r="E167" t="n">
-        <v>368.6445007324219</v>
+        <v>365.1942138671875</v>
       </c>
       <c r="F167" t="n">
-        <v>4916900</v>
+        <v>6695500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>368.3760355922912</v>
+        <v>364.5578575186544</v>
       </c>
       <c r="C168" t="n">
-        <v>369.6885161814855</v>
+        <v>367.7098380224884</v>
       </c>
       <c r="D168" t="n">
-        <v>359.7552596250864</v>
+        <v>362.6487478916185</v>
       </c>
       <c r="E168" t="n">
-        <v>361.8035583496094</v>
+        <v>367.6402282714844</v>
       </c>
       <c r="F168" t="n">
-        <v>6489000</v>
+        <v>5235400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>361.0379593902868</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="C169" t="n">
-        <v>366.45699060703</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="D169" t="n">
-        <v>356.2154964951898</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="E169" t="n">
-        <v>365.1942138671875</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="F169" t="n">
-        <v>6695500</v>
+        <v>6455100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>364.5578575186544</v>
+        <v>378.2894437474218</v>
       </c>
       <c r="C170" t="n">
-        <v>367.7098380224884</v>
+        <v>382.6246688242237</v>
       </c>
       <c r="D170" t="n">
-        <v>362.6487478916185</v>
+        <v>373.9343128299113</v>
       </c>
       <c r="E170" t="n">
-        <v>367.6402282714844</v>
+        <v>382.2567749023438</v>
       </c>
       <c r="F170" t="n">
-        <v>5235400</v>
+        <v>6949600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>369.8774674335755</v>
+        <v>380.6758011703357</v>
       </c>
       <c r="C171" t="n">
-        <v>377.8221130371094</v>
+        <v>395.1630654325308</v>
       </c>
       <c r="D171" t="n">
-        <v>369.8774674335755</v>
+        <v>379.8405751710962</v>
       </c>
       <c r="E171" t="n">
-        <v>377.8221130371094</v>
+        <v>394.138916015625</v>
       </c>
       <c r="F171" t="n">
-        <v>6455100</v>
+        <v>9236300</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>378.2894437474218</v>
+        <v>394.2482660415264</v>
       </c>
       <c r="C172" t="n">
-        <v>382.6246688242237</v>
+        <v>401.8548154208889</v>
       </c>
       <c r="D172" t="n">
-        <v>373.9343128299113</v>
+        <v>390.7681426338459</v>
       </c>
       <c r="E172" t="n">
-        <v>382.2567749023438</v>
+        <v>398.8818054199219</v>
       </c>
       <c r="F172" t="n">
-        <v>6949600</v>
+        <v>8454100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>380.6758011703357</v>
+        <v>398.7227040337817</v>
       </c>
       <c r="C173" t="n">
-        <v>395.1630654325308</v>
+        <v>399.6175868268494</v>
       </c>
       <c r="D173" t="n">
-        <v>379.8405751710962</v>
+        <v>393.7510992453305</v>
       </c>
       <c r="E173" t="n">
-        <v>394.138916015625</v>
+        <v>396.8235473632812</v>
       </c>
       <c r="F173" t="n">
-        <v>9236300</v>
+        <v>5342500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>394.2482660415264</v>
+        <v>392.0607685404387</v>
       </c>
       <c r="C174" t="n">
-        <v>401.8548154208889</v>
+        <v>395.3718745508767</v>
       </c>
       <c r="D174" t="n">
-        <v>390.7681426338459</v>
+        <v>388.0337805215488</v>
       </c>
       <c r="E174" t="n">
-        <v>398.8818054199219</v>
+        <v>391.6133422851562</v>
       </c>
       <c r="F174" t="n">
-        <v>8454100</v>
+        <v>9811200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>398.7227040337817</v>
+        <v>387.7851953583757</v>
       </c>
       <c r="C175" t="n">
-        <v>399.6175868268494</v>
+        <v>389.9130568930274</v>
       </c>
       <c r="D175" t="n">
-        <v>393.7510992453305</v>
+        <v>381.3221087690695</v>
       </c>
       <c r="E175" t="n">
-        <v>396.8235473632812</v>
+        <v>388.9087829589844</v>
       </c>
       <c r="F175" t="n">
-        <v>5342500</v>
+        <v>8400700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>392.0607685404387</v>
+        <v>387.7851736187118</v>
       </c>
       <c r="C176" t="n">
-        <v>395.3718745508767</v>
+        <v>392.7468254889498</v>
       </c>
       <c r="D176" t="n">
-        <v>388.0337805215488</v>
+        <v>385.3093241434657</v>
       </c>
       <c r="E176" t="n">
-        <v>391.6133422851562</v>
+        <v>387.0294799804688</v>
       </c>
       <c r="F176" t="n">
-        <v>9811200</v>
+        <v>5016800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>387.7851953583757</v>
+        <v>387.3377362764213</v>
       </c>
       <c r="C177" t="n">
-        <v>389.9130568930274</v>
+        <v>391.1460027273716</v>
       </c>
       <c r="D177" t="n">
-        <v>381.3221087690695</v>
+        <v>378.5380196367677</v>
       </c>
       <c r="E177" t="n">
-        <v>388.9087829589844</v>
+        <v>381.1232299804688</v>
       </c>
       <c r="F177" t="n">
-        <v>8400700</v>
+        <v>7783900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>387.7851736187118</v>
+        <v>378.9555995605828</v>
       </c>
       <c r="C178" t="n">
-        <v>392.7468254889498</v>
+        <v>383.9172514426562</v>
       </c>
       <c r="D178" t="n">
-        <v>385.3093241434657</v>
+        <v>378.3789067550467</v>
       </c>
       <c r="E178" t="n">
-        <v>387.0294799804688</v>
+        <v>380.3078918457031</v>
       </c>
       <c r="F178" t="n">
-        <v>5016800</v>
+        <v>4732500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>387.3377362764213</v>
+        <v>379.7510949944643</v>
       </c>
       <c r="C179" t="n">
-        <v>391.1460027273716</v>
+        <v>388.322137279522</v>
       </c>
       <c r="D179" t="n">
-        <v>378.5380196367677</v>
+        <v>378.846259230469</v>
       </c>
       <c r="E179" t="n">
-        <v>381.1232299804688</v>
+        <v>386.2638854980469</v>
       </c>
       <c r="F179" t="n">
-        <v>7783900</v>
+        <v>5598600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>378.9555995605828</v>
+        <v>383.8078958628703</v>
       </c>
       <c r="C180" t="n">
-        <v>383.9172514426562</v>
+        <v>384.3249318452775</v>
       </c>
       <c r="D180" t="n">
-        <v>378.3789067550467</v>
+        <v>374.2723613660349</v>
       </c>
       <c r="E180" t="n">
-        <v>380.3078918457031</v>
+        <v>374.7197875976562</v>
       </c>
       <c r="F180" t="n">
-        <v>4732500</v>
+        <v>6498100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>379.7510949944643</v>
+        <v>376.2808953624811</v>
       </c>
       <c r="C181" t="n">
-        <v>388.322137279522</v>
+        <v>382.3462596379654</v>
       </c>
       <c r="D181" t="n">
-        <v>378.846259230469</v>
+        <v>374.9485088403697</v>
       </c>
       <c r="E181" t="n">
-        <v>386.2638854980469</v>
+        <v>381.8292236328125</v>
       </c>
       <c r="F181" t="n">
-        <v>5598600</v>
+        <v>4544000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>383.8078958628703</v>
+        <v>382.7737976901378</v>
       </c>
       <c r="C182" t="n">
-        <v>384.3249318452775</v>
+        <v>387.0493961299752</v>
       </c>
       <c r="D182" t="n">
-        <v>374.2723613660349</v>
+        <v>378.7965137522062</v>
       </c>
       <c r="E182" t="n">
-        <v>374.7197875976562</v>
+        <v>380.3576049804688</v>
       </c>
       <c r="F182" t="n">
-        <v>6498100</v>
+        <v>4330800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>376.2808953624811</v>
+        <v>381.6005025160485</v>
       </c>
       <c r="C183" t="n">
-        <v>382.3462596379654</v>
+        <v>382.9328889810419</v>
       </c>
       <c r="D183" t="n">
-        <v>374.9485088403697</v>
+        <v>373.317822146985</v>
       </c>
       <c r="E183" t="n">
-        <v>381.8292236328125</v>
+        <v>378.1502075195312</v>
       </c>
       <c r="F183" t="n">
-        <v>4544000</v>
+        <v>10257900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>382.7737976901378</v>
+        <v>373.9740550559011</v>
       </c>
       <c r="C184" t="n">
-        <v>387.0493961299752</v>
+        <v>381.172959697494</v>
       </c>
       <c r="D184" t="n">
-        <v>378.7965137522062</v>
+        <v>373.7851619834815</v>
       </c>
       <c r="E184" t="n">
-        <v>380.3576049804688</v>
+        <v>377.7027587890625</v>
       </c>
       <c r="F184" t="n">
-        <v>4330800</v>
+        <v>6623700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>381.6005025160485</v>
+        <v>375.8334605430848</v>
       </c>
       <c r="C185" t="n">
-        <v>382.9328889810419</v>
+        <v>377.9215103567756</v>
       </c>
       <c r="D185" t="n">
-        <v>373.317822146985</v>
+        <v>372.5919643898307</v>
       </c>
       <c r="E185" t="n">
-        <v>378.1502075195312</v>
+        <v>375.7738037109375</v>
       </c>
       <c r="F185" t="n">
-        <v>10257900</v>
+        <v>3874400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>373.9740550559011</v>
+        <v>377.8419717237235</v>
       </c>
       <c r="C186" t="n">
-        <v>381.172959697494</v>
+        <v>385.259597724852</v>
       </c>
       <c r="D186" t="n">
-        <v>373.7851619834815</v>
+        <v>374.6700853756592</v>
       </c>
       <c r="E186" t="n">
-        <v>377.7027587890625</v>
+        <v>374.8590087890625</v>
       </c>
       <c r="F186" t="n">
-        <v>6623700</v>
+        <v>6808400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>375.8334605430848</v>
+        <v>387.7851867936407</v>
       </c>
       <c r="C187" t="n">
-        <v>377.9215103567756</v>
+        <v>399.1005645351637</v>
       </c>
       <c r="D187" t="n">
-        <v>372.5919643898307</v>
+        <v>387.606216297745</v>
       </c>
       <c r="E187" t="n">
-        <v>375.7738037109375</v>
+        <v>394.2184448242188</v>
       </c>
       <c r="F187" t="n">
-        <v>3874400</v>
+        <v>12666100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>377.8419717237235</v>
+        <v>397.2710257691138</v>
       </c>
       <c r="C188" t="n">
-        <v>385.259597724852</v>
+        <v>401.7454703246708</v>
       </c>
       <c r="D188" t="n">
-        <v>374.6700853756592</v>
+        <v>394.9443182415365</v>
       </c>
       <c r="E188" t="n">
-        <v>374.8590087890625</v>
+        <v>397.201416015625</v>
       </c>
       <c r="F188" t="n">
-        <v>6808400</v>
+        <v>10897300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>387.7851867936407</v>
+        <v>394.8746856398852</v>
       </c>
       <c r="C189" t="n">
-        <v>399.1005645351637</v>
+        <v>406.3889089451397</v>
       </c>
       <c r="D189" t="n">
-        <v>387.606216297745</v>
+        <v>392.7468242313375</v>
       </c>
       <c r="E189" t="n">
-        <v>394.2184448242188</v>
+        <v>404.2610778808594</v>
       </c>
       <c r="F189" t="n">
-        <v>12666100</v>
+        <v>6963200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>397.2710257691138</v>
+        <v>407.6616556237274</v>
       </c>
       <c r="C190" t="n">
-        <v>401.7454703246708</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="D190" t="n">
-        <v>394.9443182415365</v>
+        <v>405.1261492204914</v>
       </c>
       <c r="E190" t="n">
-        <v>397.201416015625</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="F190" t="n">
-        <v>10897300</v>
+        <v>8590400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>394.8746856398852</v>
+        <v>411.1517339543602</v>
       </c>
       <c r="C191" t="n">
-        <v>406.3889089451397</v>
+        <v>413.6176609610221</v>
       </c>
       <c r="D191" t="n">
-        <v>392.7468242313375</v>
+        <v>402.2525488568183</v>
       </c>
       <c r="E191" t="n">
-        <v>404.2610778808594</v>
+        <v>405.1460266113281</v>
       </c>
       <c r="F191" t="n">
-        <v>6963200</v>
+        <v>6512900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>407.6616556237274</v>
+        <v>406.3889145916303</v>
       </c>
       <c r="C192" t="n">
-        <v>410.6545715332031</v>
+        <v>407.6517216421196</v>
       </c>
       <c r="D192" t="n">
-        <v>405.1261492204914</v>
+        <v>400.820711098459</v>
       </c>
       <c r="E192" t="n">
-        <v>410.6545715332031</v>
+        <v>403.2468566894531</v>
       </c>
       <c r="F192" t="n">
-        <v>8590400</v>
+        <v>4938100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>411.1517339543602</v>
+        <v>406.6872501409831</v>
       </c>
       <c r="C193" t="n">
-        <v>413.6176609610221</v>
+        <v>407.5622574937536</v>
       </c>
       <c r="D193" t="n">
-        <v>402.2525488568183</v>
+        <v>402.5110897188582</v>
       </c>
       <c r="E193" t="n">
-        <v>405.1460266113281</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="F193" t="n">
-        <v>6512900</v>
+        <v>7269600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>406.3889145916303</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="C194" t="n">
-        <v>407.6517216421196</v>
+        <v>414.1600036621094</v>
       </c>
       <c r="D194" t="n">
-        <v>400.820711098459</v>
+        <v>399.6499938964844</v>
       </c>
       <c r="E194" t="n">
-        <v>403.2468566894531</v>
+        <v>411.0400085449219</v>
       </c>
       <c r="F194" t="n">
-        <v>4938100</v>
+        <v>6777900</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>406.6872501409831</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="C195" t="n">
-        <v>407.5622574937536</v>
+        <v>411.75</v>
       </c>
       <c r="D195" t="n">
-        <v>402.5110897188582</v>
+        <v>406.5400085449219</v>
       </c>
       <c r="E195" t="n">
-        <v>406.2000122070312</v>
+        <v>407.6499938964844</v>
       </c>
       <c r="F195" t="n">
-        <v>7269600</v>
+        <v>4815100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,25 +5513,25 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>406.7000122070312</v>
+        <v>409.1199951171875</v>
       </c>
       <c r="C196" t="n">
-        <v>414.1600036621094</v>
+        <v>411.1600036621094</v>
       </c>
       <c r="D196" t="n">
-        <v>399.6499938964844</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E196" t="n">
-        <v>411.0400085449219</v>
+        <v>399.5299987792969</v>
       </c>
       <c r="F196" t="n">
-        <v>6777900</v>
+        <v>5838800</v>
       </c>
       <c r="G196" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>410.6799926757812</v>
+        <v>402.7699890136719</v>
       </c>
       <c r="C197" t="n">
-        <v>411.75</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="D197" t="n">
-        <v>406.5400085449219</v>
+        <v>399.1499938964844</v>
       </c>
       <c r="E197" t="n">
-        <v>407.6499938964844</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="F197" t="n">
-        <v>4815100</v>
+        <v>11896900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>409.1199951171875</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="C198" t="n">
-        <v>411.1600036621094</v>
+        <v>409.4599914550781</v>
       </c>
       <c r="D198" t="n">
-        <v>398.5899963378906</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="E198" t="n">
-        <v>399.5299987792969</v>
+        <v>406.6799926757812</v>
       </c>
       <c r="F198" t="n">
-        <v>5838800</v>
+        <v>5818600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>402.7699890136719</v>
+        <v>409.5199890136719</v>
       </c>
       <c r="C199" t="n">
-        <v>406.2000122070312</v>
+        <v>409.8999938964844</v>
       </c>
       <c r="D199" t="n">
-        <v>399.1499938964844</v>
+        <v>402.8399963378906</v>
       </c>
       <c r="E199" t="n">
-        <v>400.9599914550781</v>
+        <v>409.25</v>
       </c>
       <c r="F199" t="n">
-        <v>11896900</v>
+        <v>6675900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>402.1400146484375</v>
+        <v>410.5400085449219</v>
       </c>
       <c r="C200" t="n">
-        <v>409.4599914550781</v>
+        <v>413.4299926757812</v>
       </c>
       <c r="D200" t="n">
-        <v>402.1400146484375</v>
+        <v>400</v>
       </c>
       <c r="E200" t="n">
-        <v>406.6799926757812</v>
+        <v>405.7999877929688</v>
       </c>
       <c r="F200" t="n">
-        <v>5818600</v>
+        <v>6858800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>409.5199890136719</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="C201" t="n">
-        <v>409.8999938964844</v>
+        <v>417.5799865722656</v>
       </c>
       <c r="D201" t="n">
-        <v>402.8399963378906</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="E201" t="n">
-        <v>409.25</v>
+        <v>415.5299987792969</v>
       </c>
       <c r="F201" t="n">
-        <v>6675900</v>
+        <v>6014400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>410.5400085449219</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="C202" t="n">
-        <v>413.4299926757812</v>
+        <v>427.9299926757812</v>
       </c>
       <c r="D202" t="n">
-        <v>400</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="E202" t="n">
-        <v>405.7999877929688</v>
+        <v>427.8900146484375</v>
       </c>
       <c r="F202" t="n">
-        <v>6858800</v>
+        <v>10588200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>406.6499938964844</v>
+        <v>426.5299987792969</v>
       </c>
       <c r="C203" t="n">
-        <v>417.5799865722656</v>
+        <v>426.7000122070312</v>
       </c>
       <c r="D203" t="n">
-        <v>406.6499938964844</v>
+        <v>415.8099975585938</v>
       </c>
       <c r="E203" t="n">
-        <v>415.5299987792969</v>
+        <v>419.8200073242188</v>
       </c>
       <c r="F203" t="n">
-        <v>6014400</v>
+        <v>5167400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>416.1600036621094</v>
+        <v>422.7200012207031</v>
       </c>
       <c r="C204" t="n">
-        <v>427.9299926757812</v>
+        <v>422.739990234375</v>
       </c>
       <c r="D204" t="n">
-        <v>416.1600036621094</v>
+        <v>413.25</v>
       </c>
       <c r="E204" t="n">
-        <v>427.8900146484375</v>
+        <v>415.6300048828125</v>
       </c>
       <c r="F204" t="n">
-        <v>10588200</v>
+        <v>5779800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>426.5299987792969</v>
+        <v>417.1099853515625</v>
       </c>
       <c r="C205" t="n">
-        <v>426.7000122070312</v>
+        <v>428.0199890136719</v>
       </c>
       <c r="D205" t="n">
-        <v>415.8099975585938</v>
+        <v>413.7300109863281</v>
       </c>
       <c r="E205" t="n">
-        <v>419.8200073242188</v>
+        <v>426.5400085449219</v>
       </c>
       <c r="F205" t="n">
-        <v>5167400</v>
+        <v>4985900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>422.7200012207031</v>
+        <v>428.1300048828125</v>
       </c>
       <c r="C206" t="n">
-        <v>422.739990234375</v>
+        <v>430.2000122070312</v>
       </c>
       <c r="D206" t="n">
-        <v>413.25</v>
+        <v>420.5400085449219</v>
       </c>
       <c r="E206" t="n">
-        <v>415.6300048828125</v>
+        <v>425.3599853515625</v>
       </c>
       <c r="F206" t="n">
-        <v>5779800</v>
+        <v>3928800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>417.1099853515625</v>
+        <v>423.489990234375</v>
       </c>
       <c r="C207" t="n">
-        <v>428.0199890136719</v>
+        <v>424.4400024414062</v>
       </c>
       <c r="D207" t="n">
-        <v>413.7300109863281</v>
+        <v>415.0499877929688</v>
       </c>
       <c r="E207" t="n">
-        <v>426.5400085449219</v>
+        <v>417.989990234375</v>
       </c>
       <c r="F207" t="n">
-        <v>4985900</v>
+        <v>6379000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>428.1300048828125</v>
+        <v>423.9500122070312</v>
       </c>
       <c r="C208" t="n">
-        <v>430.2000122070312</v>
+        <v>428.6000061035156</v>
       </c>
       <c r="D208" t="n">
-        <v>420.5400085449219</v>
+        <v>422.1300048828125</v>
       </c>
       <c r="E208" t="n">
-        <v>425.3599853515625</v>
+        <v>428.1900024414062</v>
       </c>
       <c r="F208" t="n">
-        <v>3928800</v>
+        <v>5800500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>423.489990234375</v>
+        <v>427.1499938964844</v>
       </c>
       <c r="C209" t="n">
-        <v>424.4400024414062</v>
+        <v>430.7699890136719</v>
       </c>
       <c r="D209" t="n">
-        <v>415.0499877929688</v>
+        <v>423.8299865722656</v>
       </c>
       <c r="E209" t="n">
-        <v>417.989990234375</v>
+        <v>425.6000061035156</v>
       </c>
       <c r="F209" t="n">
-        <v>6379000</v>
+        <v>3859200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>423.9500122070312</v>
+        <v>427.1099853515625</v>
       </c>
       <c r="C210" t="n">
-        <v>428.6000061035156</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="D210" t="n">
-        <v>422.1300048828125</v>
+        <v>423.5199890136719</v>
       </c>
       <c r="E210" t="n">
-        <v>428.1900024414062</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="F210" t="n">
-        <v>5800500</v>
+        <v>5566000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>427.1499938964844</v>
+        <v>431.6700134277344</v>
       </c>
       <c r="C211" t="n">
-        <v>430.7699890136719</v>
+        <v>432.8599853515625</v>
       </c>
       <c r="D211" t="n">
-        <v>423.8299865722656</v>
+        <v>423.6499938964844</v>
       </c>
       <c r="E211" t="n">
-        <v>425.6000061035156</v>
+        <v>424.6199951171875</v>
       </c>
       <c r="F211" t="n">
-        <v>3859200</v>
+        <v>3798600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>427.1099853515625</v>
+        <v>426.4700012207031</v>
       </c>
       <c r="C212" t="n">
-        <v>434.2999877929688</v>
+        <v>431.5499877929688</v>
       </c>
       <c r="D212" t="n">
-        <v>423.5199890136719</v>
+        <v>425.5299987792969</v>
       </c>
       <c r="E212" t="n">
-        <v>431.6799926757812</v>
+        <v>429.0899963378906</v>
       </c>
       <c r="F212" t="n">
-        <v>5566000</v>
+        <v>3863800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>431.6700134277344</v>
+        <v>431</v>
       </c>
       <c r="C213" t="n">
-        <v>432.8599853515625</v>
+        <v>432.1499938964844</v>
       </c>
       <c r="D213" t="n">
-        <v>423.6499938964844</v>
+        <v>421.7900085449219</v>
       </c>
       <c r="E213" t="n">
-        <v>424.6199951171875</v>
+        <v>425.1900024414062</v>
       </c>
       <c r="F213" t="n">
-        <v>3798600</v>
+        <v>5135900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>426.4700012207031</v>
+        <v>419.489990234375</v>
       </c>
       <c r="C214" t="n">
-        <v>431.5499877929688</v>
+        <v>424.1099853515625</v>
       </c>
       <c r="D214" t="n">
-        <v>425.5299987792969</v>
+        <v>414.3699951171875</v>
       </c>
       <c r="E214" t="n">
-        <v>429.0899963378906</v>
+        <v>418.5199890136719</v>
       </c>
       <c r="F214" t="n">
-        <v>3863800</v>
+        <v>6764800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>431</v>
+        <v>449.3900146484375</v>
       </c>
       <c r="C215" t="n">
-        <v>432.1499938964844</v>
+        <v>461.6199951171875</v>
       </c>
       <c r="D215" t="n">
-        <v>421.7900085449219</v>
+        <v>420.3699951171875</v>
       </c>
       <c r="E215" t="n">
-        <v>425.1900024414062</v>
+        <v>423.3800048828125</v>
       </c>
       <c r="F215" t="n">
-        <v>5135900</v>
+        <v>13281900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>419.489990234375</v>
+        <v>426.7200012207031</v>
       </c>
       <c r="C216" t="n">
-        <v>424.1099853515625</v>
+        <v>437.4700012207031</v>
       </c>
       <c r="D216" t="n">
-        <v>414.3699951171875</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="E216" t="n">
-        <v>418.5199890136719</v>
+        <v>426.0899963378906</v>
       </c>
       <c r="F216" t="n">
-        <v>6764800</v>
+        <v>10718100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>449.3900146484375</v>
+        <v>427.25</v>
       </c>
       <c r="C217" t="n">
-        <v>461.6199951171875</v>
+        <v>431.0199890136719</v>
       </c>
       <c r="D217" t="n">
-        <v>420.3699951171875</v>
+        <v>417.3800048828125</v>
       </c>
       <c r="E217" t="n">
-        <v>423.3800048828125</v>
+        <v>421.5499877929688</v>
       </c>
       <c r="F217" t="n">
-        <v>13281900</v>
+        <v>4818800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>426.7200012207031</v>
+        <v>422.4800109863281</v>
       </c>
       <c r="C218" t="n">
-        <v>437.4700012207031</v>
+        <v>437</v>
       </c>
       <c r="D218" t="n">
-        <v>425.1000061035156</v>
+        <v>420.5</v>
       </c>
       <c r="E218" t="n">
-        <v>426.0899963378906</v>
+        <v>436.3500061035156</v>
       </c>
       <c r="F218" t="n">
-        <v>10718100</v>
+        <v>6833600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>427.25</v>
+        <v>434.9500122070312</v>
       </c>
       <c r="C219" t="n">
-        <v>431.0199890136719</v>
+        <v>436.3200073242188</v>
       </c>
       <c r="D219" t="n">
-        <v>417.3800048828125</v>
+        <v>429.7000122070312</v>
       </c>
       <c r="E219" t="n">
-        <v>421.5499877929688</v>
+        <v>431.3099975585938</v>
       </c>
       <c r="F219" t="n">
-        <v>4818800</v>
+        <v>4234100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>422.4800109863281</v>
+        <v>428.2699890136719</v>
       </c>
       <c r="C220" t="n">
-        <v>437</v>
+        <v>430.489990234375</v>
       </c>
       <c r="D220" t="n">
-        <v>420.5</v>
+        <v>420.3999938964844</v>
       </c>
       <c r="E220" t="n">
-        <v>436.3500061035156</v>
+        <v>423.5599975585938</v>
       </c>
       <c r="F220" t="n">
-        <v>6833600</v>
+        <v>4868700</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>434.9500122070312</v>
+        <v>425.239990234375</v>
       </c>
       <c r="C221" t="n">
-        <v>436.3200073242188</v>
+        <v>429</v>
       </c>
       <c r="D221" t="n">
-        <v>429.7000122070312</v>
+        <v>418.9200134277344</v>
       </c>
       <c r="E221" t="n">
-        <v>431.3099975585938</v>
+        <v>420.739990234375</v>
       </c>
       <c r="F221" t="n">
-        <v>4234100</v>
+        <v>3752500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>428.2699890136719</v>
+        <v>422.510009765625</v>
       </c>
       <c r="C222" t="n">
-        <v>430.489990234375</v>
+        <v>422.8800048828125</v>
       </c>
       <c r="D222" t="n">
-        <v>420.3999938964844</v>
+        <v>412.5400085449219</v>
       </c>
       <c r="E222" t="n">
-        <v>423.5599975585938</v>
+        <v>417.6400146484375</v>
       </c>
       <c r="F222" t="n">
-        <v>4868700</v>
+        <v>4615700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>425.239990234375</v>
+        <v>419.9299926757812</v>
       </c>
       <c r="C223" t="n">
-        <v>429</v>
+        <v>430.4599914550781</v>
       </c>
       <c r="D223" t="n">
-        <v>418.9200134277344</v>
+        <v>415.1099853515625</v>
       </c>
       <c r="E223" t="n">
-        <v>420.739990234375</v>
+        <v>428.7900085449219</v>
       </c>
       <c r="F223" t="n">
-        <v>3752500</v>
+        <v>5917300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>422.510009765625</v>
+        <v>428.260009765625</v>
       </c>
       <c r="C224" t="n">
-        <v>422.8800048828125</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="D224" t="n">
-        <v>412.5400085449219</v>
+        <v>420.3500061035156</v>
       </c>
       <c r="E224" t="n">
-        <v>417.6400146484375</v>
+        <v>420.5700073242188</v>
       </c>
       <c r="F224" t="n">
-        <v>4615700</v>
+        <v>5257900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>419.9299926757812</v>
+        <v>415.1900024414062</v>
       </c>
       <c r="C225" t="n">
-        <v>430.4599914550781</v>
+        <v>427.3399963378906</v>
       </c>
       <c r="D225" t="n">
-        <v>415.1099853515625</v>
+        <v>411.2900085449219</v>
       </c>
       <c r="E225" t="n">
-        <v>428.7900085449219</v>
+        <v>421.4700012207031</v>
       </c>
       <c r="F225" t="n">
-        <v>5917300</v>
+        <v>3647500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>428.260009765625</v>
+        <v>422</v>
       </c>
       <c r="C226" t="n">
-        <v>431.6799926757812</v>
+        <v>422.8099975585938</v>
       </c>
       <c r="D226" t="n">
-        <v>420.3500061035156</v>
+        <v>414.0599975585938</v>
       </c>
       <c r="E226" t="n">
-        <v>420.5700073242188</v>
+        <v>414.3999938964844</v>
       </c>
       <c r="F226" t="n">
-        <v>5257900</v>
+        <v>3920900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>415.1900024414062</v>
+        <v>417.4299926757812</v>
       </c>
       <c r="C227" t="n">
-        <v>427.3399963378906</v>
+        <v>419.3399963378906</v>
       </c>
       <c r="D227" t="n">
-        <v>411.2900085449219</v>
+        <v>413.3200073242188</v>
       </c>
       <c r="E227" t="n">
-        <v>421.4700012207031</v>
+        <v>415.3599853515625</v>
       </c>
       <c r="F227" t="n">
-        <v>3647500</v>
+        <v>3209600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>422</v>
+        <v>415.5599975585938</v>
       </c>
       <c r="C228" t="n">
-        <v>422.8099975585938</v>
+        <v>416</v>
       </c>
       <c r="D228" t="n">
-        <v>414.0599975585938</v>
+        <v>406.6700134277344</v>
       </c>
       <c r="E228" t="n">
-        <v>414.3999938964844</v>
+        <v>407.5499877929688</v>
       </c>
       <c r="F228" t="n">
-        <v>3920900</v>
+        <v>5266300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>417.4299926757812</v>
+        <v>403.1900024414062</v>
       </c>
       <c r="C229" t="n">
-        <v>419.3399963378906</v>
+        <v>416.3599853515625</v>
       </c>
       <c r="D229" t="n">
-        <v>413.3200073242188</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="E229" t="n">
-        <v>415.3599853515625</v>
+        <v>412.75</v>
       </c>
       <c r="F229" t="n">
-        <v>3209600</v>
+        <v>5399000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>415.5599975585938</v>
+        <v>415.2699890136719</v>
       </c>
       <c r="C230" t="n">
-        <v>416</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="D230" t="n">
-        <v>406.6700134277344</v>
+        <v>402.3999938964844</v>
       </c>
       <c r="E230" t="n">
-        <v>407.5499877929688</v>
+        <v>403.9700012207031</v>
       </c>
       <c r="F230" t="n">
-        <v>5266300</v>
+        <v>4712400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>403.1900024414062</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="C231" t="n">
-        <v>416.3599853515625</v>
+        <v>410.6400146484375</v>
       </c>
       <c r="D231" t="n">
-        <v>397.7999877929688</v>
+        <v>400.6600036621094</v>
       </c>
       <c r="E231" t="n">
-        <v>412.75</v>
+        <v>407.0799865722656</v>
       </c>
       <c r="F231" t="n">
-        <v>5399000</v>
+        <v>4095900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>415.2699890136719</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="C232" t="n">
-        <v>416.9700012207031</v>
+        <v>413.0700073242188</v>
       </c>
       <c r="D232" t="n">
-        <v>402.3999938964844</v>
+        <v>407.989990234375</v>
       </c>
       <c r="E232" t="n">
-        <v>403.9700012207031</v>
+        <v>408.739990234375</v>
       </c>
       <c r="F232" t="n">
-        <v>4712400</v>
+        <v>3182200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>401.5899963378906</v>
+        <v>409</v>
       </c>
       <c r="C233" t="n">
-        <v>410.6400146484375</v>
+        <v>410.8999938964844</v>
       </c>
       <c r="D233" t="n">
-        <v>400.6600036621094</v>
+        <v>401.3200073242188</v>
       </c>
       <c r="E233" t="n">
-        <v>407.0799865722656</v>
+        <v>402.1900024414062</v>
       </c>
       <c r="F233" t="n">
-        <v>4095900</v>
+        <v>3398900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>408.6000061035156</v>
+        <v>400.9800109863281</v>
       </c>
       <c r="C234" t="n">
-        <v>413.0700073242188</v>
+        <v>407.2000122070312</v>
       </c>
       <c r="D234" t="n">
-        <v>407.989990234375</v>
+        <v>400.5</v>
       </c>
       <c r="E234" t="n">
-        <v>408.739990234375</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="F234" t="n">
-        <v>3182200</v>
+        <v>3317200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>409</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="C235" t="n">
-        <v>410.8999938964844</v>
+        <v>407.3200073242188</v>
       </c>
       <c r="D235" t="n">
-        <v>401.3200073242188</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E235" t="n">
-        <v>402.1900024414062</v>
+        <v>399.0599975585938</v>
       </c>
       <c r="F235" t="n">
-        <v>3398900</v>
+        <v>4170200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>400.9800109863281</v>
+        <v>398</v>
       </c>
       <c r="C236" t="n">
-        <v>407.2000122070312</v>
+        <v>403.1799926757812</v>
       </c>
       <c r="D236" t="n">
-        <v>400.5</v>
+        <v>396.5599975585938</v>
       </c>
       <c r="E236" t="n">
-        <v>405.5899963378906</v>
+        <v>401.7300109863281</v>
       </c>
       <c r="F236" t="n">
-        <v>3317200</v>
+        <v>3476400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>405.5899963378906</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C237" t="n">
-        <v>407.3200073242188</v>
+        <v>398.8999938964844</v>
       </c>
       <c r="D237" t="n">
-        <v>398.5899963378906</v>
+        <v>391.4299926757812</v>
       </c>
       <c r="E237" t="n">
-        <v>399.0599975585938</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="F237" t="n">
-        <v>4170200</v>
+        <v>5295100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>398</v>
+        <v>397.4299926757812</v>
       </c>
       <c r="C238" t="n">
-        <v>403.1799926757812</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="D238" t="n">
-        <v>396.5599975585938</v>
+        <v>393.510009765625</v>
       </c>
       <c r="E238" t="n">
-        <v>401.7300109863281</v>
+        <v>393.9299926757812</v>
       </c>
       <c r="F238" t="n">
-        <v>3476400</v>
+        <v>3605100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>398.5700073242188</v>
+        <v>394.5700073242188</v>
       </c>
       <c r="C239" t="n">
-        <v>398.8999938964844</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="D239" t="n">
-        <v>391.4299926757812</v>
+        <v>386.3299865722656</v>
       </c>
       <c r="E239" t="n">
-        <v>395.6199951171875</v>
+        <v>388.6099853515625</v>
       </c>
       <c r="F239" t="n">
-        <v>5295100</v>
+        <v>5268500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>397.4299926757812</v>
+        <v>388.25</v>
       </c>
       <c r="C240" t="n">
-        <v>398.7900085449219</v>
+        <v>392.7099914550781</v>
       </c>
       <c r="D240" t="n">
-        <v>393.510009765625</v>
+        <v>383.8299865722656</v>
       </c>
       <c r="E240" t="n">
-        <v>393.9299926757812</v>
+        <v>384.8500061035156</v>
       </c>
       <c r="F240" t="n">
-        <v>3605100</v>
+        <v>4497200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>394.5700073242188</v>
+        <v>386</v>
       </c>
       <c r="C241" t="n">
-        <v>396.7999877929688</v>
+        <v>393.6600036621094</v>
       </c>
       <c r="D241" t="n">
-        <v>386.3299865722656</v>
+        <v>386</v>
       </c>
       <c r="E241" t="n">
-        <v>388.6099853515625</v>
+        <v>390.1099853515625</v>
       </c>
       <c r="F241" t="n">
-        <v>5268500</v>
+        <v>4879600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>388.25</v>
+        <v>391.0400085449219</v>
       </c>
       <c r="C242" t="n">
-        <v>392.7099914550781</v>
+        <v>399.5799865722656</v>
       </c>
       <c r="D242" t="n">
-        <v>383.8299865722656</v>
+        <v>390.8599853515625</v>
       </c>
       <c r="E242" t="n">
-        <v>384.8500061035156</v>
+        <v>398.760009765625</v>
       </c>
       <c r="F242" t="n">
-        <v>4497200</v>
+        <v>4683900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>386</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="C243" t="n">
-        <v>393.6600036621094</v>
+        <v>399.0299987792969</v>
       </c>
       <c r="D243" t="n">
-        <v>386</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="E243" t="n">
-        <v>390.1099853515625</v>
+        <v>396.5899963378906</v>
       </c>
       <c r="F243" t="n">
-        <v>4879600</v>
+        <v>2655000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>391.0400085449219</v>
+        <v>396.3299865722656</v>
       </c>
       <c r="C244" t="n">
-        <v>399.5799865722656</v>
+        <v>406.25</v>
       </c>
       <c r="D244" t="n">
-        <v>390.8599853515625</v>
+        <v>396.010009765625</v>
       </c>
       <c r="E244" t="n">
-        <v>398.760009765625</v>
+        <v>401.010009765625</v>
       </c>
       <c r="F244" t="n">
-        <v>4683900</v>
+        <v>3557000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>397.7999877929688</v>
+        <v>396.8699951171875</v>
       </c>
       <c r="C245" t="n">
-        <v>399.0299987792969</v>
+        <v>399.8800048828125</v>
       </c>
       <c r="D245" t="n">
-        <v>395.6199951171875</v>
+        <v>393.7699890136719</v>
       </c>
       <c r="E245" t="n">
-        <v>396.5899963378906</v>
+        <v>395.0499877929688</v>
       </c>
       <c r="F245" t="n">
-        <v>2655000</v>
+        <v>3668200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>396.3299865722656</v>
+        <v>396.4200134277344</v>
       </c>
       <c r="C246" t="n">
-        <v>406.25</v>
+        <v>396.739990234375</v>
       </c>
       <c r="D246" t="n">
-        <v>396.010009765625</v>
+        <v>392.6600036621094</v>
       </c>
       <c r="E246" t="n">
-        <v>401.010009765625</v>
+        <v>392.9500122070312</v>
       </c>
       <c r="F246" t="n">
-        <v>3557000</v>
+        <v>2455500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>396.8699951171875</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="C247" t="n">
-        <v>399.8800048828125</v>
+        <v>394.489990234375</v>
       </c>
       <c r="D247" t="n">
-        <v>393.7699890136719</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="E247" t="n">
-        <v>395.0499877929688</v>
+        <v>389.4100036621094</v>
       </c>
       <c r="F247" t="n">
-        <v>3668200</v>
+        <v>5748000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>396.4200134277344</v>
+        <v>392.0799865722656</v>
       </c>
       <c r="C248" t="n">
-        <v>396.739990234375</v>
+        <v>399.6000061035156</v>
       </c>
       <c r="D248" t="n">
-        <v>392.6600036621094</v>
+        <v>391.7799987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>392.9500122070312</v>
+        <v>396.2999877929688</v>
       </c>
       <c r="F248" t="n">
-        <v>2455500</v>
+        <v>3716200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>393.5199890136719</v>
+        <v>399.2699890136719</v>
       </c>
       <c r="C249" t="n">
-        <v>394.489990234375</v>
+        <v>401.1400146484375</v>
       </c>
       <c r="D249" t="n">
-        <v>387.7099914550781</v>
+        <v>396.510009765625</v>
       </c>
       <c r="E249" t="n">
-        <v>389.4100036621094</v>
+        <v>399.6600036621094</v>
       </c>
       <c r="F249" t="n">
-        <v>5748000</v>
+        <v>3265300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>392.0799865722656</v>
+        <v>400.0199890136719</v>
       </c>
       <c r="C250" t="n">
-        <v>399.6000061035156</v>
+        <v>405.1600036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>391.7799987792969</v>
+        <v>395.2999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>396.2999877929688</v>
+        <v>400.9400024414062</v>
       </c>
       <c r="F250" t="n">
-        <v>3716200</v>
+        <v>5488900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>399.2699890136719</v>
+        <v>397.0499877929688</v>
       </c>
       <c r="C251" t="n">
-        <v>401.1400146484375</v>
+        <v>402.2300109863281</v>
       </c>
       <c r="D251" t="n">
-        <v>396.510009765625</v>
+        <v>395.2000122070312</v>
       </c>
       <c r="E251" t="n">
-        <v>399.6600036621094</v>
+        <v>397.1400146484375</v>
       </c>
       <c r="F251" t="n">
-        <v>3265300</v>
+        <v>5565400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>400.0199890136719</v>
-      </c>
-      <c r="C252" t="n">
-        <v>405.1600036621094</v>
-      </c>
-      <c r="D252" t="n">
-        <v>395.2999877929688</v>
-      </c>
-      <c r="E252" t="n">
-        <v>400.9400024414062</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>5488900</v>
+        <v>5545894</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>397.0499877929688</v>
-      </c>
-      <c r="C253" t="n">
-        <v>402.2300109863281</v>
-      </c>
-      <c r="D253" t="n">
-        <v>395.2000122070312</v>
-      </c>
-      <c r="E253" t="n">
-        <v>397.1400146484375</v>
-      </c>
-      <c r="F253" t="n">
-        <v>5565400</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10556,34 +10522,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>400.84</v>
+      </c>
+      <c r="D2" t="n">
         <v>397.14</v>
       </c>
-      <c r="D2" t="n">
-        <v>400.94</v>
-      </c>
       <c r="E2" t="n">
-        <v>397.05</v>
+        <v>392.4</v>
       </c>
       <c r="F2" t="n">
-        <v>402.225</v>
+        <v>403.7992</v>
       </c>
       <c r="G2" t="n">
-        <v>395.23</v>
+        <v>390.555</v>
       </c>
       <c r="H2" t="n">
-        <v>4826351</v>
+        <v>5545894</v>
       </c>
       <c r="I2" t="n">
-        <v>5349722</v>
+        <v>5323698</v>
       </c>
       <c r="J2" t="n">
-        <v>356470816768</v>
+        <v>359791919104</v>
       </c>
       <c r="K2" t="n">
-        <v>25.506744</v>
+        <v>25.74438</v>
       </c>
       <c r="L2" t="n">
-        <v>17.701515</v>
+        <v>17.866432</v>
       </c>
       <c r="M2" t="n">
         <v>15.57</v>
@@ -10622,7 +10588,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.6508217</v>
+        <v>3.6848347</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10634,7 +10600,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>405832826880</v>
+        <v>409153929216</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10661,7 +10627,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:31</t>
+          <t>2026-09-09 09:15:28</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>323.8273433349329</v>
+        <v>336.5466531982527</v>
       </c>
       <c r="C2" t="n">
-        <v>342.5362771646614</v>
+        <v>339.4781519824642</v>
       </c>
       <c r="D2" t="n">
-        <v>318.6266310717227</v>
+        <v>332.4951561509477</v>
       </c>
       <c r="E2" t="n">
-        <v>338.8451538085938</v>
+        <v>337.7348327636719</v>
       </c>
       <c r="F2" t="n">
-        <v>46408900</v>
+        <v>17804300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>336.5466531982527</v>
+        <v>339.8969161546314</v>
       </c>
       <c r="C3" t="n">
-        <v>339.4781519824642</v>
+        <v>351.5644485034896</v>
       </c>
       <c r="D3" t="n">
-        <v>332.4951561509477</v>
+        <v>336.8193359260115</v>
       </c>
       <c r="E3" t="n">
-        <v>337.7348327636719</v>
+        <v>344.3866577148438</v>
       </c>
       <c r="F3" t="n">
-        <v>17804300</v>
+        <v>18943500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>339.8969462743543</v>
+        <v>346.6169614598537</v>
       </c>
       <c r="C4" t="n">
-        <v>351.5644796571226</v>
+        <v>352.8597713233265</v>
       </c>
       <c r="D4" t="n">
-        <v>336.8193657730168</v>
+        <v>343.2666855000246</v>
       </c>
       <c r="E4" t="n">
-        <v>344.3866882324219</v>
+        <v>343.3153991699219</v>
       </c>
       <c r="F4" t="n">
-        <v>18943500</v>
+        <v>14016200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>346.6169614598537</v>
+        <v>344.2562617205344</v>
       </c>
       <c r="C5" t="n">
-        <v>352.8597713233265</v>
+        <v>344.6972712574788</v>
       </c>
       <c r="D5" t="n">
-        <v>343.2666855000246</v>
+        <v>335.7003177947291</v>
       </c>
       <c r="E5" t="n">
-        <v>343.3153991699219</v>
+        <v>340.9534606933594</v>
       </c>
       <c r="F5" t="n">
-        <v>14016200</v>
+        <v>11035900</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,25 +573,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>344.2562617205344</v>
+        <v>340.5711991051483</v>
       </c>
       <c r="C6" t="n">
-        <v>344.6972712574788</v>
+        <v>342.0805014268064</v>
       </c>
       <c r="D6" t="n">
-        <v>335.7003177947291</v>
+        <v>331.5742462609258</v>
       </c>
       <c r="E6" t="n">
-        <v>340.9534606933594</v>
+        <v>333.005126953125</v>
       </c>
       <c r="F6" t="n">
-        <v>11035900</v>
+        <v>12695800</v>
       </c>
       <c r="G6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>340.5711991051483</v>
+        <v>330.9568525731296</v>
       </c>
       <c r="C7" t="n">
-        <v>342.0805014268064</v>
+        <v>336.1609748937723</v>
       </c>
       <c r="D7" t="n">
-        <v>331.5742462609258</v>
+        <v>330.9568525731296</v>
       </c>
       <c r="E7" t="n">
-        <v>333.005126953125</v>
+        <v>334.7986755371094</v>
       </c>
       <c r="F7" t="n">
-        <v>12695800</v>
+        <v>8467700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>330.9568224057415</v>
+        <v>336.6803662104043</v>
       </c>
       <c r="C8" t="n">
-        <v>336.1609442520178</v>
+        <v>338.0524456778033</v>
       </c>
       <c r="D8" t="n">
-        <v>330.9568224057415</v>
+        <v>327.4579882805058</v>
       </c>
       <c r="E8" t="n">
-        <v>334.7986450195312</v>
+        <v>328.14404296875</v>
       </c>
       <c r="F8" t="n">
-        <v>8467700</v>
+        <v>11255600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>336.6803662104043</v>
+        <v>329.7905316198508</v>
       </c>
       <c r="C9" t="n">
-        <v>338.0524456778033</v>
+        <v>334.161595373165</v>
       </c>
       <c r="D9" t="n">
-        <v>327.4579882805058</v>
+        <v>327.1835657302883</v>
       </c>
       <c r="E9" t="n">
-        <v>328.14404296875</v>
+        <v>329.9767456054688</v>
       </c>
       <c r="F9" t="n">
-        <v>11255600</v>
+        <v>13656800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>329.7905316198508</v>
+        <v>327.7911982671105</v>
       </c>
       <c r="C10" t="n">
-        <v>334.161595373165</v>
+        <v>335.6513067387905</v>
       </c>
       <c r="D10" t="n">
-        <v>327.1835657302883</v>
+        <v>325.9682991379935</v>
       </c>
       <c r="E10" t="n">
-        <v>329.9767456054688</v>
+        <v>334.4948120117188</v>
       </c>
       <c r="F10" t="n">
-        <v>13656800</v>
+        <v>8903700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>327.7912281730855</v>
+        <v>334.2008052062361</v>
       </c>
       <c r="C11" t="n">
-        <v>335.6513373618812</v>
+        <v>345.6675310141911</v>
       </c>
       <c r="D11" t="n">
-        <v>325.9683288776566</v>
+        <v>333.1815333788629</v>
       </c>
       <c r="E11" t="n">
-        <v>334.4948425292969</v>
+        <v>340.7574157714844</v>
       </c>
       <c r="F11" t="n">
-        <v>8903700</v>
+        <v>12504100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>334.2008052062361</v>
+        <v>343.2174040946968</v>
       </c>
       <c r="C12" t="n">
-        <v>345.6675310141911</v>
+        <v>347.4316547985749</v>
       </c>
       <c r="D12" t="n">
-        <v>333.1815333788629</v>
+        <v>340.904444380264</v>
       </c>
       <c r="E12" t="n">
-        <v>340.7574157714844</v>
+        <v>344.7952880859375</v>
       </c>
       <c r="F12" t="n">
-        <v>12504100</v>
+        <v>9016300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>343.2174040946968</v>
+        <v>341.9432916493518</v>
       </c>
       <c r="C13" t="n">
-        <v>347.4316547985749</v>
+        <v>343.2075787683629</v>
       </c>
       <c r="D13" t="n">
-        <v>340.904444380264</v>
+        <v>336.7489800892123</v>
       </c>
       <c r="E13" t="n">
-        <v>344.7952880859375</v>
+        <v>338.6698913574219</v>
       </c>
       <c r="F13" t="n">
-        <v>9016300</v>
+        <v>8104900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>341.9432916493518</v>
+        <v>340.9926010114185</v>
       </c>
       <c r="C14" t="n">
-        <v>343.2075787683629</v>
+        <v>342.9919337348455</v>
       </c>
       <c r="D14" t="n">
-        <v>336.7489800892123</v>
+        <v>334.4947920920956</v>
       </c>
       <c r="E14" t="n">
-        <v>338.6698913574219</v>
+        <v>337.2193603515625</v>
       </c>
       <c r="F14" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>340.9926318704661</v>
+        <v>337.1213995584671</v>
       </c>
       <c r="C15" t="n">
-        <v>342.9919647748283</v>
+        <v>338.6600726249961</v>
       </c>
       <c r="D15" t="n">
-        <v>334.4948223631065</v>
+        <v>334.6418463806178</v>
       </c>
       <c r="E15" t="n">
-        <v>337.2193908691406</v>
+        <v>338.2974548339844</v>
       </c>
       <c r="F15" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>337.1214299699541</v>
+        <v>336.8959869118207</v>
       </c>
       <c r="C16" t="n">
-        <v>338.6601031752857</v>
+        <v>342.3549341542898</v>
       </c>
       <c r="D16" t="n">
-        <v>334.641876568426</v>
+        <v>335.5042870567964</v>
       </c>
       <c r="E16" t="n">
-        <v>338.2974853515625</v>
+        <v>338.4150695800781</v>
       </c>
       <c r="F16" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>336.8959565312304</v>
+        <v>337.042992446128</v>
       </c>
       <c r="C17" t="n">
-        <v>342.3549032814228</v>
+        <v>341.7473034781017</v>
       </c>
       <c r="D17" t="n">
-        <v>335.5042568017067</v>
+        <v>334.8182646079004</v>
       </c>
       <c r="E17" t="n">
-        <v>338.4150390625</v>
+        <v>341.3552551269531</v>
       </c>
       <c r="F17" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>337.042992446128</v>
+        <v>340.3654202552976</v>
       </c>
       <c r="C18" t="n">
-        <v>341.7473034781017</v>
+        <v>348.0000745206634</v>
       </c>
       <c r="D18" t="n">
-        <v>334.8182646079004</v>
+        <v>337.7780446522378</v>
       </c>
       <c r="E18" t="n">
-        <v>341.3552551269531</v>
+        <v>346.6672058105469</v>
       </c>
       <c r="F18" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>340.3653902924742</v>
+        <v>350.126813283771</v>
       </c>
       <c r="C19" t="n">
-        <v>348.000043885751</v>
+        <v>360.6624696666976</v>
       </c>
       <c r="D19" t="n">
-        <v>337.7780149171845</v>
+        <v>349.4995598497266</v>
       </c>
       <c r="E19" t="n">
-        <v>346.6671752929688</v>
+        <v>353.0180053710938</v>
       </c>
       <c r="F19" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>350.1267830161296</v>
+        <v>353.8314330983794</v>
       </c>
       <c r="C20" t="n">
-        <v>360.6624384882734</v>
+        <v>355.2917144647868</v>
       </c>
       <c r="D20" t="n">
-        <v>349.4995296363098</v>
+        <v>349.9895806938981</v>
       </c>
       <c r="E20" t="n">
-        <v>353.0179748535156</v>
+        <v>351.6164855957031</v>
       </c>
       <c r="F20" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>353.8314330983794</v>
+        <v>352.2437372182849</v>
       </c>
       <c r="C21" t="n">
-        <v>355.2917144647868</v>
+        <v>357.4478588776738</v>
       </c>
       <c r="D21" t="n">
-        <v>349.9895806938981</v>
+        <v>350.9206488503359</v>
       </c>
       <c r="E21" t="n">
-        <v>351.6164855957031</v>
+        <v>356.4089965820312</v>
       </c>
       <c r="F21" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>352.2437372182849</v>
+        <v>359.613786634634</v>
       </c>
       <c r="C22" t="n">
-        <v>357.4478588776738</v>
+        <v>367.1602685308417</v>
       </c>
       <c r="D22" t="n">
-        <v>350.9206488503359</v>
+        <v>358.5063128850491</v>
       </c>
       <c r="E22" t="n">
-        <v>356.4089965820312</v>
+        <v>362.544189453125</v>
       </c>
       <c r="F22" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>359.613786634634</v>
+        <v>365.0923241938757</v>
       </c>
       <c r="C23" t="n">
-        <v>367.1602685308417</v>
+        <v>368.7185619691624</v>
       </c>
       <c r="D23" t="n">
-        <v>358.5063128850491</v>
+        <v>358.7807287668154</v>
       </c>
       <c r="E23" t="n">
-        <v>362.544189453125</v>
+        <v>360.358642578125</v>
       </c>
       <c r="F23" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>365.0923241938757</v>
+        <v>362.0345124206696</v>
       </c>
       <c r="C24" t="n">
-        <v>368.7185619691624</v>
+        <v>362.0345124206696</v>
       </c>
       <c r="D24" t="n">
-        <v>358.7807287668154</v>
+        <v>345.481298369123</v>
       </c>
       <c r="E24" t="n">
-        <v>360.358642578125</v>
+        <v>347.4316101074219</v>
       </c>
       <c r="F24" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>362.0345124206696</v>
+        <v>347.6668450586018</v>
       </c>
       <c r="C25" t="n">
-        <v>362.0345124206696</v>
+        <v>351.9987280315978</v>
       </c>
       <c r="D25" t="n">
-        <v>345.481298369123</v>
+        <v>346.2751751256885</v>
       </c>
       <c r="E25" t="n">
-        <v>347.4316101074219</v>
+        <v>351.5086975097656</v>
       </c>
       <c r="F25" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>347.6668450586018</v>
+        <v>347.8726721794402</v>
       </c>
       <c r="C26" t="n">
-        <v>351.9987280315978</v>
+        <v>355.1054974076654</v>
       </c>
       <c r="D26" t="n">
-        <v>346.2751751256885</v>
+        <v>346.3535596478916</v>
       </c>
       <c r="E26" t="n">
-        <v>351.5086975097656</v>
+        <v>352.7533569335938</v>
       </c>
       <c r="F26" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>347.872702274778</v>
+        <v>352.224118197926</v>
       </c>
       <c r="C27" t="n">
-        <v>355.1055281287331</v>
+        <v>356.9577994132716</v>
       </c>
       <c r="D27" t="n">
-        <v>346.3535896118073</v>
+        <v>348.7546940700243</v>
       </c>
       <c r="E27" t="n">
-        <v>352.7533874511719</v>
+        <v>353.9490051269531</v>
       </c>
       <c r="F27" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>352.2241485667839</v>
+        <v>354.6252788942206</v>
       </c>
       <c r="C28" t="n">
-        <v>356.9578301902687</v>
+        <v>354.7820922478407</v>
       </c>
       <c r="D28" t="n">
-        <v>348.7547241397475</v>
+        <v>347.3336224508748</v>
       </c>
       <c r="E28" t="n">
-        <v>353.9490356445312</v>
+        <v>349.5583801269531</v>
       </c>
       <c r="F28" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>354.6252788942206</v>
+        <v>344.0014287463771</v>
       </c>
       <c r="C29" t="n">
-        <v>354.7820922478407</v>
+        <v>351.2440942663747</v>
       </c>
       <c r="D29" t="n">
-        <v>347.3336224508748</v>
+        <v>343.8348052077826</v>
       </c>
       <c r="E29" t="n">
-        <v>349.5583801269531</v>
+        <v>349.4897766113281</v>
       </c>
       <c r="F29" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>344.0014287463771</v>
+        <v>351.3911117321571</v>
       </c>
       <c r="C30" t="n">
-        <v>351.2440942663747</v>
+        <v>358.2809400014152</v>
       </c>
       <c r="D30" t="n">
-        <v>343.8348052077826</v>
+        <v>350.3816500053927</v>
       </c>
       <c r="E30" t="n">
-        <v>349.4897766113281</v>
+        <v>357.2126770019531</v>
       </c>
       <c r="F30" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>351.3911117321571</v>
+        <v>357.8595050033854</v>
       </c>
       <c r="C31" t="n">
-        <v>358.2809400014152</v>
+        <v>363.6516394702736</v>
       </c>
       <c r="D31" t="n">
-        <v>350.3816500053927</v>
+        <v>354.2920684364863</v>
       </c>
       <c r="E31" t="n">
-        <v>357.2126770019531</v>
+        <v>358.0848999023438</v>
       </c>
       <c r="F31" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>357.8594745050165</v>
+        <v>356.7029783280342</v>
       </c>
       <c r="C32" t="n">
-        <v>363.6516084782733</v>
+        <v>356.7421891409456</v>
       </c>
       <c r="D32" t="n">
-        <v>354.2920382421501</v>
+        <v>350.8618233858751</v>
       </c>
       <c r="E32" t="n">
-        <v>358.0848693847656</v>
+        <v>354.2822265625</v>
       </c>
       <c r="F32" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>356.7029783280342</v>
+        <v>348.4900782801277</v>
       </c>
       <c r="C33" t="n">
-        <v>356.7421891409456</v>
+        <v>355.0564989637384</v>
       </c>
       <c r="D33" t="n">
-        <v>350.8618233858751</v>
+        <v>346.588787450705</v>
       </c>
       <c r="E33" t="n">
-        <v>354.2822265625</v>
+        <v>353.2630004882812</v>
       </c>
       <c r="F33" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>348.4901083853841</v>
+        <v>354.1646514889598</v>
       </c>
       <c r="C34" t="n">
-        <v>355.0565296362527</v>
+        <v>358.1339166267961</v>
       </c>
       <c r="D34" t="n">
-        <v>346.5888173917132</v>
+        <v>352.8513732909411</v>
       </c>
       <c r="E34" t="n">
-        <v>353.2630310058594</v>
+        <v>355.2721252441406</v>
       </c>
       <c r="F34" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>354.1646514889598</v>
+        <v>356.2521771853968</v>
       </c>
       <c r="C35" t="n">
-        <v>358.1339166267961</v>
+        <v>358.9179443293374</v>
       </c>
       <c r="D35" t="n">
-        <v>352.8513732909411</v>
+        <v>354.194043082288</v>
       </c>
       <c r="E35" t="n">
-        <v>355.2721252441406</v>
+        <v>358.6827392578125</v>
       </c>
       <c r="F35" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>356.2521771853968</v>
+        <v>373.0896257903608</v>
       </c>
       <c r="C36" t="n">
-        <v>358.9179443293374</v>
+        <v>373.4032524981995</v>
       </c>
       <c r="D36" t="n">
-        <v>354.194043082288</v>
+        <v>351.4792920385495</v>
       </c>
       <c r="E36" t="n">
-        <v>358.6827392578125</v>
+        <v>360.5056457519531</v>
       </c>
       <c r="F36" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>373.0896573731999</v>
+        <v>357.0166226761716</v>
       </c>
       <c r="C37" t="n">
-        <v>373.4032841075878</v>
+        <v>358.8493319750526</v>
       </c>
       <c r="D37" t="n">
-        <v>351.4793217920273</v>
+        <v>346.8239941782638</v>
       </c>
       <c r="E37" t="n">
-        <v>360.5056762695312</v>
+        <v>348.1764831542969</v>
       </c>
       <c r="F37" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>357.0166539685856</v>
+        <v>340.5908266262187</v>
       </c>
       <c r="C38" t="n">
-        <v>358.8493634281032</v>
+        <v>347.4708747692525</v>
       </c>
       <c r="D38" t="n">
-        <v>346.8240245772966</v>
+        <v>336.7490038190758</v>
       </c>
       <c r="E38" t="n">
-        <v>348.176513671875</v>
+        <v>337.8760681152344</v>
       </c>
       <c r="F38" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>340.5908266262187</v>
+        <v>337.5232231766179</v>
       </c>
       <c r="C39" t="n">
-        <v>347.4708747692525</v>
+        <v>339.3755229195461</v>
       </c>
       <c r="D39" t="n">
-        <v>336.7490038190758</v>
+        <v>330.398160543053</v>
       </c>
       <c r="E39" t="n">
-        <v>337.8760681152344</v>
+        <v>334.7496337890625</v>
       </c>
       <c r="F39" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>337.5232231766179</v>
+        <v>332.3681048776954</v>
       </c>
       <c r="C40" t="n">
-        <v>339.3755229195461</v>
+        <v>333.9068078868114</v>
       </c>
       <c r="D40" t="n">
-        <v>330.398160543053</v>
+        <v>320.0879412577473</v>
       </c>
       <c r="E40" t="n">
-        <v>334.7496337890625</v>
+        <v>327.1345825195312</v>
       </c>
       <c r="F40" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>332.3681048776954</v>
+        <v>321.0974041522996</v>
       </c>
       <c r="C41" t="n">
-        <v>333.9068078868114</v>
+        <v>329.7905408141606</v>
       </c>
       <c r="D41" t="n">
-        <v>320.0879412577473</v>
+        <v>320.6759850821896</v>
       </c>
       <c r="E41" t="n">
-        <v>327.1345825195312</v>
+        <v>324.2335815429688</v>
       </c>
       <c r="F41" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>321.0974041522996</v>
+        <v>319.7939098851405</v>
       </c>
       <c r="C42" t="n">
-        <v>329.7905408141606</v>
+        <v>323.6259521945154</v>
       </c>
       <c r="D42" t="n">
-        <v>320.6759850821896</v>
+        <v>317.7553960532753</v>
       </c>
       <c r="E42" t="n">
-        <v>324.2335815429688</v>
+        <v>321.2052001953125</v>
       </c>
       <c r="F42" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>319.7938795016485</v>
+        <v>322.3616713627413</v>
       </c>
       <c r="C43" t="n">
-        <v>323.6259214469426</v>
+        <v>325.7428638052234</v>
       </c>
       <c r="D43" t="n">
-        <v>317.7553658634617</v>
+        <v>315.0406146307628</v>
       </c>
       <c r="E43" t="n">
-        <v>321.2051696777344</v>
+        <v>315.1484069824219</v>
       </c>
       <c r="F43" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>322.3616713627413</v>
+        <v>313.2863092733651</v>
       </c>
       <c r="C44" t="n">
-        <v>325.7428638052234</v>
+        <v>318.0787921089143</v>
       </c>
       <c r="D44" t="n">
-        <v>315.0406146307628</v>
+        <v>307.8959736628304</v>
       </c>
       <c r="E44" t="n">
-        <v>315.1484069824219</v>
+        <v>317.7455749511719</v>
       </c>
       <c r="F44" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>313.2863393626572</v>
+        <v>313.6097058862107</v>
       </c>
       <c r="C45" t="n">
-        <v>318.0788226584959</v>
+        <v>317.7847752647608</v>
       </c>
       <c r="D45" t="n">
-        <v>307.8960032344128</v>
+        <v>310.8459566317771</v>
       </c>
       <c r="E45" t="n">
-        <v>317.74560546875</v>
+        <v>315.1679992675781</v>
       </c>
       <c r="F45" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>313.6097058862107</v>
+        <v>316.8537128676349</v>
       </c>
       <c r="C46" t="n">
-        <v>317.7847752647608</v>
+        <v>321.3227886847148</v>
       </c>
       <c r="D46" t="n">
-        <v>310.8459566317771</v>
+        <v>313.5019209593692</v>
       </c>
       <c r="E46" t="n">
-        <v>315.1679992675781</v>
+        <v>320.9209899902344</v>
       </c>
       <c r="F46" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>316.8537429984404</v>
+        <v>321.9010364932658</v>
       </c>
       <c r="C47" t="n">
-        <v>321.3228192405015</v>
+        <v>336.3275351202159</v>
       </c>
       <c r="D47" t="n">
-        <v>313.5019507714403</v>
+        <v>320.5583278451826</v>
       </c>
       <c r="E47" t="n">
-        <v>320.9210205078125</v>
+        <v>332.2994689941406</v>
       </c>
       <c r="F47" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>321.9010364932658</v>
+        <v>331.6036653013031</v>
       </c>
       <c r="C48" t="n">
-        <v>336.3275351202159</v>
+        <v>332.2700996432553</v>
       </c>
       <c r="D48" t="n">
-        <v>320.5583278451826</v>
+        <v>324.6844366173477</v>
       </c>
       <c r="E48" t="n">
-        <v>332.2994689941406</v>
+        <v>325.889892578125</v>
       </c>
       <c r="F48" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>331.6036342486655</v>
+        <v>320.4309500487702</v>
       </c>
       <c r="C49" t="n">
-        <v>332.2700685282101</v>
+        <v>321.6658065479886</v>
       </c>
       <c r="D49" t="n">
-        <v>324.6844062126531</v>
+        <v>314.0997345701073</v>
       </c>
       <c r="E49" t="n">
-        <v>325.8898620605469</v>
+        <v>315.4424133300781</v>
       </c>
       <c r="F49" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>320.4309810489659</v>
+        <v>314.2075720220705</v>
       </c>
       <c r="C50" t="n">
-        <v>321.6658376676509</v>
+        <v>321.3424151200708</v>
       </c>
       <c r="D50" t="n">
-        <v>314.0997649577876</v>
+        <v>313.06088745762</v>
       </c>
       <c r="E50" t="n">
-        <v>315.4424438476562</v>
+        <v>314.129150390625</v>
       </c>
       <c r="F50" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>314.2075720220705</v>
+        <v>310.6891466030926</v>
       </c>
       <c r="C51" t="n">
-        <v>321.3424151200708</v>
+        <v>311.1693669212913</v>
       </c>
       <c r="D51" t="n">
-        <v>313.06088745762</v>
+        <v>302.6134236399317</v>
       </c>
       <c r="E51" t="n">
-        <v>314.129150390625</v>
+        <v>307.3275146484375</v>
       </c>
       <c r="F51" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>310.6891774544803</v>
+        <v>307.6705238330165</v>
       </c>
       <c r="C52" t="n">
-        <v>311.1693978203648</v>
+        <v>308.7191962173961</v>
       </c>
       <c r="D52" t="n">
-        <v>302.6134536894014</v>
+        <v>298.4579569753306</v>
       </c>
       <c r="E52" t="n">
-        <v>307.3275451660156</v>
+        <v>302.9270324707031</v>
       </c>
       <c r="F52" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>307.6705548284651</v>
+        <v>304.6127612455315</v>
       </c>
       <c r="C53" t="n">
-        <v>308.7192273184903</v>
+        <v>308.4742040318584</v>
       </c>
       <c r="D53" t="n">
-        <v>298.4579870426836</v>
+        <v>303.8189142172394</v>
       </c>
       <c r="E53" t="n">
-        <v>302.9270629882812</v>
+        <v>305.3282165527344</v>
       </c>
       <c r="F53" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>304.6127916915999</v>
+        <v>305.6908589139109</v>
       </c>
       <c r="C54" t="n">
-        <v>308.4742348638782</v>
+        <v>317.3829805678444</v>
       </c>
       <c r="D54" t="n">
-        <v>303.8189445839627</v>
+        <v>305.2302290041278</v>
       </c>
       <c r="E54" t="n">
-        <v>305.3282470703125</v>
+        <v>313.5901489257812</v>
       </c>
       <c r="F54" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>305.6908291650661</v>
+        <v>318.0592531062754</v>
       </c>
       <c r="C55" t="n">
-        <v>317.3829496811602</v>
+        <v>319.352941040257</v>
       </c>
       <c r="D55" t="n">
-        <v>305.23019930011</v>
+        <v>311.2870267728116</v>
       </c>
       <c r="E55" t="n">
-        <v>313.5901184082031</v>
+        <v>312.6885070800781</v>
       </c>
       <c r="F55" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>318.0591910227777</v>
+        <v>314.7171737995267</v>
       </c>
       <c r="C56" t="n">
-        <v>319.3528787042382</v>
+        <v>321.4599980564078</v>
       </c>
       <c r="D56" t="n">
-        <v>311.2869660112169</v>
+        <v>314.5015591898327</v>
       </c>
       <c r="E56" t="n">
-        <v>312.6884460449219</v>
+        <v>319.7742919921875</v>
       </c>
       <c r="F56" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>314.71720383448</v>
+        <v>320.07813955632</v>
       </c>
       <c r="C57" t="n">
-        <v>321.4600287348608</v>
+        <v>328.5066706952173</v>
       </c>
       <c r="D57" t="n">
-        <v>314.5015892042089</v>
+        <v>319.3921147564304</v>
       </c>
       <c r="E57" t="n">
-        <v>319.7743225097656</v>
+        <v>323.1359252929688</v>
       </c>
       <c r="F57" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>320.07813955632</v>
+        <v>325.0568726515205</v>
       </c>
       <c r="C58" t="n">
-        <v>328.5066706952173</v>
+        <v>325.4390809212725</v>
       </c>
       <c r="D58" t="n">
-        <v>319.3921147564304</v>
+        <v>322.3323040363653</v>
       </c>
       <c r="E58" t="n">
-        <v>323.1359252929688</v>
+        <v>323.1947326660156</v>
       </c>
       <c r="F58" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>325.0568726515205</v>
+        <v>320.6367557882569</v>
       </c>
       <c r="C59" t="n">
-        <v>325.4390809212725</v>
+        <v>323.4789266660114</v>
       </c>
       <c r="D59" t="n">
-        <v>322.3323040363653</v>
+        <v>316.5890991303779</v>
       </c>
       <c r="E59" t="n">
-        <v>323.1947326660156</v>
+        <v>316.7655029296875</v>
       </c>
       <c r="F59" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>320.6367557882569</v>
+        <v>316.9223461399793</v>
       </c>
       <c r="C60" t="n">
-        <v>323.4789266660114</v>
+        <v>322.1460884369951</v>
       </c>
       <c r="D60" t="n">
-        <v>316.5890991303779</v>
+        <v>316.3637041471038</v>
       </c>
       <c r="E60" t="n">
-        <v>316.7655029296875</v>
+        <v>318.0690307617188</v>
       </c>
       <c r="F60" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>316.9223157324214</v>
+        <v>319.4998951185618</v>
       </c>
       <c r="C61" t="n">
-        <v>322.146057528238</v>
+        <v>334.6026391486864</v>
       </c>
       <c r="D61" t="n">
-        <v>316.3636737931457</v>
+        <v>318.529644271779</v>
       </c>
       <c r="E61" t="n">
-        <v>318.0690002441406</v>
+        <v>332.9365234375</v>
       </c>
       <c r="F61" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>319.4998951185618</v>
+        <v>332.632709971988</v>
       </c>
       <c r="C62" t="n">
-        <v>334.6026391486864</v>
+        <v>334.4556390535126</v>
       </c>
       <c r="D62" t="n">
-        <v>318.529644271779</v>
+        <v>322.1656652751352</v>
       </c>
       <c r="E62" t="n">
-        <v>332.9365234375</v>
+        <v>326.8405456542969</v>
       </c>
       <c r="F62" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>332.632709971988</v>
+        <v>328.3204578992349</v>
       </c>
       <c r="C63" t="n">
-        <v>334.4556390535126</v>
+        <v>329.0162928832224</v>
       </c>
       <c r="D63" t="n">
-        <v>322.1656652751352</v>
+        <v>321.9598711365138</v>
       </c>
       <c r="E63" t="n">
-        <v>326.8405456542969</v>
+        <v>324.31201171875</v>
       </c>
       <c r="F63" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,25 +2081,25 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>328.3204578992349</v>
+        <v>324.3120056919803</v>
       </c>
       <c r="C64" t="n">
-        <v>329.0162928832224</v>
+        <v>324.7066598386667</v>
       </c>
       <c r="D64" t="n">
-        <v>321.9598711365138</v>
+        <v>318.5203424234218</v>
       </c>
       <c r="E64" t="n">
-        <v>324.31201171875</v>
+        <v>319.2998046875</v>
       </c>
       <c r="F64" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2107,25 +2107,25 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>324.3120366886073</v>
+        <v>318.8459617269979</v>
       </c>
       <c r="C65" t="n">
-        <v>324.7066908730135</v>
+        <v>322.0032250879344</v>
       </c>
       <c r="D65" t="n">
-        <v>318.5203728665016</v>
+        <v>318.1750466501944</v>
       </c>
       <c r="E65" t="n">
-        <v>319.2998352050781</v>
+        <v>319.2800903320312</v>
       </c>
       <c r="F65" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G65" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>318.8459617269979</v>
+        <v>318.4414486886093</v>
       </c>
       <c r="C66" t="n">
-        <v>322.0032250879344</v>
+        <v>324.341629514822</v>
       </c>
       <c r="D66" t="n">
-        <v>318.1750466501944</v>
+        <v>315.3335056374652</v>
       </c>
       <c r="E66" t="n">
-        <v>319.2800903320312</v>
+        <v>323.9864196777344</v>
       </c>
       <c r="F66" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>318.4414486886093</v>
+        <v>325.9596900029746</v>
       </c>
       <c r="C67" t="n">
-        <v>324.341629514822</v>
+        <v>334.7211504310009</v>
       </c>
       <c r="D67" t="n">
-        <v>315.3335056374652</v>
+        <v>324.3711973012736</v>
       </c>
       <c r="E67" t="n">
-        <v>323.9864196777344</v>
+        <v>332.2348022460938</v>
       </c>
       <c r="F67" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>325.9597199441495</v>
+        <v>332.9945516695081</v>
       </c>
       <c r="C68" t="n">
-        <v>334.7211811769636</v>
+        <v>340.3747084246943</v>
       </c>
       <c r="D68" t="n">
-        <v>324.3712270965368</v>
+        <v>332.8662822838281</v>
       </c>
       <c r="E68" t="n">
-        <v>332.2348327636719</v>
+        <v>337.276611328125</v>
       </c>
       <c r="F68" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>332.9945215393808</v>
+        <v>336.4379310634787</v>
       </c>
       <c r="C69" t="n">
-        <v>340.3746776267931</v>
+        <v>340.3549345980833</v>
       </c>
       <c r="D69" t="n">
-        <v>332.8662521653069</v>
+        <v>332.5012053593197</v>
       </c>
       <c r="E69" t="n">
-        <v>337.2765808105469</v>
+        <v>336.5464782714844</v>
       </c>
       <c r="F69" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>336.4379310634787</v>
+        <v>335.875584402924</v>
       </c>
       <c r="C70" t="n">
-        <v>340.3549345980833</v>
+        <v>336.4379523174861</v>
       </c>
       <c r="D70" t="n">
-        <v>332.5012053593197</v>
+        <v>326.6109215358994</v>
       </c>
       <c r="E70" t="n">
-        <v>336.5464782714844</v>
+        <v>329.7386169433594</v>
       </c>
       <c r="F70" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>335.875584402924</v>
+        <v>329.1564601038647</v>
       </c>
       <c r="C71" t="n">
-        <v>336.4379523174861</v>
+        <v>331.0409661792534</v>
       </c>
       <c r="D71" t="n">
-        <v>326.6109215358994</v>
+        <v>326.0682693196749</v>
       </c>
       <c r="E71" t="n">
-        <v>329.7386169433594</v>
+        <v>327.2029113769531</v>
       </c>
       <c r="F71" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>329.1564601038647</v>
+        <v>324.5389537288393</v>
       </c>
       <c r="C72" t="n">
-        <v>331.0409661792534</v>
+        <v>325.7722668994048</v>
       </c>
       <c r="D72" t="n">
-        <v>326.0682693196749</v>
+        <v>320.2371718427956</v>
       </c>
       <c r="E72" t="n">
-        <v>327.2029113769531</v>
+        <v>323.759521484375</v>
       </c>
       <c r="F72" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>324.5389231377919</v>
+        <v>323.6805434123363</v>
       </c>
       <c r="C73" t="n">
-        <v>325.7722361921053</v>
+        <v>330.1332457701224</v>
       </c>
       <c r="D73" t="n">
-        <v>320.2371416572342</v>
+        <v>321.7171186569828</v>
       </c>
       <c r="E73" t="n">
-        <v>323.7594909667969</v>
+        <v>323.0491027832031</v>
       </c>
       <c r="F73" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>323.6805434123363</v>
+        <v>318.5894351738589</v>
       </c>
       <c r="C74" t="n">
-        <v>330.1332457701224</v>
+        <v>325.3973174895482</v>
       </c>
       <c r="D74" t="n">
-        <v>321.7171186569828</v>
+        <v>317.3561220691985</v>
       </c>
       <c r="E74" t="n">
-        <v>323.0491027832031</v>
+        <v>320.8192749023438</v>
       </c>
       <c r="F74" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>318.5894351738589</v>
+        <v>319.6747419864576</v>
       </c>
       <c r="C75" t="n">
-        <v>325.3973174895482</v>
+        <v>323.4240016076582</v>
       </c>
       <c r="D75" t="n">
-        <v>317.3561220691985</v>
+        <v>319.4379555165406</v>
       </c>
       <c r="E75" t="n">
-        <v>320.8192749023438</v>
+        <v>320.4640502929688</v>
       </c>
       <c r="F75" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>319.6747419864576</v>
+        <v>320.8587369294642</v>
       </c>
       <c r="C76" t="n">
-        <v>323.4240016076582</v>
+        <v>324.5981204386806</v>
       </c>
       <c r="D76" t="n">
-        <v>319.4379555165406</v>
+        <v>319.8030137263066</v>
       </c>
       <c r="E76" t="n">
-        <v>320.4640502929688</v>
+        <v>323.2069396972656</v>
       </c>
       <c r="F76" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>320.8587672253223</v>
+        <v>322.8320412014528</v>
       </c>
       <c r="C77" t="n">
-        <v>324.5981510876156</v>
+        <v>327.4594342482506</v>
       </c>
       <c r="D77" t="n">
-        <v>319.8030439224821</v>
+        <v>321.9045873641298</v>
       </c>
       <c r="E77" t="n">
-        <v>323.2069702148438</v>
+        <v>327.4002075195312</v>
       </c>
       <c r="F77" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>322.8320412014528</v>
+        <v>326.4727780063231</v>
       </c>
       <c r="C78" t="n">
-        <v>327.4594342482506</v>
+        <v>329.787909026371</v>
       </c>
       <c r="D78" t="n">
-        <v>321.9045873641298</v>
+        <v>323.8976047048735</v>
       </c>
       <c r="E78" t="n">
-        <v>327.4002075195312</v>
+        <v>324.5487976074219</v>
       </c>
       <c r="F78" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>326.4728087048146</v>
+        <v>325.3282766160162</v>
       </c>
       <c r="C79" t="n">
-        <v>329.787940036587</v>
+        <v>331.6625558944407</v>
       </c>
       <c r="D79" t="n">
-        <v>323.8976351612195</v>
+        <v>325.1112123040032</v>
       </c>
       <c r="E79" t="n">
-        <v>324.548828125</v>
+        <v>327.725830078125</v>
       </c>
       <c r="F79" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>325.3282463216964</v>
+        <v>327.8837053458195</v>
       </c>
       <c r="C80" t="n">
-        <v>331.6625250102778</v>
+        <v>328.8802018879278</v>
       </c>
       <c r="D80" t="n">
-        <v>325.1111820298963</v>
+        <v>325.4762756879338</v>
       </c>
       <c r="E80" t="n">
-        <v>327.7257995605469</v>
+        <v>325.7031860351562</v>
       </c>
       <c r="F80" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>327.8837053458195</v>
+        <v>326.4826326508298</v>
       </c>
       <c r="C81" t="n">
-        <v>328.8802018879278</v>
+        <v>335.717696654991</v>
       </c>
       <c r="D81" t="n">
-        <v>325.4762756879338</v>
+        <v>323.1280270938765</v>
       </c>
       <c r="E81" t="n">
-        <v>325.7031860351562</v>
+        <v>331.9092102050781</v>
       </c>
       <c r="F81" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>326.4826326508298</v>
+        <v>330.9719222150325</v>
       </c>
       <c r="C82" t="n">
-        <v>335.717696654991</v>
+        <v>342.3085268229226</v>
       </c>
       <c r="D82" t="n">
-        <v>323.1280270938765</v>
+        <v>329.3932753932535</v>
       </c>
       <c r="E82" t="n">
-        <v>331.9092102050781</v>
+        <v>337.4541931152344</v>
       </c>
       <c r="F82" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>330.9719222150325</v>
+        <v>343.6996829189171</v>
       </c>
       <c r="C83" t="n">
-        <v>342.3085268229226</v>
+        <v>347.9027932709801</v>
       </c>
       <c r="D83" t="n">
-        <v>329.3932753932535</v>
+        <v>340.5127911940015</v>
       </c>
       <c r="E83" t="n">
-        <v>337.4541931152344</v>
+        <v>344.3114013671875</v>
       </c>
       <c r="F83" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>343.6996829189171</v>
+        <v>344.3213032237757</v>
       </c>
       <c r="C84" t="n">
-        <v>347.9027932709801</v>
+        <v>345.4361929991165</v>
       </c>
       <c r="D84" t="n">
-        <v>340.5127911940015</v>
+        <v>333.527344316932</v>
       </c>
       <c r="E84" t="n">
-        <v>344.3114013671875</v>
+        <v>337.1384887695312</v>
       </c>
       <c r="F84" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>344.3213032237757</v>
+        <v>336.4576913463828</v>
       </c>
       <c r="C85" t="n">
-        <v>345.4361929991165</v>
+        <v>343.2556975271264</v>
       </c>
       <c r="D85" t="n">
-        <v>333.527344316932</v>
+        <v>336.2504730653109</v>
       </c>
       <c r="E85" t="n">
-        <v>337.1384887695312</v>
+        <v>342.2197265625</v>
       </c>
       <c r="F85" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>336.4576913463828</v>
+        <v>342.6143979299363</v>
       </c>
       <c r="C86" t="n">
-        <v>343.2556975271264</v>
+        <v>344.4002329876533</v>
       </c>
       <c r="D86" t="n">
-        <v>336.2504730653109</v>
+        <v>337.9080857224443</v>
       </c>
       <c r="E86" t="n">
-        <v>342.2197265625</v>
+        <v>339.3880615234375</v>
       </c>
       <c r="F86" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>342.6143671222478</v>
+        <v>336.8622109944222</v>
       </c>
       <c r="C87" t="n">
-        <v>344.4002020193836</v>
+        <v>338.0757717813934</v>
       </c>
       <c r="D87" t="n">
-        <v>337.9080553379447</v>
+        <v>329.4820547645052</v>
       </c>
       <c r="E87" t="n">
-        <v>339.3880310058594</v>
+        <v>335.96435546875</v>
       </c>
       <c r="F87" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>336.8622415935578</v>
+        <v>336.9411188846722</v>
       </c>
       <c r="C88" t="n">
-        <v>338.0758024907637</v>
+        <v>337.2765764147031</v>
       </c>
       <c r="D88" t="n">
-        <v>329.4820846932586</v>
+        <v>328.4065987621919</v>
       </c>
       <c r="E88" t="n">
-        <v>335.9643859863281</v>
+        <v>329.47216796875</v>
       </c>
       <c r="F88" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>336.9411188846722</v>
+        <v>330.8929641448377</v>
       </c>
       <c r="C89" t="n">
-        <v>337.2765764147031</v>
+        <v>335.5696777492312</v>
       </c>
       <c r="D89" t="n">
-        <v>328.4065987621919</v>
+        <v>329.639928884428</v>
       </c>
       <c r="E89" t="n">
-        <v>329.47216796875</v>
+        <v>330.4884338378906</v>
       </c>
       <c r="F89" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>330.8929641448377</v>
+        <v>330.7252730384288</v>
       </c>
       <c r="C90" t="n">
-        <v>335.5696777492312</v>
+        <v>334.9185378332558</v>
       </c>
       <c r="D90" t="n">
-        <v>329.639928884428</v>
+        <v>323.6805737302307</v>
       </c>
       <c r="E90" t="n">
-        <v>330.4884338378906</v>
+        <v>334.43505859375</v>
       </c>
       <c r="F90" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>330.7252428593728</v>
+        <v>330.3897780779105</v>
       </c>
       <c r="C91" t="n">
-        <v>334.9185072715596</v>
+        <v>331.7119162692861</v>
       </c>
       <c r="D91" t="n">
-        <v>323.6805441940115</v>
+        <v>326.0189235086448</v>
       </c>
       <c r="E91" t="n">
-        <v>334.4350280761719</v>
+        <v>326.6010437011719</v>
       </c>
       <c r="F91" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>330.3897780779105</v>
+        <v>323.0293559592084</v>
       </c>
       <c r="C92" t="n">
-        <v>331.7119162692861</v>
+        <v>335.3526407320732</v>
       </c>
       <c r="D92" t="n">
-        <v>326.0189235086448</v>
+        <v>322.1413765634589</v>
       </c>
       <c r="E92" t="n">
-        <v>326.6010437011719</v>
+        <v>333.912109375</v>
       </c>
       <c r="F92" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>323.0293559592084</v>
+        <v>334.8987575018528</v>
       </c>
       <c r="C93" t="n">
-        <v>335.3526407320732</v>
+        <v>343.4332779356386</v>
       </c>
       <c r="D93" t="n">
-        <v>322.1413765634589</v>
+        <v>334.168645798694</v>
       </c>
       <c r="E93" t="n">
-        <v>333.912109375</v>
+        <v>343.1076965332031</v>
       </c>
       <c r="F93" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>334.8987575018528</v>
+        <v>342.5453159613966</v>
       </c>
       <c r="C94" t="n">
-        <v>343.4332779356386</v>
+        <v>350.2116096750548</v>
       </c>
       <c r="D94" t="n">
-        <v>334.168645798694</v>
+        <v>342.1407856401066</v>
       </c>
       <c r="E94" t="n">
-        <v>343.1076965332031</v>
+        <v>349.7380065917969</v>
       </c>
       <c r="F94" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>342.5453159613966</v>
+        <v>349.5505106781399</v>
       </c>
       <c r="C95" t="n">
-        <v>350.2116096750548</v>
+        <v>353.0925820837122</v>
       </c>
       <c r="D95" t="n">
-        <v>342.1407856401066</v>
+        <v>348.2777232015386</v>
       </c>
       <c r="E95" t="n">
-        <v>349.7380065917969</v>
+        <v>351.5040893554688</v>
       </c>
       <c r="F95" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>349.5505410261084</v>
+        <v>349.2249303389971</v>
       </c>
       <c r="C96" t="n">
-        <v>353.0926127392032</v>
+        <v>350.0537130836444</v>
       </c>
       <c r="D96" t="n">
-        <v>348.2777534390037</v>
+        <v>342.6340826093485</v>
       </c>
       <c r="E96" t="n">
-        <v>351.5041198730469</v>
+        <v>346.9457702636719</v>
       </c>
       <c r="F96" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>349.2249303389971</v>
+        <v>290.0456258453373</v>
       </c>
       <c r="C97" t="n">
-        <v>350.0537130836444</v>
+        <v>295.5018014762001</v>
       </c>
       <c r="D97" t="n">
-        <v>342.6340826093485</v>
+        <v>276.6567723884028</v>
       </c>
       <c r="E97" t="n">
-        <v>346.9457702636719</v>
+        <v>278.9260864257812</v>
       </c>
       <c r="F97" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>290.0456258453373</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="C98" t="n">
-        <v>295.5018014762001</v>
+        <v>291.0027024164021</v>
       </c>
       <c r="D98" t="n">
-        <v>276.6567723884028</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="E98" t="n">
-        <v>278.9260864257812</v>
+        <v>290.094970703125</v>
       </c>
       <c r="F98" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>279.9324825435024</v>
+        <v>290.4008067136846</v>
       </c>
       <c r="C99" t="n">
-        <v>291.0027024164021</v>
+        <v>291.6538720255555</v>
       </c>
       <c r="D99" t="n">
-        <v>279.9324825435024</v>
+        <v>285.3590374883647</v>
       </c>
       <c r="E99" t="n">
-        <v>290.094970703125</v>
+        <v>288.3880615234375</v>
       </c>
       <c r="F99" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>290.4008374442539</v>
+        <v>288.200605503728</v>
       </c>
       <c r="C100" t="n">
-        <v>291.6539028887257</v>
+        <v>289.0392644171012</v>
       </c>
       <c r="D100" t="n">
-        <v>285.3590676854078</v>
+        <v>280.8993981188336</v>
       </c>
       <c r="E100" t="n">
-        <v>288.3880920410156</v>
+        <v>283.099609375</v>
       </c>
       <c r="F100" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>288.200605503728</v>
+        <v>282.201779365365</v>
       </c>
       <c r="C101" t="n">
-        <v>289.0392644171012</v>
+        <v>286.5233135903719</v>
       </c>
       <c r="D101" t="n">
-        <v>280.8993981188336</v>
+        <v>278.5117159450099</v>
       </c>
       <c r="E101" t="n">
-        <v>283.099609375</v>
+        <v>281.7775268554688</v>
       </c>
       <c r="F101" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>282.201779365365</v>
+        <v>280.899399533992</v>
       </c>
       <c r="C102" t="n">
-        <v>286.5233135903719</v>
+        <v>284.2441289542904</v>
       </c>
       <c r="D102" t="n">
-        <v>278.5117159450099</v>
+        <v>274.8808256732182</v>
       </c>
       <c r="E102" t="n">
-        <v>281.7775268554688</v>
+        <v>280.3863220214844</v>
       </c>
       <c r="F102" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>280.899399533992</v>
+        <v>278.2453003524489</v>
       </c>
       <c r="C103" t="n">
-        <v>284.2441289542904</v>
+        <v>280.7020503139632</v>
       </c>
       <c r="D103" t="n">
-        <v>274.8808256732182</v>
+        <v>270.3915411669698</v>
       </c>
       <c r="E103" t="n">
-        <v>280.3863220214844</v>
+        <v>272.2366027832031</v>
       </c>
       <c r="F103" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>278.2453003524489</v>
+        <v>270.6283598679102</v>
       </c>
       <c r="C104" t="n">
-        <v>280.7020503139632</v>
+        <v>273.1936570552693</v>
       </c>
       <c r="D104" t="n">
-        <v>270.3915411669698</v>
+        <v>262.7351562823021</v>
       </c>
       <c r="E104" t="n">
-        <v>272.2366027832031</v>
+        <v>264.9649658203125</v>
       </c>
       <c r="F104" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>270.6283910377749</v>
+        <v>263.494873693566</v>
       </c>
       <c r="C105" t="n">
-        <v>273.1936885205944</v>
+        <v>274.1013663098342</v>
       </c>
       <c r="D105" t="n">
-        <v>262.7351865430599</v>
+        <v>262.8535569062469</v>
       </c>
       <c r="E105" t="n">
-        <v>264.9649963378906</v>
+        <v>272.9568481445312</v>
       </c>
       <c r="F105" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>263.494873693566</v>
+        <v>270.4902353878243</v>
       </c>
       <c r="C106" t="n">
-        <v>274.1013663098342</v>
+        <v>276.4397368487514</v>
       </c>
       <c r="D106" t="n">
-        <v>262.8535569062469</v>
+        <v>269.6713287006126</v>
       </c>
       <c r="E106" t="n">
-        <v>272.9568481445312</v>
+        <v>272.0195617675781</v>
       </c>
       <c r="F106" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>270.4902050418196</v>
+        <v>273.8152476410468</v>
       </c>
       <c r="C107" t="n">
-        <v>276.4397058352786</v>
+        <v>275.7589504136547</v>
       </c>
       <c r="D107" t="n">
-        <v>269.6712984464802</v>
+        <v>269.010264317998</v>
       </c>
       <c r="E107" t="n">
-        <v>272.01953125</v>
+        <v>269.5726623535156</v>
       </c>
       <c r="F107" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>273.8152476410468</v>
+        <v>268.8030465161297</v>
       </c>
       <c r="C108" t="n">
-        <v>275.7589504136547</v>
+        <v>275.9562621591264</v>
       </c>
       <c r="D108" t="n">
-        <v>269.010264317998</v>
+        <v>266.1982749187582</v>
       </c>
       <c r="E108" t="n">
-        <v>269.5726623535156</v>
+        <v>275.1866760253906</v>
       </c>
       <c r="F108" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>268.8030763257778</v>
+        <v>274.4467004687212</v>
       </c>
       <c r="C109" t="n">
-        <v>275.9562927620499</v>
+        <v>282.4878958393087</v>
       </c>
       <c r="D109" t="n">
-        <v>266.198304439543</v>
+        <v>272.1280658242715</v>
       </c>
       <c r="E109" t="n">
-        <v>275.1867065429688</v>
+        <v>280.5737915039062</v>
       </c>
       <c r="F109" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>274.4467004687212</v>
+        <v>281.8169569225497</v>
       </c>
       <c r="C110" t="n">
-        <v>282.4878958393087</v>
+        <v>289.5424162609187</v>
       </c>
       <c r="D110" t="n">
-        <v>272.1280658242715</v>
+        <v>280.7119132986369</v>
       </c>
       <c r="E110" t="n">
-        <v>280.5737915039062</v>
+        <v>289.2760314941406</v>
       </c>
       <c r="F110" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>281.8169569225497</v>
+        <v>290.0752312306441</v>
       </c>
       <c r="C111" t="n">
-        <v>289.5424162609187</v>
+        <v>290.3021716729731</v>
       </c>
       <c r="D111" t="n">
-        <v>280.7119132986369</v>
+        <v>284.4907860910092</v>
       </c>
       <c r="E111" t="n">
-        <v>289.2760314941406</v>
+        <v>285.2307739257812</v>
       </c>
       <c r="F111" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>290.0752312306441</v>
+        <v>286.1286505407075</v>
       </c>
       <c r="C112" t="n">
-        <v>290.3021716729731</v>
+        <v>286.2569199258207</v>
       </c>
       <c r="D112" t="n">
-        <v>284.4907860910092</v>
+        <v>282.4681855456762</v>
       </c>
       <c r="E112" t="n">
-        <v>285.2307739257812</v>
+        <v>284.3526916503906</v>
       </c>
       <c r="F112" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>286.1286505407075</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="C113" t="n">
-        <v>286.2569199258207</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="D113" t="n">
-        <v>282.4681855456762</v>
+        <v>283.0601744920274</v>
       </c>
       <c r="E113" t="n">
-        <v>284.3526916503906</v>
+        <v>286.0595703125</v>
       </c>
       <c r="F113" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>287.0067764654547</v>
+        <v>285.0433100706192</v>
       </c>
       <c r="C114" t="n">
-        <v>287.0067764654547</v>
+        <v>286.9179399107358</v>
       </c>
       <c r="D114" t="n">
-        <v>283.0601744920274</v>
+        <v>281.7380250284705</v>
       </c>
       <c r="E114" t="n">
-        <v>286.0595703125</v>
+        <v>286.1286315917969</v>
       </c>
       <c r="F114" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>285.0433100706192</v>
+        <v>284.6979833712643</v>
       </c>
       <c r="C115" t="n">
-        <v>286.9179399107358</v>
+        <v>287.8749991147026</v>
       </c>
       <c r="D115" t="n">
-        <v>281.7380250284705</v>
+        <v>277.9098533754537</v>
       </c>
       <c r="E115" t="n">
-        <v>286.1286315917969</v>
+        <v>278.5708923339844</v>
       </c>
       <c r="F115" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>284.6979833712643</v>
+        <v>278.4327740747045</v>
       </c>
       <c r="C116" t="n">
-        <v>287.8749991147026</v>
+        <v>278.6300861021672</v>
       </c>
       <c r="D116" t="n">
-        <v>277.9098533754537</v>
+        <v>268.1715851207944</v>
       </c>
       <c r="E116" t="n">
-        <v>278.5708923339844</v>
+        <v>270.2929077148438</v>
       </c>
       <c r="F116" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>278.4327740747045</v>
+        <v>273.5883087457124</v>
       </c>
       <c r="C117" t="n">
-        <v>278.6300861021672</v>
+        <v>280.9388364524249</v>
       </c>
       <c r="D117" t="n">
-        <v>268.1715851207944</v>
+        <v>273.1739023127244</v>
       </c>
       <c r="E117" t="n">
-        <v>270.2929077148438</v>
+        <v>280.4060668945312</v>
       </c>
       <c r="F117" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>273.5883087457124</v>
+        <v>283.1489568057956</v>
       </c>
       <c r="C118" t="n">
-        <v>280.9388364524249</v>
+        <v>291.3184213223429</v>
       </c>
       <c r="D118" t="n">
-        <v>273.1739023127244</v>
+        <v>281.422318519362</v>
       </c>
       <c r="E118" t="n">
-        <v>280.4060668945312</v>
+        <v>282.8332214355469</v>
       </c>
       <c r="F118" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>283.1489568057956</v>
+        <v>280.899378965855</v>
       </c>
       <c r="C119" t="n">
-        <v>291.3184213223429</v>
+        <v>290.2034849465505</v>
       </c>
       <c r="D119" t="n">
-        <v>281.422318519362</v>
+        <v>280.0607201096653</v>
       </c>
       <c r="E119" t="n">
-        <v>282.8332214355469</v>
+        <v>289.3549499511719</v>
       </c>
       <c r="F119" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>280.899378965855</v>
+        <v>284.3132152404683</v>
       </c>
       <c r="C120" t="n">
-        <v>290.2034849465505</v>
+        <v>291.3677603814479</v>
       </c>
       <c r="D120" t="n">
-        <v>280.0607201096653</v>
+        <v>283.6620222891216</v>
       </c>
       <c r="E120" t="n">
-        <v>289.3549499511719</v>
+        <v>290.9928283691406</v>
       </c>
       <c r="F120" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>284.3132152404683</v>
+        <v>285.1321178149137</v>
       </c>
       <c r="C121" t="n">
-        <v>291.3677603814479</v>
+        <v>289.8187076809586</v>
       </c>
       <c r="D121" t="n">
-        <v>283.6620222891216</v>
+        <v>280.5639211910132</v>
       </c>
       <c r="E121" t="n">
-        <v>290.9928283691406</v>
+        <v>285.3491821289062</v>
       </c>
       <c r="F121" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>285.1321178149137</v>
+        <v>285.1518383851878</v>
       </c>
       <c r="C122" t="n">
-        <v>289.8187076809586</v>
+        <v>290.4106717068518</v>
       </c>
       <c r="D122" t="n">
-        <v>280.5639211910132</v>
+        <v>283.839576506922</v>
       </c>
       <c r="E122" t="n">
-        <v>285.3491821289062</v>
+        <v>288.0624389648438</v>
       </c>
       <c r="F122" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>285.1518685944145</v>
+        <v>286.1779504316799</v>
       </c>
       <c r="C123" t="n">
-        <v>290.4107024732037</v>
+        <v>287.5000885291143</v>
       </c>
       <c r="D123" t="n">
-        <v>283.8396065771265</v>
+        <v>282.9121398572339</v>
       </c>
       <c r="E123" t="n">
-        <v>288.0624694824219</v>
+        <v>284.9150390625</v>
       </c>
       <c r="F123" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>286.1779504316799</v>
+        <v>283.5041446062434</v>
       </c>
       <c r="C124" t="n">
-        <v>287.5000885291143</v>
+        <v>287.4408703764128</v>
       </c>
       <c r="D124" t="n">
-        <v>282.9121398572339</v>
+        <v>279.2714056266989</v>
       </c>
       <c r="E124" t="n">
-        <v>284.9150390625</v>
+        <v>282.6556396484375</v>
       </c>
       <c r="F124" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,25 +3667,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>283.5041446062434</v>
+        <v>280.3985261413432</v>
       </c>
       <c r="C125" t="n">
-        <v>287.4408703764128</v>
+        <v>283.5803655260448</v>
       </c>
       <c r="D125" t="n">
-        <v>279.2714056266989</v>
+        <v>277.0774975936055</v>
       </c>
       <c r="E125" t="n">
-        <v>282.6556396484375</v>
+        <v>283.550537109375</v>
       </c>
       <c r="F125" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -3693,25 +3693,25 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>280.3985261413432</v>
+        <v>285.7479583300972</v>
       </c>
       <c r="C126" t="n">
-        <v>283.5803655260448</v>
+        <v>285.9468043127463</v>
       </c>
       <c r="D126" t="n">
-        <v>277.0774975936055</v>
+        <v>277.3161057836816</v>
       </c>
       <c r="E126" t="n">
-        <v>283.550537109375</v>
+        <v>280.736572265625</v>
       </c>
       <c r="F126" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>285.7479583300972</v>
+        <v>280.7763694963311</v>
       </c>
       <c r="C127" t="n">
-        <v>285.9468043127463</v>
+        <v>284.5945585040109</v>
       </c>
       <c r="D127" t="n">
-        <v>277.3161057836816</v>
+        <v>279.0064793259336</v>
       </c>
       <c r="E127" t="n">
-        <v>280.736572265625</v>
+        <v>283.6300659179688</v>
       </c>
       <c r="F127" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>280.7763694963311</v>
+        <v>283.1627358622739</v>
       </c>
       <c r="C128" t="n">
-        <v>284.5945585040109</v>
+        <v>285.9269470548217</v>
       </c>
       <c r="D128" t="n">
-        <v>279.0064793259336</v>
+        <v>274.7209602020642</v>
       </c>
       <c r="E128" t="n">
-        <v>283.6300659179688</v>
+        <v>275.4766235351562</v>
       </c>
       <c r="F128" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>283.1627358622739</v>
+        <v>276.4808941849521</v>
       </c>
       <c r="C129" t="n">
-        <v>285.9269470548217</v>
+        <v>281.2735286763525</v>
       </c>
       <c r="D129" t="n">
-        <v>274.7209602020642</v>
+        <v>276.2323139355343</v>
       </c>
       <c r="E129" t="n">
-        <v>275.4766235351562</v>
+        <v>280.4880065917969</v>
       </c>
       <c r="F129" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>276.4808941849521</v>
+        <v>282.3672788368328</v>
       </c>
       <c r="C130" t="n">
-        <v>281.2735286763525</v>
+        <v>285.767839547621</v>
       </c>
       <c r="D130" t="n">
-        <v>276.2323139355343</v>
+        <v>279.4439727693734</v>
       </c>
       <c r="E130" t="n">
-        <v>280.4880065917969</v>
+        <v>283.8686828613281</v>
       </c>
       <c r="F130" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>282.3672788368328</v>
+        <v>286.1655640520241</v>
       </c>
       <c r="C131" t="n">
-        <v>285.767839547621</v>
+        <v>287.3488084380985</v>
       </c>
       <c r="D131" t="n">
-        <v>279.4439727693734</v>
+        <v>283.2223824666901</v>
       </c>
       <c r="E131" t="n">
-        <v>283.8686828613281</v>
+        <v>285.9368896484375</v>
       </c>
       <c r="F131" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>286.1655640520241</v>
+        <v>283.5803557381978</v>
       </c>
       <c r="C132" t="n">
-        <v>287.3488084380985</v>
+        <v>286.7621646688093</v>
       </c>
       <c r="D132" t="n">
-        <v>283.2223824666901</v>
+        <v>281.4624471949345</v>
       </c>
       <c r="E132" t="n">
-        <v>285.9368896484375</v>
+        <v>282.7152709960938</v>
       </c>
       <c r="F132" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>283.5803557381978</v>
+        <v>282.3871618979052</v>
       </c>
       <c r="C133" t="n">
-        <v>286.7621646688093</v>
+        <v>285.9169892839216</v>
       </c>
       <c r="D133" t="n">
-        <v>281.4624471949345</v>
+        <v>278.4794876796185</v>
       </c>
       <c r="E133" t="n">
-        <v>282.7152709960938</v>
+        <v>278.8473815917969</v>
       </c>
       <c r="F133" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>282.3871618979052</v>
+        <v>277.4056183419098</v>
       </c>
       <c r="C134" t="n">
-        <v>285.9169892839216</v>
+        <v>281.4922936115716</v>
       </c>
       <c r="D134" t="n">
-        <v>278.4794876796185</v>
+        <v>273.4382870867091</v>
       </c>
       <c r="E134" t="n">
-        <v>278.8473815917969</v>
+        <v>274.0249328613281</v>
       </c>
       <c r="F134" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>277.4056183419098</v>
+        <v>277.5547645320462</v>
       </c>
       <c r="C135" t="n">
-        <v>281.4922936115716</v>
+        <v>279.1556066962045</v>
       </c>
       <c r="D135" t="n">
-        <v>273.4382870867091</v>
+        <v>267.5618207785692</v>
       </c>
       <c r="E135" t="n">
-        <v>274.0249328613281</v>
+        <v>268.00927734375</v>
       </c>
       <c r="F135" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>277.5547645320462</v>
+        <v>267.3430655755382</v>
       </c>
       <c r="C136" t="n">
-        <v>279.1556066962045</v>
+        <v>271.8274627132414</v>
       </c>
       <c r="D136" t="n">
-        <v>267.5618207785692</v>
+        <v>266.0703359894755</v>
       </c>
       <c r="E136" t="n">
-        <v>268.00927734375</v>
+        <v>270.7337036132812</v>
       </c>
       <c r="F136" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>267.3430655755382</v>
+        <v>273.4382596260376</v>
       </c>
       <c r="C137" t="n">
-        <v>271.8274627132414</v>
+        <v>274.5121128941823</v>
       </c>
       <c r="D137" t="n">
-        <v>266.0703359894755</v>
+        <v>265.5930528118823</v>
       </c>
       <c r="E137" t="n">
-        <v>270.7337036132812</v>
+        <v>269.0135192871094</v>
       </c>
       <c r="F137" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>273.4382596260376</v>
+        <v>268.4567257080549</v>
       </c>
       <c r="C138" t="n">
-        <v>274.5121128941823</v>
+        <v>273.0803427820733</v>
       </c>
       <c r="D138" t="n">
-        <v>265.5930528118823</v>
+        <v>265.6626860357957</v>
       </c>
       <c r="E138" t="n">
-        <v>269.0135192871094</v>
+        <v>266.5277404785156</v>
       </c>
       <c r="F138" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>268.4567257080549</v>
+        <v>265.9808641274938</v>
       </c>
       <c r="C139" t="n">
-        <v>273.0803427820733</v>
+        <v>266.1499120468286</v>
       </c>
       <c r="D139" t="n">
-        <v>265.6626860357957</v>
+        <v>254.516344356629</v>
       </c>
       <c r="E139" t="n">
-        <v>266.5277404785156</v>
+        <v>257.5490112304688</v>
       </c>
       <c r="F139" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>265.9808641274938</v>
+        <v>258.7024415515604</v>
       </c>
       <c r="C140" t="n">
-        <v>266.1499120468286</v>
+        <v>260.8402257240527</v>
       </c>
       <c r="D140" t="n">
-        <v>254.516344356629</v>
+        <v>255.2123953265358</v>
       </c>
       <c r="E140" t="n">
-        <v>257.5490112304688</v>
+        <v>260.3033142089844</v>
       </c>
       <c r="F140" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>258.7024415515604</v>
+        <v>261.506421503485</v>
       </c>
       <c r="C141" t="n">
-        <v>260.8402257240527</v>
+        <v>270.3359967880393</v>
       </c>
       <c r="D141" t="n">
-        <v>255.2123953265358</v>
+        <v>261.1186217504552</v>
       </c>
       <c r="E141" t="n">
-        <v>260.3033142089844</v>
+        <v>269.0533142089844</v>
       </c>
       <c r="F141" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>261.506421503485</v>
+        <v>272.6527466700565</v>
       </c>
       <c r="C142" t="n">
-        <v>270.3359967880393</v>
+        <v>273.7365528939259</v>
       </c>
       <c r="D142" t="n">
-        <v>261.1186217504552</v>
+        <v>269.2223575051711</v>
       </c>
       <c r="E142" t="n">
-        <v>269.0533142089844</v>
+        <v>272.424072265625</v>
       </c>
       <c r="F142" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>272.6527466700565</v>
+        <v>270.7436786461413</v>
       </c>
       <c r="C143" t="n">
-        <v>273.7365528939259</v>
+        <v>277.4553455215711</v>
       </c>
       <c r="D143" t="n">
-        <v>269.2223575051711</v>
+        <v>269.9879849618526</v>
       </c>
       <c r="E143" t="n">
-        <v>272.424072265625</v>
+        <v>275.6854553222656</v>
       </c>
       <c r="F143" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>270.7436786461413</v>
+        <v>276.3019282869355</v>
       </c>
       <c r="C144" t="n">
-        <v>277.4553455215711</v>
+        <v>281.6911311912249</v>
       </c>
       <c r="D144" t="n">
-        <v>269.9879849618526</v>
+        <v>275.6755011928929</v>
       </c>
       <c r="E144" t="n">
-        <v>275.6854553222656</v>
+        <v>279.7621459960938</v>
       </c>
       <c r="F144" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>276.3019282869355</v>
+        <v>307.0960565749332</v>
       </c>
       <c r="C145" t="n">
-        <v>281.6911311912249</v>
+        <v>310.6557125153819</v>
       </c>
       <c r="D145" t="n">
-        <v>275.6755011928929</v>
+        <v>299.0420501528358</v>
       </c>
       <c r="E145" t="n">
-        <v>279.7621459960938</v>
+        <v>305.982421875</v>
       </c>
       <c r="F145" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>307.0960565749332</v>
+        <v>310.2281413790238</v>
       </c>
       <c r="C146" t="n">
-        <v>310.6557125153819</v>
+        <v>311.1926339297742</v>
       </c>
       <c r="D146" t="n">
-        <v>299.0420501528358</v>
+        <v>303.0988467016243</v>
       </c>
       <c r="E146" t="n">
-        <v>305.982421875</v>
+        <v>304.2423400878906</v>
       </c>
       <c r="F146" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>310.2281413790238</v>
+        <v>304.0832470042582</v>
       </c>
       <c r="C147" t="n">
-        <v>311.1926339297742</v>
+        <v>306.1414986993597</v>
       </c>
       <c r="D147" t="n">
-        <v>303.0988467016243</v>
+        <v>302.4127950535677</v>
       </c>
       <c r="E147" t="n">
-        <v>304.2423400878906</v>
+        <v>305.1670532226562</v>
       </c>
       <c r="F147" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>304.0832470042582</v>
+        <v>306.2011519366599</v>
       </c>
       <c r="C148" t="n">
-        <v>306.1414986993597</v>
+        <v>308.607391668382</v>
       </c>
       <c r="D148" t="n">
-        <v>302.4127950535677</v>
+        <v>302.4724483346268</v>
       </c>
       <c r="E148" t="n">
-        <v>305.1670532226562</v>
+        <v>302.6016845703125</v>
       </c>
       <c r="F148" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>306.2011519366599</v>
+        <v>301.5278433900291</v>
       </c>
       <c r="C149" t="n">
-        <v>308.607391668382</v>
+        <v>311.5406631473035</v>
       </c>
       <c r="D149" t="n">
-        <v>302.4724483346268</v>
+        <v>301.199730811355</v>
       </c>
       <c r="E149" t="n">
-        <v>302.6016845703125</v>
+        <v>311.2224731445312</v>
       </c>
       <c r="F149" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>301.5278433900291</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="C150" t="n">
-        <v>311.5406631473035</v>
+        <v>317.8048561417646</v>
       </c>
       <c r="D150" t="n">
-        <v>301.199730811355</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="E150" t="n">
-        <v>311.2224731445312</v>
+        <v>312.4057006835938</v>
       </c>
       <c r="F150" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>310.7352487756957</v>
+        <v>314.2054174655202</v>
       </c>
       <c r="C151" t="n">
-        <v>317.8048561417646</v>
+        <v>315.9554320324556</v>
       </c>
       <c r="D151" t="n">
-        <v>310.7352487756957</v>
+        <v>309.3829548311358</v>
       </c>
       <c r="E151" t="n">
-        <v>312.4057006835938</v>
+        <v>312.2664794921875</v>
       </c>
       <c r="F151" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>314.2054174655202</v>
+        <v>313.2111061223722</v>
       </c>
       <c r="C152" t="n">
-        <v>315.9554320324556</v>
+        <v>316.8005902653832</v>
       </c>
       <c r="D152" t="n">
-        <v>309.3829548311358</v>
+        <v>311.3318249203894</v>
       </c>
       <c r="E152" t="n">
-        <v>312.2664794921875</v>
+        <v>314.6031494140625</v>
       </c>
       <c r="F152" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>313.2111061223722</v>
+        <v>318.2324307180975</v>
       </c>
       <c r="C153" t="n">
-        <v>316.8005902653832</v>
+        <v>323.4227876628706</v>
       </c>
       <c r="D153" t="n">
-        <v>311.3318249203894</v>
+        <v>315.338983249174</v>
       </c>
       <c r="E153" t="n">
-        <v>314.6031494140625</v>
+        <v>322.7864379882812</v>
       </c>
       <c r="F153" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>318.2324307180975</v>
+        <v>322.3489342821542</v>
       </c>
       <c r="C154" t="n">
-        <v>323.4227876628706</v>
+        <v>323.5520542213801</v>
       </c>
       <c r="D154" t="n">
-        <v>315.338983249174</v>
+        <v>318.3020404433487</v>
       </c>
       <c r="E154" t="n">
-        <v>322.7864379882812</v>
+        <v>321.6429748535156</v>
       </c>
       <c r="F154" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>322.3489342821542</v>
+        <v>351.0052603166191</v>
       </c>
       <c r="C155" t="n">
-        <v>323.5520542213801</v>
+        <v>355.648722319699</v>
       </c>
       <c r="D155" t="n">
-        <v>318.3020404433487</v>
+        <v>343.2694442738866</v>
       </c>
       <c r="E155" t="n">
-        <v>321.6429748535156</v>
+        <v>344.0450134277344</v>
       </c>
       <c r="F155" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>351.0052603166191</v>
+        <v>348.8873678788304</v>
       </c>
       <c r="C156" t="n">
-        <v>355.648722319699</v>
+        <v>356.5237461069854</v>
       </c>
       <c r="D156" t="n">
-        <v>343.2694442738866</v>
+        <v>347.1174776591131</v>
       </c>
       <c r="E156" t="n">
-        <v>344.0450134277344</v>
+        <v>351.5123596191406</v>
       </c>
       <c r="F156" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>348.8873678788304</v>
+        <v>352.6657614176121</v>
       </c>
       <c r="C157" t="n">
-        <v>356.5237461069854</v>
+        <v>354.8234513171886</v>
       </c>
       <c r="D157" t="n">
-        <v>347.1174776591131</v>
+        <v>348.5095069624251</v>
       </c>
       <c r="E157" t="n">
-        <v>351.5123596191406</v>
+        <v>352.5464477539062</v>
       </c>
       <c r="F157" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>352.6657614176121</v>
+        <v>354.4654798371856</v>
       </c>
       <c r="C158" t="n">
-        <v>354.8234513171886</v>
+        <v>356.2453229047883</v>
       </c>
       <c r="D158" t="n">
-        <v>348.5095069624251</v>
+        <v>349.3944670661433</v>
       </c>
       <c r="E158" t="n">
-        <v>352.5464477539062</v>
+        <v>352.9044189453125</v>
       </c>
       <c r="F158" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>354.4654798371856</v>
+        <v>351.9001510435625</v>
       </c>
       <c r="C159" t="n">
-        <v>356.2453229047883</v>
+        <v>354.4654858887946</v>
       </c>
       <c r="D159" t="n">
-        <v>349.3944670661433</v>
+        <v>346.9683273478323</v>
       </c>
       <c r="E159" t="n">
-        <v>352.9044189453125</v>
+        <v>352.6757202148438</v>
       </c>
       <c r="F159" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>351.9001510435625</v>
+        <v>354.8135029963465</v>
       </c>
       <c r="C160" t="n">
-        <v>354.4654858887946</v>
+        <v>367.5308771185002</v>
       </c>
       <c r="D160" t="n">
-        <v>346.9683273478323</v>
+        <v>353.6998683282982</v>
       </c>
       <c r="E160" t="n">
-        <v>352.6757202148438</v>
+        <v>364.6871032714844</v>
       </c>
       <c r="F160" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>354.8135029963465</v>
+        <v>363.9214802466298</v>
       </c>
       <c r="C161" t="n">
-        <v>367.5308771185002</v>
+        <v>368.7339901692348</v>
       </c>
       <c r="D161" t="n">
-        <v>353.6998683282982</v>
+        <v>362.9371121823581</v>
       </c>
       <c r="E161" t="n">
-        <v>364.6871032714844</v>
+        <v>368.6345520019531</v>
       </c>
       <c r="F161" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>363.9214802466298</v>
+        <v>366.4172241064422</v>
       </c>
       <c r="C162" t="n">
-        <v>368.7339901692348</v>
+        <v>369.87744160261</v>
       </c>
       <c r="D162" t="n">
-        <v>362.9371121823581</v>
+        <v>360.9385059451532</v>
       </c>
       <c r="E162" t="n">
-        <v>368.6345520019531</v>
+        <v>368.3760375976562</v>
       </c>
       <c r="F162" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>366.4172241064422</v>
+        <v>369.8476329800702</v>
       </c>
       <c r="C163" t="n">
-        <v>369.87744160261</v>
+        <v>370.7822971534658</v>
       </c>
       <c r="D163" t="n">
-        <v>360.9385059451532</v>
+        <v>364.9356847817637</v>
       </c>
       <c r="E163" t="n">
-        <v>368.3760375976562</v>
+        <v>366.6856994628906</v>
       </c>
       <c r="F163" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>369.8476329800702</v>
+        <v>366.4569824541582</v>
       </c>
       <c r="C164" t="n">
-        <v>370.7822971534658</v>
+        <v>368.7240330587824</v>
       </c>
       <c r="D164" t="n">
-        <v>364.9356847817637</v>
+        <v>362.5791367283888</v>
       </c>
       <c r="E164" t="n">
-        <v>366.6856994628906</v>
+        <v>368.6445007324219</v>
       </c>
       <c r="F164" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>366.4569824541582</v>
+        <v>368.3760355922912</v>
       </c>
       <c r="C165" t="n">
-        <v>368.7240330587824</v>
+        <v>369.6885161814855</v>
       </c>
       <c r="D165" t="n">
-        <v>362.5791367283888</v>
+        <v>359.7552596250864</v>
       </c>
       <c r="E165" t="n">
-        <v>368.6445007324219</v>
+        <v>361.8035583496094</v>
       </c>
       <c r="F165" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>368.3760355922912</v>
+        <v>361.0379593902868</v>
       </c>
       <c r="C166" t="n">
-        <v>369.6885161814855</v>
+        <v>366.45699060703</v>
       </c>
       <c r="D166" t="n">
-        <v>359.7552596250864</v>
+        <v>356.2154964951898</v>
       </c>
       <c r="E166" t="n">
-        <v>361.8035583496094</v>
+        <v>365.1942138671875</v>
       </c>
       <c r="F166" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>361.0379593902868</v>
+        <v>364.5578575186544</v>
       </c>
       <c r="C167" t="n">
-        <v>366.45699060703</v>
+        <v>367.7098380224884</v>
       </c>
       <c r="D167" t="n">
-        <v>356.2154964951898</v>
+        <v>362.6487478916185</v>
       </c>
       <c r="E167" t="n">
-        <v>365.1942138671875</v>
+        <v>367.6402282714844</v>
       </c>
       <c r="F167" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>364.5578575186544</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="C168" t="n">
-        <v>367.7098380224884</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="D168" t="n">
-        <v>362.6487478916185</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="E168" t="n">
-        <v>367.6402282714844</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="F168" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>369.8774674335755</v>
+        <v>378.2894437474218</v>
       </c>
       <c r="C169" t="n">
-        <v>377.8221130371094</v>
+        <v>382.6246688242237</v>
       </c>
       <c r="D169" t="n">
-        <v>369.8774674335755</v>
+        <v>373.9343128299113</v>
       </c>
       <c r="E169" t="n">
-        <v>377.8221130371094</v>
+        <v>382.2567749023438</v>
       </c>
       <c r="F169" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>378.2894437474218</v>
+        <v>380.6758011703357</v>
       </c>
       <c r="C170" t="n">
-        <v>382.6246688242237</v>
+        <v>395.1630654325308</v>
       </c>
       <c r="D170" t="n">
-        <v>373.9343128299113</v>
+        <v>379.8405751710962</v>
       </c>
       <c r="E170" t="n">
-        <v>382.2567749023438</v>
+        <v>394.138916015625</v>
       </c>
       <c r="F170" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>380.6758011703357</v>
+        <v>394.2482660415264</v>
       </c>
       <c r="C171" t="n">
-        <v>395.1630654325308</v>
+        <v>401.8548154208889</v>
       </c>
       <c r="D171" t="n">
-        <v>379.8405751710962</v>
+        <v>390.7681426338459</v>
       </c>
       <c r="E171" t="n">
-        <v>394.138916015625</v>
+        <v>398.8818054199219</v>
       </c>
       <c r="F171" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>394.2482660415264</v>
+        <v>398.7227040337817</v>
       </c>
       <c r="C172" t="n">
-        <v>401.8548154208889</v>
+        <v>399.6175868268494</v>
       </c>
       <c r="D172" t="n">
-        <v>390.7681426338459</v>
+        <v>393.7510992453305</v>
       </c>
       <c r="E172" t="n">
-        <v>398.8818054199219</v>
+        <v>396.8235473632812</v>
       </c>
       <c r="F172" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>398.7227040337817</v>
+        <v>392.0607685404387</v>
       </c>
       <c r="C173" t="n">
-        <v>399.6175868268494</v>
+        <v>395.3718745508767</v>
       </c>
       <c r="D173" t="n">
-        <v>393.7510992453305</v>
+        <v>388.0337805215488</v>
       </c>
       <c r="E173" t="n">
-        <v>396.8235473632812</v>
+        <v>391.6133422851562</v>
       </c>
       <c r="F173" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>392.0607685404387</v>
+        <v>387.7851953583757</v>
       </c>
       <c r="C174" t="n">
-        <v>395.3718745508767</v>
+        <v>389.9130568930274</v>
       </c>
       <c r="D174" t="n">
-        <v>388.0337805215488</v>
+        <v>381.3221087690695</v>
       </c>
       <c r="E174" t="n">
-        <v>391.6133422851562</v>
+        <v>388.9087829589844</v>
       </c>
       <c r="F174" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>387.7851953583757</v>
+        <v>387.7851736187118</v>
       </c>
       <c r="C175" t="n">
-        <v>389.9130568930274</v>
+        <v>392.7468254889498</v>
       </c>
       <c r="D175" t="n">
-        <v>381.3221087690695</v>
+        <v>385.3093241434657</v>
       </c>
       <c r="E175" t="n">
-        <v>388.9087829589844</v>
+        <v>387.0294799804688</v>
       </c>
       <c r="F175" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>387.7851736187118</v>
+        <v>387.3377362764213</v>
       </c>
       <c r="C176" t="n">
-        <v>392.7468254889498</v>
+        <v>391.1460027273716</v>
       </c>
       <c r="D176" t="n">
-        <v>385.3093241434657</v>
+        <v>378.5380196367677</v>
       </c>
       <c r="E176" t="n">
-        <v>387.0294799804688</v>
+        <v>381.1232299804688</v>
       </c>
       <c r="F176" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>387.3377362764213</v>
+        <v>378.9555995605828</v>
       </c>
       <c r="C177" t="n">
-        <v>391.1460027273716</v>
+        <v>383.9172514426562</v>
       </c>
       <c r="D177" t="n">
-        <v>378.5380196367677</v>
+        <v>378.3789067550467</v>
       </c>
       <c r="E177" t="n">
-        <v>381.1232299804688</v>
+        <v>380.3078918457031</v>
       </c>
       <c r="F177" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>378.9555995605828</v>
+        <v>379.7510949944643</v>
       </c>
       <c r="C178" t="n">
-        <v>383.9172514426562</v>
+        <v>388.322137279522</v>
       </c>
       <c r="D178" t="n">
-        <v>378.3789067550467</v>
+        <v>378.846259230469</v>
       </c>
       <c r="E178" t="n">
-        <v>380.3078918457031</v>
+        <v>386.2638854980469</v>
       </c>
       <c r="F178" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>379.7510949944643</v>
+        <v>383.8078958628703</v>
       </c>
       <c r="C179" t="n">
-        <v>388.322137279522</v>
+        <v>384.3249318452775</v>
       </c>
       <c r="D179" t="n">
-        <v>378.846259230469</v>
+        <v>374.2723613660349</v>
       </c>
       <c r="E179" t="n">
-        <v>386.2638854980469</v>
+        <v>374.7197875976562</v>
       </c>
       <c r="F179" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>383.8078958628703</v>
+        <v>376.2808953624811</v>
       </c>
       <c r="C180" t="n">
-        <v>384.3249318452775</v>
+        <v>382.3462596379654</v>
       </c>
       <c r="D180" t="n">
-        <v>374.2723613660349</v>
+        <v>374.9485088403697</v>
       </c>
       <c r="E180" t="n">
-        <v>374.7197875976562</v>
+        <v>381.8292236328125</v>
       </c>
       <c r="F180" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>376.2808953624811</v>
+        <v>382.7737976901378</v>
       </c>
       <c r="C181" t="n">
-        <v>382.3462596379654</v>
+        <v>387.0493961299752</v>
       </c>
       <c r="D181" t="n">
-        <v>374.9485088403697</v>
+        <v>378.7965137522062</v>
       </c>
       <c r="E181" t="n">
-        <v>381.8292236328125</v>
+        <v>380.3576049804688</v>
       </c>
       <c r="F181" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>382.7737976901378</v>
+        <v>381.6005025160485</v>
       </c>
       <c r="C182" t="n">
-        <v>387.0493961299752</v>
+        <v>382.9328889810419</v>
       </c>
       <c r="D182" t="n">
-        <v>378.7965137522062</v>
+        <v>373.317822146985</v>
       </c>
       <c r="E182" t="n">
-        <v>380.3576049804688</v>
+        <v>378.1502075195312</v>
       </c>
       <c r="F182" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>381.6005025160485</v>
+        <v>373.9740550559011</v>
       </c>
       <c r="C183" t="n">
-        <v>382.9328889810419</v>
+        <v>381.172959697494</v>
       </c>
       <c r="D183" t="n">
-        <v>373.317822146985</v>
+        <v>373.7851619834815</v>
       </c>
       <c r="E183" t="n">
-        <v>378.1502075195312</v>
+        <v>377.7027587890625</v>
       </c>
       <c r="F183" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>373.9740550559011</v>
+        <v>375.8334605430848</v>
       </c>
       <c r="C184" t="n">
-        <v>381.172959697494</v>
+        <v>377.9215103567756</v>
       </c>
       <c r="D184" t="n">
-        <v>373.7851619834815</v>
+        <v>372.5919643898307</v>
       </c>
       <c r="E184" t="n">
-        <v>377.7027587890625</v>
+        <v>375.7738037109375</v>
       </c>
       <c r="F184" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>375.8334605430848</v>
+        <v>377.8419717237235</v>
       </c>
       <c r="C185" t="n">
-        <v>377.9215103567756</v>
+        <v>385.259597724852</v>
       </c>
       <c r="D185" t="n">
-        <v>372.5919643898307</v>
+        <v>374.6700853756592</v>
       </c>
       <c r="E185" t="n">
-        <v>375.7738037109375</v>
+        <v>374.8590087890625</v>
       </c>
       <c r="F185" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>377.8419717237235</v>
+        <v>387.7851867936407</v>
       </c>
       <c r="C186" t="n">
-        <v>385.259597724852</v>
+        <v>399.1005645351637</v>
       </c>
       <c r="D186" t="n">
-        <v>374.6700853756592</v>
+        <v>387.606216297745</v>
       </c>
       <c r="E186" t="n">
-        <v>374.8590087890625</v>
+        <v>394.2184448242188</v>
       </c>
       <c r="F186" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>387.7851867936407</v>
+        <v>397.2710257691138</v>
       </c>
       <c r="C187" t="n">
-        <v>399.1005645351637</v>
+        <v>401.7454703246708</v>
       </c>
       <c r="D187" t="n">
-        <v>387.606216297745</v>
+        <v>394.9443182415365</v>
       </c>
       <c r="E187" t="n">
-        <v>394.2184448242188</v>
+        <v>397.201416015625</v>
       </c>
       <c r="F187" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>397.2710257691138</v>
+        <v>394.8746856398852</v>
       </c>
       <c r="C188" t="n">
-        <v>401.7454703246708</v>
+        <v>406.3889089451397</v>
       </c>
       <c r="D188" t="n">
-        <v>394.9443182415365</v>
+        <v>392.7468242313375</v>
       </c>
       <c r="E188" t="n">
-        <v>397.201416015625</v>
+        <v>404.2610778808594</v>
       </c>
       <c r="F188" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>394.8746856398852</v>
+        <v>407.6616556237274</v>
       </c>
       <c r="C189" t="n">
-        <v>406.3889089451397</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="D189" t="n">
-        <v>392.7468242313375</v>
+        <v>405.1261492204914</v>
       </c>
       <c r="E189" t="n">
-        <v>404.2610778808594</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="F189" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>407.6616556237274</v>
+        <v>411.1517339543602</v>
       </c>
       <c r="C190" t="n">
-        <v>410.6545715332031</v>
+        <v>413.6176609610221</v>
       </c>
       <c r="D190" t="n">
-        <v>405.1261492204914</v>
+        <v>402.2525488568183</v>
       </c>
       <c r="E190" t="n">
-        <v>410.6545715332031</v>
+        <v>405.1460266113281</v>
       </c>
       <c r="F190" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>411.1517339543602</v>
+        <v>406.3889145916303</v>
       </c>
       <c r="C191" t="n">
-        <v>413.6176609610221</v>
+        <v>407.6517216421196</v>
       </c>
       <c r="D191" t="n">
-        <v>402.2525488568183</v>
+        <v>400.820711098459</v>
       </c>
       <c r="E191" t="n">
-        <v>405.1460266113281</v>
+        <v>403.2468566894531</v>
       </c>
       <c r="F191" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>406.3889145916303</v>
+        <v>406.6872501409831</v>
       </c>
       <c r="C192" t="n">
-        <v>407.6517216421196</v>
+        <v>407.5622574937536</v>
       </c>
       <c r="D192" t="n">
-        <v>400.820711098459</v>
+        <v>402.5110897188582</v>
       </c>
       <c r="E192" t="n">
-        <v>403.2468566894531</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="F192" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,25 +5435,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>406.6872501409831</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="C193" t="n">
-        <v>407.5622574937536</v>
+        <v>414.1600036621094</v>
       </c>
       <c r="D193" t="n">
-        <v>402.5110897188582</v>
+        <v>399.6499938964844</v>
       </c>
       <c r="E193" t="n">
-        <v>406.2000122070312</v>
+        <v>411.0400085449219</v>
       </c>
       <c r="F193" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>406.7000122070312</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="C194" t="n">
-        <v>414.1600036621094</v>
+        <v>411.75</v>
       </c>
       <c r="D194" t="n">
-        <v>399.6499938964844</v>
+        <v>406.5400085449219</v>
       </c>
       <c r="E194" t="n">
-        <v>411.0400085449219</v>
+        <v>407.6499938964844</v>
       </c>
       <c r="F194" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G194" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>410.6799926757812</v>
+        <v>409.1199951171875</v>
       </c>
       <c r="C195" t="n">
-        <v>411.75</v>
+        <v>411.1600036621094</v>
       </c>
       <c r="D195" t="n">
-        <v>406.5400085449219</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E195" t="n">
-        <v>407.6499938964844</v>
+        <v>399.5299987792969</v>
       </c>
       <c r="F195" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>409.1199951171875</v>
+        <v>402.7699890136719</v>
       </c>
       <c r="C196" t="n">
-        <v>411.1600036621094</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="D196" t="n">
-        <v>398.5899963378906</v>
+        <v>399.1499938964844</v>
       </c>
       <c r="E196" t="n">
-        <v>399.5299987792969</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="F196" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>402.7699890136719</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="C197" t="n">
-        <v>406.2000122070312</v>
+        <v>409.4599914550781</v>
       </c>
       <c r="D197" t="n">
-        <v>399.1499938964844</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="E197" t="n">
-        <v>400.9599914550781</v>
+        <v>406.6799926757812</v>
       </c>
       <c r="F197" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>402.1400146484375</v>
+        <v>409.5199890136719</v>
       </c>
       <c r="C198" t="n">
-        <v>409.4599914550781</v>
+        <v>409.8999938964844</v>
       </c>
       <c r="D198" t="n">
-        <v>402.1400146484375</v>
+        <v>402.8399963378906</v>
       </c>
       <c r="E198" t="n">
-        <v>406.6799926757812</v>
+        <v>409.25</v>
       </c>
       <c r="F198" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>409.5199890136719</v>
+        <v>410.5400085449219</v>
       </c>
       <c r="C199" t="n">
-        <v>409.8999938964844</v>
+        <v>413.4299926757812</v>
       </c>
       <c r="D199" t="n">
-        <v>402.8399963378906</v>
+        <v>400</v>
       </c>
       <c r="E199" t="n">
-        <v>409.25</v>
+        <v>405.7999877929688</v>
       </c>
       <c r="F199" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>410.5400085449219</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="C200" t="n">
-        <v>413.4299926757812</v>
+        <v>417.5799865722656</v>
       </c>
       <c r="D200" t="n">
-        <v>400</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="E200" t="n">
-        <v>405.7999877929688</v>
+        <v>415.5299987792969</v>
       </c>
       <c r="F200" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>406.6499938964844</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="C201" t="n">
-        <v>417.5799865722656</v>
+        <v>427.9299926757812</v>
       </c>
       <c r="D201" t="n">
-        <v>406.6499938964844</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="E201" t="n">
-        <v>415.5299987792969</v>
+        <v>427.8900146484375</v>
       </c>
       <c r="F201" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>416.1600036621094</v>
+        <v>426.5299987792969</v>
       </c>
       <c r="C202" t="n">
-        <v>427.9299926757812</v>
+        <v>426.7000122070312</v>
       </c>
       <c r="D202" t="n">
-        <v>416.1600036621094</v>
+        <v>415.8099975585938</v>
       </c>
       <c r="E202" t="n">
-        <v>427.8900146484375</v>
+        <v>419.8200073242188</v>
       </c>
       <c r="F202" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>426.5299987792969</v>
+        <v>422.7200012207031</v>
       </c>
       <c r="C203" t="n">
-        <v>426.7000122070312</v>
+        <v>422.739990234375</v>
       </c>
       <c r="D203" t="n">
-        <v>415.8099975585938</v>
+        <v>413.25</v>
       </c>
       <c r="E203" t="n">
-        <v>419.8200073242188</v>
+        <v>415.6300048828125</v>
       </c>
       <c r="F203" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>422.7200012207031</v>
+        <v>417.1099853515625</v>
       </c>
       <c r="C204" t="n">
-        <v>422.739990234375</v>
+        <v>428.0199890136719</v>
       </c>
       <c r="D204" t="n">
-        <v>413.25</v>
+        <v>413.7300109863281</v>
       </c>
       <c r="E204" t="n">
-        <v>415.6300048828125</v>
+        <v>426.5400085449219</v>
       </c>
       <c r="F204" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>417.1099853515625</v>
+        <v>428.1300048828125</v>
       </c>
       <c r="C205" t="n">
-        <v>428.0199890136719</v>
+        <v>430.2000122070312</v>
       </c>
       <c r="D205" t="n">
-        <v>413.7300109863281</v>
+        <v>420.5400085449219</v>
       </c>
       <c r="E205" t="n">
-        <v>426.5400085449219</v>
+        <v>425.3599853515625</v>
       </c>
       <c r="F205" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>428.1300048828125</v>
+        <v>423.489990234375</v>
       </c>
       <c r="C206" t="n">
-        <v>430.2000122070312</v>
+        <v>424.4400024414062</v>
       </c>
       <c r="D206" t="n">
-        <v>420.5400085449219</v>
+        <v>415.0499877929688</v>
       </c>
       <c r="E206" t="n">
-        <v>425.3599853515625</v>
+        <v>417.989990234375</v>
       </c>
       <c r="F206" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>423.489990234375</v>
+        <v>423.9500122070312</v>
       </c>
       <c r="C207" t="n">
-        <v>424.4400024414062</v>
+        <v>428.6000061035156</v>
       </c>
       <c r="D207" t="n">
-        <v>415.0499877929688</v>
+        <v>422.1300048828125</v>
       </c>
       <c r="E207" t="n">
-        <v>417.989990234375</v>
+        <v>428.1900024414062</v>
       </c>
       <c r="F207" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>423.9500122070312</v>
+        <v>427.1499938964844</v>
       </c>
       <c r="C208" t="n">
-        <v>428.6000061035156</v>
+        <v>430.7699890136719</v>
       </c>
       <c r="D208" t="n">
-        <v>422.1300048828125</v>
+        <v>423.8299865722656</v>
       </c>
       <c r="E208" t="n">
-        <v>428.1900024414062</v>
+        <v>425.6000061035156</v>
       </c>
       <c r="F208" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>427.1499938964844</v>
+        <v>427.1099853515625</v>
       </c>
       <c r="C209" t="n">
-        <v>430.7699890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="D209" t="n">
-        <v>423.8299865722656</v>
+        <v>423.5199890136719</v>
       </c>
       <c r="E209" t="n">
-        <v>425.6000061035156</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="F209" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>427.1099853515625</v>
+        <v>431.6700134277344</v>
       </c>
       <c r="C210" t="n">
-        <v>434.2999877929688</v>
+        <v>432.8599853515625</v>
       </c>
       <c r="D210" t="n">
-        <v>423.5199890136719</v>
+        <v>423.6499938964844</v>
       </c>
       <c r="E210" t="n">
-        <v>431.6799926757812</v>
+        <v>424.6199951171875</v>
       </c>
       <c r="F210" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>431.6700134277344</v>
+        <v>426.4700012207031</v>
       </c>
       <c r="C211" t="n">
-        <v>432.8599853515625</v>
+        <v>431.5499877929688</v>
       </c>
       <c r="D211" t="n">
-        <v>423.6499938964844</v>
+        <v>425.5299987792969</v>
       </c>
       <c r="E211" t="n">
-        <v>424.6199951171875</v>
+        <v>429.0899963378906</v>
       </c>
       <c r="F211" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>426.4700012207031</v>
+        <v>431</v>
       </c>
       <c r="C212" t="n">
-        <v>431.5499877929688</v>
+        <v>432.1499938964844</v>
       </c>
       <c r="D212" t="n">
-        <v>425.5299987792969</v>
+        <v>421.7900085449219</v>
       </c>
       <c r="E212" t="n">
-        <v>429.0899963378906</v>
+        <v>425.1900024414062</v>
       </c>
       <c r="F212" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>431</v>
+        <v>419.489990234375</v>
       </c>
       <c r="C213" t="n">
-        <v>432.1499938964844</v>
+        <v>424.1099853515625</v>
       </c>
       <c r="D213" t="n">
-        <v>421.7900085449219</v>
+        <v>414.3699951171875</v>
       </c>
       <c r="E213" t="n">
-        <v>425.1900024414062</v>
+        <v>418.5199890136719</v>
       </c>
       <c r="F213" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>419.489990234375</v>
+        <v>449.3900146484375</v>
       </c>
       <c r="C214" t="n">
-        <v>424.1099853515625</v>
+        <v>461.6199951171875</v>
       </c>
       <c r="D214" t="n">
-        <v>414.3699951171875</v>
+        <v>420.3699951171875</v>
       </c>
       <c r="E214" t="n">
-        <v>418.5199890136719</v>
+        <v>423.3800048828125</v>
       </c>
       <c r="F214" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>449.3900146484375</v>
+        <v>426.7200012207031</v>
       </c>
       <c r="C215" t="n">
-        <v>461.6199951171875</v>
+        <v>437.4700012207031</v>
       </c>
       <c r="D215" t="n">
-        <v>420.3699951171875</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="E215" t="n">
-        <v>423.3800048828125</v>
+        <v>426.0899963378906</v>
       </c>
       <c r="F215" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>426.7200012207031</v>
+        <v>427.25</v>
       </c>
       <c r="C216" t="n">
-        <v>437.4700012207031</v>
+        <v>431.0199890136719</v>
       </c>
       <c r="D216" t="n">
-        <v>425.1000061035156</v>
+        <v>417.3800048828125</v>
       </c>
       <c r="E216" t="n">
-        <v>426.0899963378906</v>
+        <v>421.5499877929688</v>
       </c>
       <c r="F216" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>427.25</v>
+        <v>422.4800109863281</v>
       </c>
       <c r="C217" t="n">
-        <v>431.0199890136719</v>
+        <v>437</v>
       </c>
       <c r="D217" t="n">
-        <v>417.3800048828125</v>
+        <v>420.5</v>
       </c>
       <c r="E217" t="n">
-        <v>421.5499877929688</v>
+        <v>436.3500061035156</v>
       </c>
       <c r="F217" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>422.4800109863281</v>
+        <v>434.9500122070312</v>
       </c>
       <c r="C218" t="n">
-        <v>437</v>
+        <v>436.3200073242188</v>
       </c>
       <c r="D218" t="n">
-        <v>420.5</v>
+        <v>429.7000122070312</v>
       </c>
       <c r="E218" t="n">
-        <v>436.3500061035156</v>
+        <v>431.3099975585938</v>
       </c>
       <c r="F218" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>434.9500122070312</v>
+        <v>428.2699890136719</v>
       </c>
       <c r="C219" t="n">
-        <v>436.3200073242188</v>
+        <v>430.489990234375</v>
       </c>
       <c r="D219" t="n">
-        <v>429.7000122070312</v>
+        <v>420.3999938964844</v>
       </c>
       <c r="E219" t="n">
-        <v>431.3099975585938</v>
+        <v>423.5599975585938</v>
       </c>
       <c r="F219" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>428.2699890136719</v>
+        <v>425.239990234375</v>
       </c>
       <c r="C220" t="n">
-        <v>430.489990234375</v>
+        <v>429</v>
       </c>
       <c r="D220" t="n">
-        <v>420.3999938964844</v>
+        <v>418.9200134277344</v>
       </c>
       <c r="E220" t="n">
-        <v>423.5599975585938</v>
+        <v>420.739990234375</v>
       </c>
       <c r="F220" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>425.239990234375</v>
+        <v>422.510009765625</v>
       </c>
       <c r="C221" t="n">
-        <v>429</v>
+        <v>422.8800048828125</v>
       </c>
       <c r="D221" t="n">
-        <v>418.9200134277344</v>
+        <v>412.5400085449219</v>
       </c>
       <c r="E221" t="n">
-        <v>420.739990234375</v>
+        <v>417.6400146484375</v>
       </c>
       <c r="F221" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>422.510009765625</v>
+        <v>419.9299926757812</v>
       </c>
       <c r="C222" t="n">
-        <v>422.8800048828125</v>
+        <v>430.4599914550781</v>
       </c>
       <c r="D222" t="n">
-        <v>412.5400085449219</v>
+        <v>415.1099853515625</v>
       </c>
       <c r="E222" t="n">
-        <v>417.6400146484375</v>
+        <v>428.7900085449219</v>
       </c>
       <c r="F222" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>419.9299926757812</v>
+        <v>428.260009765625</v>
       </c>
       <c r="C223" t="n">
-        <v>430.4599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="D223" t="n">
-        <v>415.1099853515625</v>
+        <v>420.3500061035156</v>
       </c>
       <c r="E223" t="n">
-        <v>428.7900085449219</v>
+        <v>420.5700073242188</v>
       </c>
       <c r="F223" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>428.260009765625</v>
+        <v>415.1900024414062</v>
       </c>
       <c r="C224" t="n">
-        <v>431.6799926757812</v>
+        <v>427.3399963378906</v>
       </c>
       <c r="D224" t="n">
-        <v>420.3500061035156</v>
+        <v>411.2900085449219</v>
       </c>
       <c r="E224" t="n">
-        <v>420.5700073242188</v>
+        <v>421.4700012207031</v>
       </c>
       <c r="F224" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>415.1900024414062</v>
+        <v>422</v>
       </c>
       <c r="C225" t="n">
-        <v>427.3399963378906</v>
+        <v>422.8099975585938</v>
       </c>
       <c r="D225" t="n">
-        <v>411.2900085449219</v>
+        <v>414.0599975585938</v>
       </c>
       <c r="E225" t="n">
-        <v>421.4700012207031</v>
+        <v>414.3999938964844</v>
       </c>
       <c r="F225" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>422</v>
+        <v>417.4299926757812</v>
       </c>
       <c r="C226" t="n">
-        <v>422.8099975585938</v>
+        <v>419.3399963378906</v>
       </c>
       <c r="D226" t="n">
-        <v>414.0599975585938</v>
+        <v>413.3200073242188</v>
       </c>
       <c r="E226" t="n">
-        <v>414.3999938964844</v>
+        <v>415.3599853515625</v>
       </c>
       <c r="F226" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>417.4299926757812</v>
+        <v>415.5599975585938</v>
       </c>
       <c r="C227" t="n">
-        <v>419.3399963378906</v>
+        <v>416</v>
       </c>
       <c r="D227" t="n">
-        <v>413.3200073242188</v>
+        <v>406.6700134277344</v>
       </c>
       <c r="E227" t="n">
-        <v>415.3599853515625</v>
+        <v>407.5499877929688</v>
       </c>
       <c r="F227" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>415.5599975585938</v>
+        <v>403.1900024414062</v>
       </c>
       <c r="C228" t="n">
-        <v>416</v>
+        <v>416.3599853515625</v>
       </c>
       <c r="D228" t="n">
-        <v>406.6700134277344</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>407.5499877929688</v>
+        <v>412.75</v>
       </c>
       <c r="F228" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>403.1900024414062</v>
+        <v>415.2699890136719</v>
       </c>
       <c r="C229" t="n">
-        <v>416.3599853515625</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="D229" t="n">
-        <v>397.7999877929688</v>
+        <v>402.3999938964844</v>
       </c>
       <c r="E229" t="n">
-        <v>412.75</v>
+        <v>403.9700012207031</v>
       </c>
       <c r="F229" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>415.2699890136719</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="C230" t="n">
-        <v>416.9700012207031</v>
+        <v>410.6400146484375</v>
       </c>
       <c r="D230" t="n">
-        <v>402.3999938964844</v>
+        <v>400.6600036621094</v>
       </c>
       <c r="E230" t="n">
-        <v>403.9700012207031</v>
+        <v>407.0799865722656</v>
       </c>
       <c r="F230" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>401.5899963378906</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="C231" t="n">
-        <v>410.6400146484375</v>
+        <v>413.0700073242188</v>
       </c>
       <c r="D231" t="n">
-        <v>400.6600036621094</v>
+        <v>407.989990234375</v>
       </c>
       <c r="E231" t="n">
-        <v>407.0799865722656</v>
+        <v>408.739990234375</v>
       </c>
       <c r="F231" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>408.6000061035156</v>
+        <v>409</v>
       </c>
       <c r="C232" t="n">
-        <v>413.0700073242188</v>
+        <v>410.8999938964844</v>
       </c>
       <c r="D232" t="n">
-        <v>407.989990234375</v>
+        <v>401.3200073242188</v>
       </c>
       <c r="E232" t="n">
-        <v>408.739990234375</v>
+        <v>402.1900024414062</v>
       </c>
       <c r="F232" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>409</v>
+        <v>400.9800109863281</v>
       </c>
       <c r="C233" t="n">
-        <v>410.8999938964844</v>
+        <v>407.2000122070312</v>
       </c>
       <c r="D233" t="n">
-        <v>401.3200073242188</v>
+        <v>400.5</v>
       </c>
       <c r="E233" t="n">
-        <v>402.1900024414062</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="F233" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>400.9800109863281</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="C234" t="n">
-        <v>407.2000122070312</v>
+        <v>407.3200073242188</v>
       </c>
       <c r="D234" t="n">
-        <v>400.5</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E234" t="n">
-        <v>405.5899963378906</v>
+        <v>399.0599975585938</v>
       </c>
       <c r="F234" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>405.5899963378906</v>
+        <v>398</v>
       </c>
       <c r="C235" t="n">
-        <v>407.3200073242188</v>
+        <v>403.1799926757812</v>
       </c>
       <c r="D235" t="n">
-        <v>398.5899963378906</v>
+        <v>396.5599975585938</v>
       </c>
       <c r="E235" t="n">
-        <v>399.0599975585938</v>
+        <v>401.7300109863281</v>
       </c>
       <c r="F235" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>398</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C236" t="n">
-        <v>403.1799926757812</v>
+        <v>398.8999938964844</v>
       </c>
       <c r="D236" t="n">
-        <v>396.5599975585938</v>
+        <v>391.4299926757812</v>
       </c>
       <c r="E236" t="n">
-        <v>401.7300109863281</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="F236" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>398.5700073242188</v>
+        <v>397.4299926757812</v>
       </c>
       <c r="C237" t="n">
-        <v>398.8999938964844</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="D237" t="n">
-        <v>391.4299926757812</v>
+        <v>393.510009765625</v>
       </c>
       <c r="E237" t="n">
-        <v>395.6199951171875</v>
+        <v>393.9299926757812</v>
       </c>
       <c r="F237" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>397.4299926757812</v>
+        <v>394.5700073242188</v>
       </c>
       <c r="C238" t="n">
-        <v>398.7900085449219</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="D238" t="n">
-        <v>393.510009765625</v>
+        <v>386.3299865722656</v>
       </c>
       <c r="E238" t="n">
-        <v>393.9299926757812</v>
+        <v>388.6099853515625</v>
       </c>
       <c r="F238" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>394.5700073242188</v>
+        <v>388.25</v>
       </c>
       <c r="C239" t="n">
-        <v>396.7999877929688</v>
+        <v>392.7099914550781</v>
       </c>
       <c r="D239" t="n">
-        <v>386.3299865722656</v>
+        <v>383.8299865722656</v>
       </c>
       <c r="E239" t="n">
-        <v>388.6099853515625</v>
+        <v>384.8500061035156</v>
       </c>
       <c r="F239" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>388.25</v>
+        <v>386</v>
       </c>
       <c r="C240" t="n">
-        <v>392.7099914550781</v>
+        <v>393.6600036621094</v>
       </c>
       <c r="D240" t="n">
-        <v>383.8299865722656</v>
+        <v>386</v>
       </c>
       <c r="E240" t="n">
-        <v>384.8500061035156</v>
+        <v>390.1099853515625</v>
       </c>
       <c r="F240" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>386</v>
+        <v>391.0400085449219</v>
       </c>
       <c r="C241" t="n">
-        <v>393.6600036621094</v>
+        <v>399.5799865722656</v>
       </c>
       <c r="D241" t="n">
-        <v>386</v>
+        <v>390.8599853515625</v>
       </c>
       <c r="E241" t="n">
-        <v>390.1099853515625</v>
+        <v>398.760009765625</v>
       </c>
       <c r="F241" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>391.0400085449219</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="C242" t="n">
-        <v>399.5799865722656</v>
+        <v>399.0299987792969</v>
       </c>
       <c r="D242" t="n">
-        <v>390.8599853515625</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="E242" t="n">
-        <v>398.760009765625</v>
+        <v>396.5899963378906</v>
       </c>
       <c r="F242" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>397.7999877929688</v>
+        <v>396.3299865722656</v>
       </c>
       <c r="C243" t="n">
-        <v>399.0299987792969</v>
+        <v>406.25</v>
       </c>
       <c r="D243" t="n">
-        <v>395.6199951171875</v>
+        <v>396.010009765625</v>
       </c>
       <c r="E243" t="n">
-        <v>396.5899963378906</v>
+        <v>401.010009765625</v>
       </c>
       <c r="F243" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>396.3299865722656</v>
+        <v>396.8699951171875</v>
       </c>
       <c r="C244" t="n">
-        <v>406.25</v>
+        <v>399.8800048828125</v>
       </c>
       <c r="D244" t="n">
-        <v>396.010009765625</v>
+        <v>393.7699890136719</v>
       </c>
       <c r="E244" t="n">
-        <v>401.010009765625</v>
+        <v>395.0499877929688</v>
       </c>
       <c r="F244" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>396.8699951171875</v>
+        <v>396.4200134277344</v>
       </c>
       <c r="C245" t="n">
-        <v>399.8800048828125</v>
+        <v>396.739990234375</v>
       </c>
       <c r="D245" t="n">
-        <v>393.7699890136719</v>
+        <v>392.6600036621094</v>
       </c>
       <c r="E245" t="n">
-        <v>395.0499877929688</v>
+        <v>392.9500122070312</v>
       </c>
       <c r="F245" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>396.4200134277344</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="C246" t="n">
-        <v>396.739990234375</v>
+        <v>394.489990234375</v>
       </c>
       <c r="D246" t="n">
-        <v>392.6600036621094</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="E246" t="n">
-        <v>392.9500122070312</v>
+        <v>389.4100036621094</v>
       </c>
       <c r="F246" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>393.5199890136719</v>
+        <v>392.0799865722656</v>
       </c>
       <c r="C247" t="n">
-        <v>394.489990234375</v>
+        <v>399.6000061035156</v>
       </c>
       <c r="D247" t="n">
-        <v>387.7099914550781</v>
+        <v>391.7799987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>389.4100036621094</v>
+        <v>396.2999877929688</v>
       </c>
       <c r="F247" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>392.0799865722656</v>
+        <v>399.2699890136719</v>
       </c>
       <c r="C248" t="n">
-        <v>399.6000061035156</v>
+        <v>401.1400146484375</v>
       </c>
       <c r="D248" t="n">
-        <v>391.7799987792969</v>
+        <v>396.510009765625</v>
       </c>
       <c r="E248" t="n">
-        <v>396.2999877929688</v>
+        <v>399.6600036621094</v>
       </c>
       <c r="F248" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>399.2699890136719</v>
+        <v>400.0199890136719</v>
       </c>
       <c r="C249" t="n">
-        <v>401.1400146484375</v>
+        <v>405.1600036621094</v>
       </c>
       <c r="D249" t="n">
-        <v>396.510009765625</v>
+        <v>395.2999877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>399.6600036621094</v>
+        <v>400.9400024414062</v>
       </c>
       <c r="F249" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>400.0199890136719</v>
+        <v>397.0499877929688</v>
       </c>
       <c r="C250" t="n">
-        <v>405.1600036621094</v>
+        <v>402.2300109863281</v>
       </c>
       <c r="D250" t="n">
-        <v>395.2999877929688</v>
+        <v>395.2000122070312</v>
       </c>
       <c r="E250" t="n">
-        <v>400.9400024414062</v>
+        <v>397.1400146484375</v>
       </c>
       <c r="F250" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>397.0499877929688</v>
+        <v>392.3999938964844</v>
       </c>
       <c r="C251" t="n">
-        <v>402.2300109863281</v>
+        <v>403.8900146484375</v>
       </c>
       <c r="D251" t="n">
-        <v>395.2000122070312</v>
+        <v>390.4400024414062</v>
       </c>
       <c r="E251" t="n">
-        <v>397.1400146484375</v>
+        <v>400.8399963378906</v>
       </c>
       <c r="F251" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>405.1700134277344</v>
+      </c>
+      <c r="C252" t="n">
+        <v>406.5299987792969</v>
+      </c>
+      <c r="D252" t="n">
+        <v>378.0799865722656</v>
+      </c>
+      <c r="E252" t="n">
+        <v>393.0599975585938</v>
+      </c>
       <c r="F252" t="n">
-        <v>5545894</v>
+        <v>7735200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10522,34 +10530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>393.06</v>
+      </c>
+      <c r="D2" t="n">
         <v>400.84</v>
       </c>
-      <c r="D2" t="n">
-        <v>397.14</v>
-      </c>
       <c r="E2" t="n">
-        <v>392.4</v>
+        <v>405.17</v>
       </c>
       <c r="F2" t="n">
-        <v>403.7992</v>
+        <v>406.53</v>
       </c>
       <c r="G2" t="n">
-        <v>390.555</v>
+        <v>378.0801</v>
       </c>
       <c r="H2" t="n">
-        <v>5545894</v>
+        <v>7730118</v>
       </c>
       <c r="I2" t="n">
-        <v>5323698</v>
+        <v>5278940</v>
       </c>
       <c r="J2" t="n">
-        <v>359791919104</v>
+        <v>352808632320</v>
       </c>
       <c r="K2" t="n">
-        <v>25.74438</v>
+        <v>25.244701</v>
       </c>
       <c r="L2" t="n">
-        <v>17.866432</v>
+        <v>17.519657</v>
       </c>
       <c r="M2" t="n">
         <v>15.57</v>
@@ -10564,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10588,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.6848347</v>
+        <v>3.6133149</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10600,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>409153929216</v>
+        <v>402170642432</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10627,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:28</t>
+          <t>2026-09-10 18:59:46</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>336.5466531982527</v>
+        <v>339.8969161546314</v>
       </c>
       <c r="C2" t="n">
-        <v>339.4781519824642</v>
+        <v>351.5644485034896</v>
       </c>
       <c r="D2" t="n">
-        <v>332.4951561509477</v>
+        <v>336.8193359260115</v>
       </c>
       <c r="E2" t="n">
-        <v>337.7348327636719</v>
+        <v>344.3866577148438</v>
       </c>
       <c r="F2" t="n">
-        <v>17804300</v>
+        <v>18943500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>339.8969161546314</v>
+        <v>346.6169614598537</v>
       </c>
       <c r="C3" t="n">
-        <v>351.5644485034896</v>
+        <v>352.8597713233265</v>
       </c>
       <c r="D3" t="n">
-        <v>336.8193359260115</v>
+        <v>343.2666855000246</v>
       </c>
       <c r="E3" t="n">
-        <v>344.3866577148438</v>
+        <v>343.3153991699219</v>
       </c>
       <c r="F3" t="n">
-        <v>18943500</v>
+        <v>14016200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>346.6169614598537</v>
+        <v>344.2562617205344</v>
       </c>
       <c r="C4" t="n">
-        <v>352.8597713233265</v>
+        <v>344.6972712574788</v>
       </c>
       <c r="D4" t="n">
-        <v>343.2666855000246</v>
+        <v>335.7003177947291</v>
       </c>
       <c r="E4" t="n">
-        <v>343.3153991699219</v>
+        <v>340.9534606933594</v>
       </c>
       <c r="F4" t="n">
-        <v>14016200</v>
+        <v>11035900</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>344.2562617205344</v>
+        <v>340.5711991051483</v>
       </c>
       <c r="C5" t="n">
-        <v>344.6972712574788</v>
+        <v>342.0805014268064</v>
       </c>
       <c r="D5" t="n">
-        <v>335.7003177947291</v>
+        <v>331.5742462609258</v>
       </c>
       <c r="E5" t="n">
-        <v>340.9534606933594</v>
+        <v>333.005126953125</v>
       </c>
       <c r="F5" t="n">
-        <v>11035900</v>
+        <v>12695800</v>
       </c>
       <c r="G5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>340.5711991051483</v>
+        <v>330.9568224057415</v>
       </c>
       <c r="C6" t="n">
-        <v>342.0805014268064</v>
+        <v>336.1609442520178</v>
       </c>
       <c r="D6" t="n">
-        <v>331.5742462609258</v>
+        <v>330.9568224057415</v>
       </c>
       <c r="E6" t="n">
-        <v>333.005126953125</v>
+        <v>334.7986450195312</v>
       </c>
       <c r="F6" t="n">
-        <v>12695800</v>
+        <v>8467700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>330.9568525731296</v>
+        <v>336.6803662104043</v>
       </c>
       <c r="C7" t="n">
-        <v>336.1609748937723</v>
+        <v>338.0524456778033</v>
       </c>
       <c r="D7" t="n">
-        <v>330.9568525731296</v>
+        <v>327.4579882805058</v>
       </c>
       <c r="E7" t="n">
-        <v>334.7986755371094</v>
+        <v>328.14404296875</v>
       </c>
       <c r="F7" t="n">
-        <v>8467700</v>
+        <v>11255600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>336.6803662104043</v>
+        <v>329.7905316198508</v>
       </c>
       <c r="C8" t="n">
-        <v>338.0524456778033</v>
+        <v>334.161595373165</v>
       </c>
       <c r="D8" t="n">
-        <v>327.4579882805058</v>
+        <v>327.1835657302883</v>
       </c>
       <c r="E8" t="n">
-        <v>328.14404296875</v>
+        <v>329.9767456054688</v>
       </c>
       <c r="F8" t="n">
-        <v>11255600</v>
+        <v>13656800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>329.7905316198508</v>
+        <v>327.7912281730855</v>
       </c>
       <c r="C9" t="n">
-        <v>334.161595373165</v>
+        <v>335.6513373618812</v>
       </c>
       <c r="D9" t="n">
-        <v>327.1835657302883</v>
+        <v>325.9683288776566</v>
       </c>
       <c r="E9" t="n">
-        <v>329.9767456054688</v>
+        <v>334.4948425292969</v>
       </c>
       <c r="F9" t="n">
-        <v>13656800</v>
+        <v>8903700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>327.7911982671105</v>
+        <v>334.2008052062361</v>
       </c>
       <c r="C10" t="n">
-        <v>335.6513067387905</v>
+        <v>345.6675310141911</v>
       </c>
       <c r="D10" t="n">
-        <v>325.9682991379935</v>
+        <v>333.1815333788629</v>
       </c>
       <c r="E10" t="n">
-        <v>334.4948120117188</v>
+        <v>340.7574157714844</v>
       </c>
       <c r="F10" t="n">
-        <v>8903700</v>
+        <v>12504100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>334.2008052062361</v>
+        <v>343.217373716776</v>
       </c>
       <c r="C11" t="n">
-        <v>345.6675310141911</v>
+        <v>347.4316240476539</v>
       </c>
       <c r="D11" t="n">
-        <v>333.1815333788629</v>
+        <v>340.9044142070616</v>
       </c>
       <c r="E11" t="n">
-        <v>340.7574157714844</v>
+        <v>344.7952575683594</v>
       </c>
       <c r="F11" t="n">
-        <v>12504100</v>
+        <v>9016300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>343.2174040946968</v>
+        <v>341.9432916493518</v>
       </c>
       <c r="C12" t="n">
-        <v>347.4316547985749</v>
+        <v>343.2075787683629</v>
       </c>
       <c r="D12" t="n">
-        <v>340.904444380264</v>
+        <v>336.7489800892123</v>
       </c>
       <c r="E12" t="n">
-        <v>344.7952880859375</v>
+        <v>338.6698913574219</v>
       </c>
       <c r="F12" t="n">
-        <v>9016300</v>
+        <v>8104900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>341.9432916493518</v>
+        <v>340.9926010114185</v>
       </c>
       <c r="C13" t="n">
-        <v>343.2075787683629</v>
+        <v>342.9919337348455</v>
       </c>
       <c r="D13" t="n">
-        <v>336.7489800892123</v>
+        <v>334.4947920920956</v>
       </c>
       <c r="E13" t="n">
-        <v>338.6698913574219</v>
+        <v>337.2193603515625</v>
       </c>
       <c r="F13" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>340.9926010114185</v>
+        <v>337.1214299699541</v>
       </c>
       <c r="C14" t="n">
-        <v>342.9919337348455</v>
+        <v>338.6601031752857</v>
       </c>
       <c r="D14" t="n">
-        <v>334.4947920920956</v>
+        <v>334.641876568426</v>
       </c>
       <c r="E14" t="n">
-        <v>337.2193603515625</v>
+        <v>338.2974853515625</v>
       </c>
       <c r="F14" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>337.1213995584671</v>
+        <v>336.8959869118207</v>
       </c>
       <c r="C15" t="n">
-        <v>338.6600726249961</v>
+        <v>342.3549341542898</v>
       </c>
       <c r="D15" t="n">
-        <v>334.6418463806178</v>
+        <v>335.5042870567964</v>
       </c>
       <c r="E15" t="n">
-        <v>338.2974548339844</v>
+        <v>338.4150695800781</v>
       </c>
       <c r="F15" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>336.8959869118207</v>
+        <v>337.042992446128</v>
       </c>
       <c r="C16" t="n">
-        <v>342.3549341542898</v>
+        <v>341.7473034781017</v>
       </c>
       <c r="D16" t="n">
-        <v>335.5042870567964</v>
+        <v>334.8182646079004</v>
       </c>
       <c r="E16" t="n">
-        <v>338.4150695800781</v>
+        <v>341.3552551269531</v>
       </c>
       <c r="F16" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>337.042992446128</v>
+        <v>340.3653902924742</v>
       </c>
       <c r="C17" t="n">
-        <v>341.7473034781017</v>
+        <v>348.000043885751</v>
       </c>
       <c r="D17" t="n">
-        <v>334.8182646079004</v>
+        <v>337.7780149171845</v>
       </c>
       <c r="E17" t="n">
-        <v>341.3552551269531</v>
+        <v>346.6671752929688</v>
       </c>
       <c r="F17" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>340.3654202552976</v>
+        <v>350.126813283771</v>
       </c>
       <c r="C18" t="n">
-        <v>348.0000745206634</v>
+        <v>360.6624696666976</v>
       </c>
       <c r="D18" t="n">
-        <v>337.7780446522378</v>
+        <v>349.4995598497266</v>
       </c>
       <c r="E18" t="n">
-        <v>346.6672058105469</v>
+        <v>353.0180053710938</v>
       </c>
       <c r="F18" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>350.126813283771</v>
+        <v>353.8314638081978</v>
       </c>
       <c r="C19" t="n">
-        <v>360.6624696666976</v>
+        <v>355.2917453013463</v>
       </c>
       <c r="D19" t="n">
-        <v>349.4995598497266</v>
+        <v>349.9896110702735</v>
       </c>
       <c r="E19" t="n">
-        <v>353.0180053710938</v>
+        <v>351.6165161132812</v>
       </c>
       <c r="F19" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>353.8314330983794</v>
+        <v>352.243767379212</v>
       </c>
       <c r="C20" t="n">
-        <v>355.2917144647868</v>
+        <v>357.4478894842047</v>
       </c>
       <c r="D20" t="n">
-        <v>349.9895806938981</v>
+        <v>350.9206788979734</v>
       </c>
       <c r="E20" t="n">
-        <v>351.6164855957031</v>
+        <v>356.4090270996094</v>
       </c>
       <c r="F20" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>352.2437372182849</v>
+        <v>359.613786634634</v>
       </c>
       <c r="C21" t="n">
-        <v>357.4478588776738</v>
+        <v>367.1602685308417</v>
       </c>
       <c r="D21" t="n">
-        <v>350.9206488503359</v>
+        <v>358.5063128850491</v>
       </c>
       <c r="E21" t="n">
-        <v>356.4089965820312</v>
+        <v>362.544189453125</v>
       </c>
       <c r="F21" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>359.613786634634</v>
+        <v>365.0923551123336</v>
       </c>
       <c r="C22" t="n">
-        <v>367.1602685308417</v>
+        <v>368.7185931947143</v>
       </c>
       <c r="D22" t="n">
-        <v>358.5063128850491</v>
+        <v>358.7807591507652</v>
       </c>
       <c r="E22" t="n">
-        <v>362.544189453125</v>
+        <v>360.3586730957031</v>
       </c>
       <c r="F22" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>365.0923241938757</v>
+        <v>362.0345442209324</v>
       </c>
       <c r="C23" t="n">
-        <v>368.7185619691624</v>
+        <v>362.0345442209324</v>
       </c>
       <c r="D23" t="n">
-        <v>358.7807287668154</v>
+        <v>345.4813287153903</v>
       </c>
       <c r="E23" t="n">
-        <v>360.358642578125</v>
+        <v>347.431640625</v>
       </c>
       <c r="F23" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>362.0345124206696</v>
+        <v>347.6668450586018</v>
       </c>
       <c r="C24" t="n">
-        <v>362.0345124206696</v>
+        <v>351.9987280315978</v>
       </c>
       <c r="D24" t="n">
-        <v>345.481298369123</v>
+        <v>346.2751751256885</v>
       </c>
       <c r="E24" t="n">
-        <v>347.4316101074219</v>
+        <v>351.5086975097656</v>
       </c>
       <c r="F24" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>347.6668450586018</v>
+        <v>347.8726721794402</v>
       </c>
       <c r="C25" t="n">
-        <v>351.9987280315978</v>
+        <v>355.1054974076654</v>
       </c>
       <c r="D25" t="n">
-        <v>346.2751751256885</v>
+        <v>346.3535596478916</v>
       </c>
       <c r="E25" t="n">
-        <v>351.5086975097656</v>
+        <v>352.7533569335938</v>
       </c>
       <c r="F25" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>347.8726721794402</v>
+        <v>352.2241789356418</v>
       </c>
       <c r="C26" t="n">
-        <v>355.1054974076654</v>
+        <v>356.9578609672659</v>
       </c>
       <c r="D26" t="n">
-        <v>346.3535596478916</v>
+        <v>348.7547542094708</v>
       </c>
       <c r="E26" t="n">
-        <v>352.7533569335938</v>
+        <v>353.9490661621094</v>
       </c>
       <c r="F26" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>352.224118197926</v>
+        <v>354.6252788942206</v>
       </c>
       <c r="C27" t="n">
-        <v>356.9577994132716</v>
+        <v>354.7820922478407</v>
       </c>
       <c r="D27" t="n">
-        <v>348.7546940700243</v>
+        <v>347.3336224508748</v>
       </c>
       <c r="E27" t="n">
-        <v>353.9490051269531</v>
+        <v>349.5583801269531</v>
       </c>
       <c r="F27" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>354.6252788942206</v>
+        <v>344.0013987080436</v>
       </c>
       <c r="C28" t="n">
-        <v>354.7820922478407</v>
+        <v>351.2440635956089</v>
       </c>
       <c r="D28" t="n">
-        <v>347.3336224508748</v>
+        <v>343.8347751839987</v>
       </c>
       <c r="E28" t="n">
-        <v>349.5583801269531</v>
+        <v>349.48974609375</v>
       </c>
       <c r="F28" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>344.0014287463771</v>
+        <v>351.3911117321571</v>
       </c>
       <c r="C29" t="n">
-        <v>351.2440942663747</v>
+        <v>358.2809400014152</v>
       </c>
       <c r="D29" t="n">
-        <v>343.8348052077826</v>
+        <v>350.3816500053927</v>
       </c>
       <c r="E29" t="n">
-        <v>349.4897766113281</v>
+        <v>357.2126770019531</v>
       </c>
       <c r="F29" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>351.3911117321571</v>
+        <v>357.8594745050165</v>
       </c>
       <c r="C30" t="n">
-        <v>358.2809400014152</v>
+        <v>363.6516084782733</v>
       </c>
       <c r="D30" t="n">
-        <v>350.3816500053927</v>
+        <v>354.2920382421501</v>
       </c>
       <c r="E30" t="n">
-        <v>357.2126770019531</v>
+        <v>358.0848693847656</v>
       </c>
       <c r="F30" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>357.8595050033854</v>
+        <v>356.7029783280342</v>
       </c>
       <c r="C31" t="n">
-        <v>363.6516394702736</v>
+        <v>356.7421891409456</v>
       </c>
       <c r="D31" t="n">
-        <v>354.2920684364863</v>
+        <v>350.8618233858751</v>
       </c>
       <c r="E31" t="n">
-        <v>358.0848999023438</v>
+        <v>354.2822265625</v>
       </c>
       <c r="F31" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>356.7029783280342</v>
+        <v>348.4901083853841</v>
       </c>
       <c r="C32" t="n">
-        <v>356.7421891409456</v>
+        <v>355.0565296362527</v>
       </c>
       <c r="D32" t="n">
-        <v>350.8618233858751</v>
+        <v>346.5888173917132</v>
       </c>
       <c r="E32" t="n">
-        <v>354.2822265625</v>
+        <v>353.2630310058594</v>
       </c>
       <c r="F32" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>348.4900782801277</v>
+        <v>354.1646210665127</v>
       </c>
       <c r="C33" t="n">
-        <v>355.0564989637384</v>
+        <v>358.1338858633925</v>
       </c>
       <c r="D33" t="n">
-        <v>346.588787450705</v>
+        <v>352.8513429813036</v>
       </c>
       <c r="E33" t="n">
-        <v>353.2630004882812</v>
+        <v>355.2720947265625</v>
       </c>
       <c r="F33" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>354.1646514889598</v>
+        <v>356.252207496177</v>
       </c>
       <c r="C34" t="n">
-        <v>358.1339166267961</v>
+        <v>358.9179748669274</v>
       </c>
       <c r="D34" t="n">
-        <v>352.8513732909411</v>
+        <v>354.1940732179572</v>
       </c>
       <c r="E34" t="n">
-        <v>355.2721252441406</v>
+        <v>358.6827697753906</v>
       </c>
       <c r="F34" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>356.2521771853968</v>
+        <v>373.0896257903608</v>
       </c>
       <c r="C35" t="n">
-        <v>358.9179443293374</v>
+        <v>373.4032524981995</v>
       </c>
       <c r="D35" t="n">
-        <v>354.194043082288</v>
+        <v>351.4792920385495</v>
       </c>
       <c r="E35" t="n">
-        <v>358.6827392578125</v>
+        <v>360.5056457519531</v>
       </c>
       <c r="F35" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>373.0896257903608</v>
+        <v>357.0166226761716</v>
       </c>
       <c r="C36" t="n">
-        <v>373.4032524981995</v>
+        <v>358.8493319750526</v>
       </c>
       <c r="D36" t="n">
-        <v>351.4792920385495</v>
+        <v>346.8239941782638</v>
       </c>
       <c r="E36" t="n">
-        <v>360.5056457519531</v>
+        <v>348.1764831542969</v>
       </c>
       <c r="F36" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>357.0166226761716</v>
+        <v>340.5908266262187</v>
       </c>
       <c r="C37" t="n">
-        <v>358.8493319750526</v>
+        <v>347.4708747692525</v>
       </c>
       <c r="D37" t="n">
-        <v>346.8239941782638</v>
+        <v>336.7490038190758</v>
       </c>
       <c r="E37" t="n">
-        <v>348.1764831542969</v>
+        <v>337.8760681152344</v>
       </c>
       <c r="F37" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>340.5908266262187</v>
+        <v>337.5232539470514</v>
       </c>
       <c r="C38" t="n">
-        <v>347.4708747692525</v>
+        <v>339.3755538588451</v>
       </c>
       <c r="D38" t="n">
-        <v>336.7490038190758</v>
+        <v>330.3981906639274</v>
       </c>
       <c r="E38" t="n">
-        <v>337.8760681152344</v>
+        <v>334.7496643066406</v>
       </c>
       <c r="F38" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>337.5232231766179</v>
+        <v>332.3681048776954</v>
       </c>
       <c r="C39" t="n">
-        <v>339.3755229195461</v>
+        <v>333.9068078868114</v>
       </c>
       <c r="D39" t="n">
-        <v>330.398160543053</v>
+        <v>320.0879412577473</v>
       </c>
       <c r="E39" t="n">
-        <v>334.7496337890625</v>
+        <v>327.1345825195312</v>
       </c>
       <c r="F39" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>332.3681048776954</v>
+        <v>321.0974041522996</v>
       </c>
       <c r="C40" t="n">
-        <v>333.9068078868114</v>
+        <v>329.7905408141606</v>
       </c>
       <c r="D40" t="n">
-        <v>320.0879412577473</v>
+        <v>320.6759850821896</v>
       </c>
       <c r="E40" t="n">
-        <v>327.1345825195312</v>
+        <v>324.2335815429688</v>
       </c>
       <c r="F40" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>321.0974041522996</v>
+        <v>319.7939098851405</v>
       </c>
       <c r="C41" t="n">
-        <v>329.7905408141606</v>
+        <v>323.6259521945154</v>
       </c>
       <c r="D41" t="n">
-        <v>320.6759850821896</v>
+        <v>317.7553960532753</v>
       </c>
       <c r="E41" t="n">
-        <v>324.2335815429688</v>
+        <v>321.2052001953125</v>
       </c>
       <c r="F41" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>319.7939098851405</v>
+        <v>322.3617025788201</v>
       </c>
       <c r="C42" t="n">
-        <v>323.6259521945154</v>
+        <v>325.7428953487219</v>
       </c>
       <c r="D42" t="n">
-        <v>317.7553960532753</v>
+        <v>315.0406451379028</v>
       </c>
       <c r="E42" t="n">
-        <v>321.2052001953125</v>
+        <v>315.1484375</v>
       </c>
       <c r="F42" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>322.3616713627413</v>
+        <v>313.2863393626572</v>
       </c>
       <c r="C43" t="n">
-        <v>325.7428638052234</v>
+        <v>318.0788226584959</v>
       </c>
       <c r="D43" t="n">
-        <v>315.0406146307628</v>
+        <v>307.8960032344128</v>
       </c>
       <c r="E43" t="n">
-        <v>315.1484069824219</v>
+        <v>317.74560546875</v>
       </c>
       <c r="F43" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>313.2863092733651</v>
+        <v>313.6097362529</v>
       </c>
       <c r="C44" t="n">
-        <v>318.0787921089143</v>
+        <v>317.7848060357201</v>
       </c>
       <c r="D44" t="n">
-        <v>307.8959736628304</v>
+        <v>310.8459867308537</v>
       </c>
       <c r="E44" t="n">
-        <v>317.7455749511719</v>
+        <v>315.1680297851562</v>
       </c>
       <c r="F44" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>313.6097058862107</v>
+        <v>316.8537128676349</v>
       </c>
       <c r="C45" t="n">
-        <v>317.7847752647608</v>
+        <v>321.3227886847148</v>
       </c>
       <c r="D45" t="n">
-        <v>310.8459566317771</v>
+        <v>313.5019209593692</v>
       </c>
       <c r="E45" t="n">
-        <v>315.1679992675781</v>
+        <v>320.9209899902344</v>
       </c>
       <c r="F45" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>316.8537128676349</v>
+        <v>321.9010364932658</v>
       </c>
       <c r="C46" t="n">
-        <v>321.3227886847148</v>
+        <v>336.3275351202159</v>
       </c>
       <c r="D46" t="n">
-        <v>313.5019209593692</v>
+        <v>320.5583278451826</v>
       </c>
       <c r="E46" t="n">
-        <v>320.9209899902344</v>
+        <v>332.2994689941406</v>
       </c>
       <c r="F46" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>321.9010364932658</v>
+        <v>331.6036653013031</v>
       </c>
       <c r="C47" t="n">
-        <v>336.3275351202159</v>
+        <v>332.2700996432553</v>
       </c>
       <c r="D47" t="n">
-        <v>320.5583278451826</v>
+        <v>324.6844366173477</v>
       </c>
       <c r="E47" t="n">
-        <v>332.2994689941406</v>
+        <v>325.889892578125</v>
       </c>
       <c r="F47" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>331.6036653013031</v>
+        <v>320.4309500487702</v>
       </c>
       <c r="C48" t="n">
-        <v>332.2700996432553</v>
+        <v>321.6658065479886</v>
       </c>
       <c r="D48" t="n">
-        <v>324.6844366173477</v>
+        <v>314.0997345701073</v>
       </c>
       <c r="E48" t="n">
-        <v>325.889892578125</v>
+        <v>315.4424133300781</v>
       </c>
       <c r="F48" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>320.4309500487702</v>
+        <v>314.2075720220705</v>
       </c>
       <c r="C49" t="n">
-        <v>321.6658065479886</v>
+        <v>321.3424151200708</v>
       </c>
       <c r="D49" t="n">
-        <v>314.0997345701073</v>
+        <v>313.06088745762</v>
       </c>
       <c r="E49" t="n">
-        <v>315.4424133300781</v>
+        <v>314.129150390625</v>
       </c>
       <c r="F49" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>314.2075720220705</v>
+        <v>310.6891466030926</v>
       </c>
       <c r="C50" t="n">
-        <v>321.3424151200708</v>
+        <v>311.1693669212913</v>
       </c>
       <c r="D50" t="n">
-        <v>313.06088745762</v>
+        <v>302.6134236399317</v>
       </c>
       <c r="E50" t="n">
-        <v>314.129150390625</v>
+        <v>307.3275146484375</v>
       </c>
       <c r="F50" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>310.6891466030926</v>
+        <v>307.6705548284651</v>
       </c>
       <c r="C51" t="n">
-        <v>311.1693669212913</v>
+        <v>308.7192273184903</v>
       </c>
       <c r="D51" t="n">
-        <v>302.6134236399317</v>
+        <v>298.4579870426836</v>
       </c>
       <c r="E51" t="n">
-        <v>307.3275146484375</v>
+        <v>302.9270629882812</v>
       </c>
       <c r="F51" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>307.6705238330165</v>
+        <v>304.6127916915999</v>
       </c>
       <c r="C52" t="n">
-        <v>308.7191962173961</v>
+        <v>308.4742348638782</v>
       </c>
       <c r="D52" t="n">
-        <v>298.4579569753306</v>
+        <v>303.8189445839627</v>
       </c>
       <c r="E52" t="n">
-        <v>302.9270324707031</v>
+        <v>305.3282470703125</v>
       </c>
       <c r="F52" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>304.6127612455315</v>
+        <v>305.6908291650661</v>
       </c>
       <c r="C53" t="n">
-        <v>308.4742040318584</v>
+        <v>317.3829496811602</v>
       </c>
       <c r="D53" t="n">
-        <v>303.8189142172394</v>
+        <v>305.23019930011</v>
       </c>
       <c r="E53" t="n">
-        <v>305.3282165527344</v>
+        <v>313.5901184082031</v>
       </c>
       <c r="F53" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>305.6908589139109</v>
+        <v>318.0592220645265</v>
       </c>
       <c r="C54" t="n">
-        <v>317.3829805678444</v>
+        <v>319.3529098722476</v>
       </c>
       <c r="D54" t="n">
-        <v>305.2302290041278</v>
+        <v>311.2869963920142</v>
       </c>
       <c r="E54" t="n">
-        <v>313.5901489257812</v>
+        <v>312.6884765625</v>
       </c>
       <c r="F54" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>318.0592531062754</v>
+        <v>314.71720383448</v>
       </c>
       <c r="C55" t="n">
-        <v>319.352941040257</v>
+        <v>321.4600287348608</v>
       </c>
       <c r="D55" t="n">
-        <v>311.2870267728116</v>
+        <v>314.5015892042089</v>
       </c>
       <c r="E55" t="n">
-        <v>312.6885070800781</v>
+        <v>319.7743225097656</v>
       </c>
       <c r="F55" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>314.7171737995267</v>
+        <v>320.078109327525</v>
       </c>
       <c r="C56" t="n">
-        <v>321.4599980564078</v>
+        <v>328.5066396704157</v>
       </c>
       <c r="D56" t="n">
-        <v>314.5015591898327</v>
+        <v>319.3920845924249</v>
       </c>
       <c r="E56" t="n">
-        <v>319.7742919921875</v>
+        <v>323.1358947753906</v>
       </c>
       <c r="F56" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>320.07813955632</v>
+        <v>325.0568419581102</v>
       </c>
       <c r="C57" t="n">
-        <v>328.5066706952173</v>
+        <v>325.4390501917724</v>
       </c>
       <c r="D57" t="n">
-        <v>319.3921147564304</v>
+        <v>322.3322736002218</v>
       </c>
       <c r="E57" t="n">
-        <v>323.1359252929688</v>
+        <v>323.1947021484375</v>
       </c>
       <c r="F57" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>325.0568726515205</v>
+        <v>320.6367866787963</v>
       </c>
       <c r="C58" t="n">
-        <v>325.4390809212725</v>
+        <v>323.478957830369</v>
       </c>
       <c r="D58" t="n">
-        <v>322.3323040363653</v>
+        <v>316.5891296309611</v>
       </c>
       <c r="E58" t="n">
-        <v>323.1947326660156</v>
+        <v>316.7655334472656</v>
       </c>
       <c r="F58" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>320.6367557882569</v>
+        <v>316.9223461399793</v>
       </c>
       <c r="C59" t="n">
-        <v>323.4789266660114</v>
+        <v>322.1460884369951</v>
       </c>
       <c r="D59" t="n">
-        <v>316.5890991303779</v>
+        <v>316.3637041471038</v>
       </c>
       <c r="E59" t="n">
-        <v>316.7655029296875</v>
+        <v>318.0690307617188</v>
       </c>
       <c r="F59" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>316.9223461399793</v>
+        <v>319.4998951185618</v>
       </c>
       <c r="C60" t="n">
-        <v>322.1460884369951</v>
+        <v>334.6026391486864</v>
       </c>
       <c r="D60" t="n">
-        <v>316.3637041471038</v>
+        <v>318.529644271779</v>
       </c>
       <c r="E60" t="n">
-        <v>318.0690307617188</v>
+        <v>332.9365234375</v>
       </c>
       <c r="F60" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>319.4998951185618</v>
+        <v>332.632709971988</v>
       </c>
       <c r="C61" t="n">
-        <v>334.6026391486864</v>
+        <v>334.4556390535126</v>
       </c>
       <c r="D61" t="n">
-        <v>318.529644271779</v>
+        <v>322.1656652751352</v>
       </c>
       <c r="E61" t="n">
-        <v>332.9365234375</v>
+        <v>326.8405456542969</v>
       </c>
       <c r="F61" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>332.632709971988</v>
+        <v>328.3204578992349</v>
       </c>
       <c r="C62" t="n">
-        <v>334.4556390535126</v>
+        <v>329.0162928832224</v>
       </c>
       <c r="D62" t="n">
-        <v>322.1656652751352</v>
+        <v>321.9598711365138</v>
       </c>
       <c r="E62" t="n">
-        <v>326.8405456542969</v>
+        <v>324.31201171875</v>
       </c>
       <c r="F62" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>328.3204578992349</v>
+        <v>324.3120366886073</v>
       </c>
       <c r="C63" t="n">
-        <v>329.0162928832224</v>
+        <v>324.7066908730135</v>
       </c>
       <c r="D63" t="n">
-        <v>321.9598711365138</v>
+        <v>318.5203728665016</v>
       </c>
       <c r="E63" t="n">
-        <v>324.31201171875</v>
+        <v>319.2998352050781</v>
       </c>
       <c r="F63" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,25 +2081,25 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>324.3120056919803</v>
+        <v>318.8459617269979</v>
       </c>
       <c r="C64" t="n">
-        <v>324.7066598386667</v>
+        <v>322.0032250879344</v>
       </c>
       <c r="D64" t="n">
-        <v>318.5203424234218</v>
+        <v>318.1750466501944</v>
       </c>
       <c r="E64" t="n">
-        <v>319.2998046875</v>
+        <v>319.2800903320312</v>
       </c>
       <c r="F64" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G64" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>318.8459617269979</v>
+        <v>318.4414486886093</v>
       </c>
       <c r="C65" t="n">
-        <v>322.0032250879344</v>
+        <v>324.341629514822</v>
       </c>
       <c r="D65" t="n">
-        <v>318.1750466501944</v>
+        <v>315.3335056374652</v>
       </c>
       <c r="E65" t="n">
-        <v>319.2800903320312</v>
+        <v>323.9864196777344</v>
       </c>
       <c r="F65" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>318.4414486886093</v>
+        <v>325.9597199441495</v>
       </c>
       <c r="C66" t="n">
-        <v>324.341629514822</v>
+        <v>334.7211811769636</v>
       </c>
       <c r="D66" t="n">
-        <v>315.3335056374652</v>
+        <v>324.3712270965368</v>
       </c>
       <c r="E66" t="n">
-        <v>323.9864196777344</v>
+        <v>332.2348327636719</v>
       </c>
       <c r="F66" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>325.9596900029746</v>
+        <v>332.9945215393808</v>
       </c>
       <c r="C67" t="n">
-        <v>334.7211504310009</v>
+        <v>340.3746776267931</v>
       </c>
       <c r="D67" t="n">
-        <v>324.3711973012736</v>
+        <v>332.8662521653069</v>
       </c>
       <c r="E67" t="n">
-        <v>332.2348022460938</v>
+        <v>337.2765808105469</v>
       </c>
       <c r="F67" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>332.9945516695081</v>
+        <v>336.4379310634787</v>
       </c>
       <c r="C68" t="n">
-        <v>340.3747084246943</v>
+        <v>340.3549345980833</v>
       </c>
       <c r="D68" t="n">
-        <v>332.8662822838281</v>
+        <v>332.5012053593197</v>
       </c>
       <c r="E68" t="n">
-        <v>337.276611328125</v>
+        <v>336.5464782714844</v>
       </c>
       <c r="F68" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>336.4379310634787</v>
+        <v>335.875584402924</v>
       </c>
       <c r="C69" t="n">
-        <v>340.3549345980833</v>
+        <v>336.4379523174861</v>
       </c>
       <c r="D69" t="n">
-        <v>332.5012053593197</v>
+        <v>326.6109215358994</v>
       </c>
       <c r="E69" t="n">
-        <v>336.5464782714844</v>
+        <v>329.7386169433594</v>
       </c>
       <c r="F69" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>335.875584402924</v>
+        <v>329.1564601038647</v>
       </c>
       <c r="C70" t="n">
-        <v>336.4379523174861</v>
+        <v>331.0409661792534</v>
       </c>
       <c r="D70" t="n">
-        <v>326.6109215358994</v>
+        <v>326.0682693196749</v>
       </c>
       <c r="E70" t="n">
-        <v>329.7386169433594</v>
+        <v>327.2029113769531</v>
       </c>
       <c r="F70" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>329.1564601038647</v>
+        <v>324.5389231377919</v>
       </c>
       <c r="C71" t="n">
-        <v>331.0409661792534</v>
+        <v>325.7722361921053</v>
       </c>
       <c r="D71" t="n">
-        <v>326.0682693196749</v>
+        <v>320.2371416572342</v>
       </c>
       <c r="E71" t="n">
-        <v>327.2029113769531</v>
+        <v>323.7594909667969</v>
       </c>
       <c r="F71" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>324.5389537288393</v>
+        <v>323.6805434123363</v>
       </c>
       <c r="C72" t="n">
-        <v>325.7722668994048</v>
+        <v>330.1332457701224</v>
       </c>
       <c r="D72" t="n">
-        <v>320.2371718427956</v>
+        <v>321.7171186569828</v>
       </c>
       <c r="E72" t="n">
-        <v>323.759521484375</v>
+        <v>323.0491027832031</v>
       </c>
       <c r="F72" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>323.6805434123363</v>
+        <v>318.5894351738589</v>
       </c>
       <c r="C73" t="n">
-        <v>330.1332457701224</v>
+        <v>325.3973174895482</v>
       </c>
       <c r="D73" t="n">
-        <v>321.7171186569828</v>
+        <v>317.3561220691985</v>
       </c>
       <c r="E73" t="n">
-        <v>323.0491027832031</v>
+        <v>320.8192749023438</v>
       </c>
       <c r="F73" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>318.5894351738589</v>
+        <v>319.6747419864576</v>
       </c>
       <c r="C74" t="n">
-        <v>325.3973174895482</v>
+        <v>323.4240016076582</v>
       </c>
       <c r="D74" t="n">
-        <v>317.3561220691985</v>
+        <v>319.4379555165406</v>
       </c>
       <c r="E74" t="n">
-        <v>320.8192749023438</v>
+        <v>320.4640502929688</v>
       </c>
       <c r="F74" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>319.6747419864576</v>
+        <v>320.8587672253223</v>
       </c>
       <c r="C75" t="n">
-        <v>323.4240016076582</v>
+        <v>324.5981510876156</v>
       </c>
       <c r="D75" t="n">
-        <v>319.4379555165406</v>
+        <v>319.8030439224821</v>
       </c>
       <c r="E75" t="n">
-        <v>320.4640502929688</v>
+        <v>323.2069702148438</v>
       </c>
       <c r="F75" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>320.8587369294642</v>
+        <v>322.8320412014528</v>
       </c>
       <c r="C76" t="n">
-        <v>324.5981204386806</v>
+        <v>327.4594342482506</v>
       </c>
       <c r="D76" t="n">
-        <v>319.8030137263066</v>
+        <v>321.9045873641298</v>
       </c>
       <c r="E76" t="n">
-        <v>323.2069396972656</v>
+        <v>327.4002075195312</v>
       </c>
       <c r="F76" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>322.8320412014528</v>
+        <v>326.4728087048146</v>
       </c>
       <c r="C77" t="n">
-        <v>327.4594342482506</v>
+        <v>329.787940036587</v>
       </c>
       <c r="D77" t="n">
-        <v>321.9045873641298</v>
+        <v>323.8976351612195</v>
       </c>
       <c r="E77" t="n">
-        <v>327.4002075195312</v>
+        <v>324.548828125</v>
       </c>
       <c r="F77" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>326.4727780063231</v>
+        <v>325.3282463216964</v>
       </c>
       <c r="C78" t="n">
-        <v>329.787909026371</v>
+        <v>331.6625250102778</v>
       </c>
       <c r="D78" t="n">
-        <v>323.8976047048735</v>
+        <v>325.1111820298963</v>
       </c>
       <c r="E78" t="n">
-        <v>324.5487976074219</v>
+        <v>327.7257995605469</v>
       </c>
       <c r="F78" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>325.3282766160162</v>
+        <v>327.8837053458195</v>
       </c>
       <c r="C79" t="n">
-        <v>331.6625558944407</v>
+        <v>328.8802018879278</v>
       </c>
       <c r="D79" t="n">
-        <v>325.1112123040032</v>
+        <v>325.4762756879338</v>
       </c>
       <c r="E79" t="n">
-        <v>327.725830078125</v>
+        <v>325.7031860351562</v>
       </c>
       <c r="F79" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>327.8837053458195</v>
+        <v>326.4826326508298</v>
       </c>
       <c r="C80" t="n">
-        <v>328.8802018879278</v>
+        <v>335.717696654991</v>
       </c>
       <c r="D80" t="n">
-        <v>325.4762756879338</v>
+        <v>323.1280270938765</v>
       </c>
       <c r="E80" t="n">
-        <v>325.7031860351562</v>
+        <v>331.9092102050781</v>
       </c>
       <c r="F80" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>326.4826326508298</v>
+        <v>330.9719222150325</v>
       </c>
       <c r="C81" t="n">
-        <v>335.717696654991</v>
+        <v>342.3085268229226</v>
       </c>
       <c r="D81" t="n">
-        <v>323.1280270938765</v>
+        <v>329.3932753932535</v>
       </c>
       <c r="E81" t="n">
-        <v>331.9092102050781</v>
+        <v>337.4541931152344</v>
       </c>
       <c r="F81" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>330.9719222150325</v>
+        <v>343.6996829189171</v>
       </c>
       <c r="C82" t="n">
-        <v>342.3085268229226</v>
+        <v>347.9027932709801</v>
       </c>
       <c r="D82" t="n">
-        <v>329.3932753932535</v>
+        <v>340.5127911940015</v>
       </c>
       <c r="E82" t="n">
-        <v>337.4541931152344</v>
+        <v>344.3114013671875</v>
       </c>
       <c r="F82" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>343.6996829189171</v>
+        <v>344.3213032237757</v>
       </c>
       <c r="C83" t="n">
-        <v>347.9027932709801</v>
+        <v>345.4361929991165</v>
       </c>
       <c r="D83" t="n">
-        <v>340.5127911940015</v>
+        <v>333.527344316932</v>
       </c>
       <c r="E83" t="n">
-        <v>344.3114013671875</v>
+        <v>337.1384887695312</v>
       </c>
       <c r="F83" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>344.3213032237757</v>
+        <v>336.4576913463828</v>
       </c>
       <c r="C84" t="n">
-        <v>345.4361929991165</v>
+        <v>343.2556975271264</v>
       </c>
       <c r="D84" t="n">
-        <v>333.527344316932</v>
+        <v>336.2504730653109</v>
       </c>
       <c r="E84" t="n">
-        <v>337.1384887695312</v>
+        <v>342.2197265625</v>
       </c>
       <c r="F84" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>336.4576913463828</v>
+        <v>342.6143671222478</v>
       </c>
       <c r="C85" t="n">
-        <v>343.2556975271264</v>
+        <v>344.4002020193836</v>
       </c>
       <c r="D85" t="n">
-        <v>336.2504730653109</v>
+        <v>337.9080553379447</v>
       </c>
       <c r="E85" t="n">
-        <v>342.2197265625</v>
+        <v>339.3880310058594</v>
       </c>
       <c r="F85" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>342.6143979299363</v>
+        <v>336.8622415935578</v>
       </c>
       <c r="C86" t="n">
-        <v>344.4002329876533</v>
+        <v>338.0758024907637</v>
       </c>
       <c r="D86" t="n">
-        <v>337.9080857224443</v>
+        <v>329.4820846932586</v>
       </c>
       <c r="E86" t="n">
-        <v>339.3880615234375</v>
+        <v>335.9643859863281</v>
       </c>
       <c r="F86" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>336.8622109944222</v>
+        <v>336.9411188846722</v>
       </c>
       <c r="C87" t="n">
-        <v>338.0757717813934</v>
+        <v>337.2765764147031</v>
       </c>
       <c r="D87" t="n">
-        <v>329.4820547645052</v>
+        <v>328.4065987621919</v>
       </c>
       <c r="E87" t="n">
-        <v>335.96435546875</v>
+        <v>329.47216796875</v>
       </c>
       <c r="F87" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>336.9411188846722</v>
+        <v>330.8929641448377</v>
       </c>
       <c r="C88" t="n">
-        <v>337.2765764147031</v>
+        <v>335.5696777492312</v>
       </c>
       <c r="D88" t="n">
-        <v>328.4065987621919</v>
+        <v>329.639928884428</v>
       </c>
       <c r="E88" t="n">
-        <v>329.47216796875</v>
+        <v>330.4884338378906</v>
       </c>
       <c r="F88" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>330.8929641448377</v>
+        <v>330.7252428593728</v>
       </c>
       <c r="C89" t="n">
-        <v>335.5696777492312</v>
+        <v>334.9185072715596</v>
       </c>
       <c r="D89" t="n">
-        <v>329.639928884428</v>
+        <v>323.6805441940115</v>
       </c>
       <c r="E89" t="n">
-        <v>330.4884338378906</v>
+        <v>334.4350280761719</v>
       </c>
       <c r="F89" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>330.7252730384288</v>
+        <v>330.3897780779105</v>
       </c>
       <c r="C90" t="n">
-        <v>334.9185378332558</v>
+        <v>331.7119162692861</v>
       </c>
       <c r="D90" t="n">
-        <v>323.6805737302307</v>
+        <v>326.0189235086448</v>
       </c>
       <c r="E90" t="n">
-        <v>334.43505859375</v>
+        <v>326.6010437011719</v>
       </c>
       <c r="F90" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>330.3897780779105</v>
+        <v>323.0293559592084</v>
       </c>
       <c r="C91" t="n">
-        <v>331.7119162692861</v>
+        <v>335.3526407320732</v>
       </c>
       <c r="D91" t="n">
-        <v>326.0189235086448</v>
+        <v>322.1413765634589</v>
       </c>
       <c r="E91" t="n">
-        <v>326.6010437011719</v>
+        <v>333.912109375</v>
       </c>
       <c r="F91" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>323.0293559592084</v>
+        <v>334.8987575018528</v>
       </c>
       <c r="C92" t="n">
-        <v>335.3526407320732</v>
+        <v>343.4332779356386</v>
       </c>
       <c r="D92" t="n">
-        <v>322.1413765634589</v>
+        <v>334.168645798694</v>
       </c>
       <c r="E92" t="n">
-        <v>333.912109375</v>
+        <v>343.1076965332031</v>
       </c>
       <c r="F92" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>334.8987575018528</v>
+        <v>342.5453159613966</v>
       </c>
       <c r="C93" t="n">
-        <v>343.4332779356386</v>
+        <v>350.2116096750548</v>
       </c>
       <c r="D93" t="n">
-        <v>334.168645798694</v>
+        <v>342.1407856401066</v>
       </c>
       <c r="E93" t="n">
-        <v>343.1076965332031</v>
+        <v>349.7380065917969</v>
       </c>
       <c r="F93" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>342.5453159613966</v>
+        <v>349.5505410261084</v>
       </c>
       <c r="C94" t="n">
-        <v>350.2116096750548</v>
+        <v>353.0926127392032</v>
       </c>
       <c r="D94" t="n">
-        <v>342.1407856401066</v>
+        <v>348.2777534390037</v>
       </c>
       <c r="E94" t="n">
-        <v>349.7380065917969</v>
+        <v>351.5041198730469</v>
       </c>
       <c r="F94" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>349.5505106781399</v>
+        <v>349.2249303389971</v>
       </c>
       <c r="C95" t="n">
-        <v>353.0925820837122</v>
+        <v>350.0537130836444</v>
       </c>
       <c r="D95" t="n">
-        <v>348.2777232015386</v>
+        <v>342.6340826093485</v>
       </c>
       <c r="E95" t="n">
-        <v>351.5040893554688</v>
+        <v>346.9457702636719</v>
       </c>
       <c r="F95" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>349.2249303389971</v>
+        <v>290.0456258453373</v>
       </c>
       <c r="C96" t="n">
-        <v>350.0537130836444</v>
+        <v>295.5018014762001</v>
       </c>
       <c r="D96" t="n">
-        <v>342.6340826093485</v>
+        <v>276.6567723884028</v>
       </c>
       <c r="E96" t="n">
-        <v>346.9457702636719</v>
+        <v>278.9260864257812</v>
       </c>
       <c r="F96" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>290.0456258453373</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="C97" t="n">
-        <v>295.5018014762001</v>
+        <v>291.0027024164021</v>
       </c>
       <c r="D97" t="n">
-        <v>276.6567723884028</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="E97" t="n">
-        <v>278.9260864257812</v>
+        <v>290.094970703125</v>
       </c>
       <c r="F97" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>279.9324825435024</v>
+        <v>290.4008374442539</v>
       </c>
       <c r="C98" t="n">
-        <v>291.0027024164021</v>
+        <v>291.6539028887257</v>
       </c>
       <c r="D98" t="n">
-        <v>279.9324825435024</v>
+        <v>285.3590676854078</v>
       </c>
       <c r="E98" t="n">
-        <v>290.094970703125</v>
+        <v>288.3880920410156</v>
       </c>
       <c r="F98" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>290.4008067136846</v>
+        <v>288.200605503728</v>
       </c>
       <c r="C99" t="n">
-        <v>291.6538720255555</v>
+        <v>289.0392644171012</v>
       </c>
       <c r="D99" t="n">
-        <v>285.3590374883647</v>
+        <v>280.8993981188336</v>
       </c>
       <c r="E99" t="n">
-        <v>288.3880615234375</v>
+        <v>283.099609375</v>
       </c>
       <c r="F99" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>288.200605503728</v>
+        <v>282.201779365365</v>
       </c>
       <c r="C100" t="n">
-        <v>289.0392644171012</v>
+        <v>286.5233135903719</v>
       </c>
       <c r="D100" t="n">
-        <v>280.8993981188336</v>
+        <v>278.5117159450099</v>
       </c>
       <c r="E100" t="n">
-        <v>283.099609375</v>
+        <v>281.7775268554688</v>
       </c>
       <c r="F100" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>282.201779365365</v>
+        <v>280.899399533992</v>
       </c>
       <c r="C101" t="n">
-        <v>286.5233135903719</v>
+        <v>284.2441289542904</v>
       </c>
       <c r="D101" t="n">
-        <v>278.5117159450099</v>
+        <v>274.8808256732182</v>
       </c>
       <c r="E101" t="n">
-        <v>281.7775268554688</v>
+        <v>280.3863220214844</v>
       </c>
       <c r="F101" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>280.899399533992</v>
+        <v>278.2453003524489</v>
       </c>
       <c r="C102" t="n">
-        <v>284.2441289542904</v>
+        <v>280.7020503139632</v>
       </c>
       <c r="D102" t="n">
-        <v>274.8808256732182</v>
+        <v>270.3915411669698</v>
       </c>
       <c r="E102" t="n">
-        <v>280.3863220214844</v>
+        <v>272.2366027832031</v>
       </c>
       <c r="F102" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>278.2453003524489</v>
+        <v>270.6283910377749</v>
       </c>
       <c r="C103" t="n">
-        <v>280.7020503139632</v>
+        <v>273.1936885205944</v>
       </c>
       <c r="D103" t="n">
-        <v>270.3915411669698</v>
+        <v>262.7351865430599</v>
       </c>
       <c r="E103" t="n">
-        <v>272.2366027832031</v>
+        <v>264.9649963378906</v>
       </c>
       <c r="F103" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>270.6283598679102</v>
+        <v>263.494873693566</v>
       </c>
       <c r="C104" t="n">
-        <v>273.1936570552693</v>
+        <v>274.1013663098342</v>
       </c>
       <c r="D104" t="n">
-        <v>262.7351562823021</v>
+        <v>262.8535569062469</v>
       </c>
       <c r="E104" t="n">
-        <v>264.9649658203125</v>
+        <v>272.9568481445312</v>
       </c>
       <c r="F104" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>263.494873693566</v>
+        <v>270.4902050418196</v>
       </c>
       <c r="C105" t="n">
-        <v>274.1013663098342</v>
+        <v>276.4397058352786</v>
       </c>
       <c r="D105" t="n">
-        <v>262.8535569062469</v>
+        <v>269.6712984464802</v>
       </c>
       <c r="E105" t="n">
-        <v>272.9568481445312</v>
+        <v>272.01953125</v>
       </c>
       <c r="F105" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>270.4902353878243</v>
+        <v>273.8152476410468</v>
       </c>
       <c r="C106" t="n">
-        <v>276.4397368487514</v>
+        <v>275.7589504136547</v>
       </c>
       <c r="D106" t="n">
-        <v>269.6713287006126</v>
+        <v>269.010264317998</v>
       </c>
       <c r="E106" t="n">
-        <v>272.0195617675781</v>
+        <v>269.5726623535156</v>
       </c>
       <c r="F106" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>273.8152476410468</v>
+        <v>268.8030763257778</v>
       </c>
       <c r="C107" t="n">
-        <v>275.7589504136547</v>
+        <v>275.9562927620499</v>
       </c>
       <c r="D107" t="n">
-        <v>269.010264317998</v>
+        <v>266.198304439543</v>
       </c>
       <c r="E107" t="n">
-        <v>269.5726623535156</v>
+        <v>275.1867065429688</v>
       </c>
       <c r="F107" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>268.8030465161297</v>
+        <v>274.4467004687212</v>
       </c>
       <c r="C108" t="n">
-        <v>275.9562621591264</v>
+        <v>282.4878958393087</v>
       </c>
       <c r="D108" t="n">
-        <v>266.1982749187582</v>
+        <v>272.1280658242715</v>
       </c>
       <c r="E108" t="n">
-        <v>275.1866760253906</v>
+        <v>280.5737915039062</v>
       </c>
       <c r="F108" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>274.4467004687212</v>
+        <v>281.8169569225497</v>
       </c>
       <c r="C109" t="n">
-        <v>282.4878958393087</v>
+        <v>289.5424162609187</v>
       </c>
       <c r="D109" t="n">
-        <v>272.1280658242715</v>
+        <v>280.7119132986369</v>
       </c>
       <c r="E109" t="n">
-        <v>280.5737915039062</v>
+        <v>289.2760314941406</v>
       </c>
       <c r="F109" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>281.8169569225497</v>
+        <v>290.0752312306441</v>
       </c>
       <c r="C110" t="n">
-        <v>289.5424162609187</v>
+        <v>290.3021716729731</v>
       </c>
       <c r="D110" t="n">
-        <v>280.7119132986369</v>
+        <v>284.4907860910092</v>
       </c>
       <c r="E110" t="n">
-        <v>289.2760314941406</v>
+        <v>285.2307739257812</v>
       </c>
       <c r="F110" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>290.0752312306441</v>
+        <v>286.1286505407075</v>
       </c>
       <c r="C111" t="n">
-        <v>290.3021716729731</v>
+        <v>286.2569199258207</v>
       </c>
       <c r="D111" t="n">
-        <v>284.4907860910092</v>
+        <v>282.4681855456762</v>
       </c>
       <c r="E111" t="n">
-        <v>285.2307739257812</v>
+        <v>284.3526916503906</v>
       </c>
       <c r="F111" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>286.1286505407075</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="C112" t="n">
-        <v>286.2569199258207</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="D112" t="n">
-        <v>282.4681855456762</v>
+        <v>283.0601744920274</v>
       </c>
       <c r="E112" t="n">
-        <v>284.3526916503906</v>
+        <v>286.0595703125</v>
       </c>
       <c r="F112" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>287.0067764654547</v>
+        <v>285.0433100706192</v>
       </c>
       <c r="C113" t="n">
-        <v>287.0067764654547</v>
+        <v>286.9179399107358</v>
       </c>
       <c r="D113" t="n">
-        <v>283.0601744920274</v>
+        <v>281.7380250284705</v>
       </c>
       <c r="E113" t="n">
-        <v>286.0595703125</v>
+        <v>286.1286315917969</v>
       </c>
       <c r="F113" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>285.0433100706192</v>
+        <v>284.6979833712643</v>
       </c>
       <c r="C114" t="n">
-        <v>286.9179399107358</v>
+        <v>287.8749991147026</v>
       </c>
       <c r="D114" t="n">
-        <v>281.7380250284705</v>
+        <v>277.9098533754537</v>
       </c>
       <c r="E114" t="n">
-        <v>286.1286315917969</v>
+        <v>278.5708923339844</v>
       </c>
       <c r="F114" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>284.6979833712643</v>
+        <v>278.4327740747045</v>
       </c>
       <c r="C115" t="n">
-        <v>287.8749991147026</v>
+        <v>278.6300861021672</v>
       </c>
       <c r="D115" t="n">
-        <v>277.9098533754537</v>
+        <v>268.1715851207944</v>
       </c>
       <c r="E115" t="n">
-        <v>278.5708923339844</v>
+        <v>270.2929077148438</v>
       </c>
       <c r="F115" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>278.4327740747045</v>
+        <v>273.5883087457124</v>
       </c>
       <c r="C116" t="n">
-        <v>278.6300861021672</v>
+        <v>280.9388364524249</v>
       </c>
       <c r="D116" t="n">
-        <v>268.1715851207944</v>
+        <v>273.1739023127244</v>
       </c>
       <c r="E116" t="n">
-        <v>270.2929077148438</v>
+        <v>280.4060668945312</v>
       </c>
       <c r="F116" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>273.5883087457124</v>
+        <v>283.1489568057956</v>
       </c>
       <c r="C117" t="n">
-        <v>280.9388364524249</v>
+        <v>291.3184213223429</v>
       </c>
       <c r="D117" t="n">
-        <v>273.1739023127244</v>
+        <v>281.422318519362</v>
       </c>
       <c r="E117" t="n">
-        <v>280.4060668945312</v>
+        <v>282.8332214355469</v>
       </c>
       <c r="F117" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>283.1489568057956</v>
+        <v>280.899378965855</v>
       </c>
       <c r="C118" t="n">
-        <v>291.3184213223429</v>
+        <v>290.2034849465505</v>
       </c>
       <c r="D118" t="n">
-        <v>281.422318519362</v>
+        <v>280.0607201096653</v>
       </c>
       <c r="E118" t="n">
-        <v>282.8332214355469</v>
+        <v>289.3549499511719</v>
       </c>
       <c r="F118" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>280.899378965855</v>
+        <v>284.3132152404683</v>
       </c>
       <c r="C119" t="n">
-        <v>290.2034849465505</v>
+        <v>291.3677603814479</v>
       </c>
       <c r="D119" t="n">
-        <v>280.0607201096653</v>
+        <v>283.6620222891216</v>
       </c>
       <c r="E119" t="n">
-        <v>289.3549499511719</v>
+        <v>290.9928283691406</v>
       </c>
       <c r="F119" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>284.3132152404683</v>
+        <v>285.1321178149137</v>
       </c>
       <c r="C120" t="n">
-        <v>291.3677603814479</v>
+        <v>289.8187076809586</v>
       </c>
       <c r="D120" t="n">
-        <v>283.6620222891216</v>
+        <v>280.5639211910132</v>
       </c>
       <c r="E120" t="n">
-        <v>290.9928283691406</v>
+        <v>285.3491821289062</v>
       </c>
       <c r="F120" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>285.1321178149137</v>
+        <v>285.1518685944145</v>
       </c>
       <c r="C121" t="n">
-        <v>289.8187076809586</v>
+        <v>290.4107024732037</v>
       </c>
       <c r="D121" t="n">
-        <v>280.5639211910132</v>
+        <v>283.8396065771265</v>
       </c>
       <c r="E121" t="n">
-        <v>285.3491821289062</v>
+        <v>288.0624694824219</v>
       </c>
       <c r="F121" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>285.1518383851878</v>
+        <v>286.1779504316799</v>
       </c>
       <c r="C122" t="n">
-        <v>290.4106717068518</v>
+        <v>287.5000885291143</v>
       </c>
       <c r="D122" t="n">
-        <v>283.839576506922</v>
+        <v>282.9121398572339</v>
       </c>
       <c r="E122" t="n">
-        <v>288.0624389648438</v>
+        <v>284.9150390625</v>
       </c>
       <c r="F122" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>286.1779504316799</v>
+        <v>283.5041446062434</v>
       </c>
       <c r="C123" t="n">
-        <v>287.5000885291143</v>
+        <v>287.4408703764128</v>
       </c>
       <c r="D123" t="n">
-        <v>282.9121398572339</v>
+        <v>279.2714056266989</v>
       </c>
       <c r="E123" t="n">
-        <v>284.9150390625</v>
+        <v>282.6556396484375</v>
       </c>
       <c r="F123" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>283.5041446062434</v>
+        <v>280.3985261413432</v>
       </c>
       <c r="C124" t="n">
-        <v>287.4408703764128</v>
+        <v>283.5803655260448</v>
       </c>
       <c r="D124" t="n">
-        <v>279.2714056266989</v>
+        <v>277.0774975936055</v>
       </c>
       <c r="E124" t="n">
-        <v>282.6556396484375</v>
+        <v>283.550537109375</v>
       </c>
       <c r="F124" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,25 +3667,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>280.3985261413432</v>
+        <v>285.7479583300972</v>
       </c>
       <c r="C125" t="n">
-        <v>283.5803655260448</v>
+        <v>285.9468043127463</v>
       </c>
       <c r="D125" t="n">
-        <v>277.0774975936055</v>
+        <v>277.3161057836816</v>
       </c>
       <c r="E125" t="n">
-        <v>283.550537109375</v>
+        <v>280.736572265625</v>
       </c>
       <c r="F125" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G125" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>285.7479583300972</v>
+        <v>280.7763694963311</v>
       </c>
       <c r="C126" t="n">
-        <v>285.9468043127463</v>
+        <v>284.5945585040109</v>
       </c>
       <c r="D126" t="n">
-        <v>277.3161057836816</v>
+        <v>279.0064793259336</v>
       </c>
       <c r="E126" t="n">
-        <v>280.736572265625</v>
+        <v>283.6300659179688</v>
       </c>
       <c r="F126" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>280.7763694963311</v>
+        <v>283.1627358622739</v>
       </c>
       <c r="C127" t="n">
-        <v>284.5945585040109</v>
+        <v>285.9269470548217</v>
       </c>
       <c r="D127" t="n">
-        <v>279.0064793259336</v>
+        <v>274.7209602020642</v>
       </c>
       <c r="E127" t="n">
-        <v>283.6300659179688</v>
+        <v>275.4766235351562</v>
       </c>
       <c r="F127" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>283.1627358622739</v>
+        <v>276.4808941849521</v>
       </c>
       <c r="C128" t="n">
-        <v>285.9269470548217</v>
+        <v>281.2735286763525</v>
       </c>
       <c r="D128" t="n">
-        <v>274.7209602020642</v>
+        <v>276.2323139355343</v>
       </c>
       <c r="E128" t="n">
-        <v>275.4766235351562</v>
+        <v>280.4880065917969</v>
       </c>
       <c r="F128" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>276.4808941849521</v>
+        <v>282.3672788368328</v>
       </c>
       <c r="C129" t="n">
-        <v>281.2735286763525</v>
+        <v>285.767839547621</v>
       </c>
       <c r="D129" t="n">
-        <v>276.2323139355343</v>
+        <v>279.4439727693734</v>
       </c>
       <c r="E129" t="n">
-        <v>280.4880065917969</v>
+        <v>283.8686828613281</v>
       </c>
       <c r="F129" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>282.3672788368328</v>
+        <v>286.1655640520241</v>
       </c>
       <c r="C130" t="n">
-        <v>285.767839547621</v>
+        <v>287.3488084380985</v>
       </c>
       <c r="D130" t="n">
-        <v>279.4439727693734</v>
+        <v>283.2223824666901</v>
       </c>
       <c r="E130" t="n">
-        <v>283.8686828613281</v>
+        <v>285.9368896484375</v>
       </c>
       <c r="F130" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>286.1655640520241</v>
+        <v>283.5803557381978</v>
       </c>
       <c r="C131" t="n">
-        <v>287.3488084380985</v>
+        <v>286.7621646688093</v>
       </c>
       <c r="D131" t="n">
-        <v>283.2223824666901</v>
+        <v>281.4624471949345</v>
       </c>
       <c r="E131" t="n">
-        <v>285.9368896484375</v>
+        <v>282.7152709960938</v>
       </c>
       <c r="F131" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>283.5803557381978</v>
+        <v>282.3871618979052</v>
       </c>
       <c r="C132" t="n">
-        <v>286.7621646688093</v>
+        <v>285.9169892839216</v>
       </c>
       <c r="D132" t="n">
-        <v>281.4624471949345</v>
+        <v>278.4794876796185</v>
       </c>
       <c r="E132" t="n">
-        <v>282.7152709960938</v>
+        <v>278.8473815917969</v>
       </c>
       <c r="F132" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>282.3871618979052</v>
+        <v>277.4056183419098</v>
       </c>
       <c r="C133" t="n">
-        <v>285.9169892839216</v>
+        <v>281.4922936115716</v>
       </c>
       <c r="D133" t="n">
-        <v>278.4794876796185</v>
+        <v>273.4382870867091</v>
       </c>
       <c r="E133" t="n">
-        <v>278.8473815917969</v>
+        <v>274.0249328613281</v>
       </c>
       <c r="F133" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>277.4056183419098</v>
+        <v>277.5547645320462</v>
       </c>
       <c r="C134" t="n">
-        <v>281.4922936115716</v>
+        <v>279.1556066962045</v>
       </c>
       <c r="D134" t="n">
-        <v>273.4382870867091</v>
+        <v>267.5618207785692</v>
       </c>
       <c r="E134" t="n">
-        <v>274.0249328613281</v>
+        <v>268.00927734375</v>
       </c>
       <c r="F134" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>277.5547645320462</v>
+        <v>267.3430655755382</v>
       </c>
       <c r="C135" t="n">
-        <v>279.1556066962045</v>
+        <v>271.8274627132414</v>
       </c>
       <c r="D135" t="n">
-        <v>267.5618207785692</v>
+        <v>266.0703359894755</v>
       </c>
       <c r="E135" t="n">
-        <v>268.00927734375</v>
+        <v>270.7337036132812</v>
       </c>
       <c r="F135" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>267.3430655755382</v>
+        <v>273.4382596260376</v>
       </c>
       <c r="C136" t="n">
-        <v>271.8274627132414</v>
+        <v>274.5121128941823</v>
       </c>
       <c r="D136" t="n">
-        <v>266.0703359894755</v>
+        <v>265.5930528118823</v>
       </c>
       <c r="E136" t="n">
-        <v>270.7337036132812</v>
+        <v>269.0135192871094</v>
       </c>
       <c r="F136" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>273.4382596260376</v>
+        <v>268.4567257080549</v>
       </c>
       <c r="C137" t="n">
-        <v>274.5121128941823</v>
+        <v>273.0803427820733</v>
       </c>
       <c r="D137" t="n">
-        <v>265.5930528118823</v>
+        <v>265.6626860357957</v>
       </c>
       <c r="E137" t="n">
-        <v>269.0135192871094</v>
+        <v>266.5277404785156</v>
       </c>
       <c r="F137" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>268.4567257080549</v>
+        <v>265.9808641274938</v>
       </c>
       <c r="C138" t="n">
-        <v>273.0803427820733</v>
+        <v>266.1499120468286</v>
       </c>
       <c r="D138" t="n">
-        <v>265.6626860357957</v>
+        <v>254.516344356629</v>
       </c>
       <c r="E138" t="n">
-        <v>266.5277404785156</v>
+        <v>257.5490112304688</v>
       </c>
       <c r="F138" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>265.9808641274938</v>
+        <v>258.7024415515604</v>
       </c>
       <c r="C139" t="n">
-        <v>266.1499120468286</v>
+        <v>260.8402257240527</v>
       </c>
       <c r="D139" t="n">
-        <v>254.516344356629</v>
+        <v>255.2123953265358</v>
       </c>
       <c r="E139" t="n">
-        <v>257.5490112304688</v>
+        <v>260.3033142089844</v>
       </c>
       <c r="F139" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>258.7024415515604</v>
+        <v>261.506421503485</v>
       </c>
       <c r="C140" t="n">
-        <v>260.8402257240527</v>
+        <v>270.3359967880393</v>
       </c>
       <c r="D140" t="n">
-        <v>255.2123953265358</v>
+        <v>261.1186217504552</v>
       </c>
       <c r="E140" t="n">
-        <v>260.3033142089844</v>
+        <v>269.0533142089844</v>
       </c>
       <c r="F140" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>261.506421503485</v>
+        <v>272.6527466700565</v>
       </c>
       <c r="C141" t="n">
-        <v>270.3359967880393</v>
+        <v>273.7365528939259</v>
       </c>
       <c r="D141" t="n">
-        <v>261.1186217504552</v>
+        <v>269.2223575051711</v>
       </c>
       <c r="E141" t="n">
-        <v>269.0533142089844</v>
+        <v>272.424072265625</v>
       </c>
       <c r="F141" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>272.6527466700565</v>
+        <v>270.7436786461413</v>
       </c>
       <c r="C142" t="n">
-        <v>273.7365528939259</v>
+        <v>277.4553455215711</v>
       </c>
       <c r="D142" t="n">
-        <v>269.2223575051711</v>
+        <v>269.9879849618526</v>
       </c>
       <c r="E142" t="n">
-        <v>272.424072265625</v>
+        <v>275.6854553222656</v>
       </c>
       <c r="F142" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>270.7436786461413</v>
+        <v>276.3019282869355</v>
       </c>
       <c r="C143" t="n">
-        <v>277.4553455215711</v>
+        <v>281.6911311912249</v>
       </c>
       <c r="D143" t="n">
-        <v>269.9879849618526</v>
+        <v>275.6755011928929</v>
       </c>
       <c r="E143" t="n">
-        <v>275.6854553222656</v>
+        <v>279.7621459960938</v>
       </c>
       <c r="F143" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>276.3019282869355</v>
+        <v>307.0960565749332</v>
       </c>
       <c r="C144" t="n">
-        <v>281.6911311912249</v>
+        <v>310.6557125153819</v>
       </c>
       <c r="D144" t="n">
-        <v>275.6755011928929</v>
+        <v>299.0420501528358</v>
       </c>
       <c r="E144" t="n">
-        <v>279.7621459960938</v>
+        <v>305.982421875</v>
       </c>
       <c r="F144" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>307.0960565749332</v>
+        <v>310.2281413790238</v>
       </c>
       <c r="C145" t="n">
-        <v>310.6557125153819</v>
+        <v>311.1926339297742</v>
       </c>
       <c r="D145" t="n">
-        <v>299.0420501528358</v>
+        <v>303.0988467016243</v>
       </c>
       <c r="E145" t="n">
-        <v>305.982421875</v>
+        <v>304.2423400878906</v>
       </c>
       <c r="F145" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>310.2281413790238</v>
+        <v>304.0832470042582</v>
       </c>
       <c r="C146" t="n">
-        <v>311.1926339297742</v>
+        <v>306.1414986993597</v>
       </c>
       <c r="D146" t="n">
-        <v>303.0988467016243</v>
+        <v>302.4127950535677</v>
       </c>
       <c r="E146" t="n">
-        <v>304.2423400878906</v>
+        <v>305.1670532226562</v>
       </c>
       <c r="F146" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>304.0832470042582</v>
+        <v>306.2011519366599</v>
       </c>
       <c r="C147" t="n">
-        <v>306.1414986993597</v>
+        <v>308.607391668382</v>
       </c>
       <c r="D147" t="n">
-        <v>302.4127950535677</v>
+        <v>302.4724483346268</v>
       </c>
       <c r="E147" t="n">
-        <v>305.1670532226562</v>
+        <v>302.6016845703125</v>
       </c>
       <c r="F147" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>306.2011519366599</v>
+        <v>301.5278433900291</v>
       </c>
       <c r="C148" t="n">
-        <v>308.607391668382</v>
+        <v>311.5406631473035</v>
       </c>
       <c r="D148" t="n">
-        <v>302.4724483346268</v>
+        <v>301.199730811355</v>
       </c>
       <c r="E148" t="n">
-        <v>302.6016845703125</v>
+        <v>311.2224731445312</v>
       </c>
       <c r="F148" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>301.5278433900291</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="C149" t="n">
-        <v>311.5406631473035</v>
+        <v>317.8048561417646</v>
       </c>
       <c r="D149" t="n">
-        <v>301.199730811355</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="E149" t="n">
-        <v>311.2224731445312</v>
+        <v>312.4057006835938</v>
       </c>
       <c r="F149" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>310.7352487756957</v>
+        <v>314.2054174655202</v>
       </c>
       <c r="C150" t="n">
-        <v>317.8048561417646</v>
+        <v>315.9554320324556</v>
       </c>
       <c r="D150" t="n">
-        <v>310.7352487756957</v>
+        <v>309.3829548311358</v>
       </c>
       <c r="E150" t="n">
-        <v>312.4057006835938</v>
+        <v>312.2664794921875</v>
       </c>
       <c r="F150" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>314.2054174655202</v>
+        <v>313.2111061223722</v>
       </c>
       <c r="C151" t="n">
-        <v>315.9554320324556</v>
+        <v>316.8005902653832</v>
       </c>
       <c r="D151" t="n">
-        <v>309.3829548311358</v>
+        <v>311.3318249203894</v>
       </c>
       <c r="E151" t="n">
-        <v>312.2664794921875</v>
+        <v>314.6031494140625</v>
       </c>
       <c r="F151" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>313.2111061223722</v>
+        <v>318.2324307180975</v>
       </c>
       <c r="C152" t="n">
-        <v>316.8005902653832</v>
+        <v>323.4227876628706</v>
       </c>
       <c r="D152" t="n">
-        <v>311.3318249203894</v>
+        <v>315.338983249174</v>
       </c>
       <c r="E152" t="n">
-        <v>314.6031494140625</v>
+        <v>322.7864379882812</v>
       </c>
       <c r="F152" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>318.2324307180975</v>
+        <v>322.3489342821542</v>
       </c>
       <c r="C153" t="n">
-        <v>323.4227876628706</v>
+        <v>323.5520542213801</v>
       </c>
       <c r="D153" t="n">
-        <v>315.338983249174</v>
+        <v>318.3020404433487</v>
       </c>
       <c r="E153" t="n">
-        <v>322.7864379882812</v>
+        <v>321.6429748535156</v>
       </c>
       <c r="F153" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>322.3489342821542</v>
+        <v>351.0052603166191</v>
       </c>
       <c r="C154" t="n">
-        <v>323.5520542213801</v>
+        <v>355.648722319699</v>
       </c>
       <c r="D154" t="n">
-        <v>318.3020404433487</v>
+        <v>343.2694442738866</v>
       </c>
       <c r="E154" t="n">
-        <v>321.6429748535156</v>
+        <v>344.0450134277344</v>
       </c>
       <c r="F154" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>351.0052603166191</v>
+        <v>348.8873678788304</v>
       </c>
       <c r="C155" t="n">
-        <v>355.648722319699</v>
+        <v>356.5237461069854</v>
       </c>
       <c r="D155" t="n">
-        <v>343.2694442738866</v>
+        <v>347.1174776591131</v>
       </c>
       <c r="E155" t="n">
-        <v>344.0450134277344</v>
+        <v>351.5123596191406</v>
       </c>
       <c r="F155" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>348.8873678788304</v>
+        <v>352.6657614176121</v>
       </c>
       <c r="C156" t="n">
-        <v>356.5237461069854</v>
+        <v>354.8234513171886</v>
       </c>
       <c r="D156" t="n">
-        <v>347.1174776591131</v>
+        <v>348.5095069624251</v>
       </c>
       <c r="E156" t="n">
-        <v>351.5123596191406</v>
+        <v>352.5464477539062</v>
       </c>
       <c r="F156" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>352.6657614176121</v>
+        <v>354.4654798371856</v>
       </c>
       <c r="C157" t="n">
-        <v>354.8234513171886</v>
+        <v>356.2453229047883</v>
       </c>
       <c r="D157" t="n">
-        <v>348.5095069624251</v>
+        <v>349.3944670661433</v>
       </c>
       <c r="E157" t="n">
-        <v>352.5464477539062</v>
+        <v>352.9044189453125</v>
       </c>
       <c r="F157" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>354.4654798371856</v>
+        <v>351.9001510435625</v>
       </c>
       <c r="C158" t="n">
-        <v>356.2453229047883</v>
+        <v>354.4654858887946</v>
       </c>
       <c r="D158" t="n">
-        <v>349.3944670661433</v>
+        <v>346.9683273478323</v>
       </c>
       <c r="E158" t="n">
-        <v>352.9044189453125</v>
+        <v>352.6757202148438</v>
       </c>
       <c r="F158" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>351.9001510435625</v>
+        <v>354.8135029963465</v>
       </c>
       <c r="C159" t="n">
-        <v>354.4654858887946</v>
+        <v>367.5308771185002</v>
       </c>
       <c r="D159" t="n">
-        <v>346.9683273478323</v>
+        <v>353.6998683282982</v>
       </c>
       <c r="E159" t="n">
-        <v>352.6757202148438</v>
+        <v>364.6871032714844</v>
       </c>
       <c r="F159" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>354.8135029963465</v>
+        <v>363.9214802466298</v>
       </c>
       <c r="C160" t="n">
-        <v>367.5308771185002</v>
+        <v>368.7339901692348</v>
       </c>
       <c r="D160" t="n">
-        <v>353.6998683282982</v>
+        <v>362.9371121823581</v>
       </c>
       <c r="E160" t="n">
-        <v>364.6871032714844</v>
+        <v>368.6345520019531</v>
       </c>
       <c r="F160" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>363.9214802466298</v>
+        <v>366.4172241064422</v>
       </c>
       <c r="C161" t="n">
-        <v>368.7339901692348</v>
+        <v>369.87744160261</v>
       </c>
       <c r="D161" t="n">
-        <v>362.9371121823581</v>
+        <v>360.9385059451532</v>
       </c>
       <c r="E161" t="n">
-        <v>368.6345520019531</v>
+        <v>368.3760375976562</v>
       </c>
       <c r="F161" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>366.4172241064422</v>
+        <v>369.8476329800702</v>
       </c>
       <c r="C162" t="n">
-        <v>369.87744160261</v>
+        <v>370.7822971534658</v>
       </c>
       <c r="D162" t="n">
-        <v>360.9385059451532</v>
+        <v>364.9356847817637</v>
       </c>
       <c r="E162" t="n">
-        <v>368.3760375976562</v>
+        <v>366.6856994628906</v>
       </c>
       <c r="F162" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>369.8476329800702</v>
+        <v>366.4569824541582</v>
       </c>
       <c r="C163" t="n">
-        <v>370.7822971534658</v>
+        <v>368.7240330587824</v>
       </c>
       <c r="D163" t="n">
-        <v>364.9356847817637</v>
+        <v>362.5791367283888</v>
       </c>
       <c r="E163" t="n">
-        <v>366.6856994628906</v>
+        <v>368.6445007324219</v>
       </c>
       <c r="F163" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>366.4569824541582</v>
+        <v>368.3760355922912</v>
       </c>
       <c r="C164" t="n">
-        <v>368.7240330587824</v>
+        <v>369.6885161814855</v>
       </c>
       <c r="D164" t="n">
-        <v>362.5791367283888</v>
+        <v>359.7552596250864</v>
       </c>
       <c r="E164" t="n">
-        <v>368.6445007324219</v>
+        <v>361.8035583496094</v>
       </c>
       <c r="F164" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>368.3760355922912</v>
+        <v>361.0379593902868</v>
       </c>
       <c r="C165" t="n">
-        <v>369.6885161814855</v>
+        <v>366.45699060703</v>
       </c>
       <c r="D165" t="n">
-        <v>359.7552596250864</v>
+        <v>356.2154964951898</v>
       </c>
       <c r="E165" t="n">
-        <v>361.8035583496094</v>
+        <v>365.1942138671875</v>
       </c>
       <c r="F165" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>361.0379593902868</v>
+        <v>364.5578575186544</v>
       </c>
       <c r="C166" t="n">
-        <v>366.45699060703</v>
+        <v>367.7098380224884</v>
       </c>
       <c r="D166" t="n">
-        <v>356.2154964951898</v>
+        <v>362.6487478916185</v>
       </c>
       <c r="E166" t="n">
-        <v>365.1942138671875</v>
+        <v>367.6402282714844</v>
       </c>
       <c r="F166" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>364.5578575186544</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="C167" t="n">
-        <v>367.7098380224884</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="D167" t="n">
-        <v>362.6487478916185</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="E167" t="n">
-        <v>367.6402282714844</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="F167" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>369.8774674335755</v>
+        <v>378.2894437474218</v>
       </c>
       <c r="C168" t="n">
-        <v>377.8221130371094</v>
+        <v>382.6246688242237</v>
       </c>
       <c r="D168" t="n">
-        <v>369.8774674335755</v>
+        <v>373.9343128299113</v>
       </c>
       <c r="E168" t="n">
-        <v>377.8221130371094</v>
+        <v>382.2567749023438</v>
       </c>
       <c r="F168" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>378.2894437474218</v>
+        <v>380.6758011703357</v>
       </c>
       <c r="C169" t="n">
-        <v>382.6246688242237</v>
+        <v>395.1630654325308</v>
       </c>
       <c r="D169" t="n">
-        <v>373.9343128299113</v>
+        <v>379.8405751710962</v>
       </c>
       <c r="E169" t="n">
-        <v>382.2567749023438</v>
+        <v>394.138916015625</v>
       </c>
       <c r="F169" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>380.6758011703357</v>
+        <v>394.2482660415264</v>
       </c>
       <c r="C170" t="n">
-        <v>395.1630654325308</v>
+        <v>401.8548154208889</v>
       </c>
       <c r="D170" t="n">
-        <v>379.8405751710962</v>
+        <v>390.7681426338459</v>
       </c>
       <c r="E170" t="n">
-        <v>394.138916015625</v>
+        <v>398.8818054199219</v>
       </c>
       <c r="F170" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>394.2482660415264</v>
+        <v>398.7227040337817</v>
       </c>
       <c r="C171" t="n">
-        <v>401.8548154208889</v>
+        <v>399.6175868268494</v>
       </c>
       <c r="D171" t="n">
-        <v>390.7681426338459</v>
+        <v>393.7510992453305</v>
       </c>
       <c r="E171" t="n">
-        <v>398.8818054199219</v>
+        <v>396.8235473632812</v>
       </c>
       <c r="F171" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>398.7227040337817</v>
+        <v>392.0607685404387</v>
       </c>
       <c r="C172" t="n">
-        <v>399.6175868268494</v>
+        <v>395.3718745508767</v>
       </c>
       <c r="D172" t="n">
-        <v>393.7510992453305</v>
+        <v>388.0337805215488</v>
       </c>
       <c r="E172" t="n">
-        <v>396.8235473632812</v>
+        <v>391.6133422851562</v>
       </c>
       <c r="F172" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>392.0607685404387</v>
+        <v>387.7851953583757</v>
       </c>
       <c r="C173" t="n">
-        <v>395.3718745508767</v>
+        <v>389.9130568930274</v>
       </c>
       <c r="D173" t="n">
-        <v>388.0337805215488</v>
+        <v>381.3221087690695</v>
       </c>
       <c r="E173" t="n">
-        <v>391.6133422851562</v>
+        <v>388.9087829589844</v>
       </c>
       <c r="F173" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>387.7851953583757</v>
+        <v>387.7851736187118</v>
       </c>
       <c r="C174" t="n">
-        <v>389.9130568930274</v>
+        <v>392.7468254889498</v>
       </c>
       <c r="D174" t="n">
-        <v>381.3221087690695</v>
+        <v>385.3093241434657</v>
       </c>
       <c r="E174" t="n">
-        <v>388.9087829589844</v>
+        <v>387.0294799804688</v>
       </c>
       <c r="F174" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>387.7851736187118</v>
+        <v>387.3377362764213</v>
       </c>
       <c r="C175" t="n">
-        <v>392.7468254889498</v>
+        <v>391.1460027273716</v>
       </c>
       <c r="D175" t="n">
-        <v>385.3093241434657</v>
+        <v>378.5380196367677</v>
       </c>
       <c r="E175" t="n">
-        <v>387.0294799804688</v>
+        <v>381.1232299804688</v>
       </c>
       <c r="F175" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>387.3377362764213</v>
+        <v>378.9555995605828</v>
       </c>
       <c r="C176" t="n">
-        <v>391.1460027273716</v>
+        <v>383.9172514426562</v>
       </c>
       <c r="D176" t="n">
-        <v>378.5380196367677</v>
+        <v>378.3789067550467</v>
       </c>
       <c r="E176" t="n">
-        <v>381.1232299804688</v>
+        <v>380.3078918457031</v>
       </c>
       <c r="F176" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>378.9555995605828</v>
+        <v>379.7510949944643</v>
       </c>
       <c r="C177" t="n">
-        <v>383.9172514426562</v>
+        <v>388.322137279522</v>
       </c>
       <c r="D177" t="n">
-        <v>378.3789067550467</v>
+        <v>378.846259230469</v>
       </c>
       <c r="E177" t="n">
-        <v>380.3078918457031</v>
+        <v>386.2638854980469</v>
       </c>
       <c r="F177" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>379.7510949944643</v>
+        <v>383.8078958628703</v>
       </c>
       <c r="C178" t="n">
-        <v>388.322137279522</v>
+        <v>384.3249318452775</v>
       </c>
       <c r="D178" t="n">
-        <v>378.846259230469</v>
+        <v>374.2723613660349</v>
       </c>
       <c r="E178" t="n">
-        <v>386.2638854980469</v>
+        <v>374.7197875976562</v>
       </c>
       <c r="F178" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>383.8078958628703</v>
+        <v>376.2808953624811</v>
       </c>
       <c r="C179" t="n">
-        <v>384.3249318452775</v>
+        <v>382.3462596379654</v>
       </c>
       <c r="D179" t="n">
-        <v>374.2723613660349</v>
+        <v>374.9485088403697</v>
       </c>
       <c r="E179" t="n">
-        <v>374.7197875976562</v>
+        <v>381.8292236328125</v>
       </c>
       <c r="F179" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>376.2808953624811</v>
+        <v>382.7737976901378</v>
       </c>
       <c r="C180" t="n">
-        <v>382.3462596379654</v>
+        <v>387.0493961299752</v>
       </c>
       <c r="D180" t="n">
-        <v>374.9485088403697</v>
+        <v>378.7965137522062</v>
       </c>
       <c r="E180" t="n">
-        <v>381.8292236328125</v>
+        <v>380.3576049804688</v>
       </c>
       <c r="F180" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>382.7737976901378</v>
+        <v>381.6005025160485</v>
       </c>
       <c r="C181" t="n">
-        <v>387.0493961299752</v>
+        <v>382.9328889810419</v>
       </c>
       <c r="D181" t="n">
-        <v>378.7965137522062</v>
+        <v>373.317822146985</v>
       </c>
       <c r="E181" t="n">
-        <v>380.3576049804688</v>
+        <v>378.1502075195312</v>
       </c>
       <c r="F181" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>381.6005025160485</v>
+        <v>373.9740550559011</v>
       </c>
       <c r="C182" t="n">
-        <v>382.9328889810419</v>
+        <v>381.172959697494</v>
       </c>
       <c r="D182" t="n">
-        <v>373.317822146985</v>
+        <v>373.7851619834815</v>
       </c>
       <c r="E182" t="n">
-        <v>378.1502075195312</v>
+        <v>377.7027587890625</v>
       </c>
       <c r="F182" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>373.9740550559011</v>
+        <v>375.8334605430848</v>
       </c>
       <c r="C183" t="n">
-        <v>381.172959697494</v>
+        <v>377.9215103567756</v>
       </c>
       <c r="D183" t="n">
-        <v>373.7851619834815</v>
+        <v>372.5919643898307</v>
       </c>
       <c r="E183" t="n">
-        <v>377.7027587890625</v>
+        <v>375.7738037109375</v>
       </c>
       <c r="F183" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>375.8334605430848</v>
+        <v>377.8419717237235</v>
       </c>
       <c r="C184" t="n">
-        <v>377.9215103567756</v>
+        <v>385.259597724852</v>
       </c>
       <c r="D184" t="n">
-        <v>372.5919643898307</v>
+        <v>374.6700853756592</v>
       </c>
       <c r="E184" t="n">
-        <v>375.7738037109375</v>
+        <v>374.8590087890625</v>
       </c>
       <c r="F184" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>377.8419717237235</v>
+        <v>387.7851867936407</v>
       </c>
       <c r="C185" t="n">
-        <v>385.259597724852</v>
+        <v>399.1005645351637</v>
       </c>
       <c r="D185" t="n">
-        <v>374.6700853756592</v>
+        <v>387.606216297745</v>
       </c>
       <c r="E185" t="n">
-        <v>374.8590087890625</v>
+        <v>394.2184448242188</v>
       </c>
       <c r="F185" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>387.7851867936407</v>
+        <v>397.2710257691138</v>
       </c>
       <c r="C186" t="n">
-        <v>399.1005645351637</v>
+        <v>401.7454703246708</v>
       </c>
       <c r="D186" t="n">
-        <v>387.606216297745</v>
+        <v>394.9443182415365</v>
       </c>
       <c r="E186" t="n">
-        <v>394.2184448242188</v>
+        <v>397.201416015625</v>
       </c>
       <c r="F186" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>397.2710257691138</v>
+        <v>394.8746856398852</v>
       </c>
       <c r="C187" t="n">
-        <v>401.7454703246708</v>
+        <v>406.3889089451397</v>
       </c>
       <c r="D187" t="n">
-        <v>394.9443182415365</v>
+        <v>392.7468242313375</v>
       </c>
       <c r="E187" t="n">
-        <v>397.201416015625</v>
+        <v>404.2610778808594</v>
       </c>
       <c r="F187" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>394.8746856398852</v>
+        <v>407.6616556237274</v>
       </c>
       <c r="C188" t="n">
-        <v>406.3889089451397</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="D188" t="n">
-        <v>392.7468242313375</v>
+        <v>405.1261492204914</v>
       </c>
       <c r="E188" t="n">
-        <v>404.2610778808594</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="F188" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>407.6616556237274</v>
+        <v>411.1517339543602</v>
       </c>
       <c r="C189" t="n">
-        <v>410.6545715332031</v>
+        <v>413.6176609610221</v>
       </c>
       <c r="D189" t="n">
-        <v>405.1261492204914</v>
+        <v>402.2525488568183</v>
       </c>
       <c r="E189" t="n">
-        <v>410.6545715332031</v>
+        <v>405.1460266113281</v>
       </c>
       <c r="F189" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>411.1517339543602</v>
+        <v>406.3889145916303</v>
       </c>
       <c r="C190" t="n">
-        <v>413.6176609610221</v>
+        <v>407.6517216421196</v>
       </c>
       <c r="D190" t="n">
-        <v>402.2525488568183</v>
+        <v>400.820711098459</v>
       </c>
       <c r="E190" t="n">
-        <v>405.1460266113281</v>
+        <v>403.2468566894531</v>
       </c>
       <c r="F190" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>406.3889145916303</v>
+        <v>406.6872501409831</v>
       </c>
       <c r="C191" t="n">
-        <v>407.6517216421196</v>
+        <v>407.5622574937536</v>
       </c>
       <c r="D191" t="n">
-        <v>400.820711098459</v>
+        <v>402.5110897188582</v>
       </c>
       <c r="E191" t="n">
-        <v>403.2468566894531</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="F191" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,25 +5409,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>406.6872501409831</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="C192" t="n">
-        <v>407.5622574937536</v>
+        <v>414.1600036621094</v>
       </c>
       <c r="D192" t="n">
-        <v>402.5110897188582</v>
+        <v>399.6499938964844</v>
       </c>
       <c r="E192" t="n">
-        <v>406.2000122070312</v>
+        <v>411.0400085449219</v>
       </c>
       <c r="F192" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5435,25 +5435,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>406.7000122070312</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="C193" t="n">
-        <v>414.1600036621094</v>
+        <v>411.75</v>
       </c>
       <c r="D193" t="n">
-        <v>399.6499938964844</v>
+        <v>406.5400085449219</v>
       </c>
       <c r="E193" t="n">
-        <v>411.0400085449219</v>
+        <v>407.6499938964844</v>
       </c>
       <c r="F193" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G193" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>410.6799926757812</v>
+        <v>409.1199951171875</v>
       </c>
       <c r="C194" t="n">
-        <v>411.75</v>
+        <v>411.1600036621094</v>
       </c>
       <c r="D194" t="n">
-        <v>406.5400085449219</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E194" t="n">
-        <v>407.6499938964844</v>
+        <v>399.5299987792969</v>
       </c>
       <c r="F194" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>409.1199951171875</v>
+        <v>402.7699890136719</v>
       </c>
       <c r="C195" t="n">
-        <v>411.1600036621094</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="D195" t="n">
-        <v>398.5899963378906</v>
+        <v>399.1499938964844</v>
       </c>
       <c r="E195" t="n">
-        <v>399.5299987792969</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="F195" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>402.7699890136719</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="C196" t="n">
-        <v>406.2000122070312</v>
+        <v>409.4599914550781</v>
       </c>
       <c r="D196" t="n">
-        <v>399.1499938964844</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="E196" t="n">
-        <v>400.9599914550781</v>
+        <v>406.6799926757812</v>
       </c>
       <c r="F196" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>402.1400146484375</v>
+        <v>409.5199890136719</v>
       </c>
       <c r="C197" t="n">
-        <v>409.4599914550781</v>
+        <v>409.8999938964844</v>
       </c>
       <c r="D197" t="n">
-        <v>402.1400146484375</v>
+        <v>402.8399963378906</v>
       </c>
       <c r="E197" t="n">
-        <v>406.6799926757812</v>
+        <v>409.25</v>
       </c>
       <c r="F197" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>409.5199890136719</v>
+        <v>410.5400085449219</v>
       </c>
       <c r="C198" t="n">
-        <v>409.8999938964844</v>
+        <v>413.4299926757812</v>
       </c>
       <c r="D198" t="n">
-        <v>402.8399963378906</v>
+        <v>400</v>
       </c>
       <c r="E198" t="n">
-        <v>409.25</v>
+        <v>405.7999877929688</v>
       </c>
       <c r="F198" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>410.5400085449219</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="C199" t="n">
-        <v>413.4299926757812</v>
+        <v>417.5799865722656</v>
       </c>
       <c r="D199" t="n">
-        <v>400</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="E199" t="n">
-        <v>405.7999877929688</v>
+        <v>415.5299987792969</v>
       </c>
       <c r="F199" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>406.6499938964844</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="C200" t="n">
-        <v>417.5799865722656</v>
+        <v>427.9299926757812</v>
       </c>
       <c r="D200" t="n">
-        <v>406.6499938964844</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="E200" t="n">
-        <v>415.5299987792969</v>
+        <v>427.8900146484375</v>
       </c>
       <c r="F200" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>416.1600036621094</v>
+        <v>426.5299987792969</v>
       </c>
       <c r="C201" t="n">
-        <v>427.9299926757812</v>
+        <v>426.7000122070312</v>
       </c>
       <c r="D201" t="n">
-        <v>416.1600036621094</v>
+        <v>415.8099975585938</v>
       </c>
       <c r="E201" t="n">
-        <v>427.8900146484375</v>
+        <v>419.8200073242188</v>
       </c>
       <c r="F201" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>426.5299987792969</v>
+        <v>422.7200012207031</v>
       </c>
       <c r="C202" t="n">
-        <v>426.7000122070312</v>
+        <v>422.739990234375</v>
       </c>
       <c r="D202" t="n">
-        <v>415.8099975585938</v>
+        <v>413.25</v>
       </c>
       <c r="E202" t="n">
-        <v>419.8200073242188</v>
+        <v>415.6300048828125</v>
       </c>
       <c r="F202" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>422.7200012207031</v>
+        <v>417.1099853515625</v>
       </c>
       <c r="C203" t="n">
-        <v>422.739990234375</v>
+        <v>428.0199890136719</v>
       </c>
       <c r="D203" t="n">
-        <v>413.25</v>
+        <v>413.7300109863281</v>
       </c>
       <c r="E203" t="n">
-        <v>415.6300048828125</v>
+        <v>426.5400085449219</v>
       </c>
       <c r="F203" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>417.1099853515625</v>
+        <v>428.1300048828125</v>
       </c>
       <c r="C204" t="n">
-        <v>428.0199890136719</v>
+        <v>430.2000122070312</v>
       </c>
       <c r="D204" t="n">
-        <v>413.7300109863281</v>
+        <v>420.5400085449219</v>
       </c>
       <c r="E204" t="n">
-        <v>426.5400085449219</v>
+        <v>425.3599853515625</v>
       </c>
       <c r="F204" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>428.1300048828125</v>
+        <v>423.489990234375</v>
       </c>
       <c r="C205" t="n">
-        <v>430.2000122070312</v>
+        <v>424.4400024414062</v>
       </c>
       <c r="D205" t="n">
-        <v>420.5400085449219</v>
+        <v>415.0499877929688</v>
       </c>
       <c r="E205" t="n">
-        <v>425.3599853515625</v>
+        <v>417.989990234375</v>
       </c>
       <c r="F205" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>423.489990234375</v>
+        <v>423.9500122070312</v>
       </c>
       <c r="C206" t="n">
-        <v>424.4400024414062</v>
+        <v>428.6000061035156</v>
       </c>
       <c r="D206" t="n">
-        <v>415.0499877929688</v>
+        <v>422.1300048828125</v>
       </c>
       <c r="E206" t="n">
-        <v>417.989990234375</v>
+        <v>428.1900024414062</v>
       </c>
       <c r="F206" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>423.9500122070312</v>
+        <v>427.1499938964844</v>
       </c>
       <c r="C207" t="n">
-        <v>428.6000061035156</v>
+        <v>430.7699890136719</v>
       </c>
       <c r="D207" t="n">
-        <v>422.1300048828125</v>
+        <v>423.8299865722656</v>
       </c>
       <c r="E207" t="n">
-        <v>428.1900024414062</v>
+        <v>425.6000061035156</v>
       </c>
       <c r="F207" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>427.1499938964844</v>
+        <v>427.1099853515625</v>
       </c>
       <c r="C208" t="n">
-        <v>430.7699890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="D208" t="n">
-        <v>423.8299865722656</v>
+        <v>423.5199890136719</v>
       </c>
       <c r="E208" t="n">
-        <v>425.6000061035156</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="F208" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>427.1099853515625</v>
+        <v>431.6700134277344</v>
       </c>
       <c r="C209" t="n">
-        <v>434.2999877929688</v>
+        <v>432.8599853515625</v>
       </c>
       <c r="D209" t="n">
-        <v>423.5199890136719</v>
+        <v>423.6499938964844</v>
       </c>
       <c r="E209" t="n">
-        <v>431.6799926757812</v>
+        <v>424.6199951171875</v>
       </c>
       <c r="F209" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>431.6700134277344</v>
+        <v>426.4700012207031</v>
       </c>
       <c r="C210" t="n">
-        <v>432.8599853515625</v>
+        <v>431.5499877929688</v>
       </c>
       <c r="D210" t="n">
-        <v>423.6499938964844</v>
+        <v>425.5299987792969</v>
       </c>
       <c r="E210" t="n">
-        <v>424.6199951171875</v>
+        <v>429.0899963378906</v>
       </c>
       <c r="F210" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>426.4700012207031</v>
+        <v>431</v>
       </c>
       <c r="C211" t="n">
-        <v>431.5499877929688</v>
+        <v>432.1499938964844</v>
       </c>
       <c r="D211" t="n">
-        <v>425.5299987792969</v>
+        <v>421.7900085449219</v>
       </c>
       <c r="E211" t="n">
-        <v>429.0899963378906</v>
+        <v>425.1900024414062</v>
       </c>
       <c r="F211" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>431</v>
+        <v>419.489990234375</v>
       </c>
       <c r="C212" t="n">
-        <v>432.1499938964844</v>
+        <v>424.1099853515625</v>
       </c>
       <c r="D212" t="n">
-        <v>421.7900085449219</v>
+        <v>414.3699951171875</v>
       </c>
       <c r="E212" t="n">
-        <v>425.1900024414062</v>
+        <v>418.5199890136719</v>
       </c>
       <c r="F212" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>419.489990234375</v>
+        <v>449.3900146484375</v>
       </c>
       <c r="C213" t="n">
-        <v>424.1099853515625</v>
+        <v>461.6199951171875</v>
       </c>
       <c r="D213" t="n">
-        <v>414.3699951171875</v>
+        <v>420.3699951171875</v>
       </c>
       <c r="E213" t="n">
-        <v>418.5199890136719</v>
+        <v>423.3800048828125</v>
       </c>
       <c r="F213" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>449.3900146484375</v>
+        <v>426.7200012207031</v>
       </c>
       <c r="C214" t="n">
-        <v>461.6199951171875</v>
+        <v>437.4700012207031</v>
       </c>
       <c r="D214" t="n">
-        <v>420.3699951171875</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="E214" t="n">
-        <v>423.3800048828125</v>
+        <v>426.0899963378906</v>
       </c>
       <c r="F214" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>426.7200012207031</v>
+        <v>427.25</v>
       </c>
       <c r="C215" t="n">
-        <v>437.4700012207031</v>
+        <v>431.0199890136719</v>
       </c>
       <c r="D215" t="n">
-        <v>425.1000061035156</v>
+        <v>417.3800048828125</v>
       </c>
       <c r="E215" t="n">
-        <v>426.0899963378906</v>
+        <v>421.5499877929688</v>
       </c>
       <c r="F215" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>427.25</v>
+        <v>422.4800109863281</v>
       </c>
       <c r="C216" t="n">
-        <v>431.0199890136719</v>
+        <v>437</v>
       </c>
       <c r="D216" t="n">
-        <v>417.3800048828125</v>
+        <v>420.5</v>
       </c>
       <c r="E216" t="n">
-        <v>421.5499877929688</v>
+        <v>436.3500061035156</v>
       </c>
       <c r="F216" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>422.4800109863281</v>
+        <v>434.9500122070312</v>
       </c>
       <c r="C217" t="n">
-        <v>437</v>
+        <v>436.3200073242188</v>
       </c>
       <c r="D217" t="n">
-        <v>420.5</v>
+        <v>429.7000122070312</v>
       </c>
       <c r="E217" t="n">
-        <v>436.3500061035156</v>
+        <v>431.3099975585938</v>
       </c>
       <c r="F217" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>434.9500122070312</v>
+        <v>428.2699890136719</v>
       </c>
       <c r="C218" t="n">
-        <v>436.3200073242188</v>
+        <v>430.489990234375</v>
       </c>
       <c r="D218" t="n">
-        <v>429.7000122070312</v>
+        <v>420.3999938964844</v>
       </c>
       <c r="E218" t="n">
-        <v>431.3099975585938</v>
+        <v>423.5599975585938</v>
       </c>
       <c r="F218" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>428.2699890136719</v>
+        <v>425.239990234375</v>
       </c>
       <c r="C219" t="n">
-        <v>430.489990234375</v>
+        <v>429</v>
       </c>
       <c r="D219" t="n">
-        <v>420.3999938964844</v>
+        <v>418.9200134277344</v>
       </c>
       <c r="E219" t="n">
-        <v>423.5599975585938</v>
+        <v>420.739990234375</v>
       </c>
       <c r="F219" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>425.239990234375</v>
+        <v>422.510009765625</v>
       </c>
       <c r="C220" t="n">
-        <v>429</v>
+        <v>422.8800048828125</v>
       </c>
       <c r="D220" t="n">
-        <v>418.9200134277344</v>
+        <v>412.5400085449219</v>
       </c>
       <c r="E220" t="n">
-        <v>420.739990234375</v>
+        <v>417.6400146484375</v>
       </c>
       <c r="F220" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>422.510009765625</v>
+        <v>419.9299926757812</v>
       </c>
       <c r="C221" t="n">
-        <v>422.8800048828125</v>
+        <v>430.4599914550781</v>
       </c>
       <c r="D221" t="n">
-        <v>412.5400085449219</v>
+        <v>415.1099853515625</v>
       </c>
       <c r="E221" t="n">
-        <v>417.6400146484375</v>
+        <v>428.7900085449219</v>
       </c>
       <c r="F221" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>419.9299926757812</v>
+        <v>428.260009765625</v>
       </c>
       <c r="C222" t="n">
-        <v>430.4599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="D222" t="n">
-        <v>415.1099853515625</v>
+        <v>420.3500061035156</v>
       </c>
       <c r="E222" t="n">
-        <v>428.7900085449219</v>
+        <v>420.5700073242188</v>
       </c>
       <c r="F222" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>428.260009765625</v>
+        <v>415.1900024414062</v>
       </c>
       <c r="C223" t="n">
-        <v>431.6799926757812</v>
+        <v>427.3399963378906</v>
       </c>
       <c r="D223" t="n">
-        <v>420.3500061035156</v>
+        <v>411.2900085449219</v>
       </c>
       <c r="E223" t="n">
-        <v>420.5700073242188</v>
+        <v>421.4700012207031</v>
       </c>
       <c r="F223" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>415.1900024414062</v>
+        <v>422</v>
       </c>
       <c r="C224" t="n">
-        <v>427.3399963378906</v>
+        <v>422.8099975585938</v>
       </c>
       <c r="D224" t="n">
-        <v>411.2900085449219</v>
+        <v>414.0599975585938</v>
       </c>
       <c r="E224" t="n">
-        <v>421.4700012207031</v>
+        <v>414.3999938964844</v>
       </c>
       <c r="F224" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>422</v>
+        <v>417.4299926757812</v>
       </c>
       <c r="C225" t="n">
-        <v>422.8099975585938</v>
+        <v>419.3399963378906</v>
       </c>
       <c r="D225" t="n">
-        <v>414.0599975585938</v>
+        <v>413.3200073242188</v>
       </c>
       <c r="E225" t="n">
-        <v>414.3999938964844</v>
+        <v>415.3599853515625</v>
       </c>
       <c r="F225" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>417.4299926757812</v>
+        <v>415.5599975585938</v>
       </c>
       <c r="C226" t="n">
-        <v>419.3399963378906</v>
+        <v>416</v>
       </c>
       <c r="D226" t="n">
-        <v>413.3200073242188</v>
+        <v>406.6700134277344</v>
       </c>
       <c r="E226" t="n">
-        <v>415.3599853515625</v>
+        <v>407.5499877929688</v>
       </c>
       <c r="F226" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>415.5599975585938</v>
+        <v>403.1900024414062</v>
       </c>
       <c r="C227" t="n">
-        <v>416</v>
+        <v>416.3599853515625</v>
       </c>
       <c r="D227" t="n">
-        <v>406.6700134277344</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="E227" t="n">
-        <v>407.5499877929688</v>
+        <v>412.75</v>
       </c>
       <c r="F227" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>403.1900024414062</v>
+        <v>415.2699890136719</v>
       </c>
       <c r="C228" t="n">
-        <v>416.3599853515625</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="D228" t="n">
-        <v>397.7999877929688</v>
+        <v>402.3999938964844</v>
       </c>
       <c r="E228" t="n">
-        <v>412.75</v>
+        <v>403.9700012207031</v>
       </c>
       <c r="F228" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>415.2699890136719</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="C229" t="n">
-        <v>416.9700012207031</v>
+        <v>410.6400146484375</v>
       </c>
       <c r="D229" t="n">
-        <v>402.3999938964844</v>
+        <v>400.6600036621094</v>
       </c>
       <c r="E229" t="n">
-        <v>403.9700012207031</v>
+        <v>407.0799865722656</v>
       </c>
       <c r="F229" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>401.5899963378906</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="C230" t="n">
-        <v>410.6400146484375</v>
+        <v>413.0700073242188</v>
       </c>
       <c r="D230" t="n">
-        <v>400.6600036621094</v>
+        <v>407.989990234375</v>
       </c>
       <c r="E230" t="n">
-        <v>407.0799865722656</v>
+        <v>408.739990234375</v>
       </c>
       <c r="F230" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>408.6000061035156</v>
+        <v>409</v>
       </c>
       <c r="C231" t="n">
-        <v>413.0700073242188</v>
+        <v>410.8999938964844</v>
       </c>
       <c r="D231" t="n">
-        <v>407.989990234375</v>
+        <v>401.3200073242188</v>
       </c>
       <c r="E231" t="n">
-        <v>408.739990234375</v>
+        <v>402.1900024414062</v>
       </c>
       <c r="F231" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>409</v>
+        <v>400.9800109863281</v>
       </c>
       <c r="C232" t="n">
-        <v>410.8999938964844</v>
+        <v>407.2000122070312</v>
       </c>
       <c r="D232" t="n">
-        <v>401.3200073242188</v>
+        <v>400.5</v>
       </c>
       <c r="E232" t="n">
-        <v>402.1900024414062</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="F232" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>400.9800109863281</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="C233" t="n">
-        <v>407.2000122070312</v>
+        <v>407.3200073242188</v>
       </c>
       <c r="D233" t="n">
-        <v>400.5</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E233" t="n">
-        <v>405.5899963378906</v>
+        <v>399.0599975585938</v>
       </c>
       <c r="F233" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>405.5899963378906</v>
+        <v>398</v>
       </c>
       <c r="C234" t="n">
-        <v>407.3200073242188</v>
+        <v>403.1799926757812</v>
       </c>
       <c r="D234" t="n">
-        <v>398.5899963378906</v>
+        <v>396.5599975585938</v>
       </c>
       <c r="E234" t="n">
-        <v>399.0599975585938</v>
+        <v>401.7300109863281</v>
       </c>
       <c r="F234" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>398</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C235" t="n">
-        <v>403.1799926757812</v>
+        <v>398.8999938964844</v>
       </c>
       <c r="D235" t="n">
-        <v>396.5599975585938</v>
+        <v>391.4299926757812</v>
       </c>
       <c r="E235" t="n">
-        <v>401.7300109863281</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="F235" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>398.5700073242188</v>
+        <v>397.4299926757812</v>
       </c>
       <c r="C236" t="n">
-        <v>398.8999938964844</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="D236" t="n">
-        <v>391.4299926757812</v>
+        <v>393.510009765625</v>
       </c>
       <c r="E236" t="n">
-        <v>395.6199951171875</v>
+        <v>393.9299926757812</v>
       </c>
       <c r="F236" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>397.4299926757812</v>
+        <v>394.5700073242188</v>
       </c>
       <c r="C237" t="n">
-        <v>398.7900085449219</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="D237" t="n">
-        <v>393.510009765625</v>
+        <v>386.3299865722656</v>
       </c>
       <c r="E237" t="n">
-        <v>393.9299926757812</v>
+        <v>388.6099853515625</v>
       </c>
       <c r="F237" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>394.5700073242188</v>
+        <v>388.25</v>
       </c>
       <c r="C238" t="n">
-        <v>396.7999877929688</v>
+        <v>392.7099914550781</v>
       </c>
       <c r="D238" t="n">
-        <v>386.3299865722656</v>
+        <v>383.8299865722656</v>
       </c>
       <c r="E238" t="n">
-        <v>388.6099853515625</v>
+        <v>384.8500061035156</v>
       </c>
       <c r="F238" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>388.25</v>
+        <v>386</v>
       </c>
       <c r="C239" t="n">
-        <v>392.7099914550781</v>
+        <v>393.6600036621094</v>
       </c>
       <c r="D239" t="n">
-        <v>383.8299865722656</v>
+        <v>386</v>
       </c>
       <c r="E239" t="n">
-        <v>384.8500061035156</v>
+        <v>390.1099853515625</v>
       </c>
       <c r="F239" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>386</v>
+        <v>391.0400085449219</v>
       </c>
       <c r="C240" t="n">
-        <v>393.6600036621094</v>
+        <v>399.5799865722656</v>
       </c>
       <c r="D240" t="n">
-        <v>386</v>
+        <v>390.8599853515625</v>
       </c>
       <c r="E240" t="n">
-        <v>390.1099853515625</v>
+        <v>398.760009765625</v>
       </c>
       <c r="F240" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>391.0400085449219</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="C241" t="n">
-        <v>399.5799865722656</v>
+        <v>399.0299987792969</v>
       </c>
       <c r="D241" t="n">
-        <v>390.8599853515625</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="E241" t="n">
-        <v>398.760009765625</v>
+        <v>396.5899963378906</v>
       </c>
       <c r="F241" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>397.7999877929688</v>
+        <v>396.3299865722656</v>
       </c>
       <c r="C242" t="n">
-        <v>399.0299987792969</v>
+        <v>406.25</v>
       </c>
       <c r="D242" t="n">
-        <v>395.6199951171875</v>
+        <v>396.010009765625</v>
       </c>
       <c r="E242" t="n">
-        <v>396.5899963378906</v>
+        <v>401.010009765625</v>
       </c>
       <c r="F242" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>396.3299865722656</v>
+        <v>396.8699951171875</v>
       </c>
       <c r="C243" t="n">
-        <v>406.25</v>
+        <v>399.8800048828125</v>
       </c>
       <c r="D243" t="n">
-        <v>396.010009765625</v>
+        <v>393.7699890136719</v>
       </c>
       <c r="E243" t="n">
-        <v>401.010009765625</v>
+        <v>395.0499877929688</v>
       </c>
       <c r="F243" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>396.8699951171875</v>
+        <v>396.4200134277344</v>
       </c>
       <c r="C244" t="n">
-        <v>399.8800048828125</v>
+        <v>396.739990234375</v>
       </c>
       <c r="D244" t="n">
-        <v>393.7699890136719</v>
+        <v>392.6600036621094</v>
       </c>
       <c r="E244" t="n">
-        <v>395.0499877929688</v>
+        <v>392.9500122070312</v>
       </c>
       <c r="F244" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>396.4200134277344</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="C245" t="n">
-        <v>396.739990234375</v>
+        <v>394.489990234375</v>
       </c>
       <c r="D245" t="n">
-        <v>392.6600036621094</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="E245" t="n">
-        <v>392.9500122070312</v>
+        <v>389.4100036621094</v>
       </c>
       <c r="F245" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>393.5199890136719</v>
+        <v>392.0799865722656</v>
       </c>
       <c r="C246" t="n">
-        <v>394.489990234375</v>
+        <v>399.6000061035156</v>
       </c>
       <c r="D246" t="n">
-        <v>387.7099914550781</v>
+        <v>391.7799987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>389.4100036621094</v>
+        <v>396.2999877929688</v>
       </c>
       <c r="F246" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>392.0799865722656</v>
+        <v>399.2699890136719</v>
       </c>
       <c r="C247" t="n">
-        <v>399.6000061035156</v>
+        <v>401.1400146484375</v>
       </c>
       <c r="D247" t="n">
-        <v>391.7799987792969</v>
+        <v>396.510009765625</v>
       </c>
       <c r="E247" t="n">
-        <v>396.2999877929688</v>
+        <v>399.6600036621094</v>
       </c>
       <c r="F247" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>399.2699890136719</v>
+        <v>400.0199890136719</v>
       </c>
       <c r="C248" t="n">
-        <v>401.1400146484375</v>
+        <v>405.1600036621094</v>
       </c>
       <c r="D248" t="n">
-        <v>396.510009765625</v>
+        <v>395.2999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>399.6600036621094</v>
+        <v>400.9400024414062</v>
       </c>
       <c r="F248" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>400.0199890136719</v>
+        <v>397.0499877929688</v>
       </c>
       <c r="C249" t="n">
-        <v>405.1600036621094</v>
+        <v>402.2300109863281</v>
       </c>
       <c r="D249" t="n">
-        <v>395.2999877929688</v>
+        <v>395.2000122070312</v>
       </c>
       <c r="E249" t="n">
-        <v>400.9400024414062</v>
+        <v>397.1400146484375</v>
       </c>
       <c r="F249" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>397.0499877929688</v>
+        <v>392.3999938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>402.2300109863281</v>
+        <v>403.8900146484375</v>
       </c>
       <c r="D250" t="n">
-        <v>395.2000122070312</v>
+        <v>390.4400024414062</v>
       </c>
       <c r="E250" t="n">
-        <v>397.1400146484375</v>
+        <v>400.8399963378906</v>
       </c>
       <c r="F250" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>392.3999938964844</v>
+        <v>405.1700134277344</v>
       </c>
       <c r="C251" t="n">
-        <v>403.8900146484375</v>
+        <v>406.5299987792969</v>
       </c>
       <c r="D251" t="n">
-        <v>390.4400024414062</v>
+        <v>378.0799865722656</v>
       </c>
       <c r="E251" t="n">
-        <v>400.8399963378906</v>
+        <v>393.0599975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>405.1700134277344</v>
+        <v>396</v>
       </c>
       <c r="C252" t="n">
-        <v>406.5299987792969</v>
+        <v>399.2699890136719</v>
       </c>
       <c r="D252" t="n">
-        <v>378.0799865722656</v>
+        <v>387.6000061035156</v>
       </c>
       <c r="E252" t="n">
-        <v>393.0599975585938</v>
+        <v>388.2799987792969</v>
       </c>
       <c r="F252" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,34 +10530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>388.28</v>
+      </c>
+      <c r="D2" t="n">
         <v>393.06</v>
       </c>
-      <c r="D2" t="n">
-        <v>400.84</v>
-      </c>
       <c r="E2" t="n">
-        <v>405.17</v>
+        <v>396</v>
       </c>
       <c r="F2" t="n">
-        <v>406.53</v>
+        <v>399.265</v>
       </c>
       <c r="G2" t="n">
-        <v>378.0801</v>
+        <v>387.61</v>
       </c>
       <c r="H2" t="n">
-        <v>7730118</v>
+        <v>4265842</v>
       </c>
       <c r="I2" t="n">
-        <v>5278940</v>
+        <v>5324795</v>
       </c>
       <c r="J2" t="n">
-        <v>352808632320</v>
+        <v>348518121472</v>
       </c>
       <c r="K2" t="n">
-        <v>25.244701</v>
+        <v>24.9377</v>
       </c>
       <c r="L2" t="n">
-        <v>17.519657</v>
+        <v>17.3066</v>
       </c>
       <c r="M2" t="n">
         <v>15.57</v>
@@ -10572,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.6133149</v>
+        <v>3.5693734</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>402170642432</v>
+        <v>397880131584</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:46</t>
+          <t>2026-09-11 19:03:22</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>339.8969161546314</v>
+        <v>346.6169306487971</v>
       </c>
       <c r="C2" t="n">
-        <v>351.5644485034896</v>
+        <v>352.8597399573416</v>
       </c>
       <c r="D2" t="n">
-        <v>336.8193359260115</v>
+        <v>343.2666549867767</v>
       </c>
       <c r="E2" t="n">
-        <v>344.3866577148438</v>
+        <v>343.3153686523438</v>
       </c>
       <c r="F2" t="n">
-        <v>18943500</v>
+        <v>14016200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>346.6169614598537</v>
+        <v>344.2562617205344</v>
       </c>
       <c r="C3" t="n">
-        <v>352.8597713233265</v>
+        <v>344.6972712574788</v>
       </c>
       <c r="D3" t="n">
-        <v>343.2666855000246</v>
+        <v>335.7003177947291</v>
       </c>
       <c r="E3" t="n">
-        <v>343.3153991699219</v>
+        <v>340.9534606933594</v>
       </c>
       <c r="F3" t="n">
-        <v>14016200</v>
+        <v>11035900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>344.2562617205344</v>
+        <v>340.5711991051483</v>
       </c>
       <c r="C4" t="n">
-        <v>344.6972712574788</v>
+        <v>342.0805014268064</v>
       </c>
       <c r="D4" t="n">
-        <v>335.7003177947291</v>
+        <v>331.5742462609258</v>
       </c>
       <c r="E4" t="n">
-        <v>340.9534606933594</v>
+        <v>333.005126953125</v>
       </c>
       <c r="F4" t="n">
-        <v>11035900</v>
+        <v>12695800</v>
       </c>
       <c r="G4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>340.5711991051483</v>
+        <v>330.9568525731296</v>
       </c>
       <c r="C5" t="n">
-        <v>342.0805014268064</v>
+        <v>336.1609748937723</v>
       </c>
       <c r="D5" t="n">
-        <v>331.5742462609258</v>
+        <v>330.9568525731296</v>
       </c>
       <c r="E5" t="n">
-        <v>333.005126953125</v>
+        <v>334.7986755371094</v>
       </c>
       <c r="F5" t="n">
-        <v>12695800</v>
+        <v>8467700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>330.9568224057415</v>
+        <v>336.6803662104043</v>
       </c>
       <c r="C6" t="n">
-        <v>336.1609442520178</v>
+        <v>338.0524456778033</v>
       </c>
       <c r="D6" t="n">
-        <v>330.9568224057415</v>
+        <v>327.4579882805058</v>
       </c>
       <c r="E6" t="n">
-        <v>334.7986450195312</v>
+        <v>328.14404296875</v>
       </c>
       <c r="F6" t="n">
-        <v>8467700</v>
+        <v>11255600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>336.6803662104043</v>
+        <v>329.7905316198508</v>
       </c>
       <c r="C7" t="n">
-        <v>338.0524456778033</v>
+        <v>334.161595373165</v>
       </c>
       <c r="D7" t="n">
-        <v>327.4579882805058</v>
+        <v>327.1835657302883</v>
       </c>
       <c r="E7" t="n">
-        <v>328.14404296875</v>
+        <v>329.9767456054688</v>
       </c>
       <c r="F7" t="n">
-        <v>11255600</v>
+        <v>13656800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>329.7905316198508</v>
+        <v>327.7911982671105</v>
       </c>
       <c r="C8" t="n">
-        <v>334.161595373165</v>
+        <v>335.6513067387905</v>
       </c>
       <c r="D8" t="n">
-        <v>327.1835657302883</v>
+        <v>325.9682991379935</v>
       </c>
       <c r="E8" t="n">
-        <v>329.9767456054688</v>
+        <v>334.4948120117188</v>
       </c>
       <c r="F8" t="n">
-        <v>13656800</v>
+        <v>8903700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>327.7912281730855</v>
+        <v>334.2008052062361</v>
       </c>
       <c r="C9" t="n">
-        <v>335.6513373618812</v>
+        <v>345.6675310141911</v>
       </c>
       <c r="D9" t="n">
-        <v>325.9683288776566</v>
+        <v>333.1815333788629</v>
       </c>
       <c r="E9" t="n">
-        <v>334.4948425292969</v>
+        <v>340.7574157714844</v>
       </c>
       <c r="F9" t="n">
-        <v>8903700</v>
+        <v>12504100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>334.2008052062361</v>
+        <v>343.2174040946968</v>
       </c>
       <c r="C10" t="n">
-        <v>345.6675310141911</v>
+        <v>347.4316547985749</v>
       </c>
       <c r="D10" t="n">
-        <v>333.1815333788629</v>
+        <v>340.904444380264</v>
       </c>
       <c r="E10" t="n">
-        <v>340.7574157714844</v>
+        <v>344.7952880859375</v>
       </c>
       <c r="F10" t="n">
-        <v>12504100</v>
+        <v>9016300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>343.217373716776</v>
+        <v>341.9432916493518</v>
       </c>
       <c r="C11" t="n">
-        <v>347.4316240476539</v>
+        <v>343.2075787683629</v>
       </c>
       <c r="D11" t="n">
-        <v>340.9044142070616</v>
+        <v>336.7489800892123</v>
       </c>
       <c r="E11" t="n">
-        <v>344.7952575683594</v>
+        <v>338.6698913574219</v>
       </c>
       <c r="F11" t="n">
-        <v>9016300</v>
+        <v>8104900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>341.9432916493518</v>
+        <v>340.9926010114185</v>
       </c>
       <c r="C12" t="n">
-        <v>343.2075787683629</v>
+        <v>342.9919337348455</v>
       </c>
       <c r="D12" t="n">
-        <v>336.7489800892123</v>
+        <v>334.4947920920956</v>
       </c>
       <c r="E12" t="n">
-        <v>338.6698913574219</v>
+        <v>337.2193603515625</v>
       </c>
       <c r="F12" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>340.9926010114185</v>
+        <v>337.1213995584671</v>
       </c>
       <c r="C13" t="n">
-        <v>342.9919337348455</v>
+        <v>338.6600726249961</v>
       </c>
       <c r="D13" t="n">
-        <v>334.4947920920956</v>
+        <v>334.6418463806178</v>
       </c>
       <c r="E13" t="n">
-        <v>337.2193603515625</v>
+        <v>338.2974548339844</v>
       </c>
       <c r="F13" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>337.1214299699541</v>
+        <v>336.8959869118207</v>
       </c>
       <c r="C14" t="n">
-        <v>338.6601031752857</v>
+        <v>342.3549341542898</v>
       </c>
       <c r="D14" t="n">
-        <v>334.641876568426</v>
+        <v>335.5042870567964</v>
       </c>
       <c r="E14" t="n">
-        <v>338.2974853515625</v>
+        <v>338.4150695800781</v>
       </c>
       <c r="F14" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>336.8959869118207</v>
+        <v>337.042992446128</v>
       </c>
       <c r="C15" t="n">
-        <v>342.3549341542898</v>
+        <v>341.7473034781017</v>
       </c>
       <c r="D15" t="n">
-        <v>335.5042870567964</v>
+        <v>334.8182646079004</v>
       </c>
       <c r="E15" t="n">
-        <v>338.4150695800781</v>
+        <v>341.3552551269531</v>
       </c>
       <c r="F15" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>337.042992446128</v>
+        <v>340.3654202552976</v>
       </c>
       <c r="C16" t="n">
-        <v>341.7473034781017</v>
+        <v>348.0000745206634</v>
       </c>
       <c r="D16" t="n">
-        <v>334.8182646079004</v>
+        <v>337.7780446522378</v>
       </c>
       <c r="E16" t="n">
-        <v>341.3552551269531</v>
+        <v>346.6672058105469</v>
       </c>
       <c r="F16" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>340.3653902924742</v>
+        <v>350.126813283771</v>
       </c>
       <c r="C17" t="n">
-        <v>348.000043885751</v>
+        <v>360.6624696666976</v>
       </c>
       <c r="D17" t="n">
-        <v>337.7780149171845</v>
+        <v>349.4995598497266</v>
       </c>
       <c r="E17" t="n">
-        <v>346.6671752929688</v>
+        <v>353.0180053710938</v>
       </c>
       <c r="F17" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>350.126813283771</v>
+        <v>353.8314330983794</v>
       </c>
       <c r="C18" t="n">
-        <v>360.6624696666976</v>
+        <v>355.2917144647868</v>
       </c>
       <c r="D18" t="n">
-        <v>349.4995598497266</v>
+        <v>349.9895806938981</v>
       </c>
       <c r="E18" t="n">
-        <v>353.0180053710938</v>
+        <v>351.6164855957031</v>
       </c>
       <c r="F18" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>353.8314638081978</v>
+        <v>352.2437372182849</v>
       </c>
       <c r="C19" t="n">
-        <v>355.2917453013463</v>
+        <v>357.4478588776738</v>
       </c>
       <c r="D19" t="n">
-        <v>349.9896110702735</v>
+        <v>350.9206488503359</v>
       </c>
       <c r="E19" t="n">
-        <v>351.6165161132812</v>
+        <v>356.4089965820312</v>
       </c>
       <c r="F19" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>352.243767379212</v>
+        <v>359.613786634634</v>
       </c>
       <c r="C20" t="n">
-        <v>357.4478894842047</v>
+        <v>367.1602685308417</v>
       </c>
       <c r="D20" t="n">
-        <v>350.9206788979734</v>
+        <v>358.5063128850491</v>
       </c>
       <c r="E20" t="n">
-        <v>356.4090270996094</v>
+        <v>362.544189453125</v>
       </c>
       <c r="F20" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>359.613786634634</v>
+        <v>365.0923241938757</v>
       </c>
       <c r="C21" t="n">
-        <v>367.1602685308417</v>
+        <v>368.7185619691624</v>
       </c>
       <c r="D21" t="n">
-        <v>358.5063128850491</v>
+        <v>358.7807287668154</v>
       </c>
       <c r="E21" t="n">
-        <v>362.544189453125</v>
+        <v>360.358642578125</v>
       </c>
       <c r="F21" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>365.0923551123336</v>
+        <v>362.0345124206696</v>
       </c>
       <c r="C22" t="n">
-        <v>368.7185931947143</v>
+        <v>362.0345124206696</v>
       </c>
       <c r="D22" t="n">
-        <v>358.7807591507652</v>
+        <v>345.481298369123</v>
       </c>
       <c r="E22" t="n">
-        <v>360.3586730957031</v>
+        <v>347.4316101074219</v>
       </c>
       <c r="F22" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>362.0345442209324</v>
+        <v>347.6668450586018</v>
       </c>
       <c r="C23" t="n">
-        <v>362.0345442209324</v>
+        <v>351.9987280315978</v>
       </c>
       <c r="D23" t="n">
-        <v>345.4813287153903</v>
+        <v>346.2751751256885</v>
       </c>
       <c r="E23" t="n">
-        <v>347.431640625</v>
+        <v>351.5086975097656</v>
       </c>
       <c r="F23" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>347.6668450586018</v>
+        <v>347.8726721794402</v>
       </c>
       <c r="C24" t="n">
-        <v>351.9987280315978</v>
+        <v>355.1054974076654</v>
       </c>
       <c r="D24" t="n">
-        <v>346.2751751256885</v>
+        <v>346.3535596478916</v>
       </c>
       <c r="E24" t="n">
-        <v>351.5086975097656</v>
+        <v>352.7533569335938</v>
       </c>
       <c r="F24" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>347.8726721794402</v>
+        <v>352.224118197926</v>
       </c>
       <c r="C25" t="n">
-        <v>355.1054974076654</v>
+        <v>356.9577994132716</v>
       </c>
       <c r="D25" t="n">
-        <v>346.3535596478916</v>
+        <v>348.7546940700243</v>
       </c>
       <c r="E25" t="n">
-        <v>352.7533569335938</v>
+        <v>353.9490051269531</v>
       </c>
       <c r="F25" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>352.2241789356418</v>
+        <v>354.6252788942206</v>
       </c>
       <c r="C26" t="n">
-        <v>356.9578609672659</v>
+        <v>354.7820922478407</v>
       </c>
       <c r="D26" t="n">
-        <v>348.7547542094708</v>
+        <v>347.3336224508748</v>
       </c>
       <c r="E26" t="n">
-        <v>353.9490661621094</v>
+        <v>349.5583801269531</v>
       </c>
       <c r="F26" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>354.6252788942206</v>
+        <v>344.0014287463771</v>
       </c>
       <c r="C27" t="n">
-        <v>354.7820922478407</v>
+        <v>351.2440942663747</v>
       </c>
       <c r="D27" t="n">
-        <v>347.3336224508748</v>
+        <v>343.8348052077826</v>
       </c>
       <c r="E27" t="n">
-        <v>349.5583801269531</v>
+        <v>349.4897766113281</v>
       </c>
       <c r="F27" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>344.0013987080436</v>
+        <v>351.3911117321571</v>
       </c>
       <c r="C28" t="n">
-        <v>351.2440635956089</v>
+        <v>358.2809400014152</v>
       </c>
       <c r="D28" t="n">
-        <v>343.8347751839987</v>
+        <v>350.3816500053927</v>
       </c>
       <c r="E28" t="n">
-        <v>349.48974609375</v>
+        <v>357.2126770019531</v>
       </c>
       <c r="F28" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>351.3911117321571</v>
+        <v>357.8595050033854</v>
       </c>
       <c r="C29" t="n">
-        <v>358.2809400014152</v>
+        <v>363.6516394702736</v>
       </c>
       <c r="D29" t="n">
-        <v>350.3816500053927</v>
+        <v>354.2920684364863</v>
       </c>
       <c r="E29" t="n">
-        <v>357.2126770019531</v>
+        <v>358.0848999023438</v>
       </c>
       <c r="F29" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>357.8594745050165</v>
+        <v>356.7029783280342</v>
       </c>
       <c r="C30" t="n">
-        <v>363.6516084782733</v>
+        <v>356.7421891409456</v>
       </c>
       <c r="D30" t="n">
-        <v>354.2920382421501</v>
+        <v>350.8618233858751</v>
       </c>
       <c r="E30" t="n">
-        <v>358.0848693847656</v>
+        <v>354.2822265625</v>
       </c>
       <c r="F30" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>356.7029783280342</v>
+        <v>348.4900782801277</v>
       </c>
       <c r="C31" t="n">
-        <v>356.7421891409456</v>
+        <v>355.0564989637384</v>
       </c>
       <c r="D31" t="n">
-        <v>350.8618233858751</v>
+        <v>346.588787450705</v>
       </c>
       <c r="E31" t="n">
-        <v>354.2822265625</v>
+        <v>353.2630004882812</v>
       </c>
       <c r="F31" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>348.4901083853841</v>
+        <v>354.1646514889598</v>
       </c>
       <c r="C32" t="n">
-        <v>355.0565296362527</v>
+        <v>358.1339166267961</v>
       </c>
       <c r="D32" t="n">
-        <v>346.5888173917132</v>
+        <v>352.8513732909411</v>
       </c>
       <c r="E32" t="n">
-        <v>353.2630310058594</v>
+        <v>355.2721252441406</v>
       </c>
       <c r="F32" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>354.1646210665127</v>
+        <v>356.2521771853968</v>
       </c>
       <c r="C33" t="n">
-        <v>358.1338858633925</v>
+        <v>358.9179443293374</v>
       </c>
       <c r="D33" t="n">
-        <v>352.8513429813036</v>
+        <v>354.194043082288</v>
       </c>
       <c r="E33" t="n">
-        <v>355.2720947265625</v>
+        <v>358.6827392578125</v>
       </c>
       <c r="F33" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>356.252207496177</v>
+        <v>373.0896257903608</v>
       </c>
       <c r="C34" t="n">
-        <v>358.9179748669274</v>
+        <v>373.4032524981995</v>
       </c>
       <c r="D34" t="n">
-        <v>354.1940732179572</v>
+        <v>351.4792920385495</v>
       </c>
       <c r="E34" t="n">
-        <v>358.6827697753906</v>
+        <v>360.5056457519531</v>
       </c>
       <c r="F34" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>373.0896257903608</v>
+        <v>357.0166226761716</v>
       </c>
       <c r="C35" t="n">
-        <v>373.4032524981995</v>
+        <v>358.8493319750526</v>
       </c>
       <c r="D35" t="n">
-        <v>351.4792920385495</v>
+        <v>346.8239941782638</v>
       </c>
       <c r="E35" t="n">
-        <v>360.5056457519531</v>
+        <v>348.1764831542969</v>
       </c>
       <c r="F35" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>357.0166226761716</v>
+        <v>340.5908266262187</v>
       </c>
       <c r="C36" t="n">
-        <v>358.8493319750526</v>
+        <v>347.4708747692525</v>
       </c>
       <c r="D36" t="n">
-        <v>346.8239941782638</v>
+        <v>336.7490038190758</v>
       </c>
       <c r="E36" t="n">
-        <v>348.1764831542969</v>
+        <v>337.8760681152344</v>
       </c>
       <c r="F36" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>340.5908266262187</v>
+        <v>337.5232231766179</v>
       </c>
       <c r="C37" t="n">
-        <v>347.4708747692525</v>
+        <v>339.3755229195461</v>
       </c>
       <c r="D37" t="n">
-        <v>336.7490038190758</v>
+        <v>330.398160543053</v>
       </c>
       <c r="E37" t="n">
-        <v>337.8760681152344</v>
+        <v>334.7496337890625</v>
       </c>
       <c r="F37" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>337.5232539470514</v>
+        <v>332.3681048776954</v>
       </c>
       <c r="C38" t="n">
-        <v>339.3755538588451</v>
+        <v>333.9068078868114</v>
       </c>
       <c r="D38" t="n">
-        <v>330.3981906639274</v>
+        <v>320.0879412577473</v>
       </c>
       <c r="E38" t="n">
-        <v>334.7496643066406</v>
+        <v>327.1345825195312</v>
       </c>
       <c r="F38" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>332.3681048776954</v>
+        <v>321.0974041522996</v>
       </c>
       <c r="C39" t="n">
-        <v>333.9068078868114</v>
+        <v>329.7905408141606</v>
       </c>
       <c r="D39" t="n">
-        <v>320.0879412577473</v>
+        <v>320.6759850821896</v>
       </c>
       <c r="E39" t="n">
-        <v>327.1345825195312</v>
+        <v>324.2335815429688</v>
       </c>
       <c r="F39" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>321.0974041522996</v>
+        <v>319.7939098851405</v>
       </c>
       <c r="C40" t="n">
-        <v>329.7905408141606</v>
+        <v>323.6259521945154</v>
       </c>
       <c r="D40" t="n">
-        <v>320.6759850821896</v>
+        <v>317.7553960532753</v>
       </c>
       <c r="E40" t="n">
-        <v>324.2335815429688</v>
+        <v>321.2052001953125</v>
       </c>
       <c r="F40" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>319.7939098851405</v>
+        <v>322.3616713627413</v>
       </c>
       <c r="C41" t="n">
-        <v>323.6259521945154</v>
+        <v>325.7428638052234</v>
       </c>
       <c r="D41" t="n">
-        <v>317.7553960532753</v>
+        <v>315.0406146307628</v>
       </c>
       <c r="E41" t="n">
-        <v>321.2052001953125</v>
+        <v>315.1484069824219</v>
       </c>
       <c r="F41" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>322.3617025788201</v>
+        <v>313.2863092733651</v>
       </c>
       <c r="C42" t="n">
-        <v>325.7428953487219</v>
+        <v>318.0787921089143</v>
       </c>
       <c r="D42" t="n">
-        <v>315.0406451379028</v>
+        <v>307.8959736628304</v>
       </c>
       <c r="E42" t="n">
-        <v>315.1484375</v>
+        <v>317.7455749511719</v>
       </c>
       <c r="F42" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>313.2863393626572</v>
+        <v>313.6097058862107</v>
       </c>
       <c r="C43" t="n">
-        <v>318.0788226584959</v>
+        <v>317.7847752647608</v>
       </c>
       <c r="D43" t="n">
-        <v>307.8960032344128</v>
+        <v>310.8459566317771</v>
       </c>
       <c r="E43" t="n">
-        <v>317.74560546875</v>
+        <v>315.1679992675781</v>
       </c>
       <c r="F43" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>313.6097362529</v>
+        <v>316.8537128676349</v>
       </c>
       <c r="C44" t="n">
-        <v>317.7848060357201</v>
+        <v>321.3227886847148</v>
       </c>
       <c r="D44" t="n">
-        <v>310.8459867308537</v>
+        <v>313.5019209593692</v>
       </c>
       <c r="E44" t="n">
-        <v>315.1680297851562</v>
+        <v>320.9209899902344</v>
       </c>
       <c r="F44" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>316.8537128676349</v>
+        <v>321.9010364932658</v>
       </c>
       <c r="C45" t="n">
-        <v>321.3227886847148</v>
+        <v>336.3275351202159</v>
       </c>
       <c r="D45" t="n">
-        <v>313.5019209593692</v>
+        <v>320.5583278451826</v>
       </c>
       <c r="E45" t="n">
-        <v>320.9209899902344</v>
+        <v>332.2994689941406</v>
       </c>
       <c r="F45" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>321.9010364932658</v>
+        <v>331.6036653013031</v>
       </c>
       <c r="C46" t="n">
-        <v>336.3275351202159</v>
+        <v>332.2700996432553</v>
       </c>
       <c r="D46" t="n">
-        <v>320.5583278451826</v>
+        <v>324.6844366173477</v>
       </c>
       <c r="E46" t="n">
-        <v>332.2994689941406</v>
+        <v>325.889892578125</v>
       </c>
       <c r="F46" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>331.6036653013031</v>
+        <v>320.4309500487702</v>
       </c>
       <c r="C47" t="n">
-        <v>332.2700996432553</v>
+        <v>321.6658065479886</v>
       </c>
       <c r="D47" t="n">
-        <v>324.6844366173477</v>
+        <v>314.0997345701073</v>
       </c>
       <c r="E47" t="n">
-        <v>325.889892578125</v>
+        <v>315.4424133300781</v>
       </c>
       <c r="F47" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>320.4309500487702</v>
+        <v>314.2075720220705</v>
       </c>
       <c r="C48" t="n">
-        <v>321.6658065479886</v>
+        <v>321.3424151200708</v>
       </c>
       <c r="D48" t="n">
-        <v>314.0997345701073</v>
+        <v>313.06088745762</v>
       </c>
       <c r="E48" t="n">
-        <v>315.4424133300781</v>
+        <v>314.129150390625</v>
       </c>
       <c r="F48" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>314.2075720220705</v>
+        <v>310.6891466030926</v>
       </c>
       <c r="C49" t="n">
-        <v>321.3424151200708</v>
+        <v>311.1693669212913</v>
       </c>
       <c r="D49" t="n">
-        <v>313.06088745762</v>
+        <v>302.6134236399317</v>
       </c>
       <c r="E49" t="n">
-        <v>314.129150390625</v>
+        <v>307.3275146484375</v>
       </c>
       <c r="F49" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>310.6891466030926</v>
+        <v>307.6705238330165</v>
       </c>
       <c r="C50" t="n">
-        <v>311.1693669212913</v>
+        <v>308.7191962173961</v>
       </c>
       <c r="D50" t="n">
-        <v>302.6134236399317</v>
+        <v>298.4579569753306</v>
       </c>
       <c r="E50" t="n">
-        <v>307.3275146484375</v>
+        <v>302.9270324707031</v>
       </c>
       <c r="F50" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>307.6705548284651</v>
+        <v>304.6127612455315</v>
       </c>
       <c r="C51" t="n">
-        <v>308.7192273184903</v>
+        <v>308.4742040318584</v>
       </c>
       <c r="D51" t="n">
-        <v>298.4579870426836</v>
+        <v>303.8189142172394</v>
       </c>
       <c r="E51" t="n">
-        <v>302.9270629882812</v>
+        <v>305.3282165527344</v>
       </c>
       <c r="F51" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>304.6127916915999</v>
+        <v>305.6908589139109</v>
       </c>
       <c r="C52" t="n">
-        <v>308.4742348638782</v>
+        <v>317.3829805678444</v>
       </c>
       <c r="D52" t="n">
-        <v>303.8189445839627</v>
+        <v>305.2302290041278</v>
       </c>
       <c r="E52" t="n">
-        <v>305.3282470703125</v>
+        <v>313.5901489257812</v>
       </c>
       <c r="F52" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>305.6908291650661</v>
+        <v>318.0592531062754</v>
       </c>
       <c r="C53" t="n">
-        <v>317.3829496811602</v>
+        <v>319.352941040257</v>
       </c>
       <c r="D53" t="n">
-        <v>305.23019930011</v>
+        <v>311.2870267728116</v>
       </c>
       <c r="E53" t="n">
-        <v>313.5901184082031</v>
+        <v>312.6885070800781</v>
       </c>
       <c r="F53" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>318.0592220645265</v>
+        <v>314.7171737995267</v>
       </c>
       <c r="C54" t="n">
-        <v>319.3529098722476</v>
+        <v>321.4599980564078</v>
       </c>
       <c r="D54" t="n">
-        <v>311.2869963920142</v>
+        <v>314.5015591898327</v>
       </c>
       <c r="E54" t="n">
-        <v>312.6884765625</v>
+        <v>319.7742919921875</v>
       </c>
       <c r="F54" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>314.71720383448</v>
+        <v>320.07813955632</v>
       </c>
       <c r="C55" t="n">
-        <v>321.4600287348608</v>
+        <v>328.5066706952173</v>
       </c>
       <c r="D55" t="n">
-        <v>314.5015892042089</v>
+        <v>319.3921147564304</v>
       </c>
       <c r="E55" t="n">
-        <v>319.7743225097656</v>
+        <v>323.1359252929688</v>
       </c>
       <c r="F55" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>320.078109327525</v>
+        <v>325.0568726515205</v>
       </c>
       <c r="C56" t="n">
-        <v>328.5066396704157</v>
+        <v>325.4390809212725</v>
       </c>
       <c r="D56" t="n">
-        <v>319.3920845924249</v>
+        <v>322.3323040363653</v>
       </c>
       <c r="E56" t="n">
-        <v>323.1358947753906</v>
+        <v>323.1947326660156</v>
       </c>
       <c r="F56" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>325.0568419581102</v>
+        <v>320.6367557882569</v>
       </c>
       <c r="C57" t="n">
-        <v>325.4390501917724</v>
+        <v>323.4789266660114</v>
       </c>
       <c r="D57" t="n">
-        <v>322.3322736002218</v>
+        <v>316.5890991303779</v>
       </c>
       <c r="E57" t="n">
-        <v>323.1947021484375</v>
+        <v>316.7655029296875</v>
       </c>
       <c r="F57" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>320.6367866787963</v>
+        <v>316.9223461399793</v>
       </c>
       <c r="C58" t="n">
-        <v>323.478957830369</v>
+        <v>322.1460884369951</v>
       </c>
       <c r="D58" t="n">
-        <v>316.5891296309611</v>
+        <v>316.3637041471038</v>
       </c>
       <c r="E58" t="n">
-        <v>316.7655334472656</v>
+        <v>318.0690307617188</v>
       </c>
       <c r="F58" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>316.9223461399793</v>
+        <v>319.4998951185618</v>
       </c>
       <c r="C59" t="n">
-        <v>322.1460884369951</v>
+        <v>334.6026391486864</v>
       </c>
       <c r="D59" t="n">
-        <v>316.3637041471038</v>
+        <v>318.529644271779</v>
       </c>
       <c r="E59" t="n">
-        <v>318.0690307617188</v>
+        <v>332.9365234375</v>
       </c>
       <c r="F59" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>319.4998951185618</v>
+        <v>332.632709971988</v>
       </c>
       <c r="C60" t="n">
-        <v>334.6026391486864</v>
+        <v>334.4556390535126</v>
       </c>
       <c r="D60" t="n">
-        <v>318.529644271779</v>
+        <v>322.1656652751352</v>
       </c>
       <c r="E60" t="n">
-        <v>332.9365234375</v>
+        <v>326.8405456542969</v>
       </c>
       <c r="F60" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>332.632709971988</v>
+        <v>328.3204578992349</v>
       </c>
       <c r="C61" t="n">
-        <v>334.4556390535126</v>
+        <v>329.0162928832224</v>
       </c>
       <c r="D61" t="n">
-        <v>322.1656652751352</v>
+        <v>321.9598711365138</v>
       </c>
       <c r="E61" t="n">
-        <v>326.8405456542969</v>
+        <v>324.31201171875</v>
       </c>
       <c r="F61" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>328.3204578992349</v>
+        <v>324.3120056919803</v>
       </c>
       <c r="C62" t="n">
-        <v>329.0162928832224</v>
+        <v>324.7066598386667</v>
       </c>
       <c r="D62" t="n">
-        <v>321.9598711365138</v>
+        <v>318.5203424234218</v>
       </c>
       <c r="E62" t="n">
-        <v>324.31201171875</v>
+        <v>319.2998046875</v>
       </c>
       <c r="F62" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>324.3120366886073</v>
+        <v>318.8459617269979</v>
       </c>
       <c r="C63" t="n">
-        <v>324.7066908730135</v>
+        <v>322.0032250879344</v>
       </c>
       <c r="D63" t="n">
-        <v>318.5203728665016</v>
+        <v>318.1750466501944</v>
       </c>
       <c r="E63" t="n">
-        <v>319.2998352050781</v>
+        <v>319.2800903320312</v>
       </c>
       <c r="F63" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G63" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>318.8459617269979</v>
+        <v>318.4414486886093</v>
       </c>
       <c r="C64" t="n">
-        <v>322.0032250879344</v>
+        <v>324.341629514822</v>
       </c>
       <c r="D64" t="n">
-        <v>318.1750466501944</v>
+        <v>315.3335056374652</v>
       </c>
       <c r="E64" t="n">
-        <v>319.2800903320312</v>
+        <v>323.9864196777344</v>
       </c>
       <c r="F64" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>318.4414486886093</v>
+        <v>325.9596900029746</v>
       </c>
       <c r="C65" t="n">
-        <v>324.341629514822</v>
+        <v>334.7211504310009</v>
       </c>
       <c r="D65" t="n">
-        <v>315.3335056374652</v>
+        <v>324.3711973012736</v>
       </c>
       <c r="E65" t="n">
-        <v>323.9864196777344</v>
+        <v>332.2348022460938</v>
       </c>
       <c r="F65" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>325.9597199441495</v>
+        <v>332.9945516695081</v>
       </c>
       <c r="C66" t="n">
-        <v>334.7211811769636</v>
+        <v>340.3747084246943</v>
       </c>
       <c r="D66" t="n">
-        <v>324.3712270965368</v>
+        <v>332.8662822838281</v>
       </c>
       <c r="E66" t="n">
-        <v>332.2348327636719</v>
+        <v>337.276611328125</v>
       </c>
       <c r="F66" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>332.9945215393808</v>
+        <v>336.4379310634787</v>
       </c>
       <c r="C67" t="n">
-        <v>340.3746776267931</v>
+        <v>340.3549345980833</v>
       </c>
       <c r="D67" t="n">
-        <v>332.8662521653069</v>
+        <v>332.5012053593197</v>
       </c>
       <c r="E67" t="n">
-        <v>337.2765808105469</v>
+        <v>336.5464782714844</v>
       </c>
       <c r="F67" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>336.4379310634787</v>
+        <v>335.875584402924</v>
       </c>
       <c r="C68" t="n">
-        <v>340.3549345980833</v>
+        <v>336.4379523174861</v>
       </c>
       <c r="D68" t="n">
-        <v>332.5012053593197</v>
+        <v>326.6109215358994</v>
       </c>
       <c r="E68" t="n">
-        <v>336.5464782714844</v>
+        <v>329.7386169433594</v>
       </c>
       <c r="F68" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>335.875584402924</v>
+        <v>329.1564601038647</v>
       </c>
       <c r="C69" t="n">
-        <v>336.4379523174861</v>
+        <v>331.0409661792534</v>
       </c>
       <c r="D69" t="n">
-        <v>326.6109215358994</v>
+        <v>326.0682693196749</v>
       </c>
       <c r="E69" t="n">
-        <v>329.7386169433594</v>
+        <v>327.2029113769531</v>
       </c>
       <c r="F69" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>329.1564601038647</v>
+        <v>324.5389537288393</v>
       </c>
       <c r="C70" t="n">
-        <v>331.0409661792534</v>
+        <v>325.7722668994048</v>
       </c>
       <c r="D70" t="n">
-        <v>326.0682693196749</v>
+        <v>320.2371718427956</v>
       </c>
       <c r="E70" t="n">
-        <v>327.2029113769531</v>
+        <v>323.759521484375</v>
       </c>
       <c r="F70" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>324.5389231377919</v>
+        <v>323.6805434123363</v>
       </c>
       <c r="C71" t="n">
-        <v>325.7722361921053</v>
+        <v>330.1332457701224</v>
       </c>
       <c r="D71" t="n">
-        <v>320.2371416572342</v>
+        <v>321.7171186569828</v>
       </c>
       <c r="E71" t="n">
-        <v>323.7594909667969</v>
+        <v>323.0491027832031</v>
       </c>
       <c r="F71" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>323.6805434123363</v>
+        <v>318.5894351738589</v>
       </c>
       <c r="C72" t="n">
-        <v>330.1332457701224</v>
+        <v>325.3973174895482</v>
       </c>
       <c r="D72" t="n">
-        <v>321.7171186569828</v>
+        <v>317.3561220691985</v>
       </c>
       <c r="E72" t="n">
-        <v>323.0491027832031</v>
+        <v>320.8192749023438</v>
       </c>
       <c r="F72" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>318.5894351738589</v>
+        <v>319.6747419864576</v>
       </c>
       <c r="C73" t="n">
-        <v>325.3973174895482</v>
+        <v>323.4240016076582</v>
       </c>
       <c r="D73" t="n">
-        <v>317.3561220691985</v>
+        <v>319.4379555165406</v>
       </c>
       <c r="E73" t="n">
-        <v>320.8192749023438</v>
+        <v>320.4640502929688</v>
       </c>
       <c r="F73" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>319.6747419864576</v>
+        <v>320.8587369294642</v>
       </c>
       <c r="C74" t="n">
-        <v>323.4240016076582</v>
+        <v>324.5981204386806</v>
       </c>
       <c r="D74" t="n">
-        <v>319.4379555165406</v>
+        <v>319.8030137263066</v>
       </c>
       <c r="E74" t="n">
-        <v>320.4640502929688</v>
+        <v>323.2069396972656</v>
       </c>
       <c r="F74" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>320.8587672253223</v>
+        <v>322.8320412014528</v>
       </c>
       <c r="C75" t="n">
-        <v>324.5981510876156</v>
+        <v>327.4594342482506</v>
       </c>
       <c r="D75" t="n">
-        <v>319.8030439224821</v>
+        <v>321.9045873641298</v>
       </c>
       <c r="E75" t="n">
-        <v>323.2069702148438</v>
+        <v>327.4002075195312</v>
       </c>
       <c r="F75" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>322.8320412014528</v>
+        <v>326.4727780063231</v>
       </c>
       <c r="C76" t="n">
-        <v>327.4594342482506</v>
+        <v>329.787909026371</v>
       </c>
       <c r="D76" t="n">
-        <v>321.9045873641298</v>
+        <v>323.8976047048735</v>
       </c>
       <c r="E76" t="n">
-        <v>327.4002075195312</v>
+        <v>324.5487976074219</v>
       </c>
       <c r="F76" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>326.4728087048146</v>
+        <v>325.3282766160162</v>
       </c>
       <c r="C77" t="n">
-        <v>329.787940036587</v>
+        <v>331.6625558944407</v>
       </c>
       <c r="D77" t="n">
-        <v>323.8976351612195</v>
+        <v>325.1112123040032</v>
       </c>
       <c r="E77" t="n">
-        <v>324.548828125</v>
+        <v>327.725830078125</v>
       </c>
       <c r="F77" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>325.3282463216964</v>
+        <v>327.8837053458195</v>
       </c>
       <c r="C78" t="n">
-        <v>331.6625250102778</v>
+        <v>328.8802018879278</v>
       </c>
       <c r="D78" t="n">
-        <v>325.1111820298963</v>
+        <v>325.4762756879338</v>
       </c>
       <c r="E78" t="n">
-        <v>327.7257995605469</v>
+        <v>325.7031860351562</v>
       </c>
       <c r="F78" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>327.8837053458195</v>
+        <v>326.4826326508298</v>
       </c>
       <c r="C79" t="n">
-        <v>328.8802018879278</v>
+        <v>335.717696654991</v>
       </c>
       <c r="D79" t="n">
-        <v>325.4762756879338</v>
+        <v>323.1280270938765</v>
       </c>
       <c r="E79" t="n">
-        <v>325.7031860351562</v>
+        <v>331.9092102050781</v>
       </c>
       <c r="F79" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>326.4826326508298</v>
+        <v>330.9719222150325</v>
       </c>
       <c r="C80" t="n">
-        <v>335.717696654991</v>
+        <v>342.3085268229226</v>
       </c>
       <c r="D80" t="n">
-        <v>323.1280270938765</v>
+        <v>329.3932753932535</v>
       </c>
       <c r="E80" t="n">
-        <v>331.9092102050781</v>
+        <v>337.4541931152344</v>
       </c>
       <c r="F80" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>330.9719222150325</v>
+        <v>343.6996829189171</v>
       </c>
       <c r="C81" t="n">
-        <v>342.3085268229226</v>
+        <v>347.9027932709801</v>
       </c>
       <c r="D81" t="n">
-        <v>329.3932753932535</v>
+        <v>340.5127911940015</v>
       </c>
       <c r="E81" t="n">
-        <v>337.4541931152344</v>
+        <v>344.3114013671875</v>
       </c>
       <c r="F81" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>343.6996829189171</v>
+        <v>344.3213032237757</v>
       </c>
       <c r="C82" t="n">
-        <v>347.9027932709801</v>
+        <v>345.4361929991165</v>
       </c>
       <c r="D82" t="n">
-        <v>340.5127911940015</v>
+        <v>333.527344316932</v>
       </c>
       <c r="E82" t="n">
-        <v>344.3114013671875</v>
+        <v>337.1384887695312</v>
       </c>
       <c r="F82" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>344.3213032237757</v>
+        <v>336.4576913463828</v>
       </c>
       <c r="C83" t="n">
-        <v>345.4361929991165</v>
+        <v>343.2556975271264</v>
       </c>
       <c r="D83" t="n">
-        <v>333.527344316932</v>
+        <v>336.2504730653109</v>
       </c>
       <c r="E83" t="n">
-        <v>337.1384887695312</v>
+        <v>342.2197265625</v>
       </c>
       <c r="F83" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>336.4576913463828</v>
+        <v>342.6143979299363</v>
       </c>
       <c r="C84" t="n">
-        <v>343.2556975271264</v>
+        <v>344.4002329876533</v>
       </c>
       <c r="D84" t="n">
-        <v>336.2504730653109</v>
+        <v>337.9080857224443</v>
       </c>
       <c r="E84" t="n">
-        <v>342.2197265625</v>
+        <v>339.3880615234375</v>
       </c>
       <c r="F84" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>342.6143671222478</v>
+        <v>336.8622109944222</v>
       </c>
       <c r="C85" t="n">
-        <v>344.4002020193836</v>
+        <v>338.0757717813934</v>
       </c>
       <c r="D85" t="n">
-        <v>337.9080553379447</v>
+        <v>329.4820547645052</v>
       </c>
       <c r="E85" t="n">
-        <v>339.3880310058594</v>
+        <v>335.96435546875</v>
       </c>
       <c r="F85" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>336.8622415935578</v>
+        <v>336.9411188846722</v>
       </c>
       <c r="C86" t="n">
-        <v>338.0758024907637</v>
+        <v>337.2765764147031</v>
       </c>
       <c r="D86" t="n">
-        <v>329.4820846932586</v>
+        <v>328.4065987621919</v>
       </c>
       <c r="E86" t="n">
-        <v>335.9643859863281</v>
+        <v>329.47216796875</v>
       </c>
       <c r="F86" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>336.9411188846722</v>
+        <v>330.8929641448377</v>
       </c>
       <c r="C87" t="n">
-        <v>337.2765764147031</v>
+        <v>335.5696777492312</v>
       </c>
       <c r="D87" t="n">
-        <v>328.4065987621919</v>
+        <v>329.639928884428</v>
       </c>
       <c r="E87" t="n">
-        <v>329.47216796875</v>
+        <v>330.4884338378906</v>
       </c>
       <c r="F87" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>330.8929641448377</v>
+        <v>330.7252730384288</v>
       </c>
       <c r="C88" t="n">
-        <v>335.5696777492312</v>
+        <v>334.9185378332558</v>
       </c>
       <c r="D88" t="n">
-        <v>329.639928884428</v>
+        <v>323.6805737302307</v>
       </c>
       <c r="E88" t="n">
-        <v>330.4884338378906</v>
+        <v>334.43505859375</v>
       </c>
       <c r="F88" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>330.7252428593728</v>
+        <v>330.3897780779105</v>
       </c>
       <c r="C89" t="n">
-        <v>334.9185072715596</v>
+        <v>331.7119162692861</v>
       </c>
       <c r="D89" t="n">
-        <v>323.6805441940115</v>
+        <v>326.0189235086448</v>
       </c>
       <c r="E89" t="n">
-        <v>334.4350280761719</v>
+        <v>326.6010437011719</v>
       </c>
       <c r="F89" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>330.3897780779105</v>
+        <v>323.0293559592084</v>
       </c>
       <c r="C90" t="n">
-        <v>331.7119162692861</v>
+        <v>335.3526407320732</v>
       </c>
       <c r="D90" t="n">
-        <v>326.0189235086448</v>
+        <v>322.1413765634589</v>
       </c>
       <c r="E90" t="n">
-        <v>326.6010437011719</v>
+        <v>333.912109375</v>
       </c>
       <c r="F90" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>323.0293559592084</v>
+        <v>334.8987575018528</v>
       </c>
       <c r="C91" t="n">
-        <v>335.3526407320732</v>
+        <v>343.4332779356386</v>
       </c>
       <c r="D91" t="n">
-        <v>322.1413765634589</v>
+        <v>334.168645798694</v>
       </c>
       <c r="E91" t="n">
-        <v>333.912109375</v>
+        <v>343.1076965332031</v>
       </c>
       <c r="F91" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>334.8987575018528</v>
+        <v>342.5453159613966</v>
       </c>
       <c r="C92" t="n">
-        <v>343.4332779356386</v>
+        <v>350.2116096750548</v>
       </c>
       <c r="D92" t="n">
-        <v>334.168645798694</v>
+        <v>342.1407856401066</v>
       </c>
       <c r="E92" t="n">
-        <v>343.1076965332031</v>
+        <v>349.7380065917969</v>
       </c>
       <c r="F92" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>342.5453159613966</v>
+        <v>349.5505106781399</v>
       </c>
       <c r="C93" t="n">
-        <v>350.2116096750548</v>
+        <v>353.0925820837122</v>
       </c>
       <c r="D93" t="n">
-        <v>342.1407856401066</v>
+        <v>348.2777232015386</v>
       </c>
       <c r="E93" t="n">
-        <v>349.7380065917969</v>
+        <v>351.5040893554688</v>
       </c>
       <c r="F93" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>349.5505410261084</v>
+        <v>349.2249303389971</v>
       </c>
       <c r="C94" t="n">
-        <v>353.0926127392032</v>
+        <v>350.0537130836444</v>
       </c>
       <c r="D94" t="n">
-        <v>348.2777534390037</v>
+        <v>342.6340826093485</v>
       </c>
       <c r="E94" t="n">
-        <v>351.5041198730469</v>
+        <v>346.9457702636719</v>
       </c>
       <c r="F94" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>349.2249303389971</v>
+        <v>290.0456258453373</v>
       </c>
       <c r="C95" t="n">
-        <v>350.0537130836444</v>
+        <v>295.5018014762001</v>
       </c>
       <c r="D95" t="n">
-        <v>342.6340826093485</v>
+        <v>276.6567723884028</v>
       </c>
       <c r="E95" t="n">
-        <v>346.9457702636719</v>
+        <v>278.9260864257812</v>
       </c>
       <c r="F95" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>290.0456258453373</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="C96" t="n">
-        <v>295.5018014762001</v>
+        <v>291.0027024164021</v>
       </c>
       <c r="D96" t="n">
-        <v>276.6567723884028</v>
+        <v>279.9324825435024</v>
       </c>
       <c r="E96" t="n">
-        <v>278.9260864257812</v>
+        <v>290.094970703125</v>
       </c>
       <c r="F96" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>279.9324825435024</v>
+        <v>290.4008067136846</v>
       </c>
       <c r="C97" t="n">
-        <v>291.0027024164021</v>
+        <v>291.6538720255555</v>
       </c>
       <c r="D97" t="n">
-        <v>279.9324825435024</v>
+        <v>285.3590374883647</v>
       </c>
       <c r="E97" t="n">
-        <v>290.094970703125</v>
+        <v>288.3880615234375</v>
       </c>
       <c r="F97" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>290.4008374442539</v>
+        <v>288.200605503728</v>
       </c>
       <c r="C98" t="n">
-        <v>291.6539028887257</v>
+        <v>289.0392644171012</v>
       </c>
       <c r="D98" t="n">
-        <v>285.3590676854078</v>
+        <v>280.8993981188336</v>
       </c>
       <c r="E98" t="n">
-        <v>288.3880920410156</v>
+        <v>283.099609375</v>
       </c>
       <c r="F98" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>288.200605503728</v>
+        <v>282.201779365365</v>
       </c>
       <c r="C99" t="n">
-        <v>289.0392644171012</v>
+        <v>286.5233135903719</v>
       </c>
       <c r="D99" t="n">
-        <v>280.8993981188336</v>
+        <v>278.5117159450099</v>
       </c>
       <c r="E99" t="n">
-        <v>283.099609375</v>
+        <v>281.7775268554688</v>
       </c>
       <c r="F99" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>282.201779365365</v>
+        <v>280.899399533992</v>
       </c>
       <c r="C100" t="n">
-        <v>286.5233135903719</v>
+        <v>284.2441289542904</v>
       </c>
       <c r="D100" t="n">
-        <v>278.5117159450099</v>
+        <v>274.8808256732182</v>
       </c>
       <c r="E100" t="n">
-        <v>281.7775268554688</v>
+        <v>280.3863220214844</v>
       </c>
       <c r="F100" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>280.899399533992</v>
+        <v>278.2453003524489</v>
       </c>
       <c r="C101" t="n">
-        <v>284.2441289542904</v>
+        <v>280.7020503139632</v>
       </c>
       <c r="D101" t="n">
-        <v>274.8808256732182</v>
+        <v>270.3915411669698</v>
       </c>
       <c r="E101" t="n">
-        <v>280.3863220214844</v>
+        <v>272.2366027832031</v>
       </c>
       <c r="F101" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>278.2453003524489</v>
+        <v>270.6283598679102</v>
       </c>
       <c r="C102" t="n">
-        <v>280.7020503139632</v>
+        <v>273.1936570552693</v>
       </c>
       <c r="D102" t="n">
-        <v>270.3915411669698</v>
+        <v>262.7351562823021</v>
       </c>
       <c r="E102" t="n">
-        <v>272.2366027832031</v>
+        <v>264.9649658203125</v>
       </c>
       <c r="F102" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>270.6283910377749</v>
+        <v>263.494873693566</v>
       </c>
       <c r="C103" t="n">
-        <v>273.1936885205944</v>
+        <v>274.1013663098342</v>
       </c>
       <c r="D103" t="n">
-        <v>262.7351865430599</v>
+        <v>262.8535569062469</v>
       </c>
       <c r="E103" t="n">
-        <v>264.9649963378906</v>
+        <v>272.9568481445312</v>
       </c>
       <c r="F103" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>263.494873693566</v>
+        <v>270.4902353878243</v>
       </c>
       <c r="C104" t="n">
-        <v>274.1013663098342</v>
+        <v>276.4397368487514</v>
       </c>
       <c r="D104" t="n">
-        <v>262.8535569062469</v>
+        <v>269.6713287006126</v>
       </c>
       <c r="E104" t="n">
-        <v>272.9568481445312</v>
+        <v>272.0195617675781</v>
       </c>
       <c r="F104" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>270.4902050418196</v>
+        <v>273.8152476410468</v>
       </c>
       <c r="C105" t="n">
-        <v>276.4397058352786</v>
+        <v>275.7589504136547</v>
       </c>
       <c r="D105" t="n">
-        <v>269.6712984464802</v>
+        <v>269.010264317998</v>
       </c>
       <c r="E105" t="n">
-        <v>272.01953125</v>
+        <v>269.5726623535156</v>
       </c>
       <c r="F105" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>273.8152476410468</v>
+        <v>268.8030465161297</v>
       </c>
       <c r="C106" t="n">
-        <v>275.7589504136547</v>
+        <v>275.9562621591264</v>
       </c>
       <c r="D106" t="n">
-        <v>269.010264317998</v>
+        <v>266.1982749187582</v>
       </c>
       <c r="E106" t="n">
-        <v>269.5726623535156</v>
+        <v>275.1866760253906</v>
       </c>
       <c r="F106" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>268.8030763257778</v>
+        <v>274.4467004687212</v>
       </c>
       <c r="C107" t="n">
-        <v>275.9562927620499</v>
+        <v>282.4878958393087</v>
       </c>
       <c r="D107" t="n">
-        <v>266.198304439543</v>
+        <v>272.1280658242715</v>
       </c>
       <c r="E107" t="n">
-        <v>275.1867065429688</v>
+        <v>280.5737915039062</v>
       </c>
       <c r="F107" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>274.4467004687212</v>
+        <v>281.8169569225497</v>
       </c>
       <c r="C108" t="n">
-        <v>282.4878958393087</v>
+        <v>289.5424162609187</v>
       </c>
       <c r="D108" t="n">
-        <v>272.1280658242715</v>
+        <v>280.7119132986369</v>
       </c>
       <c r="E108" t="n">
-        <v>280.5737915039062</v>
+        <v>289.2760314941406</v>
       </c>
       <c r="F108" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>281.8169569225497</v>
+        <v>290.0752312306441</v>
       </c>
       <c r="C109" t="n">
-        <v>289.5424162609187</v>
+        <v>290.3021716729731</v>
       </c>
       <c r="D109" t="n">
-        <v>280.7119132986369</v>
+        <v>284.4907860910092</v>
       </c>
       <c r="E109" t="n">
-        <v>289.2760314941406</v>
+        <v>285.2307739257812</v>
       </c>
       <c r="F109" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>290.0752312306441</v>
+        <v>286.1286505407075</v>
       </c>
       <c r="C110" t="n">
-        <v>290.3021716729731</v>
+        <v>286.2569199258207</v>
       </c>
       <c r="D110" t="n">
-        <v>284.4907860910092</v>
+        <v>282.4681855456762</v>
       </c>
       <c r="E110" t="n">
-        <v>285.2307739257812</v>
+        <v>284.3526916503906</v>
       </c>
       <c r="F110" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>286.1286505407075</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="C111" t="n">
-        <v>286.2569199258207</v>
+        <v>287.0067764654547</v>
       </c>
       <c r="D111" t="n">
-        <v>282.4681855456762</v>
+        <v>283.0601744920274</v>
       </c>
       <c r="E111" t="n">
-        <v>284.3526916503906</v>
+        <v>286.0595703125</v>
       </c>
       <c r="F111" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>287.0067764654547</v>
+        <v>285.0433100706192</v>
       </c>
       <c r="C112" t="n">
-        <v>287.0067764654547</v>
+        <v>286.9179399107358</v>
       </c>
       <c r="D112" t="n">
-        <v>283.0601744920274</v>
+        <v>281.7380250284705</v>
       </c>
       <c r="E112" t="n">
-        <v>286.0595703125</v>
+        <v>286.1286315917969</v>
       </c>
       <c r="F112" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>285.0433100706192</v>
+        <v>284.6979833712643</v>
       </c>
       <c r="C113" t="n">
-        <v>286.9179399107358</v>
+        <v>287.8749991147026</v>
       </c>
       <c r="D113" t="n">
-        <v>281.7380250284705</v>
+        <v>277.9098533754537</v>
       </c>
       <c r="E113" t="n">
-        <v>286.1286315917969</v>
+        <v>278.5708923339844</v>
       </c>
       <c r="F113" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>284.6979833712643</v>
+        <v>278.4327740747045</v>
       </c>
       <c r="C114" t="n">
-        <v>287.8749991147026</v>
+        <v>278.6300861021672</v>
       </c>
       <c r="D114" t="n">
-        <v>277.9098533754537</v>
+        <v>268.1715851207944</v>
       </c>
       <c r="E114" t="n">
-        <v>278.5708923339844</v>
+        <v>270.2929077148438</v>
       </c>
       <c r="F114" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>278.4327740747045</v>
+        <v>273.5883087457124</v>
       </c>
       <c r="C115" t="n">
-        <v>278.6300861021672</v>
+        <v>280.9388364524249</v>
       </c>
       <c r="D115" t="n">
-        <v>268.1715851207944</v>
+        <v>273.1739023127244</v>
       </c>
       <c r="E115" t="n">
-        <v>270.2929077148438</v>
+        <v>280.4060668945312</v>
       </c>
       <c r="F115" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>273.5883087457124</v>
+        <v>283.1489568057956</v>
       </c>
       <c r="C116" t="n">
-        <v>280.9388364524249</v>
+        <v>291.3184213223429</v>
       </c>
       <c r="D116" t="n">
-        <v>273.1739023127244</v>
+        <v>281.422318519362</v>
       </c>
       <c r="E116" t="n">
-        <v>280.4060668945312</v>
+        <v>282.8332214355469</v>
       </c>
       <c r="F116" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>283.1489568057956</v>
+        <v>280.899378965855</v>
       </c>
       <c r="C117" t="n">
-        <v>291.3184213223429</v>
+        <v>290.2034849465505</v>
       </c>
       <c r="D117" t="n">
-        <v>281.422318519362</v>
+        <v>280.0607201096653</v>
       </c>
       <c r="E117" t="n">
-        <v>282.8332214355469</v>
+        <v>289.3549499511719</v>
       </c>
       <c r="F117" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>280.899378965855</v>
+        <v>284.3132152404683</v>
       </c>
       <c r="C118" t="n">
-        <v>290.2034849465505</v>
+        <v>291.3677603814479</v>
       </c>
       <c r="D118" t="n">
-        <v>280.0607201096653</v>
+        <v>283.6620222891216</v>
       </c>
       <c r="E118" t="n">
-        <v>289.3549499511719</v>
+        <v>290.9928283691406</v>
       </c>
       <c r="F118" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>284.3132152404683</v>
+        <v>285.1321178149137</v>
       </c>
       <c r="C119" t="n">
-        <v>291.3677603814479</v>
+        <v>289.8187076809586</v>
       </c>
       <c r="D119" t="n">
-        <v>283.6620222891216</v>
+        <v>280.5639211910132</v>
       </c>
       <c r="E119" t="n">
-        <v>290.9928283691406</v>
+        <v>285.3491821289062</v>
       </c>
       <c r="F119" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>285.1321178149137</v>
+        <v>285.1518383851878</v>
       </c>
       <c r="C120" t="n">
-        <v>289.8187076809586</v>
+        <v>290.4106717068518</v>
       </c>
       <c r="D120" t="n">
-        <v>280.5639211910132</v>
+        <v>283.839576506922</v>
       </c>
       <c r="E120" t="n">
-        <v>285.3491821289062</v>
+        <v>288.0624389648438</v>
       </c>
       <c r="F120" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>285.1518685944145</v>
+        <v>286.1779504316799</v>
       </c>
       <c r="C121" t="n">
-        <v>290.4107024732037</v>
+        <v>287.5000885291143</v>
       </c>
       <c r="D121" t="n">
-        <v>283.8396065771265</v>
+        <v>282.9121398572339</v>
       </c>
       <c r="E121" t="n">
-        <v>288.0624694824219</v>
+        <v>284.9150390625</v>
       </c>
       <c r="F121" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>286.1779504316799</v>
+        <v>283.5041446062434</v>
       </c>
       <c r="C122" t="n">
-        <v>287.5000885291143</v>
+        <v>287.4408703764128</v>
       </c>
       <c r="D122" t="n">
-        <v>282.9121398572339</v>
+        <v>279.2714056266989</v>
       </c>
       <c r="E122" t="n">
-        <v>284.9150390625</v>
+        <v>282.6556396484375</v>
       </c>
       <c r="F122" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,25 +3615,25 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>283.5041446062434</v>
+        <v>280.3985261413432</v>
       </c>
       <c r="C123" t="n">
-        <v>287.4408703764128</v>
+        <v>283.5803655260448</v>
       </c>
       <c r="D123" t="n">
-        <v>279.2714056266989</v>
+        <v>277.0774975936055</v>
       </c>
       <c r="E123" t="n">
-        <v>282.6556396484375</v>
+        <v>283.550537109375</v>
       </c>
       <c r="F123" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>280.3985261413432</v>
+        <v>285.7479583300972</v>
       </c>
       <c r="C124" t="n">
-        <v>283.5803655260448</v>
+        <v>285.9468043127463</v>
       </c>
       <c r="D124" t="n">
-        <v>277.0774975936055</v>
+        <v>277.3161057836816</v>
       </c>
       <c r="E124" t="n">
-        <v>283.550537109375</v>
+        <v>280.736572265625</v>
       </c>
       <c r="F124" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>285.7479583300972</v>
+        <v>280.7763694963311</v>
       </c>
       <c r="C125" t="n">
-        <v>285.9468043127463</v>
+        <v>284.5945585040109</v>
       </c>
       <c r="D125" t="n">
-        <v>277.3161057836816</v>
+        <v>279.0064793259336</v>
       </c>
       <c r="E125" t="n">
-        <v>280.736572265625</v>
+        <v>283.6300659179688</v>
       </c>
       <c r="F125" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>280.7763694963311</v>
+        <v>283.1627358622739</v>
       </c>
       <c r="C126" t="n">
-        <v>284.5945585040109</v>
+        <v>285.9269470548217</v>
       </c>
       <c r="D126" t="n">
-        <v>279.0064793259336</v>
+        <v>274.7209602020642</v>
       </c>
       <c r="E126" t="n">
-        <v>283.6300659179688</v>
+        <v>275.4766235351562</v>
       </c>
       <c r="F126" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>283.1627358622739</v>
+        <v>276.4808941849521</v>
       </c>
       <c r="C127" t="n">
-        <v>285.9269470548217</v>
+        <v>281.2735286763525</v>
       </c>
       <c r="D127" t="n">
-        <v>274.7209602020642</v>
+        <v>276.2323139355343</v>
       </c>
       <c r="E127" t="n">
-        <v>275.4766235351562</v>
+        <v>280.4880065917969</v>
       </c>
       <c r="F127" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>276.4808941849521</v>
+        <v>282.3672788368328</v>
       </c>
       <c r="C128" t="n">
-        <v>281.2735286763525</v>
+        <v>285.767839547621</v>
       </c>
       <c r="D128" t="n">
-        <v>276.2323139355343</v>
+        <v>279.4439727693734</v>
       </c>
       <c r="E128" t="n">
-        <v>280.4880065917969</v>
+        <v>283.8686828613281</v>
       </c>
       <c r="F128" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>282.3672788368328</v>
+        <v>286.1655640520241</v>
       </c>
       <c r="C129" t="n">
-        <v>285.767839547621</v>
+        <v>287.3488084380985</v>
       </c>
       <c r="D129" t="n">
-        <v>279.4439727693734</v>
+        <v>283.2223824666901</v>
       </c>
       <c r="E129" t="n">
-        <v>283.8686828613281</v>
+        <v>285.9368896484375</v>
       </c>
       <c r="F129" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>286.1655640520241</v>
+        <v>283.5803557381978</v>
       </c>
       <c r="C130" t="n">
-        <v>287.3488084380985</v>
+        <v>286.7621646688093</v>
       </c>
       <c r="D130" t="n">
-        <v>283.2223824666901</v>
+        <v>281.4624471949345</v>
       </c>
       <c r="E130" t="n">
-        <v>285.9368896484375</v>
+        <v>282.7152709960938</v>
       </c>
       <c r="F130" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>283.5803557381978</v>
+        <v>282.3871618979052</v>
       </c>
       <c r="C131" t="n">
-        <v>286.7621646688093</v>
+        <v>285.9169892839216</v>
       </c>
       <c r="D131" t="n">
-        <v>281.4624471949345</v>
+        <v>278.4794876796185</v>
       </c>
       <c r="E131" t="n">
-        <v>282.7152709960938</v>
+        <v>278.8473815917969</v>
       </c>
       <c r="F131" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>282.3871618979052</v>
+        <v>277.4056183419098</v>
       </c>
       <c r="C132" t="n">
-        <v>285.9169892839216</v>
+        <v>281.4922936115716</v>
       </c>
       <c r="D132" t="n">
-        <v>278.4794876796185</v>
+        <v>273.4382870867091</v>
       </c>
       <c r="E132" t="n">
-        <v>278.8473815917969</v>
+        <v>274.0249328613281</v>
       </c>
       <c r="F132" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>277.4056183419098</v>
+        <v>277.5547645320462</v>
       </c>
       <c r="C133" t="n">
-        <v>281.4922936115716</v>
+        <v>279.1556066962045</v>
       </c>
       <c r="D133" t="n">
-        <v>273.4382870867091</v>
+        <v>267.5618207785692</v>
       </c>
       <c r="E133" t="n">
-        <v>274.0249328613281</v>
+        <v>268.00927734375</v>
       </c>
       <c r="F133" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>277.5547645320462</v>
+        <v>267.3430655755382</v>
       </c>
       <c r="C134" t="n">
-        <v>279.1556066962045</v>
+        <v>271.8274627132414</v>
       </c>
       <c r="D134" t="n">
-        <v>267.5618207785692</v>
+        <v>266.0703359894755</v>
       </c>
       <c r="E134" t="n">
-        <v>268.00927734375</v>
+        <v>270.7337036132812</v>
       </c>
       <c r="F134" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>267.3430655755382</v>
+        <v>273.4382596260376</v>
       </c>
       <c r="C135" t="n">
-        <v>271.8274627132414</v>
+        <v>274.5121128941823</v>
       </c>
       <c r="D135" t="n">
-        <v>266.0703359894755</v>
+        <v>265.5930528118823</v>
       </c>
       <c r="E135" t="n">
-        <v>270.7337036132812</v>
+        <v>269.0135192871094</v>
       </c>
       <c r="F135" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>273.4382596260376</v>
+        <v>268.4567257080549</v>
       </c>
       <c r="C136" t="n">
-        <v>274.5121128941823</v>
+        <v>273.0803427820733</v>
       </c>
       <c r="D136" t="n">
-        <v>265.5930528118823</v>
+        <v>265.6626860357957</v>
       </c>
       <c r="E136" t="n">
-        <v>269.0135192871094</v>
+        <v>266.5277404785156</v>
       </c>
       <c r="F136" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>268.4567257080549</v>
+        <v>265.9808641274938</v>
       </c>
       <c r="C137" t="n">
-        <v>273.0803427820733</v>
+        <v>266.1499120468286</v>
       </c>
       <c r="D137" t="n">
-        <v>265.6626860357957</v>
+        <v>254.516344356629</v>
       </c>
       <c r="E137" t="n">
-        <v>266.5277404785156</v>
+        <v>257.5490112304688</v>
       </c>
       <c r="F137" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>265.9808641274938</v>
+        <v>258.7024415515604</v>
       </c>
       <c r="C138" t="n">
-        <v>266.1499120468286</v>
+        <v>260.8402257240527</v>
       </c>
       <c r="D138" t="n">
-        <v>254.516344356629</v>
+        <v>255.2123953265358</v>
       </c>
       <c r="E138" t="n">
-        <v>257.5490112304688</v>
+        <v>260.3033142089844</v>
       </c>
       <c r="F138" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>258.7024415515604</v>
+        <v>261.506421503485</v>
       </c>
       <c r="C139" t="n">
-        <v>260.8402257240527</v>
+        <v>270.3359967880393</v>
       </c>
       <c r="D139" t="n">
-        <v>255.2123953265358</v>
+        <v>261.1186217504552</v>
       </c>
       <c r="E139" t="n">
-        <v>260.3033142089844</v>
+        <v>269.0533142089844</v>
       </c>
       <c r="F139" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>261.506421503485</v>
+        <v>272.6527466700565</v>
       </c>
       <c r="C140" t="n">
-        <v>270.3359967880393</v>
+        <v>273.7365528939259</v>
       </c>
       <c r="D140" t="n">
-        <v>261.1186217504552</v>
+        <v>269.2223575051711</v>
       </c>
       <c r="E140" t="n">
-        <v>269.0533142089844</v>
+        <v>272.424072265625</v>
       </c>
       <c r="F140" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>272.6527466700565</v>
+        <v>270.7436786461413</v>
       </c>
       <c r="C141" t="n">
-        <v>273.7365528939259</v>
+        <v>277.4553455215711</v>
       </c>
       <c r="D141" t="n">
-        <v>269.2223575051711</v>
+        <v>269.9879849618526</v>
       </c>
       <c r="E141" t="n">
-        <v>272.424072265625</v>
+        <v>275.6854553222656</v>
       </c>
       <c r="F141" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>270.7436786461413</v>
+        <v>276.3019282869355</v>
       </c>
       <c r="C142" t="n">
-        <v>277.4553455215711</v>
+        <v>281.6911311912249</v>
       </c>
       <c r="D142" t="n">
-        <v>269.9879849618526</v>
+        <v>275.6755011928929</v>
       </c>
       <c r="E142" t="n">
-        <v>275.6854553222656</v>
+        <v>279.7621459960938</v>
       </c>
       <c r="F142" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>276.3019282869355</v>
+        <v>307.0960565749332</v>
       </c>
       <c r="C143" t="n">
-        <v>281.6911311912249</v>
+        <v>310.6557125153819</v>
       </c>
       <c r="D143" t="n">
-        <v>275.6755011928929</v>
+        <v>299.0420501528358</v>
       </c>
       <c r="E143" t="n">
-        <v>279.7621459960938</v>
+        <v>305.982421875</v>
       </c>
       <c r="F143" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>307.0960565749332</v>
+        <v>310.2281413790238</v>
       </c>
       <c r="C144" t="n">
-        <v>310.6557125153819</v>
+        <v>311.1926339297742</v>
       </c>
       <c r="D144" t="n">
-        <v>299.0420501528358</v>
+        <v>303.0988467016243</v>
       </c>
       <c r="E144" t="n">
-        <v>305.982421875</v>
+        <v>304.2423400878906</v>
       </c>
       <c r="F144" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>310.2281413790238</v>
+        <v>304.0832470042582</v>
       </c>
       <c r="C145" t="n">
-        <v>311.1926339297742</v>
+        <v>306.1414986993597</v>
       </c>
       <c r="D145" t="n">
-        <v>303.0988467016243</v>
+        <v>302.4127950535677</v>
       </c>
       <c r="E145" t="n">
-        <v>304.2423400878906</v>
+        <v>305.1670532226562</v>
       </c>
       <c r="F145" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>304.0832470042582</v>
+        <v>306.2011519366599</v>
       </c>
       <c r="C146" t="n">
-        <v>306.1414986993597</v>
+        <v>308.607391668382</v>
       </c>
       <c r="D146" t="n">
-        <v>302.4127950535677</v>
+        <v>302.4724483346268</v>
       </c>
       <c r="E146" t="n">
-        <v>305.1670532226562</v>
+        <v>302.6016845703125</v>
       </c>
       <c r="F146" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>306.2011519366599</v>
+        <v>301.5278433900291</v>
       </c>
       <c r="C147" t="n">
-        <v>308.607391668382</v>
+        <v>311.5406631473035</v>
       </c>
       <c r="D147" t="n">
-        <v>302.4724483346268</v>
+        <v>301.199730811355</v>
       </c>
       <c r="E147" t="n">
-        <v>302.6016845703125</v>
+        <v>311.2224731445312</v>
       </c>
       <c r="F147" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>301.5278433900291</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="C148" t="n">
-        <v>311.5406631473035</v>
+        <v>317.8048561417646</v>
       </c>
       <c r="D148" t="n">
-        <v>301.199730811355</v>
+        <v>310.7352487756957</v>
       </c>
       <c r="E148" t="n">
-        <v>311.2224731445312</v>
+        <v>312.4057006835938</v>
       </c>
       <c r="F148" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>310.7352487756957</v>
+        <v>314.2054174655202</v>
       </c>
       <c r="C149" t="n">
-        <v>317.8048561417646</v>
+        <v>315.9554320324556</v>
       </c>
       <c r="D149" t="n">
-        <v>310.7352487756957</v>
+        <v>309.3829548311358</v>
       </c>
       <c r="E149" t="n">
-        <v>312.4057006835938</v>
+        <v>312.2664794921875</v>
       </c>
       <c r="F149" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>314.2054174655202</v>
+        <v>313.2111061223722</v>
       </c>
       <c r="C150" t="n">
-        <v>315.9554320324556</v>
+        <v>316.8005902653832</v>
       </c>
       <c r="D150" t="n">
-        <v>309.3829548311358</v>
+        <v>311.3318249203894</v>
       </c>
       <c r="E150" t="n">
-        <v>312.2664794921875</v>
+        <v>314.6031494140625</v>
       </c>
       <c r="F150" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>313.2111061223722</v>
+        <v>318.2324307180975</v>
       </c>
       <c r="C151" t="n">
-        <v>316.8005902653832</v>
+        <v>323.4227876628706</v>
       </c>
       <c r="D151" t="n">
-        <v>311.3318249203894</v>
+        <v>315.338983249174</v>
       </c>
       <c r="E151" t="n">
-        <v>314.6031494140625</v>
+        <v>322.7864379882812</v>
       </c>
       <c r="F151" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>318.2324307180975</v>
+        <v>322.3489342821542</v>
       </c>
       <c r="C152" t="n">
-        <v>323.4227876628706</v>
+        <v>323.5520542213801</v>
       </c>
       <c r="D152" t="n">
-        <v>315.338983249174</v>
+        <v>318.3020404433487</v>
       </c>
       <c r="E152" t="n">
-        <v>322.7864379882812</v>
+        <v>321.6429748535156</v>
       </c>
       <c r="F152" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>322.3489342821542</v>
+        <v>351.0052603166191</v>
       </c>
       <c r="C153" t="n">
-        <v>323.5520542213801</v>
+        <v>355.648722319699</v>
       </c>
       <c r="D153" t="n">
-        <v>318.3020404433487</v>
+        <v>343.2694442738866</v>
       </c>
       <c r="E153" t="n">
-        <v>321.6429748535156</v>
+        <v>344.0450134277344</v>
       </c>
       <c r="F153" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>351.0052603166191</v>
+        <v>348.8873678788304</v>
       </c>
       <c r="C154" t="n">
-        <v>355.648722319699</v>
+        <v>356.5237461069854</v>
       </c>
       <c r="D154" t="n">
-        <v>343.2694442738866</v>
+        <v>347.1174776591131</v>
       </c>
       <c r="E154" t="n">
-        <v>344.0450134277344</v>
+        <v>351.5123596191406</v>
       </c>
       <c r="F154" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>348.8873678788304</v>
+        <v>352.6657614176121</v>
       </c>
       <c r="C155" t="n">
-        <v>356.5237461069854</v>
+        <v>354.8234513171886</v>
       </c>
       <c r="D155" t="n">
-        <v>347.1174776591131</v>
+        <v>348.5095069624251</v>
       </c>
       <c r="E155" t="n">
-        <v>351.5123596191406</v>
+        <v>352.5464477539062</v>
       </c>
       <c r="F155" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>352.6657614176121</v>
+        <v>354.4654798371856</v>
       </c>
       <c r="C156" t="n">
-        <v>354.8234513171886</v>
+        <v>356.2453229047883</v>
       </c>
       <c r="D156" t="n">
-        <v>348.5095069624251</v>
+        <v>349.3944670661433</v>
       </c>
       <c r="E156" t="n">
-        <v>352.5464477539062</v>
+        <v>352.9044189453125</v>
       </c>
       <c r="F156" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>354.4654798371856</v>
+        <v>351.9001510435625</v>
       </c>
       <c r="C157" t="n">
-        <v>356.2453229047883</v>
+        <v>354.4654858887946</v>
       </c>
       <c r="D157" t="n">
-        <v>349.3944670661433</v>
+        <v>346.9683273478323</v>
       </c>
       <c r="E157" t="n">
-        <v>352.9044189453125</v>
+        <v>352.6757202148438</v>
       </c>
       <c r="F157" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>351.9001510435625</v>
+        <v>354.8135029963465</v>
       </c>
       <c r="C158" t="n">
-        <v>354.4654858887946</v>
+        <v>367.5308771185002</v>
       </c>
       <c r="D158" t="n">
-        <v>346.9683273478323</v>
+        <v>353.6998683282982</v>
       </c>
       <c r="E158" t="n">
-        <v>352.6757202148438</v>
+        <v>364.6871032714844</v>
       </c>
       <c r="F158" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>354.8135029963465</v>
+        <v>363.9214802466298</v>
       </c>
       <c r="C159" t="n">
-        <v>367.5308771185002</v>
+        <v>368.7339901692348</v>
       </c>
       <c r="D159" t="n">
-        <v>353.6998683282982</v>
+        <v>362.9371121823581</v>
       </c>
       <c r="E159" t="n">
-        <v>364.6871032714844</v>
+        <v>368.6345520019531</v>
       </c>
       <c r="F159" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>363.9214802466298</v>
+        <v>366.4172241064422</v>
       </c>
       <c r="C160" t="n">
-        <v>368.7339901692348</v>
+        <v>369.87744160261</v>
       </c>
       <c r="D160" t="n">
-        <v>362.9371121823581</v>
+        <v>360.9385059451532</v>
       </c>
       <c r="E160" t="n">
-        <v>368.6345520019531</v>
+        <v>368.3760375976562</v>
       </c>
       <c r="F160" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>366.4172241064422</v>
+        <v>369.8476329800702</v>
       </c>
       <c r="C161" t="n">
-        <v>369.87744160261</v>
+        <v>370.7822971534658</v>
       </c>
       <c r="D161" t="n">
-        <v>360.9385059451532</v>
+        <v>364.9356847817637</v>
       </c>
       <c r="E161" t="n">
-        <v>368.3760375976562</v>
+        <v>366.6856994628906</v>
       </c>
       <c r="F161" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>369.8476329800702</v>
+        <v>366.4569824541582</v>
       </c>
       <c r="C162" t="n">
-        <v>370.7822971534658</v>
+        <v>368.7240330587824</v>
       </c>
       <c r="D162" t="n">
-        <v>364.9356847817637</v>
+        <v>362.5791367283888</v>
       </c>
       <c r="E162" t="n">
-        <v>366.6856994628906</v>
+        <v>368.6445007324219</v>
       </c>
       <c r="F162" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>366.4569824541582</v>
+        <v>368.3760355922912</v>
       </c>
       <c r="C163" t="n">
-        <v>368.7240330587824</v>
+        <v>369.6885161814855</v>
       </c>
       <c r="D163" t="n">
-        <v>362.5791367283888</v>
+        <v>359.7552596250864</v>
       </c>
       <c r="E163" t="n">
-        <v>368.6445007324219</v>
+        <v>361.8035583496094</v>
       </c>
       <c r="F163" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>368.3760355922912</v>
+        <v>361.0379593902868</v>
       </c>
       <c r="C164" t="n">
-        <v>369.6885161814855</v>
+        <v>366.45699060703</v>
       </c>
       <c r="D164" t="n">
-        <v>359.7552596250864</v>
+        <v>356.2154964951898</v>
       </c>
       <c r="E164" t="n">
-        <v>361.8035583496094</v>
+        <v>365.1942138671875</v>
       </c>
       <c r="F164" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>361.0379593902868</v>
+        <v>364.5578575186544</v>
       </c>
       <c r="C165" t="n">
-        <v>366.45699060703</v>
+        <v>367.7098380224884</v>
       </c>
       <c r="D165" t="n">
-        <v>356.2154964951898</v>
+        <v>362.6487478916185</v>
       </c>
       <c r="E165" t="n">
-        <v>365.1942138671875</v>
+        <v>367.6402282714844</v>
       </c>
       <c r="F165" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>364.5578575186544</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="C166" t="n">
-        <v>367.7098380224884</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="D166" t="n">
-        <v>362.6487478916185</v>
+        <v>369.8774674335755</v>
       </c>
       <c r="E166" t="n">
-        <v>367.6402282714844</v>
+        <v>377.8221130371094</v>
       </c>
       <c r="F166" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>369.8774674335755</v>
+        <v>378.2894437474218</v>
       </c>
       <c r="C167" t="n">
-        <v>377.8221130371094</v>
+        <v>382.6246688242237</v>
       </c>
       <c r="D167" t="n">
-        <v>369.8774674335755</v>
+        <v>373.9343128299113</v>
       </c>
       <c r="E167" t="n">
-        <v>377.8221130371094</v>
+        <v>382.2567749023438</v>
       </c>
       <c r="F167" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>378.2894437474218</v>
+        <v>380.6758011703357</v>
       </c>
       <c r="C168" t="n">
-        <v>382.6246688242237</v>
+        <v>395.1630654325308</v>
       </c>
       <c r="D168" t="n">
-        <v>373.9343128299113</v>
+        <v>379.8405751710962</v>
       </c>
       <c r="E168" t="n">
-        <v>382.2567749023438</v>
+        <v>394.138916015625</v>
       </c>
       <c r="F168" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>380.6758011703357</v>
+        <v>394.2482660415264</v>
       </c>
       <c r="C169" t="n">
-        <v>395.1630654325308</v>
+        <v>401.8548154208889</v>
       </c>
       <c r="D169" t="n">
-        <v>379.8405751710962</v>
+        <v>390.7681426338459</v>
       </c>
       <c r="E169" t="n">
-        <v>394.138916015625</v>
+        <v>398.8818054199219</v>
       </c>
       <c r="F169" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>394.2482660415264</v>
+        <v>398.7227040337817</v>
       </c>
       <c r="C170" t="n">
-        <v>401.8548154208889</v>
+        <v>399.6175868268494</v>
       </c>
       <c r="D170" t="n">
-        <v>390.7681426338459</v>
+        <v>393.7510992453305</v>
       </c>
       <c r="E170" t="n">
-        <v>398.8818054199219</v>
+        <v>396.8235473632812</v>
       </c>
       <c r="F170" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>398.7227040337817</v>
+        <v>392.0607685404387</v>
       </c>
       <c r="C171" t="n">
-        <v>399.6175868268494</v>
+        <v>395.3718745508767</v>
       </c>
       <c r="D171" t="n">
-        <v>393.7510992453305</v>
+        <v>388.0337805215488</v>
       </c>
       <c r="E171" t="n">
-        <v>396.8235473632812</v>
+        <v>391.6133422851562</v>
       </c>
       <c r="F171" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>392.0607685404387</v>
+        <v>387.7851953583757</v>
       </c>
       <c r="C172" t="n">
-        <v>395.3718745508767</v>
+        <v>389.9130568930274</v>
       </c>
       <c r="D172" t="n">
-        <v>388.0337805215488</v>
+        <v>381.3221087690695</v>
       </c>
       <c r="E172" t="n">
-        <v>391.6133422851562</v>
+        <v>388.9087829589844</v>
       </c>
       <c r="F172" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>387.7851953583757</v>
+        <v>387.7851736187118</v>
       </c>
       <c r="C173" t="n">
-        <v>389.9130568930274</v>
+        <v>392.7468254889498</v>
       </c>
       <c r="D173" t="n">
-        <v>381.3221087690695</v>
+        <v>385.3093241434657</v>
       </c>
       <c r="E173" t="n">
-        <v>388.9087829589844</v>
+        <v>387.0294799804688</v>
       </c>
       <c r="F173" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>387.7851736187118</v>
+        <v>387.3377362764213</v>
       </c>
       <c r="C174" t="n">
-        <v>392.7468254889498</v>
+        <v>391.1460027273716</v>
       </c>
       <c r="D174" t="n">
-        <v>385.3093241434657</v>
+        <v>378.5380196367677</v>
       </c>
       <c r="E174" t="n">
-        <v>387.0294799804688</v>
+        <v>381.1232299804688</v>
       </c>
       <c r="F174" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>387.3377362764213</v>
+        <v>378.9555995605828</v>
       </c>
       <c r="C175" t="n">
-        <v>391.1460027273716</v>
+        <v>383.9172514426562</v>
       </c>
       <c r="D175" t="n">
-        <v>378.5380196367677</v>
+        <v>378.3789067550467</v>
       </c>
       <c r="E175" t="n">
-        <v>381.1232299804688</v>
+        <v>380.3078918457031</v>
       </c>
       <c r="F175" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>378.9555995605828</v>
+        <v>379.7510949944643</v>
       </c>
       <c r="C176" t="n">
-        <v>383.9172514426562</v>
+        <v>388.322137279522</v>
       </c>
       <c r="D176" t="n">
-        <v>378.3789067550467</v>
+        <v>378.846259230469</v>
       </c>
       <c r="E176" t="n">
-        <v>380.3078918457031</v>
+        <v>386.2638854980469</v>
       </c>
       <c r="F176" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>379.7510949944643</v>
+        <v>383.8078958628703</v>
       </c>
       <c r="C177" t="n">
-        <v>388.322137279522</v>
+        <v>384.3249318452775</v>
       </c>
       <c r="D177" t="n">
-        <v>378.846259230469</v>
+        <v>374.2723613660349</v>
       </c>
       <c r="E177" t="n">
-        <v>386.2638854980469</v>
+        <v>374.7197875976562</v>
       </c>
       <c r="F177" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>383.8078958628703</v>
+        <v>376.2808953624811</v>
       </c>
       <c r="C178" t="n">
-        <v>384.3249318452775</v>
+        <v>382.3462596379654</v>
       </c>
       <c r="D178" t="n">
-        <v>374.2723613660349</v>
+        <v>374.9485088403697</v>
       </c>
       <c r="E178" t="n">
-        <v>374.7197875976562</v>
+        <v>381.8292236328125</v>
       </c>
       <c r="F178" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>376.2808953624811</v>
+        <v>382.7737976901378</v>
       </c>
       <c r="C179" t="n">
-        <v>382.3462596379654</v>
+        <v>387.0493961299752</v>
       </c>
       <c r="D179" t="n">
-        <v>374.9485088403697</v>
+        <v>378.7965137522062</v>
       </c>
       <c r="E179" t="n">
-        <v>381.8292236328125</v>
+        <v>380.3576049804688</v>
       </c>
       <c r="F179" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>382.7737976901378</v>
+        <v>381.6005025160485</v>
       </c>
       <c r="C180" t="n">
-        <v>387.0493961299752</v>
+        <v>382.9328889810419</v>
       </c>
       <c r="D180" t="n">
-        <v>378.7965137522062</v>
+        <v>373.317822146985</v>
       </c>
       <c r="E180" t="n">
-        <v>380.3576049804688</v>
+        <v>378.1502075195312</v>
       </c>
       <c r="F180" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>381.6005025160485</v>
+        <v>373.9740550559011</v>
       </c>
       <c r="C181" t="n">
-        <v>382.9328889810419</v>
+        <v>381.172959697494</v>
       </c>
       <c r="D181" t="n">
-        <v>373.317822146985</v>
+        <v>373.7851619834815</v>
       </c>
       <c r="E181" t="n">
-        <v>378.1502075195312</v>
+        <v>377.7027587890625</v>
       </c>
       <c r="F181" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>373.9740550559011</v>
+        <v>375.8334605430848</v>
       </c>
       <c r="C182" t="n">
-        <v>381.172959697494</v>
+        <v>377.9215103567756</v>
       </c>
       <c r="D182" t="n">
-        <v>373.7851619834815</v>
+        <v>372.5919643898307</v>
       </c>
       <c r="E182" t="n">
-        <v>377.7027587890625</v>
+        <v>375.7738037109375</v>
       </c>
       <c r="F182" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>375.8334605430848</v>
+        <v>377.8419717237235</v>
       </c>
       <c r="C183" t="n">
-        <v>377.9215103567756</v>
+        <v>385.259597724852</v>
       </c>
       <c r="D183" t="n">
-        <v>372.5919643898307</v>
+        <v>374.6700853756592</v>
       </c>
       <c r="E183" t="n">
-        <v>375.7738037109375</v>
+        <v>374.8590087890625</v>
       </c>
       <c r="F183" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>377.8419717237235</v>
+        <v>387.7851867936407</v>
       </c>
       <c r="C184" t="n">
-        <v>385.259597724852</v>
+        <v>399.1005645351637</v>
       </c>
       <c r="D184" t="n">
-        <v>374.6700853756592</v>
+        <v>387.606216297745</v>
       </c>
       <c r="E184" t="n">
-        <v>374.8590087890625</v>
+        <v>394.2184448242188</v>
       </c>
       <c r="F184" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>387.7851867936407</v>
+        <v>397.2710257691138</v>
       </c>
       <c r="C185" t="n">
-        <v>399.1005645351637</v>
+        <v>401.7454703246708</v>
       </c>
       <c r="D185" t="n">
-        <v>387.606216297745</v>
+        <v>394.9443182415365</v>
       </c>
       <c r="E185" t="n">
-        <v>394.2184448242188</v>
+        <v>397.201416015625</v>
       </c>
       <c r="F185" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>397.2710257691138</v>
+        <v>394.8746856398852</v>
       </c>
       <c r="C186" t="n">
-        <v>401.7454703246708</v>
+        <v>406.3889089451397</v>
       </c>
       <c r="D186" t="n">
-        <v>394.9443182415365</v>
+        <v>392.7468242313375</v>
       </c>
       <c r="E186" t="n">
-        <v>397.201416015625</v>
+        <v>404.2610778808594</v>
       </c>
       <c r="F186" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>394.8746856398852</v>
+        <v>407.6616556237274</v>
       </c>
       <c r="C187" t="n">
-        <v>406.3889089451397</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="D187" t="n">
-        <v>392.7468242313375</v>
+        <v>405.1261492204914</v>
       </c>
       <c r="E187" t="n">
-        <v>404.2610778808594</v>
+        <v>410.6545715332031</v>
       </c>
       <c r="F187" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>407.6616556237274</v>
+        <v>411.1517339543602</v>
       </c>
       <c r="C188" t="n">
-        <v>410.6545715332031</v>
+        <v>413.6176609610221</v>
       </c>
       <c r="D188" t="n">
-        <v>405.1261492204914</v>
+        <v>402.2525488568183</v>
       </c>
       <c r="E188" t="n">
-        <v>410.6545715332031</v>
+        <v>405.1460266113281</v>
       </c>
       <c r="F188" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>411.1517339543602</v>
+        <v>406.3889145916303</v>
       </c>
       <c r="C189" t="n">
-        <v>413.6176609610221</v>
+        <v>407.6517216421196</v>
       </c>
       <c r="D189" t="n">
-        <v>402.2525488568183</v>
+        <v>400.820711098459</v>
       </c>
       <c r="E189" t="n">
-        <v>405.1460266113281</v>
+        <v>403.2468566894531</v>
       </c>
       <c r="F189" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>406.3889145916303</v>
+        <v>406.6872501409831</v>
       </c>
       <c r="C190" t="n">
-        <v>407.6517216421196</v>
+        <v>407.5622574937536</v>
       </c>
       <c r="D190" t="n">
-        <v>400.820711098459</v>
+        <v>402.5110897188582</v>
       </c>
       <c r="E190" t="n">
-        <v>403.2468566894531</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="F190" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>406.6872501409831</v>
+        <v>406.7000122070312</v>
       </c>
       <c r="C191" t="n">
-        <v>407.5622574937536</v>
+        <v>414.1600036621094</v>
       </c>
       <c r="D191" t="n">
-        <v>402.5110897188582</v>
+        <v>399.6499938964844</v>
       </c>
       <c r="E191" t="n">
-        <v>406.2000122070312</v>
+        <v>411.0400085449219</v>
       </c>
       <c r="F191" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,25 +5409,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>406.7000122070312</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="C192" t="n">
-        <v>414.1600036621094</v>
+        <v>411.75</v>
       </c>
       <c r="D192" t="n">
-        <v>399.6499938964844</v>
+        <v>406.5400085449219</v>
       </c>
       <c r="E192" t="n">
-        <v>411.0400085449219</v>
+        <v>407.6499938964844</v>
       </c>
       <c r="F192" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G192" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>410.6799926757812</v>
+        <v>409.1199951171875</v>
       </c>
       <c r="C193" t="n">
-        <v>411.75</v>
+        <v>411.1600036621094</v>
       </c>
       <c r="D193" t="n">
-        <v>406.5400085449219</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E193" t="n">
-        <v>407.6499938964844</v>
+        <v>399.5299987792969</v>
       </c>
       <c r="F193" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>409.1199951171875</v>
+        <v>402.7699890136719</v>
       </c>
       <c r="C194" t="n">
-        <v>411.1600036621094</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="D194" t="n">
-        <v>398.5899963378906</v>
+        <v>399.1499938964844</v>
       </c>
       <c r="E194" t="n">
-        <v>399.5299987792969</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="F194" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>402.7699890136719</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="C195" t="n">
-        <v>406.2000122070312</v>
+        <v>409.4599914550781</v>
       </c>
       <c r="D195" t="n">
-        <v>399.1499938964844</v>
+        <v>402.1400146484375</v>
       </c>
       <c r="E195" t="n">
-        <v>400.9599914550781</v>
+        <v>406.6799926757812</v>
       </c>
       <c r="F195" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>402.1400146484375</v>
+        <v>409.5199890136719</v>
       </c>
       <c r="C196" t="n">
-        <v>409.4599914550781</v>
+        <v>409.8999938964844</v>
       </c>
       <c r="D196" t="n">
-        <v>402.1400146484375</v>
+        <v>402.8399963378906</v>
       </c>
       <c r="E196" t="n">
-        <v>406.6799926757812</v>
+        <v>409.25</v>
       </c>
       <c r="F196" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>409.5199890136719</v>
+        <v>410.5400085449219</v>
       </c>
       <c r="C197" t="n">
-        <v>409.8999938964844</v>
+        <v>413.4299926757812</v>
       </c>
       <c r="D197" t="n">
-        <v>402.8399963378906</v>
+        <v>400</v>
       </c>
       <c r="E197" t="n">
-        <v>409.25</v>
+        <v>405.7999877929688</v>
       </c>
       <c r="F197" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>410.5400085449219</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="C198" t="n">
-        <v>413.4299926757812</v>
+        <v>417.5799865722656</v>
       </c>
       <c r="D198" t="n">
-        <v>400</v>
+        <v>406.6499938964844</v>
       </c>
       <c r="E198" t="n">
-        <v>405.7999877929688</v>
+        <v>415.5299987792969</v>
       </c>
       <c r="F198" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>406.6499938964844</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="C199" t="n">
-        <v>417.5799865722656</v>
+        <v>427.9299926757812</v>
       </c>
       <c r="D199" t="n">
-        <v>406.6499938964844</v>
+        <v>416.1600036621094</v>
       </c>
       <c r="E199" t="n">
-        <v>415.5299987792969</v>
+        <v>427.8900146484375</v>
       </c>
       <c r="F199" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>416.1600036621094</v>
+        <v>426.5299987792969</v>
       </c>
       <c r="C200" t="n">
-        <v>427.9299926757812</v>
+        <v>426.7000122070312</v>
       </c>
       <c r="D200" t="n">
-        <v>416.1600036621094</v>
+        <v>415.8099975585938</v>
       </c>
       <c r="E200" t="n">
-        <v>427.8900146484375</v>
+        <v>419.8200073242188</v>
       </c>
       <c r="F200" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>426.5299987792969</v>
+        <v>422.7200012207031</v>
       </c>
       <c r="C201" t="n">
-        <v>426.7000122070312</v>
+        <v>422.739990234375</v>
       </c>
       <c r="D201" t="n">
-        <v>415.8099975585938</v>
+        <v>413.25</v>
       </c>
       <c r="E201" t="n">
-        <v>419.8200073242188</v>
+        <v>415.6300048828125</v>
       </c>
       <c r="F201" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>422.7200012207031</v>
+        <v>417.1099853515625</v>
       </c>
       <c r="C202" t="n">
-        <v>422.739990234375</v>
+        <v>428.0199890136719</v>
       </c>
       <c r="D202" t="n">
-        <v>413.25</v>
+        <v>413.7300109863281</v>
       </c>
       <c r="E202" t="n">
-        <v>415.6300048828125</v>
+        <v>426.5400085449219</v>
       </c>
       <c r="F202" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>417.1099853515625</v>
+        <v>428.1300048828125</v>
       </c>
       <c r="C203" t="n">
-        <v>428.0199890136719</v>
+        <v>430.2000122070312</v>
       </c>
       <c r="D203" t="n">
-        <v>413.7300109863281</v>
+        <v>420.5400085449219</v>
       </c>
       <c r="E203" t="n">
-        <v>426.5400085449219</v>
+        <v>425.3599853515625</v>
       </c>
       <c r="F203" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>428.1300048828125</v>
+        <v>423.489990234375</v>
       </c>
       <c r="C204" t="n">
-        <v>430.2000122070312</v>
+        <v>424.4400024414062</v>
       </c>
       <c r="D204" t="n">
-        <v>420.5400085449219</v>
+        <v>415.0499877929688</v>
       </c>
       <c r="E204" t="n">
-        <v>425.3599853515625</v>
+        <v>417.989990234375</v>
       </c>
       <c r="F204" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>423.489990234375</v>
+        <v>423.9500122070312</v>
       </c>
       <c r="C205" t="n">
-        <v>424.4400024414062</v>
+        <v>428.6000061035156</v>
       </c>
       <c r="D205" t="n">
-        <v>415.0499877929688</v>
+        <v>422.1300048828125</v>
       </c>
       <c r="E205" t="n">
-        <v>417.989990234375</v>
+        <v>428.1900024414062</v>
       </c>
       <c r="F205" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>423.9500122070312</v>
+        <v>427.1499938964844</v>
       </c>
       <c r="C206" t="n">
-        <v>428.6000061035156</v>
+        <v>430.7699890136719</v>
       </c>
       <c r="D206" t="n">
-        <v>422.1300048828125</v>
+        <v>423.8299865722656</v>
       </c>
       <c r="E206" t="n">
-        <v>428.1900024414062</v>
+        <v>425.6000061035156</v>
       </c>
       <c r="F206" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>427.1499938964844</v>
+        <v>427.1099853515625</v>
       </c>
       <c r="C207" t="n">
-        <v>430.7699890136719</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="D207" t="n">
-        <v>423.8299865722656</v>
+        <v>423.5199890136719</v>
       </c>
       <c r="E207" t="n">
-        <v>425.6000061035156</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="F207" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>427.1099853515625</v>
+        <v>431.6700134277344</v>
       </c>
       <c r="C208" t="n">
-        <v>434.2999877929688</v>
+        <v>432.8599853515625</v>
       </c>
       <c r="D208" t="n">
-        <v>423.5199890136719</v>
+        <v>423.6499938964844</v>
       </c>
       <c r="E208" t="n">
-        <v>431.6799926757812</v>
+        <v>424.6199951171875</v>
       </c>
       <c r="F208" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>431.6700134277344</v>
+        <v>426.4700012207031</v>
       </c>
       <c r="C209" t="n">
-        <v>432.8599853515625</v>
+        <v>431.5499877929688</v>
       </c>
       <c r="D209" t="n">
-        <v>423.6499938964844</v>
+        <v>425.5299987792969</v>
       </c>
       <c r="E209" t="n">
-        <v>424.6199951171875</v>
+        <v>429.0899963378906</v>
       </c>
       <c r="F209" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>426.4700012207031</v>
+        <v>431</v>
       </c>
       <c r="C210" t="n">
-        <v>431.5499877929688</v>
+        <v>432.1499938964844</v>
       </c>
       <c r="D210" t="n">
-        <v>425.5299987792969</v>
+        <v>421.7900085449219</v>
       </c>
       <c r="E210" t="n">
-        <v>429.0899963378906</v>
+        <v>425.1900024414062</v>
       </c>
       <c r="F210" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>431</v>
+        <v>419.489990234375</v>
       </c>
       <c r="C211" t="n">
-        <v>432.1499938964844</v>
+        <v>424.1099853515625</v>
       </c>
       <c r="D211" t="n">
-        <v>421.7900085449219</v>
+        <v>414.3699951171875</v>
       </c>
       <c r="E211" t="n">
-        <v>425.1900024414062</v>
+        <v>418.5199890136719</v>
       </c>
       <c r="F211" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>419.489990234375</v>
+        <v>449.3900146484375</v>
       </c>
       <c r="C212" t="n">
-        <v>424.1099853515625</v>
+        <v>461.6199951171875</v>
       </c>
       <c r="D212" t="n">
-        <v>414.3699951171875</v>
+        <v>420.3699951171875</v>
       </c>
       <c r="E212" t="n">
-        <v>418.5199890136719</v>
+        <v>423.3800048828125</v>
       </c>
       <c r="F212" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>449.3900146484375</v>
+        <v>426.7200012207031</v>
       </c>
       <c r="C213" t="n">
-        <v>461.6199951171875</v>
+        <v>437.4700012207031</v>
       </c>
       <c r="D213" t="n">
-        <v>420.3699951171875</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="E213" t="n">
-        <v>423.3800048828125</v>
+        <v>426.0899963378906</v>
       </c>
       <c r="F213" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>426.7200012207031</v>
+        <v>427.25</v>
       </c>
       <c r="C214" t="n">
-        <v>437.4700012207031</v>
+        <v>431.0199890136719</v>
       </c>
       <c r="D214" t="n">
-        <v>425.1000061035156</v>
+        <v>417.3800048828125</v>
       </c>
       <c r="E214" t="n">
-        <v>426.0899963378906</v>
+        <v>421.5499877929688</v>
       </c>
       <c r="F214" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>427.25</v>
+        <v>422.4800109863281</v>
       </c>
       <c r="C215" t="n">
-        <v>431.0199890136719</v>
+        <v>437</v>
       </c>
       <c r="D215" t="n">
-        <v>417.3800048828125</v>
+        <v>420.5</v>
       </c>
       <c r="E215" t="n">
-        <v>421.5499877929688</v>
+        <v>436.3500061035156</v>
       </c>
       <c r="F215" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>422.4800109863281</v>
+        <v>434.9500122070312</v>
       </c>
       <c r="C216" t="n">
-        <v>437</v>
+        <v>436.3200073242188</v>
       </c>
       <c r="D216" t="n">
-        <v>420.5</v>
+        <v>429.7000122070312</v>
       </c>
       <c r="E216" t="n">
-        <v>436.3500061035156</v>
+        <v>431.3099975585938</v>
       </c>
       <c r="F216" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>434.9500122070312</v>
+        <v>428.2699890136719</v>
       </c>
       <c r="C217" t="n">
-        <v>436.3200073242188</v>
+        <v>430.489990234375</v>
       </c>
       <c r="D217" t="n">
-        <v>429.7000122070312</v>
+        <v>420.3999938964844</v>
       </c>
       <c r="E217" t="n">
-        <v>431.3099975585938</v>
+        <v>423.5599975585938</v>
       </c>
       <c r="F217" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>428.2699890136719</v>
+        <v>425.239990234375</v>
       </c>
       <c r="C218" t="n">
-        <v>430.489990234375</v>
+        <v>429</v>
       </c>
       <c r="D218" t="n">
-        <v>420.3999938964844</v>
+        <v>418.9200134277344</v>
       </c>
       <c r="E218" t="n">
-        <v>423.5599975585938</v>
+        <v>420.739990234375</v>
       </c>
       <c r="F218" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>425.239990234375</v>
+        <v>422.510009765625</v>
       </c>
       <c r="C219" t="n">
-        <v>429</v>
+        <v>422.8800048828125</v>
       </c>
       <c r="D219" t="n">
-        <v>418.9200134277344</v>
+        <v>412.5400085449219</v>
       </c>
       <c r="E219" t="n">
-        <v>420.739990234375</v>
+        <v>417.6400146484375</v>
       </c>
       <c r="F219" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>422.510009765625</v>
+        <v>419.9299926757812</v>
       </c>
       <c r="C220" t="n">
-        <v>422.8800048828125</v>
+        <v>430.4599914550781</v>
       </c>
       <c r="D220" t="n">
-        <v>412.5400085449219</v>
+        <v>415.1099853515625</v>
       </c>
       <c r="E220" t="n">
-        <v>417.6400146484375</v>
+        <v>428.7900085449219</v>
       </c>
       <c r="F220" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>419.9299926757812</v>
+        <v>428.260009765625</v>
       </c>
       <c r="C221" t="n">
-        <v>430.4599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="D221" t="n">
-        <v>415.1099853515625</v>
+        <v>420.3500061035156</v>
       </c>
       <c r="E221" t="n">
-        <v>428.7900085449219</v>
+        <v>420.5700073242188</v>
       </c>
       <c r="F221" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>428.260009765625</v>
+        <v>415.1900024414062</v>
       </c>
       <c r="C222" t="n">
-        <v>431.6799926757812</v>
+        <v>427.3399963378906</v>
       </c>
       <c r="D222" t="n">
-        <v>420.3500061035156</v>
+        <v>411.2900085449219</v>
       </c>
       <c r="E222" t="n">
-        <v>420.5700073242188</v>
+        <v>421.4700012207031</v>
       </c>
       <c r="F222" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>415.1900024414062</v>
+        <v>422</v>
       </c>
       <c r="C223" t="n">
-        <v>427.3399963378906</v>
+        <v>422.8099975585938</v>
       </c>
       <c r="D223" t="n">
-        <v>411.2900085449219</v>
+        <v>414.0599975585938</v>
       </c>
       <c r="E223" t="n">
-        <v>421.4700012207031</v>
+        <v>414.3999938964844</v>
       </c>
       <c r="F223" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>422</v>
+        <v>417.4299926757812</v>
       </c>
       <c r="C224" t="n">
-        <v>422.8099975585938</v>
+        <v>419.3399963378906</v>
       </c>
       <c r="D224" t="n">
-        <v>414.0599975585938</v>
+        <v>413.3200073242188</v>
       </c>
       <c r="E224" t="n">
-        <v>414.3999938964844</v>
+        <v>415.3599853515625</v>
       </c>
       <c r="F224" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>417.4299926757812</v>
+        <v>415.5599975585938</v>
       </c>
       <c r="C225" t="n">
-        <v>419.3399963378906</v>
+        <v>416</v>
       </c>
       <c r="D225" t="n">
-        <v>413.3200073242188</v>
+        <v>406.6700134277344</v>
       </c>
       <c r="E225" t="n">
-        <v>415.3599853515625</v>
+        <v>407.5499877929688</v>
       </c>
       <c r="F225" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>415.5599975585938</v>
+        <v>403.1900024414062</v>
       </c>
       <c r="C226" t="n">
-        <v>416</v>
+        <v>416.3599853515625</v>
       </c>
       <c r="D226" t="n">
-        <v>406.6700134277344</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="E226" t="n">
-        <v>407.5499877929688</v>
+        <v>412.75</v>
       </c>
       <c r="F226" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>403.1900024414062</v>
+        <v>415.2699890136719</v>
       </c>
       <c r="C227" t="n">
-        <v>416.3599853515625</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="D227" t="n">
-        <v>397.7999877929688</v>
+        <v>402.3999938964844</v>
       </c>
       <c r="E227" t="n">
-        <v>412.75</v>
+        <v>403.9700012207031</v>
       </c>
       <c r="F227" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>415.2699890136719</v>
+        <v>401.5899963378906</v>
       </c>
       <c r="C228" t="n">
-        <v>416.9700012207031</v>
+        <v>410.6400146484375</v>
       </c>
       <c r="D228" t="n">
-        <v>402.3999938964844</v>
+        <v>400.6600036621094</v>
       </c>
       <c r="E228" t="n">
-        <v>403.9700012207031</v>
+        <v>407.0799865722656</v>
       </c>
       <c r="F228" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>401.5899963378906</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="C229" t="n">
-        <v>410.6400146484375</v>
+        <v>413.0700073242188</v>
       </c>
       <c r="D229" t="n">
-        <v>400.6600036621094</v>
+        <v>407.989990234375</v>
       </c>
       <c r="E229" t="n">
-        <v>407.0799865722656</v>
+        <v>408.739990234375</v>
       </c>
       <c r="F229" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>408.6000061035156</v>
+        <v>409</v>
       </c>
       <c r="C230" t="n">
-        <v>413.0700073242188</v>
+        <v>410.8999938964844</v>
       </c>
       <c r="D230" t="n">
-        <v>407.989990234375</v>
+        <v>401.3200073242188</v>
       </c>
       <c r="E230" t="n">
-        <v>408.739990234375</v>
+        <v>402.1900024414062</v>
       </c>
       <c r="F230" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>409</v>
+        <v>400.9800109863281</v>
       </c>
       <c r="C231" t="n">
-        <v>410.8999938964844</v>
+        <v>407.2000122070312</v>
       </c>
       <c r="D231" t="n">
-        <v>401.3200073242188</v>
+        <v>400.5</v>
       </c>
       <c r="E231" t="n">
-        <v>402.1900024414062</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="F231" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>400.9800109863281</v>
+        <v>405.5899963378906</v>
       </c>
       <c r="C232" t="n">
-        <v>407.2000122070312</v>
+        <v>407.3200073242188</v>
       </c>
       <c r="D232" t="n">
-        <v>400.5</v>
+        <v>398.5899963378906</v>
       </c>
       <c r="E232" t="n">
-        <v>405.5899963378906</v>
+        <v>399.0599975585938</v>
       </c>
       <c r="F232" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>405.5899963378906</v>
+        <v>398</v>
       </c>
       <c r="C233" t="n">
-        <v>407.3200073242188</v>
+        <v>403.1799926757812</v>
       </c>
       <c r="D233" t="n">
-        <v>398.5899963378906</v>
+        <v>396.5599975585938</v>
       </c>
       <c r="E233" t="n">
-        <v>399.0599975585938</v>
+        <v>401.7300109863281</v>
       </c>
       <c r="F233" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>398</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C234" t="n">
-        <v>403.1799926757812</v>
+        <v>398.8999938964844</v>
       </c>
       <c r="D234" t="n">
-        <v>396.5599975585938</v>
+        <v>391.4299926757812</v>
       </c>
       <c r="E234" t="n">
-        <v>401.7300109863281</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="F234" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>398.5700073242188</v>
+        <v>397.4299926757812</v>
       </c>
       <c r="C235" t="n">
-        <v>398.8999938964844</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="D235" t="n">
-        <v>391.4299926757812</v>
+        <v>393.510009765625</v>
       </c>
       <c r="E235" t="n">
-        <v>395.6199951171875</v>
+        <v>393.9299926757812</v>
       </c>
       <c r="F235" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>397.4299926757812</v>
+        <v>394.5700073242188</v>
       </c>
       <c r="C236" t="n">
-        <v>398.7900085449219</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="D236" t="n">
-        <v>393.510009765625</v>
+        <v>386.3299865722656</v>
       </c>
       <c r="E236" t="n">
-        <v>393.9299926757812</v>
+        <v>388.6099853515625</v>
       </c>
       <c r="F236" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>394.5700073242188</v>
+        <v>388.25</v>
       </c>
       <c r="C237" t="n">
-        <v>396.7999877929688</v>
+        <v>392.7099914550781</v>
       </c>
       <c r="D237" t="n">
-        <v>386.3299865722656</v>
+        <v>383.8299865722656</v>
       </c>
       <c r="E237" t="n">
-        <v>388.6099853515625</v>
+        <v>384.8500061035156</v>
       </c>
       <c r="F237" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>388.25</v>
+        <v>386</v>
       </c>
       <c r="C238" t="n">
-        <v>392.7099914550781</v>
+        <v>393.6600036621094</v>
       </c>
       <c r="D238" t="n">
-        <v>383.8299865722656</v>
+        <v>386</v>
       </c>
       <c r="E238" t="n">
-        <v>384.8500061035156</v>
+        <v>390.1099853515625</v>
       </c>
       <c r="F238" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>386</v>
+        <v>391.0400085449219</v>
       </c>
       <c r="C239" t="n">
-        <v>393.6600036621094</v>
+        <v>399.5799865722656</v>
       </c>
       <c r="D239" t="n">
-        <v>386</v>
+        <v>390.8599853515625</v>
       </c>
       <c r="E239" t="n">
-        <v>390.1099853515625</v>
+        <v>398.760009765625</v>
       </c>
       <c r="F239" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>391.0400085449219</v>
+        <v>397.7999877929688</v>
       </c>
       <c r="C240" t="n">
-        <v>399.5799865722656</v>
+        <v>399.0299987792969</v>
       </c>
       <c r="D240" t="n">
-        <v>390.8599853515625</v>
+        <v>395.6199951171875</v>
       </c>
       <c r="E240" t="n">
-        <v>398.760009765625</v>
+        <v>396.5899963378906</v>
       </c>
       <c r="F240" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>397.7999877929688</v>
+        <v>396.3299865722656</v>
       </c>
       <c r="C241" t="n">
-        <v>399.0299987792969</v>
+        <v>406.25</v>
       </c>
       <c r="D241" t="n">
-        <v>395.6199951171875</v>
+        <v>396.010009765625</v>
       </c>
       <c r="E241" t="n">
-        <v>396.5899963378906</v>
+        <v>401.010009765625</v>
       </c>
       <c r="F241" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>396.3299865722656</v>
+        <v>396.8699951171875</v>
       </c>
       <c r="C242" t="n">
-        <v>406.25</v>
+        <v>399.8800048828125</v>
       </c>
       <c r="D242" t="n">
-        <v>396.010009765625</v>
+        <v>393.7699890136719</v>
       </c>
       <c r="E242" t="n">
-        <v>401.010009765625</v>
+        <v>395.0499877929688</v>
       </c>
       <c r="F242" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>396.8699951171875</v>
+        <v>396.4200134277344</v>
       </c>
       <c r="C243" t="n">
-        <v>399.8800048828125</v>
+        <v>396.739990234375</v>
       </c>
       <c r="D243" t="n">
-        <v>393.7699890136719</v>
+        <v>392.6600036621094</v>
       </c>
       <c r="E243" t="n">
-        <v>395.0499877929688</v>
+        <v>392.9500122070312</v>
       </c>
       <c r="F243" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>396.4200134277344</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="C244" t="n">
-        <v>396.739990234375</v>
+        <v>394.489990234375</v>
       </c>
       <c r="D244" t="n">
-        <v>392.6600036621094</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="E244" t="n">
-        <v>392.9500122070312</v>
+        <v>389.4100036621094</v>
       </c>
       <c r="F244" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>393.5199890136719</v>
+        <v>392.0799865722656</v>
       </c>
       <c r="C245" t="n">
-        <v>394.489990234375</v>
+        <v>399.6000061035156</v>
       </c>
       <c r="D245" t="n">
-        <v>387.7099914550781</v>
+        <v>391.7799987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>389.4100036621094</v>
+        <v>396.2999877929688</v>
       </c>
       <c r="F245" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>392.0799865722656</v>
+        <v>399.2699890136719</v>
       </c>
       <c r="C246" t="n">
-        <v>399.6000061035156</v>
+        <v>401.1400146484375</v>
       </c>
       <c r="D246" t="n">
-        <v>391.7799987792969</v>
+        <v>396.510009765625</v>
       </c>
       <c r="E246" t="n">
-        <v>396.2999877929688</v>
+        <v>399.6600036621094</v>
       </c>
       <c r="F246" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>399.2699890136719</v>
+        <v>400.0199890136719</v>
       </c>
       <c r="C247" t="n">
-        <v>401.1400146484375</v>
+        <v>405.1600036621094</v>
       </c>
       <c r="D247" t="n">
-        <v>396.510009765625</v>
+        <v>395.2999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>399.6600036621094</v>
+        <v>400.9400024414062</v>
       </c>
       <c r="F247" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>400.0199890136719</v>
+        <v>397.0499877929688</v>
       </c>
       <c r="C248" t="n">
-        <v>405.1600036621094</v>
+        <v>402.2300109863281</v>
       </c>
       <c r="D248" t="n">
-        <v>395.2999877929688</v>
+        <v>395.2000122070312</v>
       </c>
       <c r="E248" t="n">
-        <v>400.9400024414062</v>
+        <v>397.1400146484375</v>
       </c>
       <c r="F248" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>397.0499877929688</v>
+        <v>392.3999938964844</v>
       </c>
       <c r="C249" t="n">
-        <v>402.2300109863281</v>
+        <v>403.8900146484375</v>
       </c>
       <c r="D249" t="n">
-        <v>395.2000122070312</v>
+        <v>390.4400024414062</v>
       </c>
       <c r="E249" t="n">
-        <v>397.1400146484375</v>
+        <v>400.8399963378906</v>
       </c>
       <c r="F249" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>392.3999938964844</v>
+        <v>405.1700134277344</v>
       </c>
       <c r="C250" t="n">
-        <v>403.8900146484375</v>
+        <v>406.5299987792969</v>
       </c>
       <c r="D250" t="n">
-        <v>390.4400024414062</v>
+        <v>378.0799865722656</v>
       </c>
       <c r="E250" t="n">
-        <v>400.8399963378906</v>
+        <v>393.0599975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>405.1700134277344</v>
+        <v>396</v>
       </c>
       <c r="C251" t="n">
-        <v>406.5299987792969</v>
+        <v>399.2699890136719</v>
       </c>
       <c r="D251" t="n">
-        <v>378.0799865722656</v>
+        <v>387.6000061035156</v>
       </c>
       <c r="E251" t="n">
-        <v>393.0599975585938</v>
+        <v>388.2799987792969</v>
       </c>
       <c r="F251" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>396</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="C252" t="n">
-        <v>399.2699890136719</v>
+        <v>391.7300109863281</v>
       </c>
       <c r="D252" t="n">
-        <v>387.6000061035156</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="E252" t="n">
-        <v>388.2799987792969</v>
+        <v>379.0899963378906</v>
       </c>
       <c r="F252" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="D2" t="n">
         <v>388.28</v>
       </c>
-      <c r="D2" t="n">
-        <v>393.06</v>
-      </c>
       <c r="E2" t="n">
-        <v>396</v>
+        <v>390.42</v>
       </c>
       <c r="F2" t="n">
-        <v>399.265</v>
+        <v>391.73</v>
       </c>
       <c r="G2" t="n">
-        <v>387.61</v>
+        <v>375.9</v>
       </c>
       <c r="H2" t="n">
-        <v>4265842</v>
+        <v>7449717</v>
       </c>
       <c r="I2" t="n">
-        <v>5324795</v>
+        <v>5312277</v>
       </c>
       <c r="J2" t="n">
-        <v>348518121472</v>
+        <v>340269203456</v>
       </c>
       <c r="K2" t="n">
-        <v>24.9377</v>
+        <v>24.394466</v>
       </c>
       <c r="L2" t="n">
-        <v>17.3066</v>
+        <v>16.89698</v>
       </c>
       <c r="M2" t="n">
-        <v>15.57</v>
+        <v>15.54</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10572,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.5693734</v>
+        <v>3.4848917</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>397880131584</v>
+        <v>389631246336</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:22</t>
+          <t>2026-09-12 21:47:25</t>
         </is>
       </c>
     </row>
